--- a/static/Ergunbas_Urun_Hat_Rotalari_ve_Kapasite_Analizi.xlsx
+++ b/static/Ergunbas_Urun_Hat_Rotalari_ve_Kapasite_Analizi.xlsx
@@ -1106,17 +1106,17 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>2.20 m Yan + 1.05 m Üst (Takım)</t>
+          <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>140 mm Duvar</t>
+          <t>140 x 36 mm</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>4.95 kg/takım</t>
+          <t>4.95 kg/boy</t>
         </is>
       </c>
       <c r="F7" s="11" t="n">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="K7" s="16" t="inlineStr">
         <is>
-          <t>Saatte ~13 Takım</t>
+          <t>Saatte ~13 Boy</t>
         </is>
       </c>
       <c r="L7" s="11" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="N7" s="17" t="inlineStr">
         <is>
-          <t>Saatte ~15 Takım</t>
+          <t>Saatte ~15 Boy</t>
         </is>
       </c>
       <c r="O7" s="18" t="n">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="T7" s="17" t="inlineStr">
         <is>
-          <t>Saatte ~10 Takım</t>
+          <t>Saatte ~10 Boy</t>
         </is>
       </c>
       <c r="U7" s="20" t="n">
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>2.20 m Yan + 1.05 m Üst (Takım)</t>
+          <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
         <is>
-          <t>100 mm Duvar</t>
+          <t>100 x 36 mm</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>4.00 kg/takım</t>
+          <t>4.00 kg/boy</t>
         </is>
       </c>
       <c r="F8" s="25" t="n">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K8" s="30" t="inlineStr">
         <is>
-          <t>Saatte ~16 Takım</t>
+          <t>Saatte ~16 Boy</t>
         </is>
       </c>
       <c r="L8" s="25" t="n">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="N8" s="31" t="inlineStr">
         <is>
-          <t>Saatte ~17 Takım</t>
+          <t>Saatte ~17 Boy</t>
         </is>
       </c>
       <c r="O8" s="32" t="n">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="T8" s="31" t="inlineStr">
         <is>
-          <t>Saatte ~15 Takım</t>
+          <t>Saatte ~15 Boy</t>
         </is>
       </c>
       <c r="U8" s="34" t="n">
@@ -1412,17 +1412,17 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>2.20 m Yan + 1.05 m Üst (Takım)</t>
+          <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
         <is>
-          <t>200 mm Duvar</t>
+          <t>200 x 36 mm</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>6.66 kg/takım</t>
+          <t>6.66 kg/boy</t>
         </is>
       </c>
       <c r="F10" s="25" t="n">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="K10" s="30" t="inlineStr">
         <is>
-          <t>Saatte ~11 Takım</t>
+          <t>Saatte ~11 Boy</t>
         </is>
       </c>
       <c r="L10" s="25" t="n">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="N10" s="31" t="inlineStr">
         <is>
-          <t>Saatte ~13 Takım</t>
+          <t>Saatte ~13 Boy</t>
         </is>
       </c>
       <c r="O10" s="32" t="n">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>2.20 m Yan + 1.05 m Üst (Takım)</t>
+          <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
         <is>
-          <t>140 mm Duvar</t>
+          <t>140 x 36 mm</t>
         </is>
       </c>
       <c r="E8" s="52" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="J8" s="24" t="inlineStr">
         <is>
-          <t>4.95 kg/takım</t>
+          <t>4.95 kg/boy</t>
         </is>
       </c>
       <c r="K8" s="25" t="n">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="M8" s="30" t="inlineStr">
         <is>
-          <t>Saatte ~13 Takım</t>
+          <t>Saatte ~13 Boy</t>
         </is>
       </c>
       <c r="N8" s="53" t="n">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>2.20 m Yan + 1.05 m Üst (Takım)</t>
+          <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>200 mm Duvar</t>
+          <t>200 x 36 mm</t>
         </is>
       </c>
       <c r="E9" s="54" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="J9" s="10" t="inlineStr">
         <is>
-          <t>6.66 kg/takım</t>
+          <t>6.66 kg/boy</t>
         </is>
       </c>
       <c r="K9" s="11" t="n">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="M9" s="16" t="inlineStr">
         <is>
-          <t>Saatte ~11 Takım</t>
+          <t>Saatte ~11 Boy</t>
         </is>
       </c>
       <c r="N9" s="55" t="n">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>2.20 m Yan + 1.05 m Üst (Takım)</t>
+          <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>100 mm Duvar</t>
+          <t>100 x 36 mm</t>
         </is>
       </c>
       <c r="E11" s="54" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="J11" s="10" t="inlineStr">
         <is>
-          <t>4.00 kg/takım</t>
+          <t>4.00 kg/boy</t>
         </is>
       </c>
       <c r="K11" s="11" t="n">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="M11" s="16" t="inlineStr">
         <is>
-          <t>Saatte ~15 Takım</t>
+          <t>Saatte ~15 Boy</t>
         </is>
       </c>
       <c r="N11" s="55" t="n">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>2.20 m Yan + 1.05 m Üst (Takım)</t>
+          <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
         <is>
-          <t>100 mm Duvar</t>
+          <t>100 x 36 mm</t>
         </is>
       </c>
       <c r="E12" s="52" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="J12" s="24" t="inlineStr">
         <is>
-          <t>4.00 kg/takım</t>
+          <t>4.00 kg/boy</t>
         </is>
       </c>
       <c r="K12" s="25" t="n">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="M12" s="30" t="inlineStr">
         <is>
-          <t>Saatte ~16 Takım</t>
+          <t>Saatte ~16 Boy</t>
         </is>
       </c>
       <c r="N12" s="53" t="n">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>2.20 m Yan + 1.05 m Üst (Takım)</t>
+          <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>140 mm Duvar</t>
+          <t>140 x 36 mm</t>
         </is>
       </c>
       <c r="E13" s="54" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="J13" s="10" t="inlineStr">
         <is>
-          <t>4.95 kg/takım</t>
+          <t>4.95 kg/boy</t>
         </is>
       </c>
       <c r="K13" s="11" t="n">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="M13" s="16" t="inlineStr">
         <is>
-          <t>Saatte ~14 Takım</t>
+          <t>Saatte ~14 Boy</t>
         </is>
       </c>
       <c r="N13" s="55" t="n">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>2.20 m Yan + 1.05 m Üst (Takım)</t>
+          <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
         <is>
-          <t>140 mm Duvar</t>
+          <t>140 x 36 mm</t>
         </is>
       </c>
       <c r="E20" s="52" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="J20" s="24" t="inlineStr">
         <is>
-          <t>4.95 kg/takım</t>
+          <t>4.95 kg/boy</t>
         </is>
       </c>
       <c r="K20" s="25" t="n">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="M20" s="30" t="inlineStr">
         <is>
-          <t>Saatte ~10 Takım</t>
+          <t>Saatte ~10 Boy</t>
         </is>
       </c>
       <c r="N20" s="53" t="n">
@@ -6693,12 +6693,12 @@
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>2.20 m Yan + 1.05 m Üst (Takım)</t>
+          <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>200 mm Duvar</t>
+          <t>200 x 36 mm</t>
         </is>
       </c>
       <c r="E31" s="54" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="J31" s="10" t="inlineStr">
         <is>
-          <t>6.66 kg/takım</t>
+          <t>6.66 kg/boy</t>
         </is>
       </c>
       <c r="K31" s="11" t="n">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="M31" s="16" t="inlineStr">
         <is>
-          <t>Saatte ~20 Takım</t>
+          <t>Saatte ~20 Boy</t>
         </is>
       </c>
       <c r="N31" s="55" t="n">
@@ -6873,12 +6873,12 @@
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>2.20 m Yan + 1.05 m Üst (Takım)</t>
+          <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
       <c r="D34" s="23" t="inlineStr">
         <is>
-          <t>200 mm Duvar</t>
+          <t>200 x 36 mm</t>
         </is>
       </c>
       <c r="E34" s="52" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="J34" s="24" t="inlineStr">
         <is>
-          <t>6.66 kg/takım</t>
+          <t>6.66 kg/boy</t>
         </is>
       </c>
       <c r="K34" s="25" t="n">
@@ -6913,7 +6913,7 @@
       </c>
       <c r="M34" s="30" t="inlineStr">
         <is>
-          <t>Saatte ~14 Takım</t>
+          <t>Saatte ~14 Boy</t>
         </is>
       </c>
       <c r="N34" s="53" t="n">
@@ -7113,12 +7113,12 @@
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>2.20 m Yan + 1.05 m Üst (Takım)</t>
+          <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
       <c r="D38" s="23" t="inlineStr">
         <is>
-          <t>140 mm Duvar</t>
+          <t>140 x 36 mm</t>
         </is>
       </c>
       <c r="E38" s="52" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="J38" s="24" t="inlineStr">
         <is>
-          <t>4.95 kg/takım</t>
+          <t>4.95 kg/boy</t>
         </is>
       </c>
       <c r="K38" s="25" t="n">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="M38" s="30" t="inlineStr">
         <is>
-          <t>Saatte ~6 Takım</t>
+          <t>Saatte ~6 Boy</t>
         </is>
       </c>
       <c r="N38" s="53" t="n">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>2.20 m Yan + 1.05 m Üst (Takım)</t>
+          <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>140 mm Duvar</t>
+          <t>140 x 36 mm</t>
         </is>
       </c>
       <c r="E39" s="54" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="J39" s="10" t="inlineStr">
         <is>
-          <t>4.95 kg/takım</t>
+          <t>4.95 kg/boy</t>
         </is>
       </c>
       <c r="K39" s="11" t="n">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="M39" s="16" t="inlineStr">
         <is>
-          <t>Saatte ~17 Takım</t>
+          <t>Saatte ~17 Boy</t>
         </is>
       </c>
       <c r="N39" s="55" t="n">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>2.20 m Yan + 1.05 m Üst (Takım)</t>
+          <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
       <c r="D40" s="23" t="inlineStr">
         <is>
-          <t>100 mm Duvar</t>
+          <t>100 x 36 mm</t>
         </is>
       </c>
       <c r="E40" s="52" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="J40" s="24" t="inlineStr">
         <is>
-          <t>4.00 kg/takım</t>
+          <t>4.00 kg/boy</t>
         </is>
       </c>
       <c r="K40" s="25" t="n">
@@ -7273,7 +7273,7 @@
       </c>
       <c r="M40" s="30" t="inlineStr">
         <is>
-          <t>Saatte ~14 Takım</t>
+          <t>Saatte ~14 Boy</t>
         </is>
       </c>
       <c r="N40" s="53" t="n">
@@ -7293,12 +7293,12 @@
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>2.20 m Yan + 1.05 m Üst (Takım)</t>
+          <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>100 mm Duvar</t>
+          <t>100 x 36 mm</t>
         </is>
       </c>
       <c r="E41" s="54" t="inlineStr">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="J41" s="10" t="inlineStr">
         <is>
-          <t>4.00 kg/takım</t>
+          <t>4.00 kg/boy</t>
         </is>
       </c>
       <c r="K41" s="11" t="n">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="M41" s="16" t="inlineStr">
         <is>
-          <t>Saatte ~14 Takım</t>
+          <t>Saatte ~14 Boy</t>
         </is>
       </c>
       <c r="N41" s="55" t="n">

--- a/static/Ergunbas_Urun_Hat_Rotalari_ve_Kapasite_Analizi.xlsx
+++ b/static/Ergunbas_Urun_Hat_Rotalari_ve_Kapasite_Analizi.xlsx
@@ -292,18 +292,6 @@
     <xf numFmtId="165" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -321,6 +309,18 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="4" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -701,7 +701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X33"/>
+  <dimension ref="A1:X31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1296,7 +1296,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>DIŞBUDAK Levha</t>
+          <t>DİŞBUDAK Levha</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -3619,251 +3619,41 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>DİŞBUDAK Levha</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>WPC Levha Plaka</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>207 cm (2.07 m)</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>En: 94 cm (2 mm)</t>
-        </is>
-      </c>
-      <c r="E31" s="10" t="inlineStr">
-        <is>
-          <t>4.77 kg/plaka</t>
-        </is>
-      </c>
-      <c r="F31" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="12" t="inlineStr">
-        <is>
-          <t>Hat 201</t>
-        </is>
-      </c>
-      <c r="H31" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L31" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="13" t="n">
-        <v>187.9</v>
-      </c>
-      <c r="N31" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~39 Plaka</t>
-        </is>
-      </c>
-      <c r="O31" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" s="17" t="inlineStr">
-        <is>
-          <t>KLP-201</t>
-        </is>
-      </c>
-      <c r="Q31" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R31" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T31" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U31" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V31" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W31" s="14" t="n">
-        <v>90</v>
-      </c>
-      <c r="X31" s="8" t="inlineStr">
-        <is>
-          <t>Levha Özel Hattı (Hat 201)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="22" t="inlineStr">
-        <is>
-          <t>SEREN (Çift Kafa)</t>
-        </is>
-      </c>
-      <c r="B32" s="23" t="inlineStr">
-        <is>
-          <t>Seren Çıtası</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>2.10 Metre</t>
-        </is>
-      </c>
-      <c r="D32" s="23" t="inlineStr">
-        <is>
-          <t>38 x 45 mm</t>
-        </is>
-      </c>
-      <c r="E32" s="24" t="inlineStr">
-        <is>
-          <t>3.39 kg/boy</t>
-        </is>
-      </c>
-      <c r="F32" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="26" t="inlineStr">
-        <is>
-          <t>Hat 104</t>
-        </is>
-      </c>
-      <c r="H32" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L32" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="27" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="N32" s="31" t="inlineStr">
-        <is>
-          <t>Saatte ~29 Boy</t>
-        </is>
-      </c>
-      <c r="O32" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" s="31" t="inlineStr">
-        <is>
-          <t>KLP-104</t>
-        </is>
-      </c>
-      <c r="Q32" s="33" t="inlineStr">
-        <is>
-          <t>Hat 105</t>
-        </is>
-      </c>
-      <c r="R32" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S32" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T32" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U32" s="34" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="V32" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W32" s="28" t="n">
-        <v>45</v>
-      </c>
-      <c r="X32" s="23" t="inlineStr">
-        <is>
-          <t>Standart Planlama</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="42" t="inlineStr">
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="38" t="inlineStr">
         <is>
           <t>GENEL TOPLAM / FABRİKA</t>
         </is>
       </c>
-      <c r="B33" s="43" t="n"/>
-      <c r="C33" s="43" t="n"/>
-      <c r="D33" s="43" t="n"/>
-      <c r="E33" s="43" t="n"/>
-      <c r="F33" s="44" t="n">
+      <c r="B31" s="39" t="n"/>
+      <c r="C31" s="39" t="n"/>
+      <c r="D31" s="39" t="n"/>
+      <c r="E31" s="39" t="n"/>
+      <c r="F31" s="40" t="n">
         <v>1237183.51</v>
       </c>
-      <c r="G33" s="43" t="n"/>
-      <c r="H33" s="45" t="n">
+      <c r="G31" s="39" t="n"/>
+      <c r="H31" s="41" t="n">
         <v>11580</v>
       </c>
-      <c r="I33" s="43" t="n"/>
-      <c r="J33" s="43" t="n"/>
-      <c r="K33" s="43" t="n"/>
-      <c r="L33" s="43" t="n"/>
-      <c r="M33" s="43" t="n"/>
-      <c r="N33" s="43" t="n"/>
-      <c r="O33" s="43" t="n"/>
-      <c r="P33" s="43" t="n"/>
-      <c r="Q33" s="43" t="n"/>
-      <c r="R33" s="45" t="n">
+      <c r="I31" s="39" t="n"/>
+      <c r="J31" s="39" t="n"/>
+      <c r="K31" s="39" t="n"/>
+      <c r="L31" s="39" t="n"/>
+      <c r="M31" s="39" t="n"/>
+      <c r="N31" s="39" t="n"/>
+      <c r="O31" s="39" t="n"/>
+      <c r="P31" s="39" t="n"/>
+      <c r="Q31" s="39" t="n"/>
+      <c r="R31" s="41" t="n">
         <v>4908</v>
       </c>
-      <c r="S33" s="43" t="n"/>
-      <c r="T33" s="43" t="n"/>
-      <c r="U33" s="43" t="n"/>
-      <c r="V33" s="43" t="n"/>
-      <c r="W33" s="43" t="n"/>
-      <c r="X33" s="43" t="n"/>
+      <c r="S31" s="39" t="n"/>
+      <c r="T31" s="39" t="n"/>
+      <c r="U31" s="39" t="n"/>
+      <c r="V31" s="39" t="n"/>
+      <c r="W31" s="39" t="n"/>
+      <c r="X31" s="39" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -3992,7 +3782,7 @@
       <c r="E4" s="25" t="n">
         <v>33263.65</v>
       </c>
-      <c r="F4" s="46" t="n">
+      <c r="F4" s="42" t="n">
         <v>33.26</v>
       </c>
       <c r="G4" s="29" t="n">
@@ -4007,7 +3797,7 @@
       <c r="J4" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="K4" s="47" t="inlineStr">
+      <c r="K4" s="43" t="inlineStr">
         <is>
           <t>35X100 PERVAZ, 35X150 PERVAZ, 35X80 PERVAZ</t>
         </is>
@@ -4033,7 +3823,7 @@
       <c r="E5" s="11" t="n">
         <v>91560.17999999998</v>
       </c>
-      <c r="F5" s="48" t="n">
+      <c r="F5" s="44" t="n">
         <v>91.56</v>
       </c>
       <c r="G5" s="15" t="n">
@@ -4048,7 +3838,7 @@
       <c r="J5" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="K5" s="49" t="inlineStr">
+      <c r="K5" s="45" t="inlineStr">
         <is>
           <t>100 mm KASA, 140 mm KASA, CAM ÇITASI</t>
         </is>
@@ -4074,7 +3864,7 @@
       <c r="E6" s="25" t="n">
         <v>69803</v>
       </c>
-      <c r="F6" s="46" t="n">
+      <c r="F6" s="42" t="n">
         <v>69.8</v>
       </c>
       <c r="G6" s="29" t="n">
@@ -4089,7 +3879,7 @@
       <c r="J6" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="K6" s="47" t="inlineStr">
+      <c r="K6" s="43" t="inlineStr">
         <is>
           <t>50X80 PERVAZ, SEREN</t>
         </is>
@@ -4115,7 +3905,7 @@
       <c r="E7" s="11" t="n">
         <v>154861.98</v>
       </c>
-      <c r="F7" s="48" t="n">
+      <c r="F7" s="44" t="n">
         <v>154.86</v>
       </c>
       <c r="G7" s="15" t="n">
@@ -4130,7 +3920,7 @@
       <c r="J7" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="K7" s="49" t="inlineStr">
+      <c r="K7" s="45" t="inlineStr">
         <is>
           <t>SEREN</t>
         </is>
@@ -4156,7 +3946,7 @@
       <c r="E8" s="25" t="n">
         <v>137071.86</v>
       </c>
-      <c r="F8" s="46" t="n">
+      <c r="F8" s="42" t="n">
         <v>137.07</v>
       </c>
       <c r="G8" s="29" t="n">
@@ -4171,7 +3961,7 @@
       <c r="J8" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="K8" s="47" t="inlineStr">
+      <c r="K8" s="43" t="inlineStr">
         <is>
           <t>140 mm KASA, SEREN</t>
         </is>
@@ -4197,7 +3987,7 @@
       <c r="E9" s="11" t="n">
         <v>112898.9699999999</v>
       </c>
-      <c r="F9" s="48" t="n">
+      <c r="F9" s="44" t="n">
         <v>112.9</v>
       </c>
       <c r="G9" s="15" t="n">
@@ -4212,7 +4002,7 @@
       <c r="J9" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="K9" s="49" t="inlineStr">
+      <c r="K9" s="45" t="inlineStr">
         <is>
           <t>100 mm KASA, 140 mm KASA, 200 mm KASA</t>
         </is>
@@ -4238,7 +4028,7 @@
       <c r="E10" s="25" t="n">
         <v>135361.61</v>
       </c>
-      <c r="F10" s="46" t="n">
+      <c r="F10" s="42" t="n">
         <v>135.36</v>
       </c>
       <c r="G10" s="29" t="n">
@@ -4253,7 +4043,7 @@
       <c r="J10" s="28" t="n">
         <v>8</v>
       </c>
-      <c r="K10" s="47" t="inlineStr">
+      <c r="K10" s="43" t="inlineStr">
         <is>
           <t>100 mm KASA, 140 mm KASA, 200 mm KASA</t>
         </is>
@@ -4279,7 +4069,7 @@
       <c r="E11" s="11" t="n">
         <v>109257.63</v>
       </c>
-      <c r="F11" s="48" t="n">
+      <c r="F11" s="44" t="n">
         <v>109.26</v>
       </c>
       <c r="G11" s="15" t="n">
@@ -4294,7 +4084,7 @@
       <c r="J11" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="K11" s="49" t="inlineStr">
+      <c r="K11" s="45" t="inlineStr">
         <is>
           <t>100 mm KASA, 140 mm KASA, 200 mm KASA</t>
         </is>
@@ -4320,7 +4110,7 @@
       <c r="E12" s="25" t="n">
         <v>118327.55</v>
       </c>
-      <c r="F12" s="46" t="n">
+      <c r="F12" s="42" t="n">
         <v>118.33</v>
       </c>
       <c r="G12" s="29" t="n">
@@ -4335,7 +4125,7 @@
       <c r="J12" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="K12" s="47" t="inlineStr">
+      <c r="K12" s="43" t="inlineStr">
         <is>
           <t>50X80 PERVAZ, 80X80 PERVAZ</t>
         </is>
@@ -4361,7 +4151,7 @@
       <c r="E13" s="11" t="n">
         <v>274777.0800000001</v>
       </c>
-      <c r="F13" s="48" t="n">
+      <c r="F13" s="44" t="n">
         <v>274.78</v>
       </c>
       <c r="G13" s="15" t="n">
@@ -4376,7 +4166,7 @@
       <c r="J13" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="K13" s="49" t="inlineStr">
+      <c r="K13" s="45" t="inlineStr">
         <is>
           <t>ANTRASİT Levha, AY GRİ Levha, BEYAZ TEAK Levha</t>
         </is>
@@ -4402,22 +4192,22 @@
       <c r="E14" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="40" t="n">
+      <c r="F14" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="46" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="34" t="n">
         <v>250</v>
       </c>
-      <c r="I14" s="41" t="n">
+      <c r="I14" s="47" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="K14" s="47" t="inlineStr">
+      <c r="K14" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4443,22 +4233,22 @@
       <c r="E15" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="38" t="n">
+      <c r="F15" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="48" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="20" t="n">
         <v>250</v>
       </c>
-      <c r="I15" s="39" t="n">
+      <c r="I15" s="49" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="K15" s="49" t="inlineStr">
+      <c r="K15" s="45" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4484,22 +4274,22 @@
       <c r="E16" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="40" t="n">
+      <c r="F16" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="46" t="n">
         <v>0</v>
       </c>
       <c r="H16" s="34" t="n">
         <v>250</v>
       </c>
-      <c r="I16" s="41" t="n">
+      <c r="I16" s="47" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="47" t="inlineStr">
+      <c r="K16" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4525,22 +4315,22 @@
       <c r="E17" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="38" t="n">
+      <c r="F17" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="48" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="20" t="n">
         <v>250</v>
       </c>
-      <c r="I17" s="39" t="n">
+      <c r="I17" s="49" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="K17" s="49" t="inlineStr">
+      <c r="K17" s="45" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4566,22 +4356,22 @@
       <c r="E18" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F18" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="40" t="n">
+      <c r="F18" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="46" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="34" t="n">
         <v>180</v>
       </c>
-      <c r="I18" s="41" t="n">
+      <c r="I18" s="47" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="K18" s="47" t="inlineStr">
+      <c r="K18" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4607,22 +4397,22 @@
       <c r="E19" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="38" t="n">
+      <c r="F19" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="48" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="20" t="n">
         <v>180</v>
       </c>
-      <c r="I19" s="39" t="n">
+      <c r="I19" s="49" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="49" t="inlineStr">
+      <c r="K19" s="45" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4648,22 +4438,22 @@
       <c r="E20" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F20" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="40" t="n">
+      <c r="F20" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="46" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="34" t="n">
         <v>180</v>
       </c>
-      <c r="I20" s="41" t="n">
+      <c r="I20" s="47" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="47" t="inlineStr">
+      <c r="K20" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4689,22 +4479,22 @@
       <c r="E21" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F21" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="38" t="n">
+      <c r="F21" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="48" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="20" t="n">
         <v>180</v>
       </c>
-      <c r="I21" s="39" t="n">
+      <c r="I21" s="49" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="K21" s="49" t="inlineStr">
+      <c r="K21" s="45" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4730,22 +4520,22 @@
       <c r="E22" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F22" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="40" t="n">
+      <c r="F22" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="46" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="34" t="n">
         <v>180</v>
       </c>
-      <c r="I22" s="41" t="n">
+      <c r="I22" s="47" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="K22" s="47" t="inlineStr">
+      <c r="K22" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4771,22 +4561,22 @@
       <c r="E23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F23" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="38" t="n">
+      <c r="F23" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="48" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="20" t="n">
         <v>180</v>
       </c>
-      <c r="I23" s="39" t="n">
+      <c r="I23" s="49" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="K23" s="49" t="inlineStr">
+      <c r="K23" s="45" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4812,22 +4602,22 @@
       <c r="E24" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F24" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="40" t="n">
+      <c r="F24" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="46" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="34" t="n">
         <v>400</v>
       </c>
-      <c r="I24" s="41" t="n">
+      <c r="I24" s="47" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="K24" s="47" t="inlineStr">
+      <c r="K24" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4853,22 +4643,22 @@
       <c r="E25" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F25" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="38" t="n">
+      <c r="F25" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="48" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="20" t="n">
         <v>400</v>
       </c>
-      <c r="I25" s="39" t="n">
+      <c r="I25" s="49" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="K25" s="49" t="inlineStr">
+      <c r="K25" s="45" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4894,22 +4684,22 @@
       <c r="E26" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F26" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="40" t="n">
+      <c r="F26" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="46" t="n">
         <v>0</v>
       </c>
       <c r="H26" s="34" t="n">
         <v>400</v>
       </c>
-      <c r="I26" s="41" t="n">
+      <c r="I26" s="47" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="K26" s="47" t="inlineStr">
+      <c r="K26" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4921,24 +4711,24 @@
           <t>GENEL MAKİNE TOPLAMI</t>
         </is>
       </c>
-      <c r="B27" s="43" t="n"/>
-      <c r="C27" s="45" t="n">
+      <c r="B27" s="39" t="n"/>
+      <c r="C27" s="41" t="n">
         <v>17304</v>
       </c>
-      <c r="D27" s="44" t="n">
+      <c r="D27" s="40" t="n">
         <v>1442</v>
       </c>
-      <c r="E27" s="44" t="n">
+      <c r="E27" s="40" t="n">
         <v>1237183.51</v>
       </c>
       <c r="F27" s="51" t="n">
         <v>1237.18</v>
       </c>
-      <c r="G27" s="43" t="n"/>
-      <c r="H27" s="43" t="n"/>
-      <c r="I27" s="43" t="n"/>
-      <c r="J27" s="43" t="n"/>
-      <c r="K27" s="43" t="n"/>
+      <c r="G27" s="39" t="n"/>
+      <c r="H27" s="39" t="n"/>
+      <c r="I27" s="39" t="n"/>
+      <c r="J27" s="39" t="n"/>
+      <c r="K27" s="39" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5183,7 +4973,7 @@
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="22" t="inlineStr">
         <is>
-          <t>DIŞBUDAK Levha</t>
+          <t>DİŞBUDAK Levha</t>
         </is>
       </c>
       <c r="B6" s="23" t="inlineStr">
@@ -7466,25 +7256,25 @@
           <t>GENEL TOPLAM</t>
         </is>
       </c>
-      <c r="B44" s="43" t="n"/>
-      <c r="C44" s="43" t="n"/>
-      <c r="D44" s="43" t="n"/>
-      <c r="E44" s="43" t="n"/>
-      <c r="F44" s="43" t="n"/>
-      <c r="G44" s="45" t="n">
+      <c r="B44" s="39" t="n"/>
+      <c r="C44" s="39" t="n"/>
+      <c r="D44" s="39" t="n"/>
+      <c r="E44" s="39" t="n"/>
+      <c r="F44" s="39" t="n"/>
+      <c r="G44" s="41" t="n">
         <v>17304</v>
       </c>
-      <c r="H44" s="43" t="n"/>
-      <c r="I44" s="44" t="n">
+      <c r="H44" s="39" t="n"/>
+      <c r="I44" s="40" t="n">
         <v>379264</v>
       </c>
-      <c r="J44" s="43" t="n"/>
-      <c r="K44" s="44" t="n">
+      <c r="J44" s="39" t="n"/>
+      <c r="K44" s="40" t="n">
         <v>1237183.51</v>
       </c>
-      <c r="L44" s="43" t="n"/>
-      <c r="M44" s="43" t="n"/>
-      <c r="N44" s="43" t="n"/>
+      <c r="L44" s="39" t="n"/>
+      <c r="M44" s="39" t="n"/>
+      <c r="N44" s="39" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/static/Ergunbas_Urun_Hat_Rotalari_ve_Kapasite_Analizi.xlsx
+++ b/static/Ergunbas_Urun_Hat_Rotalari_ve_Kapasite_Analizi.xlsx
@@ -981,7 +981,7 @@
       </c>
       <c r="V5" s="21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hat 107</t>
         </is>
       </c>
       <c r="W5" s="14" t="n">
@@ -1162,18 +1162,18 @@
       </c>
       <c r="Q7" s="19" t="inlineStr">
         <is>
-          <t>Hat 102</t>
+          <t>Hat 108</t>
         </is>
       </c>
       <c r="R7" s="20" t="n">
-        <v>312</v>
+        <v>636</v>
       </c>
       <c r="S7" s="20" t="n">
-        <v>49.8</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="T7" s="17" t="inlineStr">
         <is>
-          <t>Saatte ~10 Boy</t>
+          <t>Saatte ~14 Boy</t>
         </is>
       </c>
       <c r="U7" s="20" t="n">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="V7" s="21" t="inlineStr">
         <is>
-          <t>Hat 108</t>
+          <t>Hat 102</t>
         </is>
       </c>
       <c r="W7" s="14" t="n">
@@ -1224,68 +1224,68 @@
       </c>
       <c r="G8" s="26" t="inlineStr">
         <is>
+          <t>Hat 102</t>
+        </is>
+      </c>
+      <c r="H8" s="27" t="n">
+        <v>1140</v>
+      </c>
+      <c r="I8" s="28" t="n">
+        <v>95</v>
+      </c>
+      <c r="J8" s="29" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="K8" s="30" t="inlineStr">
+        <is>
+          <t>Saatte ~15 Boy</t>
+        </is>
+      </c>
+      <c r="L8" s="25" t="n">
+        <v>1408.8</v>
+      </c>
+      <c r="M8" s="27" t="n">
+        <v>63</v>
+      </c>
+      <c r="N8" s="31" t="inlineStr">
+        <is>
+          <t>Saatte ~16 Boy</t>
+        </is>
+      </c>
+      <c r="O8" s="32" t="n">
+        <v>0.9320000000000001</v>
+      </c>
+      <c r="P8" s="31" t="inlineStr">
+        <is>
+          <t>KLP-102</t>
+        </is>
+      </c>
+      <c r="Q8" s="33" t="inlineStr">
+        <is>
           <t>Hat 108</t>
         </is>
       </c>
-      <c r="H8" s="27" t="n">
+      <c r="R8" s="34" t="n">
         <v>1008</v>
       </c>
-      <c r="I8" s="28" t="n">
-        <v>84</v>
-      </c>
-      <c r="J8" s="29" t="n">
+      <c r="S8" s="34" t="n">
         <v>63.6</v>
       </c>
-      <c r="K8" s="30" t="inlineStr">
+      <c r="T8" s="31" t="inlineStr">
         <is>
           <t>Saatte ~16 Boy</t>
         </is>
       </c>
-      <c r="L8" s="25" t="n">
-        <v>1526.4</v>
-      </c>
-      <c r="M8" s="27" t="n">
+      <c r="U8" s="34" t="n">
         <v>69.5</v>
       </c>
-      <c r="N8" s="31" t="inlineStr">
-        <is>
-          <t>Saatte ~17 Boy</t>
-        </is>
-      </c>
-      <c r="O8" s="32" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="P8" s="31" t="inlineStr">
-        <is>
-          <t>KLP-106</t>
-        </is>
-      </c>
-      <c r="Q8" s="33" t="inlineStr">
-        <is>
-          <t>Hat 102</t>
-        </is>
-      </c>
-      <c r="R8" s="34" t="n">
-        <v>1140</v>
-      </c>
-      <c r="S8" s="34" t="n">
-        <v>58.7</v>
-      </c>
-      <c r="T8" s="31" t="inlineStr">
-        <is>
-          <t>Saatte ~15 Boy</t>
-        </is>
-      </c>
-      <c r="U8" s="34" t="n">
-        <v>63</v>
-      </c>
       <c r="V8" s="35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hat 107</t>
         </is>
       </c>
       <c r="W8" s="28" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="X8" s="23" t="inlineStr">
         <is>
@@ -1466,34 +1466,28 @@
           <t>KLP-107</t>
         </is>
       </c>
-      <c r="Q10" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R10" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S10" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Q10" s="33" t="inlineStr">
+        <is>
+          <t>Hat 106</t>
+        </is>
+      </c>
+      <c r="R10" s="34" t="n">
+        <v>24</v>
+      </c>
+      <c r="S10" s="34" t="n">
+        <v>136.5</v>
       </c>
       <c r="T10" s="31" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U10" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Saatte ~20 Boy</t>
+        </is>
+      </c>
+      <c r="U10" s="34" t="n">
+        <v>76.14</v>
       </c>
       <c r="V10" s="35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hat 108</t>
         </is>
       </c>
       <c r="W10" s="28" t="n">
@@ -1501,7 +1495,7 @@
       </c>
       <c r="X10" s="23" t="inlineStr">
         <is>
-          <t>Tek Hat Kalıp Atamalı</t>
+          <t>Aktif Çift Hatlı Üretim (Yüksek Hacimli)</t>
         </is>
       </c>
     </row>
@@ -2172,68 +2166,68 @@
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
+          <t>Hat 101</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="n">
+        <v>324</v>
+      </c>
+      <c r="I17" s="14" t="n">
+        <v>27</v>
+      </c>
+      <c r="J17" s="15" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="K17" s="16" t="inlineStr">
+        <is>
+          <t>Saatte ~18 Boy</t>
+        </is>
+      </c>
+      <c r="L17" s="11" t="n">
+        <v>950.4</v>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="N17" s="17" t="inlineStr">
+        <is>
+          <t>Saatte ~21 Boy</t>
+        </is>
+      </c>
+      <c r="O17" s="18" t="n">
+        <v>0.852</v>
+      </c>
+      <c r="P17" s="17" t="inlineStr">
+        <is>
+          <t>KLP-101</t>
+        </is>
+      </c>
+      <c r="Q17" s="19" t="inlineStr">
+        <is>
           <t>Hat 109</t>
         </is>
       </c>
-      <c r="H17" s="13" t="n">
+      <c r="R17" s="20" t="n">
         <v>12</v>
       </c>
-      <c r="I17" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="15" t="n">
+      <c r="S17" s="20" t="n">
         <v>126.5</v>
       </c>
-      <c r="K17" s="16" t="inlineStr">
+      <c r="T17" s="17" t="inlineStr">
         <is>
           <t>Saatte ~58 Boy</t>
         </is>
       </c>
-      <c r="L17" s="11" t="n">
-        <v>3036</v>
-      </c>
-      <c r="M17" s="13" t="n">
+      <c r="U17" s="20" t="n">
         <v>85</v>
       </c>
-      <c r="N17" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~39 Boy</t>
-        </is>
-      </c>
-      <c r="O17" s="18" t="n">
-        <v>1.488</v>
-      </c>
-      <c r="P17" s="17" t="inlineStr">
-        <is>
-          <t>KLP-103</t>
-        </is>
-      </c>
-      <c r="Q17" s="19" t="inlineStr">
-        <is>
-          <t>Hat 101</t>
-        </is>
-      </c>
-      <c r="R17" s="20" t="n">
-        <v>324</v>
-      </c>
-      <c r="S17" s="20" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="T17" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~18 Boy</t>
-        </is>
-      </c>
-      <c r="U17" s="20" t="n">
-        <v>46.5</v>
-      </c>
       <c r="V17" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="W17" s="14" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="X17" s="8" t="inlineStr">
         <is>
@@ -3634,7 +3628,7 @@
       </c>
       <c r="G31" s="39" t="n"/>
       <c r="H31" s="41" t="n">
-        <v>11580</v>
+        <v>12024</v>
       </c>
       <c r="I31" s="39" t="n"/>
       <c r="J31" s="39" t="n"/>
@@ -3646,7 +3640,7 @@
       <c r="P31" s="39" t="n"/>
       <c r="Q31" s="39" t="n"/>
       <c r="R31" s="41" t="n">
-        <v>4908</v>
+        <v>4812</v>
       </c>
       <c r="S31" s="39" t="n"/>
       <c r="T31" s="39" t="n"/>

--- a/static/Ergunbas_Urun_Hat_Rotalari_ve_Kapasite_Analizi.xlsx
+++ b/static/Ergunbas_Urun_Hat_Rotalari_ve_Kapasite_Analizi.xlsx
@@ -89,7 +89,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -124,6 +124,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00ECFDF5"/>
         <bgColor rgb="00ECFDF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0F2FE"/>
+        <bgColor rgb="00E0F2FE"/>
       </patternFill>
     </fill>
     <fill>
@@ -179,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -217,6 +223,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -244,64 +253,64 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -310,10 +319,10 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -322,12 +331,12 @@
     <xf numFmtId="165" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="4" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="4" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -701,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X31"/>
+  <dimension ref="A1:Z31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -711,23 +720,25 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="15" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="24" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
     <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="13" customWidth="1" min="23" max="23"/>
-    <col width="28" customWidth="1" min="24" max="24"/>
+    <col width="24" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="28" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -740,7 +751,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Standart Boy Ölçüleri (2.20m Pervaz, 2.10m Seren, 207cm Levha) | Saatteki Boy/Adet Hızları | Ana Rota vs Yedek Rota Kapasiteleri</t>
+          <t>Standart Boy Ölçüleri (2.20m Pervaz, 2.10m Seren, 207cm Levha) | Kalıp Göz Sayıları (1 Göz / 2 Göz) | Saatteki Boy Hızları | Rota Kapasiteleri</t>
         </is>
       </c>
     </row>
@@ -755,17 +766,17 @@
           <t>ANA ROTA (BİRİNCİL MAKİNE)</t>
         </is>
       </c>
-      <c r="Q3" s="5" t="inlineStr">
+      <c r="R3" s="5" t="inlineStr">
         <is>
           <t>YEDEK ROTA 1 (İKİNCİL MAKİNE)</t>
         </is>
       </c>
-      <c r="V3" s="3" t="inlineStr">
+      <c r="X3" s="3" t="inlineStr">
         <is>
           <t>YEDEK ROTA 2 &amp; KALIP</t>
         </is>
       </c>
-      <c r="X3" s="3" t="inlineStr">
+      <c r="Z3" s="3" t="inlineStr">
         <is>
           <t>STRATEJİ</t>
         </is>
@@ -809,85 +820,95 @@
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
+          <t>Kalıp Göz Sayısı</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
           <t>Fiili Çalışma (Saat)</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>Vardiya Sayısı</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>Fiili Hız (kg/sa)</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
         <is>
           <t>Fiili Hız (Saatteki Boy/Adet)</t>
         </is>
       </c>
-      <c r="L4" s="6" t="inlineStr">
+      <c r="M4" s="6" t="inlineStr">
         <is>
           <t>24s Fiili Kapasite (kg/gün)</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="N4" s="6" t="inlineStr">
         <is>
           <t>Teknik Kapasite (kg/sa)</t>
         </is>
       </c>
-      <c r="N4" s="6" t="inlineStr">
+      <c r="O4" s="6" t="inlineStr">
         <is>
           <t>Teknik Hız (Saatteki Boy/Adet)</t>
         </is>
       </c>
-      <c r="O4" s="6" t="inlineStr">
+      <c r="P4" s="6" t="inlineStr">
         <is>
           <t>Verim / OEE (%)</t>
         </is>
       </c>
-      <c r="P4" s="6" t="inlineStr">
+      <c r="Q4" s="6" t="inlineStr">
         <is>
           <t>Kalıp Kodu</t>
         </is>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>Yedek Rota 1 Hat</t>
         </is>
       </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="S4" s="6" t="inlineStr">
+        <is>
+          <t>Yedek 1 Göz Sayısı</t>
+        </is>
+      </c>
+      <c r="T4" s="6" t="inlineStr">
         <is>
           <t>Yedek 1 Fiili Saat</t>
         </is>
       </c>
-      <c r="S4" s="6" t="inlineStr">
+      <c r="U4" s="6" t="inlineStr">
         <is>
           <t>Yedek 1 Fiili Hız (kg/sa)</t>
         </is>
       </c>
-      <c r="T4" s="6" t="inlineStr">
+      <c r="V4" s="6" t="inlineStr">
         <is>
           <t>Yedek 1 Hız (Saatteki Boy)</t>
         </is>
       </c>
-      <c r="U4" s="6" t="inlineStr">
+      <c r="W4" s="6" t="inlineStr">
         <is>
           <t>Yedek 1 Teknik Hız (kg/sa)</t>
         </is>
       </c>
-      <c r="V4" s="6" t="inlineStr">
+      <c r="X4" s="6" t="inlineStr">
         <is>
           <t>Yedek Rota 2 Hat</t>
         </is>
       </c>
-      <c r="W4" s="6" t="inlineStr">
+      <c r="Y4" s="6" t="inlineStr">
         <is>
           <t>Setup Süresi (dk)</t>
         </is>
       </c>
-      <c r="X4" s="6" t="inlineStr">
+      <c r="Z4" s="6" t="inlineStr">
         <is>
           <t>Planlama &amp; Rota Durumu</t>
         </is>
@@ -927,167 +948,187 @@
           <t>Hat 104</t>
         </is>
       </c>
-      <c r="H5" s="13" t="n">
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>2 Göz (Çift Çıkış)</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="n">
         <v>1716</v>
       </c>
-      <c r="I5" s="14" t="n">
+      <c r="J5" s="15" t="n">
         <v>143</v>
       </c>
-      <c r="J5" s="15" t="n">
+      <c r="K5" s="16" t="n">
         <v>90.2</v>
       </c>
-      <c r="K5" s="16" t="inlineStr">
+      <c r="L5" s="17" t="inlineStr">
         <is>
           <t>Saatte ~27 Boy</t>
         </is>
       </c>
-      <c r="L5" s="11" t="n">
+      <c r="M5" s="11" t="n">
         <v>2164.8</v>
       </c>
-      <c r="M5" s="13" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="N5" s="14" t="n">
+        <v>110</v>
+      </c>
+      <c r="O5" s="18" t="inlineStr">
+        <is>
+          <t>Saatte ~32 Boy</t>
+        </is>
+      </c>
+      <c r="P5" s="19" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="Q5" s="18" t="inlineStr">
+        <is>
+          <t>KLP-104</t>
+        </is>
+      </c>
+      <c r="R5" s="20" t="inlineStr">
+        <is>
+          <t>Hat 105</t>
+        </is>
+      </c>
+      <c r="S5" s="13" t="inlineStr">
+        <is>
+          <t>2 Göz (Çift Çıkış)</t>
+        </is>
+      </c>
+      <c r="T5" s="21" t="n">
+        <v>1620</v>
+      </c>
+      <c r="U5" s="21" t="n">
+        <v>84</v>
+      </c>
+      <c r="V5" s="18" t="inlineStr">
+        <is>
+          <t>Saatte ~25 Boy</t>
+        </is>
+      </c>
+      <c r="W5" s="21" t="n">
+        <v>105</v>
+      </c>
+      <c r="X5" s="22" t="inlineStr">
+        <is>
+          <t>Hat 107</t>
+        </is>
+      </c>
+      <c r="Y5" s="15" t="n">
+        <v>45</v>
+      </c>
+      <c r="Z5" s="8" t="inlineStr">
+        <is>
+          <t>Aktif Çift Hatlı Üretim (Yüksek Hacimli)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>50X80 PERVAZ</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>Pervaz Profili</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>2.20 Metre</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>50 x 80 mm</t>
+        </is>
+      </c>
+      <c r="E6" s="25" t="inlineStr">
+        <is>
+          <t>1.55 kg/boy</t>
+        </is>
+      </c>
+      <c r="F6" s="26" t="n">
+        <v>185087.05</v>
+      </c>
+      <c r="G6" s="27" t="inlineStr">
+        <is>
+          <t>Hat 109</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>2 Göz (Çift Çıkış)</t>
+        </is>
+      </c>
+      <c r="I6" s="28" t="n">
+        <v>1776</v>
+      </c>
+      <c r="J6" s="29" t="n">
+        <v>148</v>
+      </c>
+      <c r="K6" s="30" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="L6" s="31" t="inlineStr">
+        <is>
+          <t>Saatte ~42 Boy</t>
+        </is>
+      </c>
+      <c r="M6" s="26" t="n">
+        <v>1579.2</v>
+      </c>
+      <c r="N6" s="28" t="n">
+        <v>88</v>
+      </c>
+      <c r="O6" s="32" t="inlineStr">
+        <is>
+          <t>Saatte ~57 Boy</t>
+        </is>
+      </c>
+      <c r="P6" s="33" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="Q6" s="32" t="inlineStr">
+        <is>
+          <t>KLP-PRV-50</t>
+        </is>
+      </c>
+      <c r="R6" s="34" t="inlineStr">
+        <is>
+          <t>Hat 103</t>
+        </is>
+      </c>
+      <c r="S6" s="13" t="inlineStr">
+        <is>
+          <t>2 Göz (Çift Çıkış)</t>
+        </is>
+      </c>
+      <c r="T6" s="35" t="n">
+        <v>1512</v>
+      </c>
+      <c r="U6" s="35" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="V6" s="32" t="inlineStr">
         <is>
           <t>Saatte ~29 Boy</t>
         </is>
       </c>
-      <c r="O5" s="18" t="n">
-        <v>0.909</v>
-      </c>
-      <c r="P5" s="17" t="inlineStr">
-        <is>
-          <t>KLP-104</t>
-        </is>
-      </c>
-      <c r="Q5" s="19" t="inlineStr">
-        <is>
-          <t>Hat 105</t>
-        </is>
-      </c>
-      <c r="R5" s="20" t="n">
-        <v>1620</v>
-      </c>
-      <c r="S5" s="20" t="n">
-        <v>84</v>
-      </c>
-      <c r="T5" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~25 Boy</t>
-        </is>
-      </c>
-      <c r="U5" s="20" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="V5" s="21" t="inlineStr">
-        <is>
-          <t>Hat 107</t>
-        </is>
-      </c>
-      <c r="W5" s="14" t="n">
-        <v>45</v>
-      </c>
-      <c r="X5" s="8" t="inlineStr">
-        <is>
-          <t>Aktif Çift Hatlı Üretim (Yüksek Hacimli)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="22" t="inlineStr">
-        <is>
-          <t>50X80 PERVAZ</t>
-        </is>
-      </c>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>Pervaz Profili</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>2.20 Metre</t>
-        </is>
-      </c>
-      <c r="D6" s="23" t="inlineStr">
-        <is>
-          <t>50 x 80 mm</t>
-        </is>
-      </c>
-      <c r="E6" s="24" t="inlineStr">
-        <is>
-          <t>1.55 kg/boy</t>
-        </is>
-      </c>
-      <c r="F6" s="25" t="n">
-        <v>185087.05</v>
-      </c>
-      <c r="G6" s="26" t="inlineStr">
-        <is>
-          <t>Hat 109</t>
-        </is>
-      </c>
-      <c r="H6" s="27" t="n">
-        <v>1776</v>
-      </c>
-      <c r="I6" s="28" t="n">
-        <v>148</v>
-      </c>
-      <c r="J6" s="29" t="n">
-        <v>65.8</v>
-      </c>
-      <c r="K6" s="30" t="inlineStr">
-        <is>
-          <t>Saatte ~42 Boy</t>
-        </is>
-      </c>
-      <c r="L6" s="25" t="n">
-        <v>1579.2</v>
-      </c>
-      <c r="M6" s="27" t="n">
-        <v>74</v>
-      </c>
-      <c r="N6" s="31" t="inlineStr">
-        <is>
-          <t>Saatte ~48 Boy</t>
-        </is>
-      </c>
-      <c r="O6" s="32" t="n">
-        <v>0.889</v>
-      </c>
-      <c r="P6" s="31" t="inlineStr">
-        <is>
-          <t>KLP-PRV-50</t>
-        </is>
-      </c>
-      <c r="Q6" s="33" t="inlineStr">
-        <is>
-          <t>Hat 103</t>
-        </is>
-      </c>
-      <c r="R6" s="34" t="n">
-        <v>1512</v>
-      </c>
-      <c r="S6" s="34" t="n">
-        <v>45.2</v>
-      </c>
-      <c r="T6" s="31" t="inlineStr">
-        <is>
-          <t>Saatte ~29 Boy</t>
-        </is>
-      </c>
-      <c r="U6" s="34" t="n">
-        <v>53</v>
-      </c>
-      <c r="V6" s="35" t="inlineStr">
+      <c r="W6" s="35" t="n">
+        <v>55</v>
+      </c>
+      <c r="X6" s="36" t="inlineStr">
         <is>
           <t>Hat 101</t>
         </is>
       </c>
-      <c r="W6" s="28" t="n">
+      <c r="Y6" s="29" t="n">
         <v>35</v>
       </c>
-      <c r="X6" s="23" t="inlineStr">
+      <c r="Z6" s="24" t="inlineStr">
         <is>
           <t>Aktif Çift Hatlı Üretim (Yüksek Hacimli)</t>
         </is>
@@ -1127,79 +1168,89 @@
           <t>Hat 106</t>
         </is>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="n">
         <v>1668</v>
       </c>
-      <c r="I7" s="14" t="n">
+      <c r="J7" s="15" t="n">
         <v>139</v>
       </c>
-      <c r="J7" s="15" t="n">
+      <c r="K7" s="16" t="n">
         <v>65.3</v>
       </c>
-      <c r="K7" s="16" t="inlineStr">
+      <c r="L7" s="17" t="inlineStr">
         <is>
           <t>Saatte ~13 Boy</t>
         </is>
       </c>
-      <c r="L7" s="11" t="n">
+      <c r="M7" s="11" t="n">
         <v>1567.2</v>
       </c>
-      <c r="M7" s="13" t="n">
+      <c r="N7" s="14" t="n">
         <v>74.09999999999999</v>
       </c>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="O7" s="18" t="inlineStr">
         <is>
           <t>Saatte ~15 Boy</t>
         </is>
       </c>
-      <c r="O7" s="18" t="n">
+      <c r="P7" s="19" t="n">
         <v>0.8809999999999999</v>
       </c>
-      <c r="P7" s="17" t="inlineStr">
+      <c r="Q7" s="18" t="inlineStr">
         <is>
           <t>KLP-106</t>
         </is>
       </c>
-      <c r="Q7" s="19" t="inlineStr">
+      <c r="R7" s="20" t="inlineStr">
         <is>
           <t>Hat 108</t>
         </is>
       </c>
-      <c r="R7" s="20" t="n">
+      <c r="S7" s="18" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="T7" s="21" t="n">
         <v>636</v>
       </c>
-      <c r="S7" s="20" t="n">
+      <c r="U7" s="21" t="n">
         <v>67.40000000000001</v>
       </c>
-      <c r="T7" s="17" t="inlineStr">
+      <c r="V7" s="18" t="inlineStr">
         <is>
           <t>Saatte ~14 Boy</t>
         </is>
       </c>
-      <c r="U7" s="20" t="n">
+      <c r="W7" s="21" t="n">
         <v>65</v>
       </c>
-      <c r="V7" s="21" t="inlineStr">
+      <c r="X7" s="22" t="inlineStr">
         <is>
           <t>Hat 102</t>
         </is>
       </c>
-      <c r="W7" s="14" t="n">
+      <c r="Y7" s="15" t="n">
         <v>55</v>
       </c>
-      <c r="X7" s="8" t="inlineStr">
+      <c r="Z7" s="8" t="inlineStr">
         <is>
           <t>Aktif Çift Hatlı Üretim (Yüksek Hacimli)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>100 mm KASA</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>Kasa Profili</t>
         </is>
@@ -1209,85 +1260,95 @@
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t>100 x 36 mm</t>
         </is>
       </c>
-      <c r="E8" s="24" t="inlineStr">
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t>4.00 kg/boy</t>
         </is>
       </c>
-      <c r="F8" s="25" t="n">
+      <c r="F8" s="26" t="n">
         <v>132276</v>
       </c>
-      <c r="G8" s="26" t="inlineStr">
+      <c r="G8" s="27" t="inlineStr">
         <is>
           <t>Hat 102</t>
         </is>
       </c>
-      <c r="H8" s="27" t="n">
+      <c r="H8" s="32" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="I8" s="28" t="n">
         <v>1140</v>
       </c>
-      <c r="I8" s="28" t="n">
+      <c r="J8" s="29" t="n">
         <v>95</v>
       </c>
-      <c r="J8" s="29" t="n">
+      <c r="K8" s="30" t="n">
         <v>58.7</v>
       </c>
-      <c r="K8" s="30" t="inlineStr">
+      <c r="L8" s="31" t="inlineStr">
         <is>
           <t>Saatte ~15 Boy</t>
         </is>
       </c>
-      <c r="L8" s="25" t="n">
+      <c r="M8" s="26" t="n">
         <v>1408.8</v>
       </c>
-      <c r="M8" s="27" t="n">
+      <c r="N8" s="28" t="n">
         <v>63</v>
       </c>
-      <c r="N8" s="31" t="inlineStr">
+      <c r="O8" s="32" t="inlineStr">
         <is>
           <t>Saatte ~16 Boy</t>
         </is>
       </c>
-      <c r="O8" s="32" t="n">
+      <c r="P8" s="37" t="n">
         <v>0.9320000000000001</v>
       </c>
-      <c r="P8" s="31" t="inlineStr">
+      <c r="Q8" s="32" t="inlineStr">
         <is>
           <t>KLP-102</t>
         </is>
       </c>
-      <c r="Q8" s="33" t="inlineStr">
+      <c r="R8" s="34" t="inlineStr">
         <is>
           <t>Hat 108</t>
         </is>
       </c>
-      <c r="R8" s="34" t="n">
+      <c r="S8" s="32" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="T8" s="35" t="n">
         <v>1008</v>
       </c>
-      <c r="S8" s="34" t="n">
+      <c r="U8" s="35" t="n">
         <v>63.6</v>
       </c>
-      <c r="T8" s="31" t="inlineStr">
+      <c r="V8" s="32" t="inlineStr">
         <is>
           <t>Saatte ~16 Boy</t>
         </is>
       </c>
-      <c r="U8" s="34" t="n">
+      <c r="W8" s="35" t="n">
         <v>69.5</v>
       </c>
-      <c r="V8" s="35" t="inlineStr">
+      <c r="X8" s="36" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="W8" s="28" t="n">
+      <c r="Y8" s="29" t="n">
         <v>65</v>
       </c>
-      <c r="X8" s="23" t="inlineStr">
+      <c r="Z8" s="24" t="inlineStr">
         <is>
           <t>Aktif Çift Hatlı Üretim (Yüksek Hacimli)</t>
         </is>
@@ -1327,55 +1388,55 @@
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="I9" s="14" t="n">
         <v>972</v>
       </c>
-      <c r="I9" s="14" t="n">
+      <c r="J9" s="15" t="n">
         <v>81</v>
       </c>
-      <c r="J9" s="15" t="n">
+      <c r="K9" s="16" t="n">
         <v>122.2</v>
       </c>
-      <c r="K9" s="16" t="inlineStr">
+      <c r="L9" s="17" t="inlineStr">
         <is>
           <t>Saatte ~26 Plaka</t>
         </is>
       </c>
-      <c r="L9" s="11" t="n">
+      <c r="M9" s="11" t="n">
         <v>2932.8</v>
       </c>
-      <c r="M9" s="13" t="n">
+      <c r="N9" s="14" t="n">
         <v>187.9</v>
       </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="O9" s="18" t="inlineStr">
         <is>
           <t>Saatte ~39 Plaka</t>
         </is>
       </c>
-      <c r="O9" s="36" t="n">
+      <c r="P9" s="38" t="n">
         <v>0.65</v>
       </c>
-      <c r="P9" s="17" t="inlineStr">
+      <c r="Q9" s="18" t="inlineStr">
         <is>
           <t>KLP-201</t>
         </is>
       </c>
-      <c r="Q9" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R9" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T9" s="17" t="inlineStr">
+      <c r="R9" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S9" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T9" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1385,27 +1446,37 @@
           <t>—</t>
         </is>
       </c>
-      <c r="V9" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W9" s="14" t="n">
+      <c r="V9" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W9" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X9" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y9" s="15" t="n">
         <v>90</v>
       </c>
-      <c r="X9" s="8" t="inlineStr">
+      <c r="Z9" s="8" t="inlineStr">
         <is>
           <t>Levha Özel Hattı (Hat 201)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>200 mm KASA</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>Kasa Profili</t>
         </is>
@@ -1415,85 +1486,95 @@
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D10" s="24" t="inlineStr">
         <is>
           <t>200 x 36 mm</t>
         </is>
       </c>
-      <c r="E10" s="24" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t>6.66 kg/boy</t>
         </is>
       </c>
-      <c r="F10" s="25" t="n">
+      <c r="F10" s="26" t="n">
         <v>81365.22</v>
       </c>
-      <c r="G10" s="26" t="inlineStr">
+      <c r="G10" s="27" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="H10" s="27" t="n">
+      <c r="H10" s="32" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="I10" s="28" t="n">
         <v>1032</v>
       </c>
-      <c r="I10" s="28" t="n">
+      <c r="J10" s="29" t="n">
         <v>86</v>
       </c>
-      <c r="J10" s="29" t="n">
+      <c r="K10" s="30" t="n">
         <v>73.40000000000001</v>
       </c>
-      <c r="K10" s="30" t="inlineStr">
+      <c r="L10" s="31" t="inlineStr">
         <is>
           <t>Saatte ~11 Boy</t>
         </is>
       </c>
-      <c r="L10" s="25" t="n">
+      <c r="M10" s="26" t="n">
         <v>1761.6</v>
       </c>
-      <c r="M10" s="27" t="n">
+      <c r="N10" s="28" t="n">
         <v>84.59999999999999</v>
       </c>
-      <c r="N10" s="31" t="inlineStr">
+      <c r="O10" s="32" t="inlineStr">
         <is>
           <t>Saatte ~13 Boy</t>
         </is>
       </c>
-      <c r="O10" s="32" t="n">
+      <c r="P10" s="37" t="n">
         <v>0.868</v>
       </c>
-      <c r="P10" s="31" t="inlineStr">
+      <c r="Q10" s="32" t="inlineStr">
         <is>
           <t>KLP-107</t>
         </is>
       </c>
-      <c r="Q10" s="33" t="inlineStr">
+      <c r="R10" s="34" t="inlineStr">
         <is>
           <t>Hat 106</t>
         </is>
       </c>
-      <c r="R10" s="34" t="n">
+      <c r="S10" s="32" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="T10" s="35" t="n">
         <v>24</v>
       </c>
-      <c r="S10" s="34" t="n">
+      <c r="U10" s="35" t="n">
         <v>136.5</v>
       </c>
-      <c r="T10" s="31" t="inlineStr">
+      <c r="V10" s="32" t="inlineStr">
         <is>
           <t>Saatte ~20 Boy</t>
         </is>
       </c>
-      <c r="U10" s="34" t="n">
+      <c r="W10" s="35" t="n">
         <v>76.14</v>
       </c>
-      <c r="V10" s="35" t="inlineStr">
+      <c r="X10" s="36" t="inlineStr">
         <is>
           <t>Hat 108</t>
         </is>
       </c>
-      <c r="W10" s="28" t="n">
+      <c r="Y10" s="29" t="n">
         <v>60</v>
       </c>
-      <c r="X10" s="23" t="inlineStr">
+      <c r="Z10" s="24" t="inlineStr">
         <is>
           <t>Aktif Çift Hatlı Üretim (Yüksek Hacimli)</t>
         </is>
@@ -1533,55 +1614,55 @@
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="H11" s="18" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="I11" s="14" t="n">
         <v>444</v>
       </c>
-      <c r="I11" s="14" t="n">
+      <c r="J11" s="15" t="n">
         <v>37</v>
       </c>
-      <c r="J11" s="15" t="n">
+      <c r="K11" s="16" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="K11" s="16" t="inlineStr">
+      <c r="L11" s="17" t="inlineStr">
         <is>
           <t>Saatte ~21 Plaka</t>
         </is>
       </c>
-      <c r="L11" s="11" t="n">
+      <c r="M11" s="11" t="n">
         <v>2150.4</v>
       </c>
-      <c r="M11" s="13" t="n">
+      <c r="N11" s="14" t="n">
         <v>145.5</v>
       </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="O11" s="18" t="inlineStr">
         <is>
           <t>Saatte ~34 Plaka</t>
         </is>
       </c>
-      <c r="O11" s="36" t="n">
+      <c r="P11" s="38" t="n">
         <v>0.616</v>
       </c>
-      <c r="P11" s="17" t="inlineStr">
+      <c r="Q11" s="18" t="inlineStr">
         <is>
           <t>KLP-201</t>
         </is>
       </c>
-      <c r="Q11" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R11" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T11" s="17" t="inlineStr">
+      <c r="R11" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S11" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T11" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1591,27 +1672,37 @@
           <t>—</t>
         </is>
       </c>
-      <c r="V11" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W11" s="14" t="n">
+      <c r="V11" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W11" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X11" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y11" s="15" t="n">
         <v>90</v>
       </c>
-      <c r="X11" s="8" t="inlineStr">
+      <c r="Z11" s="8" t="inlineStr">
         <is>
           <t>Levha Özel Hattı (Hat 201)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="A12" s="23" t="inlineStr">
         <is>
           <t>BEYAZ TEAK Levha</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>WPC Levha Plaka</t>
         </is>
@@ -1621,91 +1712,101 @@
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D12" s="24" t="inlineStr">
         <is>
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E12" s="24" t="inlineStr">
+      <c r="E12" s="25" t="inlineStr">
         <is>
           <t>4.41 kg/plaka</t>
         </is>
       </c>
-      <c r="F12" s="25" t="n">
+      <c r="F12" s="26" t="n">
         <v>32060.7</v>
       </c>
-      <c r="G12" s="26" t="inlineStr">
+      <c r="G12" s="27" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="H12" s="27" t="n">
+      <c r="H12" s="32" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="I12" s="28" t="n">
         <v>360</v>
       </c>
-      <c r="I12" s="28" t="n">
+      <c r="J12" s="29" t="n">
         <v>30</v>
       </c>
-      <c r="J12" s="29" t="n">
+      <c r="K12" s="30" t="n">
         <v>89.09999999999999</v>
       </c>
-      <c r="K12" s="30" t="inlineStr">
+      <c r="L12" s="31" t="inlineStr">
         <is>
           <t>Saatte ~20 Plaka</t>
         </is>
       </c>
-      <c r="L12" s="25" t="n">
+      <c r="M12" s="26" t="n">
         <v>2138.4</v>
       </c>
-      <c r="M12" s="27" t="n">
+      <c r="N12" s="28" t="n">
         <v>148.4</v>
       </c>
-      <c r="N12" s="31" t="inlineStr">
+      <c r="O12" s="32" t="inlineStr">
         <is>
           <t>Saatte ~34 Plaka</t>
         </is>
       </c>
-      <c r="O12" s="37" t="n">
+      <c r="P12" s="33" t="n">
         <v>0.6</v>
       </c>
-      <c r="P12" s="31" t="inlineStr">
+      <c r="Q12" s="32" t="inlineStr">
         <is>
           <t>KLP-201</t>
         </is>
       </c>
-      <c r="Q12" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R12" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S12" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T12" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U12" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V12" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W12" s="28" t="n">
+      <c r="R12" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S12" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V12" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W12" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X12" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y12" s="29" t="n">
         <v>90</v>
       </c>
-      <c r="X12" s="23" t="inlineStr">
+      <c r="Z12" s="24" t="inlineStr">
         <is>
           <t>Levha Özel Hattı (Hat 201)</t>
         </is>
@@ -1745,55 +1846,55 @@
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="I13" s="14" t="n">
         <v>336</v>
       </c>
-      <c r="I13" s="14" t="n">
+      <c r="J13" s="15" t="n">
         <v>28</v>
       </c>
-      <c r="J13" s="15" t="n">
+      <c r="K13" s="16" t="n">
         <v>91.09999999999999</v>
       </c>
-      <c r="K13" s="16" t="inlineStr">
+      <c r="L13" s="17" t="inlineStr">
         <is>
           <t>Saatte ~21 Plaka</t>
         </is>
       </c>
-      <c r="L13" s="11" t="n">
+      <c r="M13" s="11" t="n">
         <v>2186.4</v>
       </c>
-      <c r="M13" s="13" t="n">
+      <c r="N13" s="14" t="n">
         <v>145.5</v>
       </c>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="O13" s="18" t="inlineStr">
         <is>
           <t>Saatte ~34 Plaka</t>
         </is>
       </c>
-      <c r="O13" s="36" t="n">
+      <c r="P13" s="38" t="n">
         <v>0.626</v>
       </c>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="Q13" s="18" t="inlineStr">
         <is>
           <t>KLP-201</t>
         </is>
       </c>
-      <c r="Q13" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R13" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T13" s="17" t="inlineStr">
+      <c r="R13" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S13" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T13" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1803,27 +1904,37 @@
           <t>—</t>
         </is>
       </c>
-      <c r="V13" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W13" s="14" t="n">
+      <c r="V13" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W13" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X13" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y13" s="15" t="n">
         <v>90</v>
       </c>
-      <c r="X13" s="8" t="inlineStr">
+      <c r="Z13" s="8" t="inlineStr">
         <is>
           <t>Levha Özel Hattı (Hat 201)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t>SEREN(39mm)</t>
         </is>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>Seren Çıtası</t>
         </is>
@@ -1833,91 +1944,101 @@
           <t>2.10 Metre</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D14" s="24" t="inlineStr">
         <is>
           <t>39 x 45 mm</t>
         </is>
       </c>
-      <c r="E14" s="24" t="inlineStr">
+      <c r="E14" s="25" t="inlineStr">
         <is>
           <t>3.81 kg/boy</t>
         </is>
       </c>
-      <c r="F14" s="25" t="n">
+      <c r="F14" s="26" t="n">
         <v>27310.08</v>
       </c>
-      <c r="G14" s="26" t="inlineStr">
+      <c r="G14" s="27" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="H14" s="27" t="n">
+      <c r="H14" s="32" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="I14" s="28" t="n">
         <v>276</v>
       </c>
-      <c r="I14" s="28" t="n">
+      <c r="J14" s="29" t="n">
         <v>23</v>
       </c>
-      <c r="J14" s="29" t="n">
+      <c r="K14" s="30" t="n">
         <v>98.90000000000001</v>
       </c>
-      <c r="K14" s="30" t="inlineStr">
+      <c r="L14" s="31" t="inlineStr">
         <is>
           <t>Saatte ~26 Boy</t>
         </is>
       </c>
-      <c r="L14" s="25" t="n">
+      <c r="M14" s="26" t="n">
         <v>2373.6</v>
       </c>
-      <c r="M14" s="27" t="n">
+      <c r="N14" s="28" t="n">
         <v>96.09999999999999</v>
       </c>
-      <c r="N14" s="31" t="inlineStr">
+      <c r="O14" s="32" t="inlineStr">
         <is>
           <t>Saatte ~25 Boy</t>
         </is>
       </c>
-      <c r="O14" s="32" t="n">
+      <c r="P14" s="37" t="n">
         <v>1.029</v>
       </c>
-      <c r="P14" s="31" t="inlineStr">
+      <c r="Q14" s="32" t="inlineStr">
         <is>
           <t>KLP-107</t>
         </is>
       </c>
-      <c r="Q14" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R14" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S14" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T14" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U14" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V14" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W14" s="28" t="n">
+      <c r="R14" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S14" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U14" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V14" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W14" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X14" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y14" s="29" t="n">
         <v>60</v>
       </c>
-      <c r="X14" s="23" t="inlineStr">
+      <c r="Z14" s="24" t="inlineStr">
         <is>
           <t>Tek Hat Kalıp Atamalı</t>
         </is>
@@ -1957,55 +2078,55 @@
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="H15" s="13" t="n">
+      <c r="H15" s="18" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="I15" s="14" t="n">
         <v>264</v>
       </c>
-      <c r="I15" s="14" t="n">
+      <c r="J15" s="15" t="n">
         <v>22</v>
       </c>
-      <c r="J15" s="15" t="n">
+      <c r="K15" s="16" t="n">
         <v>69.59999999999999</v>
       </c>
-      <c r="K15" s="16" t="inlineStr">
+      <c r="L15" s="17" t="inlineStr">
         <is>
           <t>Saatte ~15 Plaka</t>
         </is>
       </c>
-      <c r="L15" s="11" t="n">
+      <c r="M15" s="11" t="n">
         <v>1670.4</v>
       </c>
-      <c r="M15" s="13" t="n">
+      <c r="N15" s="14" t="n">
         <v>116.2</v>
       </c>
-      <c r="N15" s="17" t="inlineStr">
+      <c r="O15" s="18" t="inlineStr">
         <is>
           <t>Saatte ~24 Plaka</t>
         </is>
       </c>
-      <c r="O15" s="36" t="n">
+      <c r="P15" s="38" t="n">
         <v>0.599</v>
       </c>
-      <c r="P15" s="17" t="inlineStr">
+      <c r="Q15" s="18" t="inlineStr">
         <is>
           <t>KLP-201</t>
         </is>
       </c>
-      <c r="Q15" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R15" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T15" s="17" t="inlineStr">
+      <c r="R15" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S15" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T15" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2015,27 +2136,37 @@
           <t>—</t>
         </is>
       </c>
-      <c r="V15" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W15" s="14" t="n">
+      <c r="V15" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W15" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X15" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y15" s="15" t="n">
         <v>90</v>
       </c>
-      <c r="X15" s="8" t="inlineStr">
+      <c r="Z15" s="8" t="inlineStr">
         <is>
           <t>Levha Özel Hattı (Hat 201)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="22" t="inlineStr">
+      <c r="A16" s="23" t="inlineStr">
         <is>
           <t>KT100-220x24-ANT</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>Deck / WPC Zemin</t>
         </is>
@@ -2045,91 +2176,101 @@
           <t>3.00 Metre</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="D16" s="24" t="inlineStr">
         <is>
           <t>220 x 24 mm</t>
         </is>
       </c>
-      <c r="E16" s="24" t="inlineStr">
+      <c r="E16" s="25" t="inlineStr">
         <is>
           <t>10.33 kg/boy</t>
         </is>
       </c>
-      <c r="F16" s="25" t="n">
+      <c r="F16" s="26" t="n">
         <v>17684.96</v>
       </c>
-      <c r="G16" s="26" t="inlineStr">
+      <c r="G16" s="27" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="H16" s="27" t="n">
+      <c r="H16" s="32" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="I16" s="28" t="n">
         <v>276</v>
       </c>
-      <c r="I16" s="28" t="n">
+      <c r="J16" s="29" t="n">
         <v>23</v>
       </c>
-      <c r="J16" s="29" t="n">
+      <c r="K16" s="30" t="n">
         <v>64.09999999999999</v>
       </c>
-      <c r="K16" s="30" t="inlineStr">
+      <c r="L16" s="31" t="inlineStr">
         <is>
           <t>Saatte ~6 Boy</t>
         </is>
       </c>
-      <c r="L16" s="25" t="n">
+      <c r="M16" s="26" t="n">
         <v>1538.4</v>
       </c>
-      <c r="M16" s="27" t="n">
+      <c r="N16" s="28" t="n">
         <v>84.7</v>
       </c>
-      <c r="N16" s="31" t="inlineStr">
+      <c r="O16" s="32" t="inlineStr">
         <is>
           <t>Saatte ~8 Boy</t>
         </is>
       </c>
-      <c r="O16" s="37" t="n">
+      <c r="P16" s="33" t="n">
         <v>0.757</v>
       </c>
-      <c r="P16" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q16" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R16" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S16" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T16" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U16" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V16" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W16" s="28" t="n">
+      <c r="Q16" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R16" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S16" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U16" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V16" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W16" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X16" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y16" s="29" t="n">
         <v>45</v>
       </c>
-      <c r="X16" s="23" t="inlineStr">
+      <c r="Z16" s="24" t="inlineStr">
         <is>
           <t>Tek Hat Kalıp Atamalı</t>
         </is>
@@ -2169,79 +2310,89 @@
           <t>Hat 101</t>
         </is>
       </c>
-      <c r="H17" s="13" t="n">
+      <c r="H17" s="18" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="I17" s="14" t="n">
         <v>324</v>
       </c>
-      <c r="I17" s="14" t="n">
+      <c r="J17" s="15" t="n">
         <v>27</v>
       </c>
-      <c r="J17" s="15" t="n">
+      <c r="K17" s="16" t="n">
         <v>39.6</v>
       </c>
-      <c r="K17" s="16" t="inlineStr">
+      <c r="L17" s="17" t="inlineStr">
         <is>
           <t>Saatte ~18 Boy</t>
         </is>
       </c>
-      <c r="L17" s="11" t="n">
+      <c r="M17" s="11" t="n">
         <v>950.4</v>
       </c>
-      <c r="M17" s="13" t="n">
+      <c r="N17" s="14" t="n">
         <v>46.5</v>
       </c>
-      <c r="N17" s="17" t="inlineStr">
+      <c r="O17" s="18" t="inlineStr">
         <is>
           <t>Saatte ~21 Boy</t>
         </is>
       </c>
-      <c r="O17" s="18" t="n">
+      <c r="P17" s="19" t="n">
         <v>0.852</v>
       </c>
-      <c r="P17" s="17" t="inlineStr">
+      <c r="Q17" s="18" t="inlineStr">
         <is>
           <t>KLP-101</t>
         </is>
       </c>
-      <c r="Q17" s="19" t="inlineStr">
+      <c r="R17" s="20" t="inlineStr">
         <is>
           <t>Hat 109</t>
         </is>
       </c>
-      <c r="R17" s="20" t="n">
+      <c r="S17" s="13" t="inlineStr">
+        <is>
+          <t>2 Göz (Çift Çıkış)</t>
+        </is>
+      </c>
+      <c r="T17" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="S17" s="20" t="n">
+      <c r="U17" s="21" t="n">
         <v>126.5</v>
       </c>
-      <c r="T17" s="17" t="inlineStr">
+      <c r="V17" s="18" t="inlineStr">
         <is>
           <t>Saatte ~58 Boy</t>
         </is>
       </c>
-      <c r="U17" s="20" t="n">
-        <v>85</v>
-      </c>
-      <c r="V17" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W17" s="14" t="n">
+      <c r="W17" s="21" t="n">
+        <v>140</v>
+      </c>
+      <c r="X17" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y17" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="X17" s="8" t="inlineStr">
+      <c r="Z17" s="8" t="inlineStr">
         <is>
           <t>Aktif Çift Hatlı Üretim (Yüksek Hacimli)</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="22" t="inlineStr">
+      <c r="A18" s="23" t="inlineStr">
         <is>
           <t>35X100 PERVAZ</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t>Pervaz Profili</t>
         </is>
@@ -2251,91 +2402,101 @@
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D18" s="24" t="inlineStr">
         <is>
           <t>35 x 100 mm</t>
         </is>
       </c>
-      <c r="E18" s="24" t="inlineStr">
+      <c r="E18" s="25" t="inlineStr">
         <is>
           <t>2.08 kg/boy</t>
         </is>
       </c>
-      <c r="F18" s="25" t="n">
+      <c r="F18" s="26" t="n">
         <v>10389.6</v>
       </c>
-      <c r="G18" s="26" t="inlineStr">
+      <c r="G18" s="27" t="inlineStr">
         <is>
           <t>Hat 101</t>
         </is>
       </c>
-      <c r="H18" s="27" t="n">
+      <c r="H18" s="32" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="I18" s="28" t="n">
         <v>264</v>
       </c>
-      <c r="I18" s="28" t="n">
+      <c r="J18" s="29" t="n">
         <v>22</v>
       </c>
-      <c r="J18" s="29" t="n">
+      <c r="K18" s="30" t="n">
         <v>39.4</v>
       </c>
-      <c r="K18" s="30" t="inlineStr">
+      <c r="L18" s="31" t="inlineStr">
         <is>
           <t>Saatte ~19 Boy</t>
         </is>
       </c>
-      <c r="L18" s="25" t="n">
+      <c r="M18" s="26" t="n">
         <v>945.6</v>
       </c>
-      <c r="M18" s="27" t="n">
+      <c r="N18" s="28" t="n">
         <v>63.8</v>
       </c>
-      <c r="N18" s="31" t="inlineStr">
+      <c r="O18" s="32" t="inlineStr">
         <is>
           <t>Saatte ~31 Boy</t>
         </is>
       </c>
-      <c r="O18" s="37" t="n">
+      <c r="P18" s="33" t="n">
         <v>0.618</v>
       </c>
-      <c r="P18" s="31" t="inlineStr">
+      <c r="Q18" s="32" t="inlineStr">
         <is>
           <t>KLP-101</t>
         </is>
       </c>
-      <c r="Q18" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R18" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S18" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T18" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U18" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V18" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W18" s="28" t="n">
+      <c r="R18" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S18" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T18" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U18" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V18" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W18" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X18" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y18" s="29" t="n">
         <v>40</v>
       </c>
-      <c r="X18" s="23" t="inlineStr">
+      <c r="Z18" s="24" t="inlineStr">
         <is>
           <t>Tek Hat Kalıp Atamalı</t>
         </is>
@@ -2375,55 +2536,55 @@
           <t>Hat 101</t>
         </is>
       </c>
-      <c r="H19" s="13" t="n">
+      <c r="H19" s="18" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="I19" s="14" t="n">
         <v>240</v>
       </c>
-      <c r="I19" s="14" t="n">
+      <c r="J19" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="J19" s="15" t="n">
+      <c r="K19" s="16" t="n">
         <v>39.7</v>
       </c>
-      <c r="K19" s="16" t="inlineStr">
+      <c r="L19" s="17" t="inlineStr">
         <is>
           <t>Saatte ~13 Boy</t>
         </is>
       </c>
-      <c r="L19" s="11" t="n">
+      <c r="M19" s="11" t="n">
         <v>952.8</v>
       </c>
-      <c r="M19" s="13" t="n">
+      <c r="N19" s="14" t="n">
         <v>41.2</v>
       </c>
-      <c r="N19" s="17" t="inlineStr">
+      <c r="O19" s="18" t="inlineStr">
         <is>
           <t>Saatte ~14 Boy</t>
         </is>
       </c>
-      <c r="O19" s="18" t="n">
+      <c r="P19" s="19" t="n">
         <v>0.9640000000000001</v>
       </c>
-      <c r="P19" s="17" t="inlineStr">
+      <c r="Q19" s="18" t="inlineStr">
         <is>
           <t>KLP-101</t>
         </is>
       </c>
-      <c r="Q19" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R19" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T19" s="17" t="inlineStr">
+      <c r="R19" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S19" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2433,27 +2594,37 @@
           <t>—</t>
         </is>
       </c>
-      <c r="V19" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W19" s="14" t="n">
+      <c r="V19" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W19" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X19" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y19" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="X19" s="8" t="inlineStr">
+      <c r="Z19" s="8" t="inlineStr">
         <is>
           <t>Tek Hat Kalıp Atamalı</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="22" t="inlineStr">
+      <c r="A20" s="23" t="inlineStr">
         <is>
           <t>KT102-219x26-ANT</t>
         </is>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t>Deck / WPC Zemin</t>
         </is>
@@ -2463,91 +2634,101 @@
           <t>3.00 Metre</t>
         </is>
       </c>
-      <c r="D20" s="23" t="inlineStr">
+      <c r="D20" s="24" t="inlineStr">
         <is>
           <t>219 x 26 mm</t>
         </is>
       </c>
-      <c r="E20" s="24" t="inlineStr">
+      <c r="E20" s="25" t="inlineStr">
         <is>
           <t>10.52 kg/boy</t>
         </is>
       </c>
-      <c r="F20" s="25" t="n">
+      <c r="F20" s="26" t="n">
         <v>9415.4</v>
       </c>
-      <c r="G20" s="26" t="inlineStr">
+      <c r="G20" s="27" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="H20" s="27" t="n">
+      <c r="H20" s="32" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="I20" s="28" t="n">
         <v>120</v>
       </c>
-      <c r="I20" s="28" t="n">
+      <c r="J20" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="J20" s="29" t="n">
+      <c r="K20" s="30" t="n">
         <v>78.5</v>
       </c>
-      <c r="K20" s="30" t="inlineStr">
+      <c r="L20" s="31" t="inlineStr">
         <is>
           <t>Saatte ~8 Boy</t>
         </is>
       </c>
-      <c r="L20" s="25" t="n">
+      <c r="M20" s="26" t="n">
         <v>1884</v>
       </c>
-      <c r="M20" s="27" t="n">
+      <c r="N20" s="28" t="n">
         <v>108.2</v>
       </c>
-      <c r="N20" s="31" t="inlineStr">
+      <c r="O20" s="32" t="inlineStr">
         <is>
           <t>Saatte ~10 Boy</t>
         </is>
       </c>
-      <c r="O20" s="37" t="n">
+      <c r="P20" s="33" t="n">
         <v>0.726</v>
       </c>
-      <c r="P20" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q20" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R20" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S20" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T20" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U20" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V20" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W20" s="28" t="n">
+      <c r="Q20" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R20" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S20" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U20" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V20" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W20" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X20" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y20" s="29" t="n">
         <v>45</v>
       </c>
-      <c r="X20" s="23" t="inlineStr">
+      <c r="Z20" s="24" t="inlineStr">
         <is>
           <t>Tek Hat Kalıp Atamalı</t>
         </is>
@@ -2587,55 +2768,55 @@
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="H21" s="13" t="n">
+      <c r="H21" s="18" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="I21" s="14" t="n">
         <v>108</v>
       </c>
-      <c r="I21" s="14" t="n">
+      <c r="J21" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="J21" s="15" t="n">
+      <c r="K21" s="16" t="n">
         <v>84.5</v>
       </c>
-      <c r="K21" s="16" t="inlineStr">
+      <c r="L21" s="17" t="inlineStr">
         <is>
           <t>Saatte ~20 Plaka</t>
         </is>
       </c>
-      <c r="L21" s="11" t="n">
+      <c r="M21" s="11" t="n">
         <v>2028</v>
       </c>
-      <c r="M21" s="13" t="n">
+      <c r="N21" s="14" t="n">
         <v>145.5</v>
       </c>
-      <c r="N21" s="17" t="inlineStr">
+      <c r="O21" s="18" t="inlineStr">
         <is>
           <t>Saatte ~34 Plaka</t>
         </is>
       </c>
-      <c r="O21" s="36" t="n">
+      <c r="P21" s="38" t="n">
         <v>0.581</v>
       </c>
-      <c r="P21" s="17" t="inlineStr">
+      <c r="Q21" s="18" t="inlineStr">
         <is>
           <t>KLP-201</t>
         </is>
       </c>
-      <c r="Q21" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R21" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T21" s="17" t="inlineStr">
+      <c r="R21" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S21" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T21" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2645,27 +2826,37 @@
           <t>—</t>
         </is>
       </c>
-      <c r="V21" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W21" s="14" t="n">
+      <c r="V21" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W21" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X21" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y21" s="15" t="n">
         <v>90</v>
       </c>
-      <c r="X21" s="8" t="inlineStr">
+      <c r="Z21" s="8" t="inlineStr">
         <is>
           <t>Levha Özel Hattı (Hat 201)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="22" t="inlineStr">
+      <c r="A22" s="23" t="inlineStr">
         <is>
           <t>CAM ÇITASI</t>
         </is>
       </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>Cam Çıtası</t>
         </is>
@@ -2675,91 +2866,101 @@
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="D22" s="23" t="inlineStr">
+      <c r="D22" s="24" t="inlineStr">
         <is>
           <t>15 x 20 mm</t>
         </is>
       </c>
-      <c r="E22" s="24" t="inlineStr">
+      <c r="E22" s="25" t="inlineStr">
         <is>
           <t>1.50 kg/boy</t>
         </is>
       </c>
-      <c r="F22" s="25" t="n">
+      <c r="F22" s="26" t="n">
         <v>7780.5</v>
       </c>
-      <c r="G22" s="26" t="inlineStr">
+      <c r="G22" s="27" t="inlineStr">
         <is>
           <t>Hat 102</t>
         </is>
       </c>
-      <c r="H22" s="27" t="n">
+      <c r="H22" s="32" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="I22" s="28" t="n">
         <v>168</v>
       </c>
-      <c r="I22" s="28" t="n">
+      <c r="J22" s="29" t="n">
         <v>14</v>
       </c>
-      <c r="J22" s="29" t="n">
+      <c r="K22" s="30" t="n">
         <v>46.3</v>
       </c>
-      <c r="K22" s="30" t="inlineStr">
+      <c r="L22" s="31" t="inlineStr">
         <is>
           <t>Saatte ~31 Boy</t>
         </is>
       </c>
-      <c r="L22" s="25" t="n">
+      <c r="M22" s="26" t="n">
         <v>1111.2</v>
       </c>
-      <c r="M22" s="27" t="n">
+      <c r="N22" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="N22" s="31" t="inlineStr">
+      <c r="O22" s="32" t="inlineStr">
         <is>
           <t>Saatte ~33 Boy</t>
         </is>
       </c>
-      <c r="O22" s="32" t="n">
+      <c r="P22" s="37" t="n">
         <v>0.9259999999999999</v>
       </c>
-      <c r="P22" s="31" t="inlineStr">
+      <c r="Q22" s="32" t="inlineStr">
         <is>
           <t>KLP-102</t>
         </is>
       </c>
-      <c r="Q22" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R22" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S22" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T22" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U22" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V22" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W22" s="28" t="n">
+      <c r="R22" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S22" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T22" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U22" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V22" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W22" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X22" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y22" s="29" t="n">
         <v>40</v>
       </c>
-      <c r="X22" s="23" t="inlineStr">
+      <c r="Z22" s="24" t="inlineStr">
         <is>
           <t>Tek Hat Kalıp Atamalı</t>
         </is>
@@ -2799,55 +3000,55 @@
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="H23" s="13" t="n">
+      <c r="H23" s="18" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="I23" s="14" t="n">
         <v>156</v>
       </c>
-      <c r="I23" s="14" t="n">
+      <c r="J23" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="J23" s="15" t="n">
+      <c r="K23" s="16" t="n">
         <v>49.3</v>
       </c>
-      <c r="K23" s="16" t="inlineStr">
+      <c r="L23" s="17" t="inlineStr">
         <is>
           <t>Saatte ~11 Plaka</t>
         </is>
       </c>
-      <c r="L23" s="11" t="n">
+      <c r="M23" s="11" t="n">
         <v>1183.2</v>
       </c>
-      <c r="M23" s="13" t="n">
+      <c r="N23" s="14" t="n">
         <v>113.1</v>
       </c>
-      <c r="N23" s="17" t="inlineStr">
+      <c r="O23" s="18" t="inlineStr">
         <is>
           <t>Saatte ~26 Plaka</t>
         </is>
       </c>
-      <c r="O23" s="36" t="n">
+      <c r="P23" s="38" t="n">
         <v>0.436</v>
       </c>
-      <c r="P23" s="17" t="inlineStr">
+      <c r="Q23" s="18" t="inlineStr">
         <is>
           <t>KLP-201</t>
         </is>
       </c>
-      <c r="Q23" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R23" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T23" s="17" t="inlineStr">
+      <c r="R23" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S23" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T23" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2857,27 +3058,37 @@
           <t>—</t>
         </is>
       </c>
-      <c r="V23" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W23" s="14" t="n">
+      <c r="V23" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W23" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X23" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y23" s="15" t="n">
         <v>90</v>
       </c>
-      <c r="X23" s="8" t="inlineStr">
+      <c r="Z23" s="8" t="inlineStr">
         <is>
           <t>Levha Özel Hattı (Hat 201)</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="22" t="inlineStr">
+      <c r="A24" s="23" t="inlineStr">
         <is>
           <t>AY GRİ Levha</t>
         </is>
       </c>
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B24" s="24" t="inlineStr">
         <is>
           <t>WPC Levha Plaka</t>
         </is>
@@ -2887,91 +3098,101 @@
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="24" t="inlineStr">
         <is>
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E24" s="24" t="inlineStr">
+      <c r="E24" s="25" t="inlineStr">
         <is>
           <t>4.64 kg/plaka</t>
         </is>
       </c>
-      <c r="F24" s="25" t="n">
+      <c r="F24" s="26" t="n">
         <v>6018.08</v>
       </c>
-      <c r="G24" s="26" t="inlineStr">
+      <c r="G24" s="27" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="H24" s="27" t="n">
+      <c r="H24" s="32" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="I24" s="28" t="n">
         <v>96</v>
       </c>
-      <c r="I24" s="28" t="n">
+      <c r="J24" s="29" t="n">
         <v>8</v>
       </c>
-      <c r="J24" s="29" t="n">
+      <c r="K24" s="30" t="n">
         <v>62.7</v>
       </c>
-      <c r="K24" s="30" t="inlineStr">
+      <c r="L24" s="31" t="inlineStr">
         <is>
           <t>Saatte ~14 Plaka</t>
         </is>
       </c>
-      <c r="L24" s="25" t="n">
+      <c r="M24" s="26" t="n">
         <v>1504.8</v>
       </c>
-      <c r="M24" s="27" t="n">
+      <c r="N24" s="28" t="n">
         <v>144.9</v>
       </c>
-      <c r="N24" s="31" t="inlineStr">
+      <c r="O24" s="32" t="inlineStr">
         <is>
           <t>Saatte ~31 Plaka</t>
         </is>
       </c>
-      <c r="O24" s="37" t="n">
+      <c r="P24" s="33" t="n">
         <v>0.433</v>
       </c>
-      <c r="P24" s="31" t="inlineStr">
+      <c r="Q24" s="32" t="inlineStr">
         <is>
           <t>KLP-201</t>
         </is>
       </c>
-      <c r="Q24" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R24" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S24" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T24" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U24" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V24" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W24" s="28" t="n">
+      <c r="R24" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S24" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T24" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U24" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V24" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W24" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X24" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y24" s="29" t="n">
         <v>90</v>
       </c>
-      <c r="X24" s="23" t="inlineStr">
+      <c r="Z24" s="24" t="inlineStr">
         <is>
           <t>Levha Özel Hattı (Hat 201)</t>
         </is>
@@ -3011,55 +3232,55 @@
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="H25" s="13" t="n">
+      <c r="H25" s="18" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="I25" s="14" t="n">
         <v>96</v>
       </c>
-      <c r="I25" s="14" t="n">
+      <c r="J25" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="J25" s="15" t="n">
+      <c r="K25" s="16" t="n">
         <v>58.4</v>
       </c>
-      <c r="K25" s="16" t="inlineStr">
+      <c r="L25" s="17" t="inlineStr">
         <is>
           <t>Saatte ~12 Plaka</t>
         </is>
       </c>
-      <c r="L25" s="11" t="n">
+      <c r="M25" s="11" t="n">
         <v>1401.6</v>
       </c>
-      <c r="M25" s="13" t="n">
+      <c r="N25" s="14" t="n">
         <v>111.8</v>
       </c>
-      <c r="N25" s="17" t="inlineStr">
+      <c r="O25" s="18" t="inlineStr">
         <is>
           <t>Saatte ~23 Plaka</t>
         </is>
       </c>
-      <c r="O25" s="36" t="n">
+      <c r="P25" s="38" t="n">
         <v>0.522</v>
       </c>
-      <c r="P25" s="17" t="inlineStr">
+      <c r="Q25" s="18" t="inlineStr">
         <is>
           <t>KLP-201</t>
         </is>
       </c>
-      <c r="Q25" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R25" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T25" s="17" t="inlineStr">
+      <c r="R25" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S25" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T25" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3069,27 +3290,37 @@
           <t>—</t>
         </is>
       </c>
-      <c r="V25" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W25" s="14" t="n">
+      <c r="V25" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W25" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X25" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y25" s="15" t="n">
         <v>90</v>
       </c>
-      <c r="X25" s="8" t="inlineStr">
+      <c r="Z25" s="8" t="inlineStr">
         <is>
           <t>Levha Özel Hattı (Hat 201)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="22" t="inlineStr">
+      <c r="A26" s="23" t="inlineStr">
         <is>
           <t>KOYU CEVİZ Levha</t>
         </is>
       </c>
-      <c r="B26" s="23" t="inlineStr">
+      <c r="B26" s="24" t="inlineStr">
         <is>
           <t>WPC Levha Plaka</t>
         </is>
@@ -3099,91 +3330,101 @@
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="D26" s="23" t="inlineStr">
+      <c r="D26" s="24" t="inlineStr">
         <is>
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E26" s="24" t="inlineStr">
+      <c r="E26" s="25" t="inlineStr">
         <is>
           <t>4.79 kg/plaka</t>
         </is>
       </c>
-      <c r="F26" s="25" t="n">
+      <c r="F26" s="26" t="n">
         <v>3846.37</v>
       </c>
-      <c r="G26" s="26" t="inlineStr">
+      <c r="G26" s="27" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="H26" s="27" t="n">
+      <c r="H26" s="32" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="I26" s="28" t="n">
         <v>84</v>
       </c>
-      <c r="I26" s="28" t="n">
+      <c r="J26" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="J26" s="29" t="n">
+      <c r="K26" s="30" t="n">
         <v>45.8</v>
       </c>
-      <c r="K26" s="30" t="inlineStr">
+      <c r="L26" s="31" t="inlineStr">
         <is>
           <t>Saatte ~10 Plaka</t>
         </is>
       </c>
-      <c r="L26" s="25" t="n">
+      <c r="M26" s="26" t="n">
         <v>1099.2</v>
       </c>
-      <c r="M26" s="27" t="n">
+      <c r="N26" s="28" t="n">
         <v>140</v>
       </c>
-      <c r="N26" s="31" t="inlineStr">
+      <c r="O26" s="32" t="inlineStr">
         <is>
           <t>Saatte ~29 Plaka</t>
         </is>
       </c>
-      <c r="O26" s="37" t="n">
+      <c r="P26" s="33" t="n">
         <v>0.327</v>
       </c>
-      <c r="P26" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q26" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R26" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S26" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T26" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U26" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V26" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W26" s="28" t="n">
+      <c r="Q26" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R26" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S26" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T26" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U26" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V26" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W26" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X26" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y26" s="29" t="n">
         <v>45</v>
       </c>
-      <c r="X26" s="23" t="inlineStr">
+      <c r="Z26" s="24" t="inlineStr">
         <is>
           <t>Levha Özel Hattı (Hat 201)</t>
         </is>
@@ -3223,55 +3464,55 @@
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="H27" s="13" t="n">
+      <c r="H27" s="18" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="I27" s="14" t="n">
         <v>36</v>
       </c>
-      <c r="I27" s="14" t="n">
+      <c r="J27" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="J27" s="15" t="n">
+      <c r="K27" s="16" t="n">
         <v>79.8</v>
       </c>
-      <c r="K27" s="16" t="inlineStr">
+      <c r="L27" s="17" t="inlineStr">
         <is>
           <t>Saatte ~17 Plaka</t>
         </is>
       </c>
-      <c r="L27" s="11" t="n">
+      <c r="M27" s="11" t="n">
         <v>1915.2</v>
       </c>
-      <c r="M27" s="13" t="n">
+      <c r="N27" s="14" t="n">
         <v>140</v>
       </c>
-      <c r="N27" s="17" t="inlineStr">
+      <c r="O27" s="18" t="inlineStr">
         <is>
           <t>Saatte ~29 Plaka</t>
         </is>
       </c>
-      <c r="O27" s="36" t="n">
+      <c r="P27" s="38" t="n">
         <v>0.57</v>
       </c>
-      <c r="P27" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q27" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R27" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T27" s="17" t="inlineStr">
+      <c r="Q27" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R27" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S27" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T27" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3281,27 +3522,37 @@
           <t>—</t>
         </is>
       </c>
-      <c r="V27" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W27" s="14" t="n">
+      <c r="V27" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W27" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X27" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y27" s="15" t="n">
         <v>45</v>
       </c>
-      <c r="X27" s="8" t="inlineStr">
+      <c r="Z27" s="8" t="inlineStr">
         <is>
           <t>Levha Özel Hattı (Hat 201)</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="22" t="inlineStr">
+      <c r="A28" s="23" t="inlineStr">
         <is>
           <t>U KAPAMA</t>
         </is>
       </c>
-      <c r="B28" s="23" t="inlineStr">
+      <c r="B28" s="24" t="inlineStr">
         <is>
           <t>U Kapama / Lambiri</t>
         </is>
@@ -3311,91 +3562,101 @@
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="D28" s="23" t="inlineStr">
+      <c r="D28" s="24" t="inlineStr">
         <is>
           <t>30 x 15 mm</t>
         </is>
       </c>
-      <c r="E28" s="24" t="inlineStr">
+      <c r="E28" s="25" t="inlineStr">
         <is>
           <t>0.48 kg/boy</t>
         </is>
       </c>
-      <c r="F28" s="25" t="n">
+      <c r="F28" s="26" t="n">
         <v>1392.48</v>
       </c>
-      <c r="G28" s="26" t="inlineStr">
+      <c r="G28" s="27" t="inlineStr">
         <is>
           <t>Hat 102</t>
         </is>
       </c>
-      <c r="H28" s="27" t="n">
+      <c r="H28" s="32" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="I28" s="28" t="n">
         <v>48</v>
       </c>
-      <c r="I28" s="28" t="n">
+      <c r="J28" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="J28" s="29" t="n">
+      <c r="K28" s="30" t="n">
         <v>29</v>
       </c>
-      <c r="K28" s="30" t="inlineStr">
+      <c r="L28" s="31" t="inlineStr">
         <is>
           <t>Saatte ~60 Boy</t>
         </is>
       </c>
-      <c r="L28" s="25" t="n">
+      <c r="M28" s="26" t="n">
         <v>696</v>
       </c>
-      <c r="M28" s="27" t="n">
+      <c r="N28" s="28" t="n">
         <v>40.7</v>
       </c>
-      <c r="N28" s="31" t="inlineStr">
+      <c r="O28" s="32" t="inlineStr">
         <is>
           <t>Saatte ~85 Boy</t>
         </is>
       </c>
-      <c r="O28" s="37" t="n">
+      <c r="P28" s="33" t="n">
         <v>0.713</v>
       </c>
-      <c r="P28" s="31" t="inlineStr">
+      <c r="Q28" s="32" t="inlineStr">
         <is>
           <t>KLP-102</t>
         </is>
       </c>
-      <c r="Q28" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R28" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S28" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T28" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U28" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V28" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W28" s="28" t="n">
+      <c r="R28" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S28" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T28" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U28" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V28" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W28" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X28" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y28" s="29" t="n">
         <v>40</v>
       </c>
-      <c r="X28" s="23" t="inlineStr">
+      <c r="Z28" s="24" t="inlineStr">
         <is>
           <t>Tek Hat Kalıp Atamalı</t>
         </is>
@@ -3435,55 +3696,55 @@
           <t>Hat 101</t>
         </is>
       </c>
-      <c r="H29" s="13" t="n">
+      <c r="H29" s="18" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="I29" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="I29" s="14" t="n">
+      <c r="J29" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="J29" s="15" t="n">
+      <c r="K29" s="16" t="n">
         <v>44.1</v>
       </c>
-      <c r="K29" s="16" t="inlineStr">
+      <c r="L29" s="17" t="inlineStr">
         <is>
           <t>Saatte ~15 Boy</t>
         </is>
       </c>
-      <c r="L29" s="11" t="n">
+      <c r="M29" s="11" t="n">
         <v>1058.4</v>
       </c>
-      <c r="M29" s="13" t="n">
+      <c r="N29" s="14" t="n">
         <v>44.2</v>
       </c>
-      <c r="N29" s="17" t="inlineStr">
+      <c r="O29" s="18" t="inlineStr">
         <is>
           <t>Saatte ~15 Boy</t>
         </is>
       </c>
-      <c r="O29" s="18" t="n">
+      <c r="P29" s="19" t="n">
         <v>0.998</v>
       </c>
-      <c r="P29" s="17" t="inlineStr">
+      <c r="Q29" s="18" t="inlineStr">
         <is>
           <t>KLP-101</t>
         </is>
       </c>
-      <c r="Q29" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R29" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T29" s="17" t="inlineStr">
+      <c r="R29" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S29" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T29" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3493,27 +3754,37 @@
           <t>—</t>
         </is>
       </c>
-      <c r="V29" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W29" s="14" t="n">
+      <c r="V29" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W29" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X29" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y29" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="X29" s="8" t="inlineStr">
+      <c r="Z29" s="8" t="inlineStr">
         <is>
           <t>Tek Hat Kalıp Atamalı</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="22" t="inlineStr">
+      <c r="A30" s="23" t="inlineStr">
         <is>
           <t>KT102-219x26-KAH</t>
         </is>
       </c>
-      <c r="B30" s="23" t="inlineStr">
+      <c r="B30" s="24" t="inlineStr">
         <is>
           <t>Deck / WPC Zemin</t>
         </is>
@@ -3523,141 +3794,153 @@
           <t>3.00 Metre</t>
         </is>
       </c>
-      <c r="D30" s="23" t="inlineStr">
+      <c r="D30" s="24" t="inlineStr">
         <is>
           <t>219 x 26 mm</t>
         </is>
       </c>
-      <c r="E30" s="24" t="inlineStr">
+      <c r="E30" s="25" t="inlineStr">
         <is>
           <t>9.26 kg/boy</t>
         </is>
       </c>
-      <c r="F30" s="25" t="n">
+      <c r="F30" s="26" t="n">
         <v>463</v>
       </c>
-      <c r="G30" s="26" t="inlineStr">
+      <c r="G30" s="27" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="H30" s="27" t="n">
+      <c r="H30" s="32" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="I30" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="I30" s="28" t="n">
+      <c r="J30" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="29" t="n">
+      <c r="K30" s="30" t="n">
         <v>38.6</v>
       </c>
-      <c r="K30" s="30" t="inlineStr">
+      <c r="L30" s="31" t="inlineStr">
         <is>
           <t>Saatte ~4 Boy</t>
         </is>
       </c>
-      <c r="L30" s="25" t="n">
+      <c r="M30" s="26" t="n">
         <v>926.4</v>
       </c>
-      <c r="M30" s="27" t="n">
+      <c r="N30" s="28" t="n">
         <v>115.8</v>
       </c>
-      <c r="N30" s="31" t="inlineStr">
+      <c r="O30" s="32" t="inlineStr">
         <is>
           <t>Saatte ~12 Boy</t>
         </is>
       </c>
-      <c r="O30" s="37" t="n">
+      <c r="P30" s="33" t="n">
         <v>0.333</v>
       </c>
-      <c r="P30" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q30" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R30" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S30" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T30" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U30" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V30" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W30" s="28" t="n">
+      <c r="Q30" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R30" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S30" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T30" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U30" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V30" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W30" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X30" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y30" s="29" t="n">
         <v>45</v>
       </c>
-      <c r="X30" s="23" t="inlineStr">
+      <c r="Z30" s="24" t="inlineStr">
         <is>
           <t>Tek Hat Kalıp Atamalı</t>
         </is>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="38" t="inlineStr">
+      <c r="A31" s="39" t="inlineStr">
         <is>
           <t>GENEL TOPLAM / FABRİKA</t>
         </is>
       </c>
-      <c r="B31" s="39" t="n"/>
-      <c r="C31" s="39" t="n"/>
-      <c r="D31" s="39" t="n"/>
-      <c r="E31" s="39" t="n"/>
-      <c r="F31" s="40" t="n">
+      <c r="B31" s="40" t="n"/>
+      <c r="C31" s="40" t="n"/>
+      <c r="D31" s="40" t="n"/>
+      <c r="E31" s="40" t="n"/>
+      <c r="F31" s="41" t="n">
         <v>1237183.51</v>
       </c>
-      <c r="G31" s="39" t="n"/>
-      <c r="H31" s="41" t="n">
+      <c r="G31" s="40" t="n"/>
+      <c r="H31" s="40" t="n"/>
+      <c r="I31" s="42" t="n">
         <v>12024</v>
       </c>
-      <c r="I31" s="39" t="n"/>
-      <c r="J31" s="39" t="n"/>
-      <c r="K31" s="39" t="n"/>
-      <c r="L31" s="39" t="n"/>
-      <c r="M31" s="39" t="n"/>
-      <c r="N31" s="39" t="n"/>
-      <c r="O31" s="39" t="n"/>
-      <c r="P31" s="39" t="n"/>
-      <c r="Q31" s="39" t="n"/>
-      <c r="R31" s="41" t="n">
+      <c r="J31" s="40" t="n"/>
+      <c r="K31" s="40" t="n"/>
+      <c r="L31" s="40" t="n"/>
+      <c r="M31" s="40" t="n"/>
+      <c r="N31" s="40" t="n"/>
+      <c r="O31" s="40" t="n"/>
+      <c r="P31" s="40" t="n"/>
+      <c r="Q31" s="40" t="n"/>
+      <c r="R31" s="40" t="n"/>
+      <c r="S31" s="40" t="n"/>
+      <c r="T31" s="42" t="n">
         <v>4812</v>
       </c>
-      <c r="S31" s="39" t="n"/>
-      <c r="T31" s="39" t="n"/>
-      <c r="U31" s="39" t="n"/>
-      <c r="V31" s="39" t="n"/>
-      <c r="W31" s="39" t="n"/>
-      <c r="X31" s="39" t="n"/>
+      <c r="U31" s="40" t="n"/>
+      <c r="V31" s="40" t="n"/>
+      <c r="W31" s="40" t="n"/>
+      <c r="X31" s="40" t="n"/>
+      <c r="Y31" s="40" t="n"/>
+      <c r="Z31" s="40" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="X3"/>
-    <mergeCell ref="Q3:U3"/>
-    <mergeCell ref="A2:X2"/>
-    <mergeCell ref="G3:P3"/>
-    <mergeCell ref="A1:X1"/>
+    <mergeCell ref="G3:Q3"/>
+    <mergeCell ref="Z3"/>
+    <mergeCell ref="A1:Z1"/>
+    <mergeCell ref="R3:W3"/>
+    <mergeCell ref="A2:Z2"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="X3:Y3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3757,41 +4040,41 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Hat 101</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>Ekstrüzyon Hattı</t>
         </is>
       </c>
-      <c r="C4" s="27" t="n">
+      <c r="C4" s="28" t="n">
         <v>840</v>
       </c>
-      <c r="D4" s="28" t="n">
+      <c r="D4" s="29" t="n">
         <v>70</v>
       </c>
-      <c r="E4" s="25" t="n">
+      <c r="E4" s="26" t="n">
         <v>33263.65</v>
       </c>
-      <c r="F4" s="42" t="n">
+      <c r="F4" s="43" t="n">
         <v>33.26</v>
       </c>
-      <c r="G4" s="29" t="n">
+      <c r="G4" s="30" t="n">
         <v>39.6</v>
       </c>
-      <c r="H4" s="34" t="n">
+      <c r="H4" s="35" t="n">
         <v>50</v>
       </c>
-      <c r="I4" s="37" t="n">
+      <c r="I4" s="33" t="n">
         <v>0.792</v>
       </c>
-      <c r="J4" s="28" t="n">
+      <c r="J4" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="K4" s="43" t="inlineStr">
+      <c r="K4" s="44" t="inlineStr">
         <is>
           <t>35X100 PERVAZ, 35X150 PERVAZ, 35X80 PERVAZ</t>
         </is>
@@ -3808,72 +4091,72 @@
           <t>Ekstrüzyon Hattı</t>
         </is>
       </c>
-      <c r="C5" s="13" t="n">
+      <c r="C5" s="14" t="n">
         <v>1668</v>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="15" t="n">
         <v>139</v>
       </c>
       <c r="E5" s="11" t="n">
         <v>91560.17999999998</v>
       </c>
-      <c r="F5" s="44" t="n">
+      <c r="F5" s="45" t="n">
         <v>91.56</v>
       </c>
-      <c r="G5" s="15" t="n">
+      <c r="G5" s="16" t="n">
         <v>54.9</v>
       </c>
-      <c r="H5" s="20" t="n">
+      <c r="H5" s="21" t="n">
         <v>65</v>
       </c>
-      <c r="I5" s="18" t="n">
+      <c r="I5" s="19" t="n">
         <v>0.845</v>
       </c>
-      <c r="J5" s="14" t="n">
+      <c r="J5" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="K5" s="45" t="inlineStr">
+      <c r="K5" s="46" t="inlineStr">
         <is>
           <t>100 mm KASA, 140 mm KASA, CAM ÇITASI</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="22" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>Hat 103</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>Ekstrüzyon Hattı</t>
         </is>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="28" t="n">
         <v>1524</v>
       </c>
-      <c r="D6" s="28" t="n">
+      <c r="D6" s="29" t="n">
         <v>127</v>
       </c>
-      <c r="E6" s="25" t="n">
+      <c r="E6" s="26" t="n">
         <v>69803</v>
       </c>
-      <c r="F6" s="42" t="n">
+      <c r="F6" s="43" t="n">
         <v>69.8</v>
       </c>
-      <c r="G6" s="29" t="n">
+      <c r="G6" s="30" t="n">
         <v>45.8</v>
       </c>
-      <c r="H6" s="34" t="n">
+      <c r="H6" s="35" t="n">
         <v>55</v>
       </c>
-      <c r="I6" s="32" t="n">
+      <c r="I6" s="37" t="n">
         <v>0.833</v>
       </c>
-      <c r="J6" s="28" t="n">
+      <c r="J6" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="K6" s="43" t="inlineStr">
+      <c r="K6" s="44" t="inlineStr">
         <is>
           <t>50X80 PERVAZ, SEREN</t>
         </is>
@@ -3890,72 +4173,72 @@
           <t>Ekstrüzyon Hattı</t>
         </is>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="14" t="n">
         <v>1716</v>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="15" t="n">
         <v>143</v>
       </c>
       <c r="E7" s="11" t="n">
         <v>154861.98</v>
       </c>
-      <c r="F7" s="44" t="n">
+      <c r="F7" s="45" t="n">
         <v>154.86</v>
       </c>
-      <c r="G7" s="15" t="n">
+      <c r="G7" s="16" t="n">
         <v>90.2</v>
       </c>
-      <c r="H7" s="20" t="n">
+      <c r="H7" s="21" t="n">
         <v>100</v>
       </c>
-      <c r="I7" s="18" t="n">
+      <c r="I7" s="19" t="n">
         <v>0.902</v>
       </c>
-      <c r="J7" s="14" t="n">
+      <c r="J7" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="K7" s="45" t="inlineStr">
+      <c r="K7" s="46" t="inlineStr">
         <is>
           <t>SEREN</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>Hat 105</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>Ekstrüzyon Hattı</t>
         </is>
       </c>
-      <c r="C8" s="27" t="n">
+      <c r="C8" s="28" t="n">
         <v>1632</v>
       </c>
-      <c r="D8" s="28" t="n">
+      <c r="D8" s="29" t="n">
         <v>136</v>
       </c>
-      <c r="E8" s="25" t="n">
+      <c r="E8" s="26" t="n">
         <v>137071.86</v>
       </c>
-      <c r="F8" s="42" t="n">
+      <c r="F8" s="43" t="n">
         <v>137.07</v>
       </c>
-      <c r="G8" s="29" t="n">
+      <c r="G8" s="30" t="n">
         <v>84</v>
       </c>
-      <c r="H8" s="34" t="n">
+      <c r="H8" s="35" t="n">
         <v>95</v>
       </c>
-      <c r="I8" s="32" t="n">
+      <c r="I8" s="37" t="n">
         <v>0.884</v>
       </c>
-      <c r="J8" s="28" t="n">
+      <c r="J8" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="K8" s="43" t="inlineStr">
+      <c r="K8" s="44" t="inlineStr">
         <is>
           <t>140 mm KASA, SEREN</t>
         </is>
@@ -3972,72 +4255,72 @@
           <t>Ekstrüzyon Hattı</t>
         </is>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="14" t="n">
         <v>1704</v>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D9" s="15" t="n">
         <v>142</v>
       </c>
       <c r="E9" s="11" t="n">
         <v>112898.9699999999</v>
       </c>
-      <c r="F9" s="44" t="n">
+      <c r="F9" s="45" t="n">
         <v>112.9</v>
       </c>
-      <c r="G9" s="15" t="n">
+      <c r="G9" s="16" t="n">
         <v>66.3</v>
       </c>
-      <c r="H9" s="20" t="n">
+      <c r="H9" s="21" t="n">
         <v>75</v>
       </c>
-      <c r="I9" s="18" t="n">
+      <c r="I9" s="19" t="n">
         <v>0.884</v>
       </c>
-      <c r="J9" s="14" t="n">
+      <c r="J9" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="K9" s="45" t="inlineStr">
+      <c r="K9" s="46" t="inlineStr">
         <is>
           <t>100 mm KASA, 140 mm KASA, 200 mm KASA</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>Ekstrüzyon Hattı</t>
         </is>
       </c>
-      <c r="C10" s="27" t="n">
+      <c r="C10" s="28" t="n">
         <v>1812</v>
       </c>
-      <c r="D10" s="28" t="n">
+      <c r="D10" s="29" t="n">
         <v>151</v>
       </c>
-      <c r="E10" s="25" t="n">
+      <c r="E10" s="26" t="n">
         <v>135361.61</v>
       </c>
-      <c r="F10" s="42" t="n">
+      <c r="F10" s="43" t="n">
         <v>135.36</v>
       </c>
-      <c r="G10" s="29" t="n">
+      <c r="G10" s="30" t="n">
         <v>74.7</v>
       </c>
-      <c r="H10" s="34" t="n">
+      <c r="H10" s="35" t="n">
         <v>85</v>
       </c>
-      <c r="I10" s="32" t="n">
+      <c r="I10" s="37" t="n">
         <v>0.879</v>
       </c>
-      <c r="J10" s="28" t="n">
+      <c r="J10" s="29" t="n">
         <v>8</v>
       </c>
-      <c r="K10" s="43" t="inlineStr">
+      <c r="K10" s="44" t="inlineStr">
         <is>
           <t>100 mm KASA, 140 mm KASA, 200 mm KASA</t>
         </is>
@@ -4054,72 +4337,72 @@
           <t>Ekstrüzyon Hattı</t>
         </is>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="14" t="n">
         <v>1668</v>
       </c>
-      <c r="D11" s="14" t="n">
+      <c r="D11" s="15" t="n">
         <v>139</v>
       </c>
       <c r="E11" s="11" t="n">
         <v>109257.63</v>
       </c>
-      <c r="F11" s="44" t="n">
+      <c r="F11" s="45" t="n">
         <v>109.26</v>
       </c>
-      <c r="G11" s="15" t="n">
+      <c r="G11" s="16" t="n">
         <v>65.5</v>
       </c>
-      <c r="H11" s="20" t="n">
+      <c r="H11" s="21" t="n">
         <v>70</v>
       </c>
-      <c r="I11" s="18" t="n">
+      <c r="I11" s="19" t="n">
         <v>0.9360000000000001</v>
       </c>
-      <c r="J11" s="14" t="n">
+      <c r="J11" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="K11" s="45" t="inlineStr">
+      <c r="K11" s="46" t="inlineStr">
         <is>
           <t>100 mm KASA, 140 mm KASA, 200 mm KASA</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="A12" s="23" t="inlineStr">
         <is>
           <t>Hat 109</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>Ekstrüzyon Hattı</t>
         </is>
       </c>
-      <c r="C12" s="27" t="n">
+      <c r="C12" s="28" t="n">
         <v>1788</v>
       </c>
-      <c r="D12" s="28" t="n">
+      <c r="D12" s="29" t="n">
         <v>149</v>
       </c>
-      <c r="E12" s="25" t="n">
+      <c r="E12" s="26" t="n">
         <v>118327.55</v>
       </c>
-      <c r="F12" s="42" t="n">
+      <c r="F12" s="43" t="n">
         <v>118.33</v>
       </c>
-      <c r="G12" s="29" t="n">
+      <c r="G12" s="30" t="n">
         <v>66.2</v>
       </c>
-      <c r="H12" s="34" t="n">
+      <c r="H12" s="35" t="n">
         <v>80</v>
       </c>
-      <c r="I12" s="32" t="n">
+      <c r="I12" s="37" t="n">
         <v>0.828</v>
       </c>
-      <c r="J12" s="28" t="n">
+      <c r="J12" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="K12" s="43" t="inlineStr">
+      <c r="K12" s="44" t="inlineStr">
         <is>
           <t>50X80 PERVAZ, 80X80 PERVAZ</t>
         </is>
@@ -4136,72 +4419,72 @@
           <t>Levha Hattı</t>
         </is>
       </c>
-      <c r="C13" s="13" t="n">
+      <c r="C13" s="14" t="n">
         <v>2952</v>
       </c>
-      <c r="D13" s="14" t="n">
+      <c r="D13" s="15" t="n">
         <v>246</v>
       </c>
       <c r="E13" s="11" t="n">
         <v>274777.0800000001</v>
       </c>
-      <c r="F13" s="44" t="n">
+      <c r="F13" s="45" t="n">
         <v>274.78</v>
       </c>
-      <c r="G13" s="15" t="n">
+      <c r="G13" s="16" t="n">
         <v>93.09999999999999</v>
       </c>
-      <c r="H13" s="20" t="n">
+      <c r="H13" s="21" t="n">
         <v>150</v>
       </c>
-      <c r="I13" s="36" t="n">
+      <c r="I13" s="38" t="n">
         <v>0.621</v>
       </c>
-      <c r="J13" s="14" t="n">
+      <c r="J13" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="K13" s="45" t="inlineStr">
+      <c r="K13" s="46" t="inlineStr">
         <is>
           <t>ANTRASİT Levha, AY GRİ Levha, BEYAZ TEAK Levha</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t>Kırım 1</t>
         </is>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>Kırım / Geri Dönüşüm</t>
         </is>
       </c>
-      <c r="C14" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="34" t="n">
+      <c r="C14" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="35" t="n">
         <v>250</v>
       </c>
-      <c r="I14" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="43" t="inlineStr">
+      <c r="I14" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4218,72 +4501,72 @@
           <t>Kırım / Geri Dönüşüm</t>
         </is>
       </c>
-      <c r="C15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="14" t="n">
+      <c r="C15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="15" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="20" t="n">
+      <c r="F15" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="21" t="n">
         <v>250</v>
       </c>
-      <c r="I15" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="45" t="inlineStr">
+      <c r="I15" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="46" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="22" t="inlineStr">
+      <c r="A16" s="23" t="inlineStr">
         <is>
           <t>Kırım 3</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>Kırım / Geri Dönüşüm</t>
         </is>
       </c>
-      <c r="C16" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="34" t="n">
+      <c r="C16" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="35" t="n">
         <v>250</v>
       </c>
-      <c r="I16" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="43" t="inlineStr">
+      <c r="I16" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4300,72 +4583,72 @@
           <t>Kırım / Geri Dönüşüm</t>
         </is>
       </c>
-      <c r="C17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="14" t="n">
+      <c r="C17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="15" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="20" t="n">
+      <c r="F17" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="21" t="n">
         <v>250</v>
       </c>
-      <c r="I17" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="45" t="inlineStr">
+      <c r="I17" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="46" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="22" t="inlineStr">
+      <c r="A18" s="23" t="inlineStr">
         <is>
           <t>Mikronize 1</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t>Mikronize Değirmeni</t>
         </is>
       </c>
-      <c r="C18" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="34" t="n">
+      <c r="C18" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="35" t="n">
         <v>180</v>
       </c>
-      <c r="I18" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="43" t="inlineStr">
+      <c r="I18" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4382,72 +4665,72 @@
           <t>Mikronize Değirmeni</t>
         </is>
       </c>
-      <c r="C19" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="14" t="n">
+      <c r="C19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="15" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="20" t="n">
+      <c r="F19" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="21" t="n">
         <v>180</v>
       </c>
-      <c r="I19" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="45" t="inlineStr">
+      <c r="I19" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="46" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="22" t="inlineStr">
+      <c r="A20" s="23" t="inlineStr">
         <is>
           <t>Mikronize 3</t>
         </is>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t>Mikronize Değirmeni</t>
         </is>
       </c>
-      <c r="C20" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="34" t="n">
+      <c r="C20" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="35" t="n">
         <v>180</v>
       </c>
-      <c r="I20" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="43" t="inlineStr">
+      <c r="I20" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4464,72 +4747,72 @@
           <t>Mikronize Değirmeni</t>
         </is>
       </c>
-      <c r="C21" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="14" t="n">
+      <c r="C21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="15" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F21" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="20" t="n">
+      <c r="F21" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="21" t="n">
         <v>180</v>
       </c>
-      <c r="I21" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="45" t="inlineStr">
+      <c r="I21" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="46" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="22" t="inlineStr">
+      <c r="A22" s="23" t="inlineStr">
         <is>
           <t>Mikronize 5</t>
         </is>
       </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>Mikronize Değirmeni</t>
         </is>
       </c>
-      <c r="C22" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="34" t="n">
+      <c r="C22" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="35" t="n">
         <v>180</v>
       </c>
-      <c r="I22" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="43" t="inlineStr">
+      <c r="I22" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4546,72 +4829,72 @@
           <t>Mikronize Değirmeni</t>
         </is>
       </c>
-      <c r="C23" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="14" t="n">
+      <c r="C23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="15" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F23" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="20" t="n">
+      <c r="F23" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="21" t="n">
         <v>180</v>
       </c>
-      <c r="I23" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="45" t="inlineStr">
+      <c r="I23" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="46" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="22" t="inlineStr">
+      <c r="A24" s="23" t="inlineStr">
         <is>
           <t>Mixer 1</t>
         </is>
       </c>
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B24" s="24" t="inlineStr">
         <is>
           <t>Mikser / Karışım</t>
         </is>
       </c>
-      <c r="C24" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="34" t="n">
+      <c r="C24" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="35" t="n">
         <v>400</v>
       </c>
-      <c r="I24" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="43" t="inlineStr">
+      <c r="I24" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4628,101 +4911,101 @@
           <t>Mikser / Karışım</t>
         </is>
       </c>
-      <c r="C25" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="14" t="n">
+      <c r="C25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="15" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F25" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="20" t="n">
+      <c r="F25" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="21" t="n">
         <v>400</v>
       </c>
-      <c r="I25" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="45" t="inlineStr">
+      <c r="I25" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="46" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="22" t="inlineStr">
+      <c r="A26" s="23" t="inlineStr">
         <is>
           <t>Mixer 3</t>
         </is>
       </c>
-      <c r="B26" s="23" t="inlineStr">
+      <c r="B26" s="24" t="inlineStr">
         <is>
           <t>Mikser / Karışım</t>
         </is>
       </c>
-      <c r="C26" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="34" t="n">
+      <c r="C26" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="35" t="n">
         <v>400</v>
       </c>
-      <c r="I26" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="43" t="inlineStr">
+      <c r="I26" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="50" t="inlineStr">
+      <c r="A27" s="51" t="inlineStr">
         <is>
           <t>GENEL MAKİNE TOPLAMI</t>
         </is>
       </c>
-      <c r="B27" s="39" t="n"/>
-      <c r="C27" s="41" t="n">
+      <c r="B27" s="40" t="n"/>
+      <c r="C27" s="42" t="n">
         <v>17304</v>
       </c>
-      <c r="D27" s="40" t="n">
+      <c r="D27" s="41" t="n">
         <v>1442</v>
       </c>
-      <c r="E27" s="40" t="n">
+      <c r="E27" s="41" t="n">
         <v>1237183.51</v>
       </c>
-      <c r="F27" s="51" t="n">
+      <c r="F27" s="52" t="n">
         <v>1237.18</v>
       </c>
-      <c r="G27" s="39" t="n"/>
-      <c r="H27" s="39" t="n"/>
-      <c r="I27" s="39" t="n"/>
-      <c r="J27" s="39" t="n"/>
-      <c r="K27" s="39" t="n"/>
+      <c r="G27" s="40" t="n"/>
+      <c r="H27" s="40" t="n"/>
+      <c r="I27" s="40" t="n"/>
+      <c r="J27" s="40" t="n"/>
+      <c r="K27" s="40" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4739,7 +5022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:O44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4747,28 +5030,29 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ERGUNBAS GROUP — ÜRÜNLERİN HANGİ HATLARDA KAÇ SAAT ÇALIŞTIĞININ AYRINTILI LİSTESİ</t>
+          <t>ERGUNBAS GROUP — ÜRÜN BAZINDA HAT ÜRETİM DAĞILIMI, KALIP GÖZ SAYILARI VE KAPASİTE PERFORMANSI</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Her bir ürünün çalıştığı tüm makineler, kesim boyları, çekilen toplam boy/plaka adetleri, net tonajlar ve saatteki net boy hızları</t>
+          <t>Her bir ürünün çalıştığı makineler, kalıp göz sayıları (1 Göz / 2 Göz Çift Çıkış), kesim boyları, çekilen boy adetleri ve net hızlar</t>
         </is>
       </c>
     </row>
@@ -4800,57 +5084,62 @@
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
+          <t>Kalıp Göz Sayısı (Kafa)</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
           <t>Rota Sınıfı</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>Fiili Çalışma (Saat)</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>Vardiya Sayısı</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>Üretilen Miktar (Adet)</t>
-        </is>
-      </c>
       <c r="J3" s="6" t="inlineStr">
         <is>
+          <t>Üretilen Miktar (Adet/Boy)</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
           <t>Birim Ağırlık</t>
         </is>
       </c>
-      <c r="K3" s="6" t="inlineStr">
+      <c r="L3" s="6" t="inlineStr">
         <is>
           <t>Toplam Üretim (kg)</t>
         </is>
       </c>
-      <c r="L3" s="6" t="inlineStr">
+      <c r="M3" s="6" t="inlineStr">
         <is>
           <t>Fiili Hız (kg/sa)</t>
         </is>
       </c>
-      <c r="M3" s="6" t="inlineStr">
+      <c r="N3" s="6" t="inlineStr">
         <is>
           <t>Fiili Hız (Saatteki Boy/Adet)</t>
         </is>
       </c>
-      <c r="N3" s="6" t="inlineStr">
+      <c r="O3" s="6" t="inlineStr">
         <is>
           <t>Kapasite Payı (%)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>SEREN</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>Seren Çıtası</t>
         </is>
@@ -4860,47 +5149,52 @@
           <t>2.10 Metre</t>
         </is>
       </c>
-      <c r="D4" s="23" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>38 x 45 mm</t>
         </is>
       </c>
-      <c r="E4" s="52" t="inlineStr">
+      <c r="E4" s="53" t="inlineStr">
         <is>
           <t>Hat 104</t>
         </is>
       </c>
-      <c r="F4" s="26" t="inlineStr">
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>2 Göz (Çift Çıkış)</t>
+        </is>
+      </c>
+      <c r="G4" s="27" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="G4" s="27" t="n">
+      <c r="H4" s="28" t="n">
         <v>1716</v>
       </c>
-      <c r="H4" s="28" t="n">
+      <c r="I4" s="29" t="n">
         <v>143</v>
       </c>
-      <c r="I4" s="28" t="n">
+      <c r="J4" s="29" t="n">
         <v>45682</v>
       </c>
-      <c r="J4" s="24" t="inlineStr">
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t>3.39 kg/boy</t>
         </is>
       </c>
-      <c r="K4" s="25" t="n">
+      <c r="L4" s="26" t="n">
         <v>154861.98</v>
       </c>
-      <c r="L4" s="29" t="n">
+      <c r="M4" s="30" t="n">
         <v>90.2</v>
       </c>
-      <c r="M4" s="30" t="inlineStr">
+      <c r="N4" s="31" t="inlineStr">
         <is>
           <t>Saatte ~27 Boy</t>
         </is>
       </c>
-      <c r="N4" s="53" t="n">
+      <c r="O4" s="54" t="n">
         <v>0.5243210981796479</v>
       </c>
     </row>
@@ -4925,52 +5219,57 @@
           <t>38 x 45 mm</t>
         </is>
       </c>
-      <c r="E5" s="54" t="inlineStr">
+      <c r="E5" s="55" t="inlineStr">
         <is>
           <t>Hat 105</t>
         </is>
       </c>
-      <c r="F5" s="19" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>2 Göz (Çift Çıkış)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>YEDEK ROTA 1</t>
         </is>
       </c>
-      <c r="G5" s="13" t="n">
+      <c r="H5" s="14" t="n">
         <v>1620</v>
       </c>
-      <c r="H5" s="14" t="n">
+      <c r="I5" s="15" t="n">
         <v>135</v>
       </c>
-      <c r="I5" s="14" t="n">
+      <c r="J5" s="15" t="n">
         <v>40129</v>
       </c>
-      <c r="J5" s="10" t="inlineStr">
+      <c r="K5" s="10" t="inlineStr">
         <is>
           <t>3.39 kg/boy</t>
         </is>
       </c>
-      <c r="K5" s="11" t="n">
+      <c r="L5" s="11" t="n">
         <v>136037.31</v>
       </c>
-      <c r="L5" s="15" t="n">
+      <c r="M5" s="16" t="n">
         <v>84</v>
       </c>
-      <c r="M5" s="16" t="inlineStr">
+      <c r="N5" s="17" t="inlineStr">
         <is>
           <t>Saatte ~25 Boy</t>
         </is>
       </c>
-      <c r="N5" s="55" t="n">
+      <c r="O5" s="56" t="n">
         <v>0.4605858182402497</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="22" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>DİŞBUDAK Levha</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>WPC Levha Plaka</t>
         </is>
@@ -4980,47 +5279,52 @@
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D6" s="24" t="inlineStr">
         <is>
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E6" s="52" t="inlineStr">
+      <c r="E6" s="53" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="F6" s="26" t="inlineStr">
+      <c r="F6" s="32" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="G6" s="27" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="G6" s="27" t="n">
+      <c r="H6" s="28" t="n">
         <v>972</v>
       </c>
-      <c r="H6" s="28" t="n">
+      <c r="I6" s="29" t="n">
         <v>81</v>
       </c>
-      <c r="I6" s="28" t="n">
+      <c r="J6" s="29" t="n">
         <v>24904</v>
       </c>
-      <c r="J6" s="24" t="inlineStr">
+      <c r="K6" s="25" t="inlineStr">
         <is>
           <t>4.77 kg/plaka</t>
         </is>
       </c>
-      <c r="K6" s="25" t="n">
+      <c r="L6" s="26" t="n">
         <v>118792.08</v>
       </c>
-      <c r="L6" s="29" t="n">
+      <c r="M6" s="30" t="n">
         <v>122.2</v>
       </c>
-      <c r="M6" s="30" t="inlineStr">
+      <c r="N6" s="31" t="inlineStr">
         <is>
           <t>Saatte ~26 Plaka</t>
         </is>
       </c>
-      <c r="N6" s="53" t="n">
+      <c r="O6" s="54" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5045,52 +5349,57 @@
           <t>50 x 80 mm</t>
         </is>
       </c>
-      <c r="E7" s="54" t="inlineStr">
+      <c r="E7" s="55" t="inlineStr">
         <is>
           <t>Hat 109</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>2 Göz (Çift Çıkış)</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="H7" s="14" t="n">
         <v>1776</v>
       </c>
-      <c r="H7" s="14" t="n">
+      <c r="I7" s="15" t="n">
         <v>148</v>
       </c>
-      <c r="I7" s="14" t="n">
+      <c r="J7" s="15" t="n">
         <v>75361</v>
       </c>
-      <c r="J7" s="10" t="inlineStr">
+      <c r="K7" s="10" t="inlineStr">
         <is>
           <t>1.55 kg/boy</t>
         </is>
       </c>
-      <c r="K7" s="11" t="n">
+      <c r="L7" s="11" t="n">
         <v>116809.55</v>
       </c>
-      <c r="L7" s="15" t="n">
+      <c r="M7" s="16" t="n">
         <v>65.8</v>
       </c>
-      <c r="M7" s="16" t="inlineStr">
+      <c r="N7" s="17" t="inlineStr">
         <is>
           <t>Saatte ~42 Boy</t>
         </is>
       </c>
-      <c r="N7" s="55" t="n">
+      <c r="O7" s="56" t="n">
         <v>0.6311060120089439</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>140 mm KASA</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>Kasa Profili</t>
         </is>
@@ -5100,47 +5409,52 @@
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t>140 x 36 mm</t>
         </is>
       </c>
-      <c r="E8" s="52" t="inlineStr">
+      <c r="E8" s="53" t="inlineStr">
         <is>
           <t>Hat 106</t>
         </is>
       </c>
-      <c r="F8" s="26" t="inlineStr">
+      <c r="F8" s="32" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="G8" s="27" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="G8" s="27" t="n">
+      <c r="H8" s="28" t="n">
         <v>1668</v>
       </c>
-      <c r="H8" s="28" t="n">
+      <c r="I8" s="29" t="n">
         <v>139</v>
       </c>
-      <c r="I8" s="28" t="n">
+      <c r="J8" s="29" t="n">
         <v>22015</v>
       </c>
-      <c r="J8" s="24" t="inlineStr">
+      <c r="K8" s="25" t="inlineStr">
         <is>
           <t>4.95 kg/boy</t>
         </is>
       </c>
-      <c r="K8" s="25" t="n">
+      <c r="L8" s="26" t="n">
         <v>108974.2499999999</v>
       </c>
-      <c r="L8" s="29" t="n">
+      <c r="M8" s="30" t="n">
         <v>65.3</v>
       </c>
-      <c r="M8" s="30" t="inlineStr">
+      <c r="N8" s="31" t="inlineStr">
         <is>
           <t>Saatte ~13 Boy</t>
         </is>
       </c>
-      <c r="N8" s="53" t="n">
+      <c r="O8" s="54" t="n">
         <v>0.6429426710668495</v>
       </c>
     </row>
@@ -5165,52 +5479,57 @@
           <t>200 x 36 mm</t>
         </is>
       </c>
-      <c r="E9" s="54" t="inlineStr">
+      <c r="E9" s="55" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="H9" s="14" t="n">
         <v>1032</v>
       </c>
-      <c r="H9" s="14" t="n">
+      <c r="I9" s="15" t="n">
         <v>86</v>
       </c>
-      <c r="I9" s="14" t="n">
+      <c r="J9" s="15" t="n">
         <v>11377</v>
       </c>
-      <c r="J9" s="10" t="inlineStr">
+      <c r="K9" s="10" t="inlineStr">
         <is>
           <t>6.66 kg/boy</t>
         </is>
       </c>
-      <c r="K9" s="11" t="n">
+      <c r="L9" s="11" t="n">
         <v>75770.82000000001</v>
       </c>
-      <c r="L9" s="15" t="n">
+      <c r="M9" s="16" t="n">
         <v>73.40000000000001</v>
       </c>
-      <c r="M9" s="16" t="inlineStr">
+      <c r="N9" s="17" t="inlineStr">
         <is>
           <t>Saatte ~11 Boy</t>
         </is>
       </c>
-      <c r="N9" s="55" t="n">
+      <c r="O9" s="56" t="n">
         <v>0.9312433494311206</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>50X80 PERVAZ</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>Pervaz Profili</t>
         </is>
@@ -5220,47 +5539,52 @@
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D10" s="24" t="inlineStr">
         <is>
           <t>50 x 80 mm</t>
         </is>
       </c>
-      <c r="E10" s="52" t="inlineStr">
+      <c r="E10" s="53" t="inlineStr">
         <is>
           <t>Hat 103</t>
         </is>
       </c>
-      <c r="F10" s="33" t="inlineStr">
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>2 Göz (Çift Çıkış)</t>
+        </is>
+      </c>
+      <c r="G10" s="34" t="inlineStr">
         <is>
           <t>YEDEK ROTA 1</t>
         </is>
       </c>
-      <c r="G10" s="27" t="n">
+      <c r="H10" s="28" t="n">
         <v>1512</v>
       </c>
-      <c r="H10" s="28" t="n">
+      <c r="I10" s="29" t="n">
         <v>126</v>
       </c>
-      <c r="I10" s="28" t="n">
+      <c r="J10" s="29" t="n">
         <v>44050</v>
       </c>
-      <c r="J10" s="24" t="inlineStr">
+      <c r="K10" s="25" t="inlineStr">
         <is>
           <t>1.55 kg/boy</t>
         </is>
       </c>
-      <c r="K10" s="25" t="n">
+      <c r="L10" s="26" t="n">
         <v>68277.5</v>
       </c>
-      <c r="L10" s="29" t="n">
+      <c r="M10" s="30" t="n">
         <v>45.2</v>
       </c>
-      <c r="M10" s="30" t="inlineStr">
+      <c r="N10" s="31" t="inlineStr">
         <is>
           <t>Saatte ~29 Boy</t>
         </is>
       </c>
-      <c r="N10" s="53" t="n">
+      <c r="O10" s="54" t="n">
         <v>0.368893987991056</v>
       </c>
     </row>
@@ -5285,52 +5609,57 @@
           <t>100 x 36 mm</t>
         </is>
       </c>
-      <c r="E11" s="54" t="inlineStr">
+      <c r="E11" s="55" t="inlineStr">
         <is>
           <t>Hat 102</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="H11" s="14" t="n">
         <v>1140</v>
       </c>
-      <c r="H11" s="14" t="n">
+      <c r="I11" s="15" t="n">
         <v>95</v>
       </c>
-      <c r="I11" s="14" t="n">
+      <c r="J11" s="15" t="n">
         <v>16716</v>
       </c>
-      <c r="J11" s="10" t="inlineStr">
+      <c r="K11" s="10" t="inlineStr">
         <is>
           <t>4.00 kg/boy</t>
         </is>
       </c>
-      <c r="K11" s="11" t="n">
+      <c r="L11" s="11" t="n">
         <v>66864</v>
       </c>
-      <c r="L11" s="15" t="n">
+      <c r="M11" s="16" t="n">
         <v>58.7</v>
       </c>
-      <c r="M11" s="16" t="inlineStr">
+      <c r="N11" s="17" t="inlineStr">
         <is>
           <t>Saatte ~15 Boy</t>
         </is>
       </c>
-      <c r="N11" s="55" t="n">
+      <c r="O11" s="56" t="n">
         <v>0.5054885239952825</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="A12" s="23" t="inlineStr">
         <is>
           <t>100 mm KASA</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>Kasa Profili</t>
         </is>
@@ -5340,47 +5669,52 @@
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D12" s="24" t="inlineStr">
         <is>
           <t>100 x 36 mm</t>
         </is>
       </c>
-      <c r="E12" s="52" t="inlineStr">
+      <c r="E12" s="53" t="inlineStr">
         <is>
           <t>Hat 108</t>
         </is>
       </c>
-      <c r="F12" s="33" t="inlineStr">
+      <c r="F12" s="32" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="G12" s="34" t="inlineStr">
         <is>
           <t>YEDEK ROTA 1</t>
         </is>
       </c>
-      <c r="G12" s="27" t="n">
+      <c r="H12" s="28" t="n">
         <v>1008</v>
       </c>
-      <c r="H12" s="28" t="n">
+      <c r="I12" s="29" t="n">
         <v>84</v>
       </c>
-      <c r="I12" s="28" t="n">
+      <c r="J12" s="29" t="n">
         <v>16017</v>
       </c>
-      <c r="J12" s="24" t="inlineStr">
+      <c r="K12" s="25" t="inlineStr">
         <is>
           <t>4.00 kg/boy</t>
         </is>
       </c>
-      <c r="K12" s="25" t="n">
+      <c r="L12" s="26" t="n">
         <v>64068</v>
       </c>
-      <c r="L12" s="29" t="n">
+      <c r="M12" s="30" t="n">
         <v>63.6</v>
       </c>
-      <c r="M12" s="30" t="inlineStr">
+      <c r="N12" s="31" t="inlineStr">
         <is>
           <t>Saatte ~16 Boy</t>
         </is>
       </c>
-      <c r="N12" s="53" t="n">
+      <c r="O12" s="54" t="n">
         <v>0.4843509026580786</v>
       </c>
     </row>
@@ -5405,52 +5739,57 @@
           <t>140 x 36 mm</t>
         </is>
       </c>
-      <c r="E13" s="54" t="inlineStr">
+      <c r="E13" s="55" t="inlineStr">
         <is>
           <t>Hat 108</t>
         </is>
       </c>
-      <c r="F13" s="19" t="inlineStr">
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>YEDEK ROTA 1</t>
         </is>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="H13" s="14" t="n">
         <v>636</v>
       </c>
-      <c r="H13" s="14" t="n">
+      <c r="I13" s="15" t="n">
         <v>53</v>
       </c>
-      <c r="I13" s="14" t="n">
+      <c r="J13" s="15" t="n">
         <v>8661</v>
       </c>
-      <c r="J13" s="10" t="inlineStr">
+      <c r="K13" s="10" t="inlineStr">
         <is>
           <t>4.95 kg/boy</t>
         </is>
       </c>
-      <c r="K13" s="11" t="n">
+      <c r="L13" s="11" t="n">
         <v>42871.95</v>
       </c>
-      <c r="L13" s="15" t="n">
+      <c r="M13" s="16" t="n">
         <v>67.40000000000001</v>
       </c>
-      <c r="M13" s="16" t="inlineStr">
+      <c r="N13" s="17" t="inlineStr">
         <is>
           <t>Saatte ~14 Boy</t>
         </is>
       </c>
-      <c r="N13" s="55" t="n">
+      <c r="O13" s="56" t="n">
         <v>0.2529423790193045</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t>TEAK Levha</t>
         </is>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>WPC Levha Plaka</t>
         </is>
@@ -5460,47 +5799,52 @@
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D14" s="24" t="inlineStr">
         <is>
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E14" s="52" t="inlineStr">
+      <c r="E14" s="53" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="F14" s="26" t="inlineStr">
+      <c r="F14" s="32" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="G14" s="27" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="G14" s="27" t="n">
+      <c r="H14" s="28" t="n">
         <v>444</v>
       </c>
-      <c r="H14" s="28" t="n">
+      <c r="I14" s="29" t="n">
         <v>37</v>
       </c>
-      <c r="I14" s="28" t="n">
+      <c r="J14" s="29" t="n">
         <v>9359</v>
       </c>
-      <c r="J14" s="24" t="inlineStr">
+      <c r="K14" s="25" t="inlineStr">
         <is>
           <t>4.25 kg/plaka</t>
         </is>
       </c>
-      <c r="K14" s="25" t="n">
+      <c r="L14" s="26" t="n">
         <v>39775.75</v>
       </c>
-      <c r="L14" s="29" t="n">
+      <c r="M14" s="30" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="M14" s="30" t="inlineStr">
+      <c r="N14" s="31" t="inlineStr">
         <is>
           <t>Saatte ~21 Plaka</t>
         </is>
       </c>
-      <c r="N14" s="53" t="n">
+      <c r="O14" s="54" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5525,52 +5869,57 @@
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E15" s="54" t="inlineStr">
+      <c r="E15" s="55" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr">
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="H15" s="14" t="n">
         <v>360</v>
       </c>
-      <c r="H15" s="14" t="n">
+      <c r="I15" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="I15" s="14" t="n">
+      <c r="J15" s="15" t="n">
         <v>7270</v>
       </c>
-      <c r="J15" s="10" t="inlineStr">
+      <c r="K15" s="10" t="inlineStr">
         <is>
           <t>4.41 kg/plaka</t>
         </is>
       </c>
-      <c r="K15" s="11" t="n">
+      <c r="L15" s="11" t="n">
         <v>32060.7</v>
       </c>
-      <c r="L15" s="15" t="n">
+      <c r="M15" s="16" t="n">
         <v>89.09999999999999</v>
       </c>
-      <c r="M15" s="16" t="inlineStr">
+      <c r="N15" s="17" t="inlineStr">
         <is>
           <t>Saatte ~20 Plaka</t>
         </is>
       </c>
-      <c r="N15" s="55" t="n">
+      <c r="O15" s="56" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="22" t="inlineStr">
+      <c r="A16" s="23" t="inlineStr">
         <is>
           <t>MIX TEAK Levha</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>WPC Levha Plaka</t>
         </is>
@@ -5580,47 +5929,52 @@
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="D16" s="24" t="inlineStr">
         <is>
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E16" s="52" t="inlineStr">
+      <c r="E16" s="53" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="F16" s="26" t="inlineStr">
+      <c r="F16" s="32" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="G16" s="27" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="G16" s="27" t="n">
+      <c r="H16" s="28" t="n">
         <v>336</v>
       </c>
-      <c r="H16" s="28" t="n">
+      <c r="I16" s="29" t="n">
         <v>28</v>
       </c>
-      <c r="I16" s="28" t="n">
+      <c r="J16" s="29" t="n">
         <v>7205</v>
       </c>
-      <c r="J16" s="24" t="inlineStr">
+      <c r="K16" s="25" t="inlineStr">
         <is>
           <t>4.25 kg/plaka</t>
         </is>
       </c>
-      <c r="K16" s="25" t="n">
+      <c r="L16" s="26" t="n">
         <v>30621.25</v>
       </c>
-      <c r="L16" s="29" t="n">
+      <c r="M16" s="30" t="n">
         <v>91.09999999999999</v>
       </c>
-      <c r="M16" s="30" t="inlineStr">
+      <c r="N16" s="31" t="inlineStr">
         <is>
           <t>Saatte ~21 Plaka</t>
         </is>
       </c>
-      <c r="N16" s="53" t="n">
+      <c r="O16" s="54" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5645,52 +5999,57 @@
           <t>39 x 45 mm</t>
         </is>
       </c>
-      <c r="E17" s="54" t="inlineStr">
+      <c r="E17" s="55" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="F17" s="12" t="inlineStr">
+      <c r="F17" s="18" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="H17" s="14" t="n">
         <v>276</v>
       </c>
-      <c r="H17" s="14" t="n">
+      <c r="I17" s="15" t="n">
         <v>23</v>
       </c>
-      <c r="I17" s="14" t="n">
+      <c r="J17" s="15" t="n">
         <v>7168</v>
       </c>
-      <c r="J17" s="10" t="inlineStr">
+      <c r="K17" s="10" t="inlineStr">
         <is>
           <t>3.81 kg/boy</t>
         </is>
       </c>
-      <c r="K17" s="11" t="n">
+      <c r="L17" s="11" t="n">
         <v>27310.08</v>
       </c>
-      <c r="L17" s="15" t="n">
+      <c r="M17" s="16" t="n">
         <v>98.90000000000001</v>
       </c>
-      <c r="M17" s="16" t="inlineStr">
+      <c r="N17" s="17" t="inlineStr">
         <is>
           <t>Saatte ~26 Boy</t>
         </is>
       </c>
-      <c r="N17" s="55" t="n">
+      <c r="O17" s="56" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="22" t="inlineStr">
+      <c r="A18" s="23" t="inlineStr">
         <is>
           <t>VIZON Levha</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t>WPC Levha Plaka</t>
         </is>
@@ -5700,47 +6059,52 @@
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D18" s="24" t="inlineStr">
         <is>
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E18" s="52" t="inlineStr">
+      <c r="E18" s="53" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="F18" s="26" t="inlineStr">
+      <c r="F18" s="32" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="G18" s="27" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="G18" s="27" t="n">
+      <c r="H18" s="28" t="n">
         <v>264</v>
       </c>
-      <c r="H18" s="28" t="n">
+      <c r="I18" s="29" t="n">
         <v>22</v>
       </c>
-      <c r="I18" s="28" t="n">
+      <c r="J18" s="29" t="n">
         <v>3850</v>
       </c>
-      <c r="J18" s="24" t="inlineStr">
+      <c r="K18" s="25" t="inlineStr">
         <is>
           <t>4.77 kg/plaka</t>
         </is>
       </c>
-      <c r="K18" s="25" t="n">
+      <c r="L18" s="26" t="n">
         <v>18364.5</v>
       </c>
-      <c r="L18" s="29" t="n">
+      <c r="M18" s="30" t="n">
         <v>69.59999999999999</v>
       </c>
-      <c r="M18" s="30" t="inlineStr">
+      <c r="N18" s="31" t="inlineStr">
         <is>
           <t>Saatte ~15 Plaka</t>
         </is>
       </c>
-      <c r="N18" s="53" t="n">
+      <c r="O18" s="54" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5765,52 +6129,57 @@
           <t>220 x 24 mm</t>
         </is>
       </c>
-      <c r="E19" s="54" t="inlineStr">
+      <c r="E19" s="55" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="F19" s="12" t="inlineStr">
+      <c r="F19" s="18" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="H19" s="14" t="n">
         <v>276</v>
       </c>
-      <c r="H19" s="14" t="n">
+      <c r="I19" s="15" t="n">
         <v>23</v>
       </c>
-      <c r="I19" s="14" t="n">
+      <c r="J19" s="15" t="n">
         <v>1712</v>
       </c>
-      <c r="J19" s="10" t="inlineStr">
+      <c r="K19" s="10" t="inlineStr">
         <is>
           <t>10.33 kg/boy</t>
         </is>
       </c>
-      <c r="K19" s="11" t="n">
+      <c r="L19" s="11" t="n">
         <v>17684.96</v>
       </c>
-      <c r="L19" s="15" t="n">
+      <c r="M19" s="16" t="n">
         <v>64.09999999999999</v>
       </c>
-      <c r="M19" s="16" t="inlineStr">
+      <c r="N19" s="17" t="inlineStr">
         <is>
           <t>Saatte ~6 Boy</t>
         </is>
       </c>
-      <c r="N19" s="55" t="n">
+      <c r="O19" s="56" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="22" t="inlineStr">
+      <c r="A20" s="23" t="inlineStr">
         <is>
           <t>140 mm KASA</t>
         </is>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t>Kasa Profili</t>
         </is>
@@ -5820,47 +6189,52 @@
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="D20" s="23" t="inlineStr">
+      <c r="D20" s="24" t="inlineStr">
         <is>
           <t>140 x 36 mm</t>
         </is>
       </c>
-      <c r="E20" s="52" t="inlineStr">
+      <c r="E20" s="53" t="inlineStr">
         <is>
           <t>Hat 102</t>
         </is>
       </c>
-      <c r="F20" s="33" t="inlineStr">
+      <c r="F20" s="32" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="G20" s="34" t="inlineStr">
         <is>
           <t>YEDEK ROTA 2</t>
         </is>
       </c>
-      <c r="G20" s="27" t="n">
+      <c r="H20" s="28" t="n">
         <v>312</v>
       </c>
-      <c r="H20" s="28" t="n">
+      <c r="I20" s="29" t="n">
         <v>26</v>
       </c>
-      <c r="I20" s="28" t="n">
+      <c r="J20" s="29" t="n">
         <v>3136</v>
       </c>
-      <c r="J20" s="24" t="inlineStr">
+      <c r="K20" s="25" t="inlineStr">
         <is>
           <t>4.95 kg/boy</t>
         </is>
       </c>
-      <c r="K20" s="25" t="n">
+      <c r="L20" s="26" t="n">
         <v>15523.2</v>
       </c>
-      <c r="L20" s="29" t="n">
+      <c r="M20" s="30" t="n">
         <v>49.8</v>
       </c>
-      <c r="M20" s="30" t="inlineStr">
+      <c r="N20" s="31" t="inlineStr">
         <is>
           <t>Saatte ~10 Boy</t>
         </is>
       </c>
-      <c r="N20" s="53" t="n">
+      <c r="O20" s="54" t="n">
         <v>0.09158611021874363</v>
       </c>
     </row>
@@ -5885,52 +6259,57 @@
           <t>80 x 80 mm</t>
         </is>
       </c>
-      <c r="E21" s="54" t="inlineStr">
+      <c r="E21" s="55" t="inlineStr">
         <is>
           <t>Hat 101</t>
         </is>
       </c>
-      <c r="F21" s="12" t="inlineStr">
+      <c r="F21" s="18" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="G21" s="13" t="n">
+      <c r="H21" s="14" t="n">
         <v>324</v>
       </c>
-      <c r="H21" s="14" t="n">
+      <c r="I21" s="15" t="n">
         <v>27</v>
       </c>
-      <c r="I21" s="14" t="n">
+      <c r="J21" s="15" t="n">
         <v>5830</v>
       </c>
-      <c r="J21" s="10" t="inlineStr">
+      <c r="K21" s="10" t="inlineStr">
         <is>
           <t>2.20 kg/boy</t>
         </is>
       </c>
-      <c r="K21" s="11" t="n">
+      <c r="L21" s="11" t="n">
         <v>12826</v>
       </c>
-      <c r="L21" s="15" t="n">
+      <c r="M21" s="16" t="n">
         <v>39.6</v>
       </c>
-      <c r="M21" s="16" t="inlineStr">
+      <c r="N21" s="17" t="inlineStr">
         <is>
           <t>Saatte ~18 Boy</t>
         </is>
       </c>
-      <c r="N21" s="55" t="n">
+      <c r="O21" s="56" t="n">
         <v>0.8941717791411042</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="22" t="inlineStr">
+      <c r="A22" s="23" t="inlineStr">
         <is>
           <t>35X100 PERVAZ</t>
         </is>
       </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>Pervaz Profili</t>
         </is>
@@ -5940,47 +6319,52 @@
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="D22" s="23" t="inlineStr">
+      <c r="D22" s="24" t="inlineStr">
         <is>
           <t>35 x 100 mm</t>
         </is>
       </c>
-      <c r="E22" s="52" t="inlineStr">
+      <c r="E22" s="53" t="inlineStr">
         <is>
           <t>Hat 101</t>
         </is>
       </c>
-      <c r="F22" s="26" t="inlineStr">
+      <c r="F22" s="32" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="G22" s="27" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="G22" s="27" t="n">
+      <c r="H22" s="28" t="n">
         <v>264</v>
       </c>
-      <c r="H22" s="28" t="n">
+      <c r="I22" s="29" t="n">
         <v>22</v>
       </c>
-      <c r="I22" s="28" t="n">
+      <c r="J22" s="29" t="n">
         <v>4995</v>
       </c>
-      <c r="J22" s="24" t="inlineStr">
+      <c r="K22" s="25" t="inlineStr">
         <is>
           <t>2.08 kg/boy</t>
         </is>
       </c>
-      <c r="K22" s="25" t="n">
+      <c r="L22" s="26" t="n">
         <v>10389.6</v>
       </c>
-      <c r="L22" s="29" t="n">
+      <c r="M22" s="30" t="n">
         <v>39.4</v>
       </c>
-      <c r="M22" s="30" t="inlineStr">
+      <c r="N22" s="31" t="inlineStr">
         <is>
           <t>Saatte ~19 Boy</t>
         </is>
       </c>
-      <c r="N22" s="53" t="n">
+      <c r="O22" s="54" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6005,52 +6389,57 @@
           <t>35 x 150 mm</t>
         </is>
       </c>
-      <c r="E23" s="54" t="inlineStr">
+      <c r="E23" s="55" t="inlineStr">
         <is>
           <t>Hat 101</t>
         </is>
       </c>
-      <c r="F23" s="12" t="inlineStr">
+      <c r="F23" s="18" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="H23" s="14" t="n">
         <v>240</v>
       </c>
-      <c r="H23" s="14" t="n">
+      <c r="I23" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="I23" s="14" t="n">
+      <c r="J23" s="15" t="n">
         <v>3205</v>
       </c>
-      <c r="J23" s="10" t="inlineStr">
+      <c r="K23" s="10" t="inlineStr">
         <is>
           <t>2.97 kg/boy</t>
         </is>
       </c>
-      <c r="K23" s="11" t="n">
+      <c r="L23" s="11" t="n">
         <v>9518.850000000002</v>
       </c>
-      <c r="L23" s="15" t="n">
+      <c r="M23" s="16" t="n">
         <v>39.7</v>
       </c>
-      <c r="M23" s="16" t="inlineStr">
+      <c r="N23" s="17" t="inlineStr">
         <is>
           <t>Saatte ~13 Boy</t>
         </is>
       </c>
-      <c r="N23" s="55" t="n">
+      <c r="O23" s="56" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="22" t="inlineStr">
+      <c r="A24" s="23" t="inlineStr">
         <is>
           <t>KT102-219x26-ANT</t>
         </is>
       </c>
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B24" s="24" t="inlineStr">
         <is>
           <t>Deck / WPC Zemin</t>
         </is>
@@ -6060,47 +6449,52 @@
           <t>3.00 Metre</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="24" t="inlineStr">
         <is>
           <t>219 x 26 mm</t>
         </is>
       </c>
-      <c r="E24" s="52" t="inlineStr">
+      <c r="E24" s="53" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="F24" s="26" t="inlineStr">
+      <c r="F24" s="32" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="G24" s="27" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="G24" s="27" t="n">
+      <c r="H24" s="28" t="n">
         <v>120</v>
       </c>
-      <c r="H24" s="28" t="n">
+      <c r="I24" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="I24" s="28" t="n">
+      <c r="J24" s="29" t="n">
         <v>895</v>
       </c>
-      <c r="J24" s="24" t="inlineStr">
+      <c r="K24" s="25" t="inlineStr">
         <is>
           <t>10.52 kg/boy</t>
         </is>
       </c>
-      <c r="K24" s="25" t="n">
+      <c r="L24" s="26" t="n">
         <v>9415.4</v>
       </c>
-      <c r="L24" s="29" t="n">
+      <c r="M24" s="30" t="n">
         <v>78.5</v>
       </c>
-      <c r="M24" s="30" t="inlineStr">
+      <c r="N24" s="31" t="inlineStr">
         <is>
           <t>Saatte ~8 Boy</t>
         </is>
       </c>
-      <c r="N24" s="53" t="n">
+      <c r="O24" s="54" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6125,52 +6519,57 @@
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E25" s="54" t="inlineStr">
+      <c r="E25" s="55" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="F25" s="12" t="inlineStr">
+      <c r="F25" s="18" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="G25" s="12" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="H25" s="14" t="n">
         <v>108</v>
       </c>
-      <c r="H25" s="14" t="n">
+      <c r="I25" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="I25" s="14" t="n">
+      <c r="J25" s="15" t="n">
         <v>2147</v>
       </c>
-      <c r="J25" s="10" t="inlineStr">
+      <c r="K25" s="10" t="inlineStr">
         <is>
           <t>4.25 kg/plaka</t>
         </is>
       </c>
-      <c r="K25" s="11" t="n">
+      <c r="L25" s="11" t="n">
         <v>9124.75</v>
       </c>
-      <c r="L25" s="15" t="n">
+      <c r="M25" s="16" t="n">
         <v>84.5</v>
       </c>
-      <c r="M25" s="16" t="inlineStr">
+      <c r="N25" s="17" t="inlineStr">
         <is>
           <t>Saatte ~20 Plaka</t>
         </is>
       </c>
-      <c r="N25" s="55" t="n">
+      <c r="O25" s="56" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="22" t="inlineStr">
+      <c r="A26" s="23" t="inlineStr">
         <is>
           <t>CAM ÇITASI</t>
         </is>
       </c>
-      <c r="B26" s="23" t="inlineStr">
+      <c r="B26" s="24" t="inlineStr">
         <is>
           <t>Cam Çıtası</t>
         </is>
@@ -6180,47 +6579,52 @@
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="D26" s="23" t="inlineStr">
+      <c r="D26" s="24" t="inlineStr">
         <is>
           <t>15 x 20 mm</t>
         </is>
       </c>
-      <c r="E26" s="52" t="inlineStr">
+      <c r="E26" s="53" t="inlineStr">
         <is>
           <t>Hat 102</t>
         </is>
       </c>
-      <c r="F26" s="26" t="inlineStr">
+      <c r="F26" s="32" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="G26" s="27" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="G26" s="27" t="n">
+      <c r="H26" s="28" t="n">
         <v>168</v>
       </c>
-      <c r="H26" s="28" t="n">
+      <c r="I26" s="29" t="n">
         <v>14</v>
       </c>
-      <c r="I26" s="28" t="n">
+      <c r="J26" s="29" t="n">
         <v>5187</v>
       </c>
-      <c r="J26" s="24" t="inlineStr">
+      <c r="K26" s="25" t="inlineStr">
         <is>
           <t>1.50 kg/boy</t>
         </is>
       </c>
-      <c r="K26" s="25" t="n">
+      <c r="L26" s="26" t="n">
         <v>7780.5</v>
       </c>
-      <c r="L26" s="29" t="n">
+      <c r="M26" s="30" t="n">
         <v>46.3</v>
       </c>
-      <c r="M26" s="30" t="inlineStr">
+      <c r="N26" s="31" t="inlineStr">
         <is>
           <t>Saatte ~31 Boy</t>
         </is>
       </c>
-      <c r="N26" s="53" t="n">
+      <c r="O26" s="54" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6245,52 +6649,57 @@
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E27" s="54" t="inlineStr">
+      <c r="E27" s="55" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="F27" s="12" t="inlineStr">
+      <c r="F27" s="18" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="G27" s="13" t="n">
+      <c r="H27" s="14" t="n">
         <v>156</v>
       </c>
-      <c r="H27" s="14" t="n">
+      <c r="I27" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="I27" s="14" t="n">
+      <c r="J27" s="15" t="n">
         <v>1776</v>
       </c>
-      <c r="J27" s="10" t="inlineStr">
+      <c r="K27" s="10" t="inlineStr">
         <is>
           <t>4.33 kg/plaka</t>
         </is>
       </c>
-      <c r="K27" s="11" t="n">
+      <c r="L27" s="11" t="n">
         <v>7690.08</v>
       </c>
-      <c r="L27" s="15" t="n">
+      <c r="M27" s="16" t="n">
         <v>49.3</v>
       </c>
-      <c r="M27" s="16" t="inlineStr">
+      <c r="N27" s="17" t="inlineStr">
         <is>
           <t>Saatte ~11 Plaka</t>
         </is>
       </c>
-      <c r="N27" s="55" t="n">
+      <c r="O27" s="56" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="22" t="inlineStr">
+      <c r="A28" s="23" t="inlineStr">
         <is>
           <t>AY GRİ Levha</t>
         </is>
       </c>
-      <c r="B28" s="23" t="inlineStr">
+      <c r="B28" s="24" t="inlineStr">
         <is>
           <t>WPC Levha Plaka</t>
         </is>
@@ -6300,47 +6709,52 @@
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="D28" s="23" t="inlineStr">
+      <c r="D28" s="24" t="inlineStr">
         <is>
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E28" s="52" t="inlineStr">
+      <c r="E28" s="53" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="F28" s="26" t="inlineStr">
+      <c r="F28" s="32" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="G28" s="27" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="G28" s="27" t="n">
+      <c r="H28" s="28" t="n">
         <v>96</v>
       </c>
-      <c r="H28" s="28" t="n">
+      <c r="I28" s="29" t="n">
         <v>8</v>
       </c>
-      <c r="I28" s="28" t="n">
+      <c r="J28" s="29" t="n">
         <v>1297</v>
       </c>
-      <c r="J28" s="24" t="inlineStr">
+      <c r="K28" s="25" t="inlineStr">
         <is>
           <t>4.64 kg/plaka</t>
         </is>
       </c>
-      <c r="K28" s="25" t="n">
+      <c r="L28" s="26" t="n">
         <v>6018.08</v>
       </c>
-      <c r="L28" s="29" t="n">
+      <c r="M28" s="30" t="n">
         <v>62.7</v>
       </c>
-      <c r="M28" s="30" t="inlineStr">
+      <c r="N28" s="31" t="inlineStr">
         <is>
           <t>Saatte ~14 Plaka</t>
         </is>
       </c>
-      <c r="N28" s="53" t="n">
+      <c r="O28" s="54" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6365,52 +6779,57 @@
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E29" s="54" t="inlineStr">
+      <c r="E29" s="55" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="F29" s="12" t="inlineStr">
+      <c r="F29" s="18" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="G29" s="13" t="n">
+      <c r="H29" s="14" t="n">
         <v>96</v>
       </c>
-      <c r="H29" s="14" t="n">
+      <c r="I29" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="I29" s="14" t="n">
+      <c r="J29" s="15" t="n">
         <v>1176</v>
       </c>
-      <c r="J29" s="10" t="inlineStr">
+      <c r="K29" s="10" t="inlineStr">
         <is>
           <t>4.77 kg/plaka</t>
         </is>
       </c>
-      <c r="K29" s="11" t="n">
+      <c r="L29" s="11" t="n">
         <v>5609.52</v>
       </c>
-      <c r="L29" s="15" t="n">
+      <c r="M29" s="16" t="n">
         <v>58.4</v>
       </c>
-      <c r="M29" s="16" t="inlineStr">
+      <c r="N29" s="17" t="inlineStr">
         <is>
           <t>Saatte ~12 Plaka</t>
         </is>
       </c>
-      <c r="N29" s="55" t="n">
+      <c r="O29" s="56" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="22" t="inlineStr">
+      <c r="A30" s="23" t="inlineStr">
         <is>
           <t>KOYU CEVİZ Levha</t>
         </is>
       </c>
-      <c r="B30" s="23" t="inlineStr">
+      <c r="B30" s="24" t="inlineStr">
         <is>
           <t>WPC Levha Plaka</t>
         </is>
@@ -6420,47 +6839,52 @@
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="D30" s="23" t="inlineStr">
+      <c r="D30" s="24" t="inlineStr">
         <is>
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E30" s="52" t="inlineStr">
+      <c r="E30" s="53" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="F30" s="26" t="inlineStr">
+      <c r="F30" s="32" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="G30" s="27" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="G30" s="27" t="n">
+      <c r="H30" s="28" t="n">
         <v>84</v>
       </c>
-      <c r="H30" s="28" t="n">
+      <c r="I30" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="I30" s="28" t="n">
+      <c r="J30" s="29" t="n">
         <v>803</v>
       </c>
-      <c r="J30" s="24" t="inlineStr">
+      <c r="K30" s="25" t="inlineStr">
         <is>
           <t>4.79 kg/plaka</t>
         </is>
       </c>
-      <c r="K30" s="25" t="n">
+      <c r="L30" s="26" t="n">
         <v>3846.37</v>
       </c>
-      <c r="L30" s="29" t="n">
+      <c r="M30" s="30" t="n">
         <v>45.8</v>
       </c>
-      <c r="M30" s="30" t="inlineStr">
+      <c r="N30" s="31" t="inlineStr">
         <is>
           <t>Saatte ~10 Plaka</t>
         </is>
       </c>
-      <c r="N30" s="53" t="n">
+      <c r="O30" s="54" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6485,52 +6909,57 @@
           <t>200 x 36 mm</t>
         </is>
       </c>
-      <c r="E31" s="54" t="inlineStr">
+      <c r="E31" s="55" t="inlineStr">
         <is>
           <t>Hat 106</t>
         </is>
       </c>
-      <c r="F31" s="19" t="inlineStr">
+      <c r="F31" s="18" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="G31" s="20" t="inlineStr">
         <is>
           <t>YEDEK ROTA 1</t>
         </is>
       </c>
-      <c r="G31" s="13" t="n">
+      <c r="H31" s="14" t="n">
         <v>24</v>
       </c>
-      <c r="H31" s="14" t="n">
+      <c r="I31" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I31" s="14" t="n">
+      <c r="J31" s="15" t="n">
         <v>492</v>
       </c>
-      <c r="J31" s="10" t="inlineStr">
+      <c r="K31" s="10" t="inlineStr">
         <is>
           <t>6.66 kg/boy</t>
         </is>
       </c>
-      <c r="K31" s="11" t="n">
+      <c r="L31" s="11" t="n">
         <v>3276.72</v>
       </c>
-      <c r="L31" s="15" t="n">
+      <c r="M31" s="16" t="n">
         <v>136.5</v>
       </c>
-      <c r="M31" s="16" t="inlineStr">
+      <c r="N31" s="17" t="inlineStr">
         <is>
           <t>Saatte ~20 Boy</t>
         </is>
       </c>
-      <c r="N31" s="55" t="n">
+      <c r="O31" s="56" t="n">
         <v>0.04027175247605796</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="22" t="inlineStr">
+      <c r="A32" s="23" t="inlineStr">
         <is>
           <t>SEREN</t>
         </is>
       </c>
-      <c r="B32" s="23" t="inlineStr">
+      <c r="B32" s="24" t="inlineStr">
         <is>
           <t>Seren Çıtası</t>
         </is>
@@ -6540,47 +6969,52 @@
           <t>2.10 Metre</t>
         </is>
       </c>
-      <c r="D32" s="23" t="inlineStr">
+      <c r="D32" s="24" t="inlineStr">
         <is>
           <t>38 x 45 mm</t>
         </is>
       </c>
-      <c r="E32" s="52" t="inlineStr">
+      <c r="E32" s="53" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="F32" s="33" t="inlineStr">
+      <c r="F32" s="32" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="G32" s="34" t="inlineStr">
         <is>
           <t>YEDEK ROTA 2</t>
         </is>
       </c>
-      <c r="G32" s="27" t="n">
+      <c r="H32" s="28" t="n">
         <v>48</v>
       </c>
-      <c r="H32" s="28" t="n">
+      <c r="I32" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="I32" s="28" t="n">
+      <c r="J32" s="29" t="n">
         <v>865</v>
       </c>
-      <c r="J32" s="24" t="inlineStr">
+      <c r="K32" s="25" t="inlineStr">
         <is>
           <t>3.39 kg/boy</t>
         </is>
       </c>
-      <c r="K32" s="25" t="n">
+      <c r="L32" s="26" t="n">
         <v>2932.35</v>
       </c>
-      <c r="L32" s="29" t="n">
+      <c r="M32" s="30" t="n">
         <v>61.1</v>
       </c>
-      <c r="M32" s="30" t="inlineStr">
+      <c r="N32" s="31" t="inlineStr">
         <is>
           <t>Saatte ~18 Boy</t>
         </is>
       </c>
-      <c r="N32" s="53" t="n">
+      <c r="O32" s="54" t="n">
         <v>0.009928150035580655</v>
       </c>
     </row>
@@ -6605,52 +7039,57 @@
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E33" s="54" t="inlineStr">
+      <c r="E33" s="55" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="F33" s="12" t="inlineStr">
+      <c r="F33" s="18" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="G33" s="13" t="n">
+      <c r="H33" s="14" t="n">
         <v>36</v>
       </c>
-      <c r="H33" s="14" t="n">
+      <c r="I33" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="I33" s="14" t="n">
+      <c r="J33" s="15" t="n">
         <v>600</v>
       </c>
-      <c r="J33" s="10" t="inlineStr">
+      <c r="K33" s="10" t="inlineStr">
         <is>
           <t>4.79 kg/plaka</t>
         </is>
       </c>
-      <c r="K33" s="11" t="n">
+      <c r="L33" s="11" t="n">
         <v>2874</v>
       </c>
-      <c r="L33" s="15" t="n">
+      <c r="M33" s="16" t="n">
         <v>79.8</v>
       </c>
-      <c r="M33" s="16" t="inlineStr">
+      <c r="N33" s="17" t="inlineStr">
         <is>
           <t>Saatte ~17 Plaka</t>
         </is>
       </c>
-      <c r="N33" s="55" t="n">
+      <c r="O33" s="56" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="22" t="inlineStr">
+      <c r="A34" s="23" t="inlineStr">
         <is>
           <t>200 mm KASA</t>
         </is>
       </c>
-      <c r="B34" s="23" t="inlineStr">
+      <c r="B34" s="24" t="inlineStr">
         <is>
           <t>Kasa Profili</t>
         </is>
@@ -6660,47 +7099,52 @@
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="D34" s="23" t="inlineStr">
+      <c r="D34" s="24" t="inlineStr">
         <is>
           <t>200 x 36 mm</t>
         </is>
       </c>
-      <c r="E34" s="52" t="inlineStr">
+      <c r="E34" s="53" t="inlineStr">
         <is>
           <t>Hat 108</t>
         </is>
       </c>
-      <c r="F34" s="33" t="inlineStr">
+      <c r="F34" s="32" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="G34" s="34" t="inlineStr">
         <is>
           <t>YEDEK ROTA 2</t>
         </is>
       </c>
-      <c r="G34" s="27" t="n">
+      <c r="H34" s="28" t="n">
         <v>24</v>
       </c>
-      <c r="H34" s="28" t="n">
+      <c r="I34" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="I34" s="28" t="n">
+      <c r="J34" s="29" t="n">
         <v>348</v>
       </c>
-      <c r="J34" s="24" t="inlineStr">
+      <c r="K34" s="25" t="inlineStr">
         <is>
           <t>6.66 kg/boy</t>
         </is>
       </c>
-      <c r="K34" s="25" t="n">
+      <c r="L34" s="26" t="n">
         <v>2317.68</v>
       </c>
-      <c r="L34" s="29" t="n">
+      <c r="M34" s="30" t="n">
         <v>96.59999999999999</v>
       </c>
-      <c r="M34" s="30" t="inlineStr">
+      <c r="N34" s="31" t="inlineStr">
         <is>
           <t>Saatte ~14 Boy</t>
         </is>
       </c>
-      <c r="N34" s="53" t="n">
+      <c r="O34" s="54" t="n">
         <v>0.02848489809282148</v>
       </c>
     </row>
@@ -6725,52 +7169,57 @@
           <t>38 x 45 mm</t>
         </is>
       </c>
-      <c r="E35" s="54" t="inlineStr">
+      <c r="E35" s="55" t="inlineStr">
         <is>
           <t>Hat 103</t>
         </is>
       </c>
-      <c r="F35" s="19" t="inlineStr">
+      <c r="F35" s="13" t="inlineStr">
+        <is>
+          <t>2 Göz (Çift Çıkış)</t>
+        </is>
+      </c>
+      <c r="G35" s="20" t="inlineStr">
         <is>
           <t>YEDEK ROTA 3</t>
         </is>
       </c>
-      <c r="G35" s="13" t="n">
+      <c r="H35" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="H35" s="14" t="n">
+      <c r="I35" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I35" s="14" t="n">
+      <c r="J35" s="15" t="n">
         <v>450</v>
       </c>
-      <c r="J35" s="10" t="inlineStr">
+      <c r="K35" s="10" t="inlineStr">
         <is>
           <t>3.39 kg/boy</t>
         </is>
       </c>
-      <c r="K35" s="11" t="n">
+      <c r="L35" s="11" t="n">
         <v>1525.5</v>
       </c>
-      <c r="L35" s="15" t="n">
+      <c r="M35" s="16" t="n">
         <v>127.1</v>
       </c>
-      <c r="M35" s="16" t="inlineStr">
+      <c r="N35" s="17" t="inlineStr">
         <is>
           <t>Saatte ~38 Boy</t>
         </is>
       </c>
-      <c r="N35" s="55" t="n">
+      <c r="O35" s="56" t="n">
         <v>0.005164933544521728</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="22" t="inlineStr">
+      <c r="A36" s="23" t="inlineStr">
         <is>
           <t>80X80 PERVAZ</t>
         </is>
       </c>
-      <c r="B36" s="23" t="inlineStr">
+      <c r="B36" s="24" t="inlineStr">
         <is>
           <t>Pervaz Profili</t>
         </is>
@@ -6780,47 +7229,52 @@
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="D36" s="23" t="inlineStr">
+      <c r="D36" s="24" t="inlineStr">
         <is>
           <t>80 x 80 mm</t>
         </is>
       </c>
-      <c r="E36" s="52" t="inlineStr">
+      <c r="E36" s="53" t="inlineStr">
         <is>
           <t>Hat 109</t>
         </is>
       </c>
-      <c r="F36" s="33" t="inlineStr">
+      <c r="F36" s="13" t="inlineStr">
+        <is>
+          <t>2 Göz (Çift Çıkış)</t>
+        </is>
+      </c>
+      <c r="G36" s="34" t="inlineStr">
         <is>
           <t>YEDEK ROTA 1</t>
         </is>
       </c>
-      <c r="G36" s="27" t="n">
+      <c r="H36" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="H36" s="28" t="n">
+      <c r="I36" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="I36" s="28" t="n">
+      <c r="J36" s="29" t="n">
         <v>690</v>
       </c>
-      <c r="J36" s="24" t="inlineStr">
+      <c r="K36" s="25" t="inlineStr">
         <is>
           <t>2.20 kg/boy</t>
         </is>
       </c>
-      <c r="K36" s="25" t="n">
+      <c r="L36" s="26" t="n">
         <v>1518</v>
       </c>
-      <c r="L36" s="29" t="n">
+      <c r="M36" s="30" t="n">
         <v>126.5</v>
       </c>
-      <c r="M36" s="30" t="inlineStr">
+      <c r="N36" s="31" t="inlineStr">
         <is>
           <t>Saatte ~58 Boy</t>
         </is>
       </c>
-      <c r="N36" s="53" t="n">
+      <c r="O36" s="54" t="n">
         <v>0.1058282208588957</v>
       </c>
     </row>
@@ -6845,52 +7299,57 @@
           <t>30 x 15 mm</t>
         </is>
       </c>
-      <c r="E37" s="54" t="inlineStr">
+      <c r="E37" s="55" t="inlineStr">
         <is>
           <t>Hat 102</t>
         </is>
       </c>
-      <c r="F37" s="12" t="inlineStr">
+      <c r="F37" s="18" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="G37" s="13" t="n">
+      <c r="H37" s="14" t="n">
         <v>48</v>
       </c>
-      <c r="H37" s="14" t="n">
+      <c r="I37" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="I37" s="14" t="n">
+      <c r="J37" s="15" t="n">
         <v>2901</v>
       </c>
-      <c r="J37" s="10" t="inlineStr">
+      <c r="K37" s="10" t="inlineStr">
         <is>
           <t>0.48 kg/boy</t>
         </is>
       </c>
-      <c r="K37" s="11" t="n">
+      <c r="L37" s="11" t="n">
         <v>1392.48</v>
       </c>
-      <c r="L37" s="15" t="n">
+      <c r="M37" s="16" t="n">
         <v>29</v>
       </c>
-      <c r="M37" s="16" t="inlineStr">
+      <c r="N37" s="17" t="inlineStr">
         <is>
           <t>Saatte ~60 Boy</t>
         </is>
       </c>
-      <c r="N37" s="55" t="n">
+      <c r="O37" s="56" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="22" t="inlineStr">
+      <c r="A38" s="23" t="inlineStr">
         <is>
           <t>140 mm KASA</t>
         </is>
       </c>
-      <c r="B38" s="23" t="inlineStr">
+      <c r="B38" s="24" t="inlineStr">
         <is>
           <t>Kasa Profili</t>
         </is>
@@ -6900,47 +7359,52 @@
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="D38" s="23" t="inlineStr">
+      <c r="D38" s="24" t="inlineStr">
         <is>
           <t>140 x 36 mm</t>
         </is>
       </c>
-      <c r="E38" s="52" t="inlineStr">
+      <c r="E38" s="53" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="F38" s="33" t="inlineStr">
+      <c r="F38" s="32" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="G38" s="34" t="inlineStr">
         <is>
           <t>YEDEK ROTA 3</t>
         </is>
       </c>
-      <c r="G38" s="27" t="n">
+      <c r="H38" s="28" t="n">
         <v>36</v>
       </c>
-      <c r="H38" s="28" t="n">
+      <c r="I38" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="I38" s="28" t="n">
+      <c r="J38" s="29" t="n">
         <v>220</v>
       </c>
-      <c r="J38" s="24" t="inlineStr">
+      <c r="K38" s="25" t="inlineStr">
         <is>
           <t>4.95 kg/boy</t>
         </is>
       </c>
-      <c r="K38" s="25" t="n">
+      <c r="L38" s="26" t="n">
         <v>1089</v>
       </c>
-      <c r="L38" s="29" t="n">
+      <c r="M38" s="30" t="n">
         <v>30.2</v>
       </c>
-      <c r="M38" s="30" t="inlineStr">
+      <c r="N38" s="31" t="inlineStr">
         <is>
           <t>Saatte ~6 Boy</t>
         </is>
       </c>
-      <c r="N38" s="53" t="n">
+      <c r="O38" s="54" t="n">
         <v>0.006425045997488394</v>
       </c>
     </row>
@@ -6965,52 +7429,57 @@
           <t>140 x 36 mm</t>
         </is>
       </c>
-      <c r="E39" s="54" t="inlineStr">
+      <c r="E39" s="55" t="inlineStr">
         <is>
           <t>Hat 105</t>
         </is>
       </c>
-      <c r="F39" s="19" t="inlineStr">
+      <c r="F39" s="18" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="G39" s="20" t="inlineStr">
         <is>
           <t>YEDEK ROTA 4</t>
         </is>
       </c>
-      <c r="G39" s="13" t="n">
+      <c r="H39" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="H39" s="14" t="n">
+      <c r="I39" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I39" s="14" t="n">
+      <c r="J39" s="15" t="n">
         <v>209</v>
       </c>
-      <c r="J39" s="10" t="inlineStr">
+      <c r="K39" s="10" t="inlineStr">
         <is>
           <t>4.95 kg/boy</t>
         </is>
       </c>
-      <c r="K39" s="11" t="n">
+      <c r="L39" s="11" t="n">
         <v>1034.55</v>
       </c>
-      <c r="L39" s="15" t="n">
+      <c r="M39" s="16" t="n">
         <v>86.2</v>
       </c>
-      <c r="M39" s="16" t="inlineStr">
+      <c r="N39" s="17" t="inlineStr">
         <is>
           <t>Saatte ~17 Boy</t>
         </is>
       </c>
-      <c r="N39" s="55" t="n">
+      <c r="O39" s="56" t="n">
         <v>0.006103793697613974</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="22" t="inlineStr">
+      <c r="A40" s="23" t="inlineStr">
         <is>
           <t>100 mm KASA</t>
         </is>
       </c>
-      <c r="B40" s="23" t="inlineStr">
+      <c r="B40" s="24" t="inlineStr">
         <is>
           <t>Kasa Profili</t>
         </is>
@@ -7020,47 +7489,52 @@
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="D40" s="23" t="inlineStr">
+      <c r="D40" s="24" t="inlineStr">
         <is>
           <t>100 x 36 mm</t>
         </is>
       </c>
-      <c r="E40" s="52" t="inlineStr">
+      <c r="E40" s="53" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="F40" s="33" t="inlineStr">
+      <c r="F40" s="32" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="G40" s="34" t="inlineStr">
         <is>
           <t>YEDEK ROTA 2</t>
         </is>
       </c>
-      <c r="G40" s="27" t="n">
+      <c r="H40" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="H40" s="28" t="n">
+      <c r="I40" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="I40" s="28" t="n">
+      <c r="J40" s="29" t="n">
         <v>174</v>
       </c>
-      <c r="J40" s="24" t="inlineStr">
+      <c r="K40" s="25" t="inlineStr">
         <is>
           <t>4.00 kg/boy</t>
         </is>
       </c>
-      <c r="K40" s="25" t="n">
+      <c r="L40" s="26" t="n">
         <v>696</v>
       </c>
-      <c r="L40" s="29" t="n">
+      <c r="M40" s="30" t="n">
         <v>58</v>
       </c>
-      <c r="M40" s="30" t="inlineStr">
+      <c r="N40" s="31" t="inlineStr">
         <is>
           <t>Saatte ~14 Boy</t>
         </is>
       </c>
-      <c r="N40" s="53" t="n">
+      <c r="O40" s="54" t="n">
         <v>0.005261725483080831</v>
       </c>
     </row>
@@ -7085,52 +7559,57 @@
           <t>100 x 36 mm</t>
         </is>
       </c>
-      <c r="E41" s="54" t="inlineStr">
+      <c r="E41" s="55" t="inlineStr">
         <is>
           <t>Hat 106</t>
         </is>
       </c>
-      <c r="F41" s="19" t="inlineStr">
+      <c r="F41" s="18" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="G41" s="20" t="inlineStr">
         <is>
           <t>YEDEK ROTA 3</t>
         </is>
       </c>
-      <c r="G41" s="13" t="n">
+      <c r="H41" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="H41" s="14" t="n">
+      <c r="I41" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I41" s="14" t="n">
+      <c r="J41" s="15" t="n">
         <v>162</v>
       </c>
-      <c r="J41" s="10" t="inlineStr">
+      <c r="K41" s="10" t="inlineStr">
         <is>
           <t>4.00 kg/boy</t>
         </is>
       </c>
-      <c r="K41" s="11" t="n">
+      <c r="L41" s="11" t="n">
         <v>648</v>
       </c>
-      <c r="L41" s="15" t="n">
+      <c r="M41" s="16" t="n">
         <v>54</v>
       </c>
-      <c r="M41" s="16" t="inlineStr">
+      <c r="N41" s="17" t="inlineStr">
         <is>
           <t>Saatte ~14 Boy</t>
         </is>
       </c>
-      <c r="N41" s="55" t="n">
+      <c r="O41" s="56" t="n">
         <v>0.004898847863558015</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="22" t="inlineStr">
+      <c r="A42" s="23" t="inlineStr">
         <is>
           <t>35X80 PERVAZ</t>
         </is>
       </c>
-      <c r="B42" s="23" t="inlineStr">
+      <c r="B42" s="24" t="inlineStr">
         <is>
           <t>Pervaz Profili</t>
         </is>
@@ -7140,47 +7619,52 @@
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="D42" s="23" t="inlineStr">
+      <c r="D42" s="24" t="inlineStr">
         <is>
           <t>35 x 80 mm</t>
         </is>
       </c>
-      <c r="E42" s="52" t="inlineStr">
+      <c r="E42" s="53" t="inlineStr">
         <is>
           <t>Hat 101</t>
         </is>
       </c>
-      <c r="F42" s="26" t="inlineStr">
+      <c r="F42" s="32" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="G42" s="27" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="G42" s="27" t="n">
+      <c r="H42" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="H42" s="28" t="n">
+      <c r="I42" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="I42" s="28" t="n">
+      <c r="J42" s="29" t="n">
         <v>180</v>
       </c>
-      <c r="J42" s="24" t="inlineStr">
+      <c r="K42" s="25" t="inlineStr">
         <is>
           <t>2.94 kg/boy</t>
         </is>
       </c>
-      <c r="K42" s="25" t="n">
+      <c r="L42" s="26" t="n">
         <v>529.2</v>
       </c>
-      <c r="L42" s="29" t="n">
+      <c r="M42" s="30" t="n">
         <v>44.1</v>
       </c>
-      <c r="M42" s="30" t="inlineStr">
+      <c r="N42" s="31" t="inlineStr">
         <is>
           <t>Saatte ~15 Boy</t>
         </is>
       </c>
-      <c r="N42" s="53" t="n">
+      <c r="O42" s="54" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7205,75 +7689,81 @@
           <t>219 x 26 mm</t>
         </is>
       </c>
-      <c r="E43" s="54" t="inlineStr">
+      <c r="E43" s="55" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="F43" s="12" t="inlineStr">
+      <c r="F43" s="18" t="inlineStr">
+        <is>
+          <t>1 Göz (Tek Çıkış)</t>
+        </is>
+      </c>
+      <c r="G43" s="12" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="G43" s="13" t="n">
+      <c r="H43" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="H43" s="14" t="n">
+      <c r="I43" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I43" s="14" t="n">
+      <c r="J43" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="J43" s="10" t="inlineStr">
+      <c r="K43" s="10" t="inlineStr">
         <is>
           <t>9.26 kg/boy</t>
         </is>
       </c>
-      <c r="K43" s="11" t="n">
+      <c r="L43" s="11" t="n">
         <v>463</v>
       </c>
-      <c r="L43" s="15" t="n">
+      <c r="M43" s="16" t="n">
         <v>38.6</v>
       </c>
-      <c r="M43" s="16" t="inlineStr">
+      <c r="N43" s="17" t="inlineStr">
         <is>
           <t>Saatte ~4 Boy</t>
         </is>
       </c>
-      <c r="N43" s="55" t="n">
+      <c r="O43" s="56" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1">
-      <c r="A44" s="50" t="inlineStr">
+      <c r="A44" s="51" t="inlineStr">
         <is>
           <t>GENEL TOPLAM</t>
         </is>
       </c>
-      <c r="B44" s="39" t="n"/>
-      <c r="C44" s="39" t="n"/>
-      <c r="D44" s="39" t="n"/>
-      <c r="E44" s="39" t="n"/>
-      <c r="F44" s="39" t="n"/>
-      <c r="G44" s="41" t="n">
+      <c r="B44" s="40" t="n"/>
+      <c r="C44" s="40" t="n"/>
+      <c r="D44" s="40" t="n"/>
+      <c r="E44" s="40" t="n"/>
+      <c r="F44" s="40" t="n"/>
+      <c r="G44" s="40" t="n"/>
+      <c r="H44" s="42" t="n">
         <v>17304</v>
       </c>
-      <c r="H44" s="39" t="n"/>
-      <c r="I44" s="40" t="n">
+      <c r="I44" s="40" t="n"/>
+      <c r="J44" s="41" t="n">
         <v>379264</v>
       </c>
-      <c r="J44" s="39" t="n"/>
-      <c r="K44" s="40" t="n">
+      <c r="K44" s="40" t="n"/>
+      <c r="L44" s="41" t="n">
         <v>1237183.51</v>
       </c>
-      <c r="L44" s="39" t="n"/>
-      <c r="M44" s="39" t="n"/>
-      <c r="N44" s="39" t="n"/>
+      <c r="M44" s="40" t="n"/>
+      <c r="N44" s="40" t="n"/>
+      <c r="O44" s="40" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/static/Ergunbas_Urun_Hat_Rotalari_ve_Kapasite_Analizi.xlsx
+++ b/static/Ergunbas_Urun_Hat_Rotalari_ve_Kapasite_Analizi.xlsx
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>296887.79</v>
+        <v>298093.79</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -972,13 +972,13 @@
         </is>
       </c>
       <c r="I5" s="14" t="n">
-        <v>1598.4</v>
+        <v>1622.4</v>
       </c>
       <c r="J5" s="15" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K5" s="16" t="n">
-        <v>97.5</v>
+        <v>96.8</v>
       </c>
       <c r="L5" s="17" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="M5" s="11" t="n">
-        <v>2340</v>
+        <v>2323.2</v>
       </c>
       <c r="N5" s="14" t="n">
         <v>99.2</v>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="P5" s="19" t="n">
-        <v>0.983</v>
+        <v>0.976</v>
       </c>
       <c r="Q5" s="15" t="n">
         <v>45</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="F6" s="26" t="n">
-        <v>185908.31</v>
+        <v>188073.31</v>
       </c>
       <c r="G6" s="27" t="inlineStr">
         <is>
@@ -1077,13 +1077,13 @@
         </is>
       </c>
       <c r="I6" s="28" t="n">
-        <v>1520.2</v>
+        <v>1538.2</v>
       </c>
       <c r="J6" s="29" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K6" s="30" t="n">
-        <v>74.3</v>
+        <v>73.7</v>
       </c>
       <c r="L6" s="31" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="M6" s="26" t="n">
-        <v>1783.2</v>
+        <v>1768.8</v>
       </c>
       <c r="N6" s="28" t="n">
         <v>73.59999999999999</v>
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="P6" s="33" t="n">
-        <v>1.01</v>
+        <v>1.001</v>
       </c>
       <c r="Q6" s="29" t="n">
         <v>35</v>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="T6" s="35" t="n">
-        <v>1397</v>
+        <v>1421</v>
       </c>
       <c r="U6" s="35" t="n">
-        <v>52.3</v>
+        <v>52.6</v>
       </c>
       <c r="V6" s="32" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="F7" s="11" t="n">
-        <v>170210</v>
+        <v>172895</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1182,21 +1182,21 @@
         </is>
       </c>
       <c r="I7" s="14" t="n">
-        <v>1561.3</v>
+        <v>1585.3</v>
       </c>
       <c r="J7" s="15" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="K7" s="16" t="n">
-        <v>72</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="L7" s="17" t="inlineStr">
         <is>
-          <t>Saatte ~14 Boy</t>
+          <t>Saatte ~15 Boy</t>
         </is>
       </c>
       <c r="M7" s="11" t="n">
-        <v>1728</v>
+        <v>1730.4</v>
       </c>
       <c r="N7" s="14" t="n">
         <v>74.09999999999999</v>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="P7" s="19" t="n">
-        <v>0.972</v>
+        <v>0.973</v>
       </c>
       <c r="Q7" s="15" t="n">
         <v>55</v>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="F8" s="26" t="n">
-        <v>131789.8</v>
+        <v>132867.8</v>
       </c>
       <c r="G8" s="27" t="inlineStr">
         <is>
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="T8" s="35" t="n">
-        <v>911</v>
+        <v>935</v>
       </c>
       <c r="U8" s="35" t="n">
-        <v>67.90000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="V8" s="32" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F9" s="11" t="n">
-        <v>118792.08</v>
+        <v>119746.08</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="I9" s="14" t="n">
-        <v>1198.5</v>
+        <v>1204.5</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K9" s="16" t="n">
-        <v>99.09999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="L9" s="17" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="M9" s="11" t="n">
-        <v>2378.4</v>
+        <v>2385.6</v>
       </c>
       <c r="N9" s="14" t="n">
         <v>187.9</v>
@@ -1417,7 +1417,7 @@
         </is>
       </c>
       <c r="P9" s="37" t="n">
-        <v>0.527</v>
+        <v>0.529</v>
       </c>
       <c r="Q9" s="15" t="n">
         <v>90</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="F13" s="11" t="n">
-        <v>30621.25</v>
+        <v>32023.75</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="I13" s="14" t="n">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K13" s="16" t="n">
-        <v>92.5</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="L13" s="17" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         </is>
       </c>
       <c r="M13" s="11" t="n">
-        <v>2220</v>
+        <v>2253.6</v>
       </c>
       <c r="N13" s="14" t="n">
         <v>131.5</v>
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="P13" s="37" t="n">
-        <v>0.703</v>
+        <v>0.7140000000000001</v>
       </c>
       <c r="Q13" s="15" t="n">
         <v>90</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="F14" s="26" t="n">
-        <v>27487</v>
+        <v>30342</v>
       </c>
       <c r="G14" s="27" t="inlineStr">
         <is>
@@ -1941,21 +1941,21 @@
         </is>
       </c>
       <c r="I14" s="28" t="n">
-        <v>255</v>
+        <v>279</v>
       </c>
       <c r="J14" s="29" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K14" s="30" t="n">
-        <v>107.8</v>
+        <v>108.8</v>
       </c>
       <c r="L14" s="31" t="inlineStr">
         <is>
-          <t>Saatte ~28 Boy</t>
+          <t>Saatte ~29 Boy</t>
         </is>
       </c>
       <c r="M14" s="26" t="n">
-        <v>2587.2</v>
+        <v>2611.2</v>
       </c>
       <c r="N14" s="28" t="n">
         <v>96.09999999999999</v>
@@ -1966,7 +1966,7 @@
         </is>
       </c>
       <c r="P14" s="33" t="n">
-        <v>1.122</v>
+        <v>1.132</v>
       </c>
       <c r="Q14" s="29" t="n">
         <v>60</v>
@@ -3793,12 +3793,12 @@
       <c r="D31" s="40" t="n"/>
       <c r="E31" s="40" t="n"/>
       <c r="F31" s="41" t="n">
-        <v>1239963.98</v>
+        <v>1252309.48</v>
       </c>
       <c r="G31" s="40" t="n"/>
       <c r="H31" s="40" t="n"/>
       <c r="I31" s="42" t="n">
-        <v>10874.7</v>
+        <v>10980.7</v>
       </c>
       <c r="J31" s="40" t="n"/>
       <c r="K31" s="40" t="n"/>
@@ -3811,7 +3811,7 @@
       <c r="R31" s="40" t="n"/>
       <c r="S31" s="40" t="n"/>
       <c r="T31" s="42" t="n">
-        <v>4436.7</v>
+        <v>4484.7</v>
       </c>
       <c r="U31" s="40" t="n"/>
       <c r="V31" s="40" t="n"/>
@@ -3990,16 +3990,16 @@
         </is>
       </c>
       <c r="D5" s="14" t="n">
-        <v>1539.1</v>
+        <v>1560.1</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>94501</v>
+        <v>95369</v>
       </c>
       <c r="G5" s="16" t="n">
-        <v>61.4</v>
+        <v>61.1</v>
       </c>
       <c r="H5" s="46" t="n">
         <v>4</v>
@@ -4037,16 +4037,16 @@
         </is>
       </c>
       <c r="D6" s="28" t="n">
-        <v>1409</v>
+        <v>1433</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F6" s="26" t="n">
-        <v>73771</v>
+        <v>75496</v>
       </c>
       <c r="G6" s="30" t="n">
-        <v>52.4</v>
+        <v>52.7</v>
       </c>
       <c r="H6" s="44" t="n">
         <v>2</v>
@@ -4084,16 +4084,16 @@
         </is>
       </c>
       <c r="D7" s="14" t="n">
-        <v>1598.4</v>
+        <v>1622.4</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>155845.32</v>
+        <v>157051.32</v>
       </c>
       <c r="G7" s="16" t="n">
-        <v>97.5</v>
+        <v>96.8</v>
       </c>
       <c r="H7" s="46" t="n">
         <v>1</v>
@@ -4178,16 +4178,16 @@
         </is>
       </c>
       <c r="D9" s="14" t="n">
-        <v>1597.3</v>
+        <v>1621.3</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>115692</v>
+        <v>117509</v>
       </c>
       <c r="G9" s="16" t="n">
-        <v>72.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="H9" s="46" t="n">
         <v>3</v>
@@ -4225,16 +4225,16 @@
         </is>
       </c>
       <c r="D10" s="28" t="n">
-        <v>1545.7</v>
+        <v>1569.7</v>
       </c>
       <c r="E10" s="29" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F10" s="26" t="n">
-        <v>138070</v>
+        <v>140925</v>
       </c>
       <c r="G10" s="30" t="n">
-        <v>89.3</v>
+        <v>89.8</v>
       </c>
       <c r="H10" s="44" t="n">
         <v>8</v>
@@ -4272,16 +4272,16 @@
         </is>
       </c>
       <c r="D11" s="14" t="n">
-        <v>1525.2</v>
+        <v>1549.2</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>102062.8</v>
+        <v>103140.8</v>
       </c>
       <c r="G11" s="16" t="n">
-        <v>66.90000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="H11" s="46" t="n">
         <v>3</v>
@@ -4319,16 +4319,16 @@
         </is>
       </c>
       <c r="D12" s="28" t="n">
-        <v>1532.2</v>
+        <v>1550.2</v>
       </c>
       <c r="E12" s="29" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F12" s="26" t="n">
-        <v>113918.31</v>
+        <v>114358.31</v>
       </c>
       <c r="G12" s="30" t="n">
-        <v>74.3</v>
+        <v>73.8</v>
       </c>
       <c r="H12" s="44" t="n">
         <v>2</v>
@@ -4366,23 +4366,23 @@
         </is>
       </c>
       <c r="D13" s="14" t="n">
-        <v>2730.5</v>
+        <v>2746.5</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>274777.0800000001</v>
+        <v>277133.5800000001</v>
       </c>
       <c r="G13" s="16" t="n">
-        <v>100.6</v>
+        <v>100.9</v>
       </c>
       <c r="H13" s="46" t="n">
         <v>11</v>
       </c>
       <c r="I13" s="12" t="inlineStr">
         <is>
-          <t>Tek Göz (Geniş Düz Dudak)</t>
+          <t>Levha Kalıbı (Tek Kafa)</t>
         </is>
       </c>
       <c r="J13" s="8" t="inlineStr">
@@ -4405,16 +4405,16 @@
       <c r="B14" s="40" t="n"/>
       <c r="C14" s="40" t="n"/>
       <c r="D14" s="42" t="n">
-        <v>15736.4</v>
+        <v>15911.4</v>
       </c>
       <c r="E14" s="41" t="n">
-        <v>1444</v>
+        <v>1461</v>
       </c>
       <c r="F14" s="41" t="n">
-        <v>1239963.98</v>
+        <v>1252309.48</v>
       </c>
       <c r="G14" s="42" t="n">
-        <v>78.8</v>
+        <v>78.7</v>
       </c>
       <c r="H14" s="40" t="n"/>
       <c r="I14" s="40" t="n"/>
@@ -4584,13 +4584,13 @@
         </is>
       </c>
       <c r="H4" s="28" t="n">
-        <v>1598.4</v>
+        <v>1622.4</v>
       </c>
       <c r="I4" s="29" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J4" s="29" t="n">
-        <v>45682</v>
+        <v>46047</v>
       </c>
       <c r="K4" s="25" t="inlineStr">
         <is>
@@ -4598,18 +4598,18 @@
         </is>
       </c>
       <c r="L4" s="26" t="n">
-        <v>155845.32</v>
+        <v>157051.32</v>
       </c>
       <c r="M4" s="30" t="n">
-        <v>97.5</v>
+        <v>96.8</v>
       </c>
       <c r="N4" s="31" t="inlineStr">
         <is>
-          <t>Saatte ~29 Boy</t>
+          <t>Saatte ~28 Boy</t>
         </is>
       </c>
       <c r="O4" s="48" t="n">
-        <v>0.5249300417507907</v>
+        <v>0.526852035394632</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -4674,7 +4674,7 @@
         </is>
       </c>
       <c r="O5" s="49" t="n">
-        <v>0.4607985730905269</v>
+        <v>0.4589343172831611</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -4714,13 +4714,13 @@
         </is>
       </c>
       <c r="H6" s="28" t="n">
-        <v>1198.5</v>
+        <v>1204.5</v>
       </c>
       <c r="I6" s="29" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J6" s="29" t="n">
-        <v>24904</v>
+        <v>25104</v>
       </c>
       <c r="K6" s="25" t="inlineStr">
         <is>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="L6" s="26" t="n">
-        <v>118792.08</v>
+        <v>119746.08</v>
       </c>
       <c r="M6" s="30" t="n">
-        <v>99.09999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="N6" s="31" t="inlineStr">
         <is>
@@ -4745,32 +4745,32 @@
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>50X80 PERVAZ</t>
+          <t>140 mm KASA</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Pervaz Profili</t>
+          <t>Kasa Profili</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>2.20 Metre</t>
+          <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>50 x 80 mm</t>
+          <t>140 x 36 mm</t>
         </is>
       </c>
       <c r="E7" s="45" t="inlineStr">
         <is>
-          <t>Hat 109</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>Çift Göz (2 Kafa)</t>
+          <t>Hat 106</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
@@ -4779,63 +4779,63 @@
         </is>
       </c>
       <c r="H7" s="14" t="n">
-        <v>1520.2</v>
+        <v>1585.3</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="J7" s="15" t="n">
-        <v>75361</v>
+        <v>22355</v>
       </c>
       <c r="K7" s="10" t="inlineStr">
         <is>
-          <t>1.55 kg/boy</t>
+          <t>4.95 kg/boy</t>
         </is>
       </c>
       <c r="L7" s="11" t="n">
-        <v>112897.31</v>
+        <v>114247</v>
       </c>
       <c r="M7" s="16" t="n">
-        <v>74.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="N7" s="17" t="inlineStr">
         <is>
-          <t>Saatte ~50 Boy</t>
+          <t>Saatte ~14 Boy</t>
         </is>
       </c>
       <c r="O7" s="49" t="n">
-        <v>0.6072741449803938</v>
+        <v>0.6607883397437752</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="23" t="inlineStr">
         <is>
-          <t>140 mm KASA</t>
+          <t>50X80 PERVAZ</t>
         </is>
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>Kasa Profili</t>
+          <t>Pervaz Profili</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>2.15 Metre (215 cm)</t>
+          <t>2.20 Metre</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>140 x 36 mm</t>
+          <t>50 x 80 mm</t>
         </is>
       </c>
       <c r="E8" s="43" t="inlineStr">
         <is>
-          <t>Hat 106</t>
-        </is>
-      </c>
-      <c r="F8" s="32" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
+          <t>Hat 109</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>Çift Göz (2 Kafa)</t>
         </is>
       </c>
       <c r="G8" s="27" t="inlineStr">
@@ -4844,32 +4844,32 @@
         </is>
       </c>
       <c r="H8" s="28" t="n">
-        <v>1561.3</v>
+        <v>1538.2</v>
       </c>
       <c r="I8" s="29" t="n">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="J8" s="29" t="n">
-        <v>22015</v>
+        <v>75716</v>
       </c>
       <c r="K8" s="25" t="inlineStr">
         <is>
-          <t>4.95 kg/boy</t>
+          <t>1.55 kg/boy</t>
         </is>
       </c>
       <c r="L8" s="26" t="n">
-        <v>112430</v>
+        <v>113337.31</v>
       </c>
       <c r="M8" s="30" t="n">
-        <v>72</v>
+        <v>73.7</v>
       </c>
       <c r="N8" s="31" t="inlineStr">
         <is>
-          <t>Saatte ~14 Boy</t>
+          <t>Saatte ~49 Boy</t>
         </is>
       </c>
       <c r="O8" s="48" t="n">
-        <v>0.6605369837259856</v>
+        <v>0.6026230409833272</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -4974,13 +4974,13 @@
         </is>
       </c>
       <c r="H10" s="28" t="n">
-        <v>1397</v>
+        <v>1421</v>
       </c>
       <c r="I10" s="29" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J10" s="29" t="n">
-        <v>44050</v>
+        <v>45110</v>
       </c>
       <c r="K10" s="25" t="inlineStr">
         <is>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="L10" s="26" t="n">
-        <v>73011</v>
+        <v>74736</v>
       </c>
       <c r="M10" s="30" t="n">
-        <v>52.3</v>
+        <v>52.6</v>
       </c>
       <c r="N10" s="31" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         </is>
       </c>
       <c r="O10" s="48" t="n">
-        <v>0.3927258550196062</v>
+        <v>0.3973769590166728</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -5064,7 +5064,7 @@
         </is>
       </c>
       <c r="O11" s="49" t="n">
-        <v>0.5155254807276436</v>
+        <v>0.511342853573251</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -5104,13 +5104,13 @@
         </is>
       </c>
       <c r="H12" s="28" t="n">
-        <v>911</v>
+        <v>935</v>
       </c>
       <c r="I12" s="29" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J12" s="29" t="n">
-        <v>16017</v>
+        <v>16287</v>
       </c>
       <c r="K12" s="25" t="inlineStr">
         <is>
@@ -5118,18 +5118,18 @@
         </is>
       </c>
       <c r="L12" s="26" t="n">
-        <v>61854.8</v>
+        <v>62932.8</v>
       </c>
       <c r="M12" s="30" t="n">
-        <v>67.90000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="N12" s="31" t="inlineStr">
         <is>
-          <t>Saatte ~18 Boy</t>
+          <t>Saatte ~17 Boy</t>
         </is>
       </c>
       <c r="O12" s="48" t="n">
-        <v>0.4693443650419077</v>
+        <v>0.4736497480954754</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -5259,7 +5259,7 @@
         </is>
       </c>
       <c r="O14" s="48" t="n">
-        <v>0.2251571588038306</v>
+        <v>0.2216605454177391</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -5364,13 +5364,13 @@
         </is>
       </c>
       <c r="H16" s="28" t="n">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="I16" s="29" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J16" s="29" t="n">
-        <v>7205</v>
+        <v>7535</v>
       </c>
       <c r="K16" s="25" t="inlineStr">
         <is>
@@ -5378,10 +5378,10 @@
         </is>
       </c>
       <c r="L16" s="26" t="n">
-        <v>30621.25</v>
+        <v>32023.75</v>
       </c>
       <c r="M16" s="30" t="n">
-        <v>92.5</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="N16" s="31" t="inlineStr">
         <is>
@@ -5429,13 +5429,13 @@
         </is>
       </c>
       <c r="H17" s="14" t="n">
-        <v>255</v>
+        <v>279</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>7168</v>
+        <v>7938</v>
       </c>
       <c r="K17" s="10" t="inlineStr">
         <is>
@@ -5443,10 +5443,10 @@
         </is>
       </c>
       <c r="L17" s="11" t="n">
-        <v>27487</v>
+        <v>30342</v>
       </c>
       <c r="M17" s="16" t="n">
-        <v>107.8</v>
+        <v>108.8</v>
       </c>
       <c r="N17" s="17" t="inlineStr">
         <is>
@@ -5525,27 +5525,27 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>KT100-220x24-ANT</t>
+          <t>140 mm KASA</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Deck / WPC Zemin</t>
+          <t>Kasa Profili</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>3.00 Metre</t>
+          <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>220 x 24 mm</t>
+          <t>140 x 36 mm</t>
         </is>
       </c>
       <c r="E19" s="45" t="inlineStr">
         <is>
-          <t>Hat 107</t>
+          <t>Hat 102</t>
         </is>
       </c>
       <c r="F19" s="18" t="inlineStr">
@@ -5553,64 +5553,64 @@
           <t>Tek Göz (1 Kafa)</t>
         </is>
       </c>
-      <c r="G19" s="12" t="inlineStr">
-        <is>
-          <t>ANA ROTA</t>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>YEDEK ROTA 2</t>
         </is>
       </c>
       <c r="H19" s="14" t="n">
-        <v>205.7</v>
+        <v>302</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>1712</v>
+        <v>3301</v>
       </c>
       <c r="K19" s="10" t="inlineStr">
         <is>
-          <t>10.33 kg/boy</t>
+          <t>4.95 kg/boy</t>
         </is>
       </c>
       <c r="L19" s="11" t="n">
-        <v>17678</v>
+        <v>18238</v>
       </c>
       <c r="M19" s="16" t="n">
-        <v>85.90000000000001</v>
+        <v>60.4</v>
       </c>
       <c r="N19" s="17" t="inlineStr">
         <is>
-          <t>Saatte ~8 Boy</t>
+          <t>Saatte ~11 Boy</t>
         </is>
       </c>
       <c r="O19" s="49" t="n">
-        <v>1</v>
+        <v>0.1054859886058012</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="23" t="inlineStr">
         <is>
-          <t>140 mm KASA</t>
+          <t>KT100-220x24-ANT</t>
         </is>
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>Kasa Profili</t>
+          <t>Deck / WPC Zemin</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>2.15 Metre (215 cm)</t>
+          <t>3.00 Metre</t>
         </is>
       </c>
       <c r="D20" s="24" t="inlineStr">
         <is>
-          <t>140 x 36 mm</t>
+          <t>220 x 24 mm</t>
         </is>
       </c>
       <c r="E20" s="43" t="inlineStr">
         <is>
-          <t>Hat 102</t>
+          <t>Hat 107</t>
         </is>
       </c>
       <c r="F20" s="32" t="inlineStr">
@@ -5618,38 +5618,38 @@
           <t>Tek Göz (1 Kafa)</t>
         </is>
       </c>
-      <c r="G20" s="34" t="inlineStr">
-        <is>
-          <t>YEDEK ROTA 2</t>
+      <c r="G20" s="27" t="inlineStr">
+        <is>
+          <t>ANA ROTA</t>
         </is>
       </c>
       <c r="H20" s="28" t="n">
-        <v>281</v>
+        <v>205.7</v>
       </c>
       <c r="I20" s="29" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J20" s="29" t="n">
-        <v>3136</v>
+        <v>1712</v>
       </c>
       <c r="K20" s="25" t="inlineStr">
         <is>
-          <t>4.95 kg/boy</t>
+          <t>10.33 kg/boy</t>
         </is>
       </c>
       <c r="L20" s="26" t="n">
-        <v>17370</v>
+        <v>17678</v>
       </c>
       <c r="M20" s="30" t="n">
-        <v>61.8</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="N20" s="31" t="inlineStr">
         <is>
-          <t>Saatte ~11 Boy</t>
+          <t>Saatte ~8 Boy</t>
         </is>
       </c>
       <c r="O20" s="48" t="n">
-        <v>0.1020504083191352</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="O31" s="49" t="n">
-        <v>0.01171149544412049</v>
+        <v>0.01166411417024152</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
@@ -6689,7 +6689,7 @@
         </is>
       </c>
       <c r="O36" s="48" t="n">
-        <v>0.008048880794312908</v>
+        <v>0.007923884438532057</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
@@ -6754,7 +6754,7 @@
         </is>
       </c>
       <c r="O37" s="49" t="n">
-        <v>0.008748780254617582</v>
+        <v>0.008677798533579995</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
@@ -6884,7 +6884,7 @@
         </is>
       </c>
       <c r="O39" s="49" t="n">
-        <v>0.00638137397583121</v>
+        <v>0.006329599797693648</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
@@ -6949,7 +6949,7 @@
         </is>
       </c>
       <c r="O40" s="48" t="n">
-        <v>0.002559889714561856</v>
+        <v>0.00254953315196536</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="O41" s="49" t="n">
-        <v>0.004206568356735797</v>
+        <v>0.00414124179415252</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
@@ -7160,15 +7160,15 @@
       <c r="F44" s="40" t="n"/>
       <c r="G44" s="40" t="n"/>
       <c r="H44" s="42" t="n">
-        <v>15736.4</v>
+        <v>15911.4</v>
       </c>
       <c r="I44" s="40" t="n"/>
       <c r="J44" s="41" t="n">
-        <v>379264</v>
+        <v>383119</v>
       </c>
       <c r="K44" s="40" t="n"/>
       <c r="L44" s="41" t="n">
-        <v>1239963.98</v>
+        <v>1252309.48</v>
       </c>
       <c r="M44" s="40" t="n"/>
       <c r="N44" s="40" t="n"/>
@@ -7469,30 +7469,30 @@
         </is>
       </c>
       <c r="E7" s="14" t="n">
-        <v>911</v>
+        <v>935</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>61854.8</v>
+        <v>62932.8</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>16017</v>
+        <v>16287</v>
       </c>
       <c r="I7" s="16" t="n">
-        <v>67.90000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>Saatte ~18 Boy</t>
+          <t>Saatte ~17 Boy</t>
         </is>
       </c>
       <c r="K7" s="14" t="n">
         <v>69.5</v>
       </c>
       <c r="L7" s="19" t="n">
-        <v>0.9769784172661872</v>
+        <v>0.9683453237410071</v>
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
@@ -7522,19 +7522,19 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="F8" s="29" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G8" s="26" t="n">
-        <v>17370</v>
+        <v>18238</v>
       </c>
       <c r="H8" s="29" t="n">
-        <v>3136</v>
+        <v>3301</v>
       </c>
       <c r="I8" s="30" t="n">
-        <v>61.8</v>
+        <v>60.4</v>
       </c>
       <c r="J8" s="31" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>51.8</v>
       </c>
       <c r="L8" s="33" t="n">
-        <v>1.193050193050193</v>
+        <v>1.166023166023166</v>
       </c>
       <c r="M8" s="24" t="inlineStr">
         <is>
@@ -7628,19 +7628,19 @@
         </is>
       </c>
       <c r="E10" s="28" t="n">
-        <v>1561.3</v>
+        <v>1585.3</v>
       </c>
       <c r="F10" s="29" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G10" s="26" t="n">
-        <v>112430</v>
+        <v>114247</v>
       </c>
       <c r="H10" s="29" t="n">
-        <v>22015</v>
+        <v>22355</v>
       </c>
       <c r="I10" s="30" t="n">
-        <v>72</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="J10" s="31" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>74.09999999999999</v>
       </c>
       <c r="L10" s="33" t="n">
-        <v>0.97165991902834</v>
+        <v>0.9730094466936572</v>
       </c>
       <c r="M10" s="24" t="inlineStr">
         <is>
@@ -8158,19 +8158,19 @@
         </is>
       </c>
       <c r="E20" s="55" t="n">
-        <v>1325</v>
+        <v>1349</v>
       </c>
       <c r="F20" s="56" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G20" s="57" t="n">
-        <v>68720</v>
+        <v>70445</v>
       </c>
       <c r="H20" s="56" t="n">
-        <v>41310</v>
+        <v>42370</v>
       </c>
       <c r="I20" s="58" t="n">
-        <v>51.9</v>
+        <v>52.2</v>
       </c>
       <c r="J20" s="59" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>53.1</v>
       </c>
       <c r="L20" s="60" t="n">
-        <v>0.9774011299435028</v>
+        <v>0.9830508474576272</v>
       </c>
       <c r="M20" s="61" t="inlineStr">
         <is>
@@ -8264,19 +8264,19 @@
         </is>
       </c>
       <c r="E22" s="55" t="n">
-        <v>1402.2</v>
+        <v>1420.2</v>
       </c>
       <c r="F22" s="56" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G22" s="57" t="n">
-        <v>105156.75</v>
+        <v>105596.75</v>
       </c>
       <c r="H22" s="56" t="n">
-        <v>70115</v>
+        <v>70470</v>
       </c>
       <c r="I22" s="58" t="n">
-        <v>75</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="J22" s="59" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
         <v>73.59999999999999</v>
       </c>
       <c r="L22" s="60" t="n">
-        <v>1.019021739130435</v>
+        <v>1.010869565217391</v>
       </c>
       <c r="M22" s="61" t="inlineStr">
         <is>
@@ -8688,19 +8688,19 @@
         </is>
       </c>
       <c r="E30" s="28" t="n">
-        <v>1198.5</v>
+        <v>1204.5</v>
       </c>
       <c r="F30" s="29" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G30" s="26" t="n">
-        <v>118792.08</v>
+        <v>119746.08</v>
       </c>
       <c r="H30" s="29" t="n">
-        <v>24904</v>
+        <v>25104</v>
       </c>
       <c r="I30" s="30" t="n">
-        <v>99.09999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="J30" s="31" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         <v>187.9</v>
       </c>
       <c r="L30" s="38" t="n">
-        <v>0.5274081958488557</v>
+        <v>0.5290047897817989</v>
       </c>
       <c r="M30" s="24" t="inlineStr">
         <is>
@@ -9006,19 +9006,19 @@
         </is>
       </c>
       <c r="E36" s="28" t="n">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F36" s="29" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G36" s="26" t="n">
-        <v>30621.25</v>
+        <v>32023.75</v>
       </c>
       <c r="H36" s="29" t="n">
-        <v>7205</v>
+        <v>7535</v>
       </c>
       <c r="I36" s="30" t="n">
-        <v>92.5</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="J36" s="31" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         <v>131.5</v>
       </c>
       <c r="L36" s="38" t="n">
-        <v>0.7034220532319392</v>
+        <v>0.7140684410646387</v>
       </c>
       <c r="M36" s="24" t="inlineStr">
         <is>
@@ -9165,19 +9165,19 @@
         </is>
       </c>
       <c r="E39" s="55" t="n">
-        <v>1502.4</v>
+        <v>1526.4</v>
       </c>
       <c r="F39" s="56" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G39" s="57" t="n">
-        <v>144935.32</v>
+        <v>146141.32</v>
       </c>
       <c r="H39" s="56" t="n">
-        <v>42511</v>
+        <v>42876</v>
       </c>
       <c r="I39" s="58" t="n">
-        <v>96.5</v>
+        <v>95.7</v>
       </c>
       <c r="J39" s="59" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>99.2</v>
       </c>
       <c r="L39" s="60" t="n">
-        <v>0.9727822580645161</v>
+        <v>0.9647177419354839</v>
       </c>
       <c r="M39" s="61" t="inlineStr">
         <is>
@@ -9377,19 +9377,19 @@
         </is>
       </c>
       <c r="E43" s="14" t="n">
-        <v>255</v>
+        <v>279</v>
       </c>
       <c r="F43" s="15" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G43" s="11" t="n">
-        <v>27487</v>
+        <v>30342</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>7168</v>
+        <v>7938</v>
       </c>
       <c r="I43" s="16" t="n">
-        <v>107.8</v>
+        <v>108.8</v>
       </c>
       <c r="J43" s="17" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>96.09999999999999</v>
       </c>
       <c r="L43" s="19" t="n">
-        <v>1.121748178980229</v>
+        <v>1.132154006243496</v>
       </c>
       <c r="M43" s="8" t="inlineStr">
         <is>

--- a/static/Ergunbas_Urun_Hat_Rotalari_ve_Kapasite_Analizi.xlsx
+++ b/static/Ergunbas_Urun_Hat_Rotalari_ve_Kapasite_Analizi.xlsx
@@ -192,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -254,6 +254,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -294,6 +297,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -734,7 +740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y31"/>
+  <dimension ref="A1:X31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -753,15 +759,14 @@
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="24" customWidth="1" min="15" max="15"/>
     <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="24" customWidth="1" min="22" max="22"/>
-    <col width="16" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="28" customWidth="1" min="25" max="25"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="28" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -789,17 +794,17 @@
           <t>ANA ROTA (BİRİNCİL MAKİNE)</t>
         </is>
       </c>
-      <c r="R3" s="5" t="inlineStr">
+      <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>YEDEK ROTA 1 (İKİNCİL MAKİNE)</t>
         </is>
       </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>YEDEK ROTA 2</t>
+        </is>
+      </c>
       <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>YEDEK ROTA 2</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="inlineStr">
         <is>
           <t>STRATEJİ</t>
         </is>
@@ -888,45 +893,40 @@
       </c>
       <c r="Q4" s="6" t="inlineStr">
         <is>
-          <t>Setup Süresi (dk)</t>
+          <t>Yedek Rota 1 Hat</t>
         </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>Yedek Rota 1 Hat</t>
+          <t>Yedek 1 Kalıp Çıkışı</t>
         </is>
       </c>
       <c r="S4" s="6" t="inlineStr">
         <is>
-          <t>Yedek 1 Kalıp Çıkışı</t>
+          <t>Yedek 1 Fiili Saat</t>
         </is>
       </c>
       <c r="T4" s="6" t="inlineStr">
         <is>
-          <t>Yedek 1 Fiili Saat</t>
+          <t>Yedek 1 Fiili Hız (kg/sa)</t>
         </is>
       </c>
       <c r="U4" s="6" t="inlineStr">
         <is>
-          <t>Yedek 1 Fiili Hız (kg/sa)</t>
+          <t>Yedek 1 Hız (Saatte ~X Boy)</t>
         </is>
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>Yedek 1 Hız (Saatte ~X Boy)</t>
+          <t>Yedek 1 Standart Hız (kg/sa)</t>
         </is>
       </c>
       <c r="W4" s="6" t="inlineStr">
         <is>
-          <t>Yedek 1 Standart Hız (kg/sa)</t>
+          <t>Yedek Rota 2 Hat</t>
         </is>
       </c>
       <c r="X4" s="6" t="inlineStr">
-        <is>
-          <t>Yedek Rota 2 Hat</t>
-        </is>
-      </c>
-      <c r="Y4" s="6" t="inlineStr">
         <is>
           <t>Planlama &amp; Rota Durumu</t>
         </is>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>298093.79</v>
+        <v>299377.79</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -972,21 +972,21 @@
         </is>
       </c>
       <c r="I5" s="14" t="n">
-        <v>1622.4</v>
+        <v>1646.4</v>
       </c>
       <c r="J5" s="15" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K5" s="16" t="n">
-        <v>96.8</v>
+        <v>96.2</v>
       </c>
       <c r="L5" s="17" t="inlineStr">
         <is>
-          <t>Saatte ~29 Boy</t>
+          <t>Saatte ~28 Boy</t>
         </is>
       </c>
       <c r="M5" s="11" t="n">
-        <v>2323.2</v>
+        <v>2308.8</v>
       </c>
       <c r="N5" s="14" t="n">
         <v>99.2</v>
@@ -997,53 +997,50 @@
         </is>
       </c>
       <c r="P5" s="19" t="n">
-        <v>0.976</v>
-      </c>
-      <c r="Q5" s="15" t="n">
-        <v>45</v>
-      </c>
-      <c r="R5" s="20" t="inlineStr">
+        <v>0.97</v>
+      </c>
+      <c r="Q5" s="20" t="inlineStr">
         <is>
           <t>Hat 105</t>
         </is>
       </c>
-      <c r="S5" s="13" t="inlineStr">
+      <c r="R5" s="21" t="inlineStr">
         <is>
           <t>Çift Göz (2 Kafa)</t>
         </is>
       </c>
-      <c r="T5" s="21" t="n">
+      <c r="S5" s="22" t="n">
         <v>1502.5</v>
       </c>
-      <c r="U5" s="21" t="n">
+      <c r="T5" s="22" t="n">
         <v>91.09999999999999</v>
       </c>
-      <c r="V5" s="18" t="inlineStr">
+      <c r="U5" s="18" t="inlineStr">
         <is>
           <t>Saatte ~27 Boy</t>
         </is>
       </c>
-      <c r="W5" s="21" t="n">
+      <c r="V5" s="22" t="n">
         <v>92.2</v>
       </c>
-      <c r="X5" s="22" t="inlineStr">
+      <c r="W5" s="23" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="Y5" s="8" t="inlineStr">
+      <c r="X5" s="8" t="inlineStr">
         <is>
           <t>Aktif Çift Hatlı Üretim (Yüksek Hacimli)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>50X80 PERVAZ</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Pervaz Profili</t>
         </is>
@@ -1053,20 +1050,20 @@
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>50 x 80 mm</t>
         </is>
       </c>
-      <c r="E6" s="25" t="inlineStr">
+      <c r="E6" s="26" t="inlineStr">
         <is>
           <t>1.55 kg/boy</t>
         </is>
       </c>
-      <c r="F6" s="26" t="n">
-        <v>188073.31</v>
-      </c>
-      <c r="G6" s="27" t="inlineStr">
+      <c r="F6" s="27" t="n">
+        <v>190911.31</v>
+      </c>
+      <c r="G6" s="28" t="inlineStr">
         <is>
           <t>Hat 109</t>
         </is>
@@ -1076,67 +1073,64 @@
           <t>Çift Göz (2 Kafa)</t>
         </is>
       </c>
-      <c r="I6" s="28" t="n">
-        <v>1538.2</v>
-      </c>
-      <c r="J6" s="29" t="n">
-        <v>150</v>
-      </c>
-      <c r="K6" s="30" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="L6" s="31" t="inlineStr">
+      <c r="I6" s="29" t="n">
+        <v>1562.2</v>
+      </c>
+      <c r="J6" s="30" t="n">
+        <v>152</v>
+      </c>
+      <c r="K6" s="31" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="L6" s="32" t="inlineStr">
+        <is>
+          <t>Saatte ~47 Boy</t>
+        </is>
+      </c>
+      <c r="M6" s="27" t="n">
+        <v>1761.6</v>
+      </c>
+      <c r="N6" s="29" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="O6" s="33" t="inlineStr">
         <is>
           <t>Saatte ~48 Boy</t>
         </is>
       </c>
-      <c r="M6" s="26" t="n">
-        <v>1768.8</v>
-      </c>
-      <c r="N6" s="28" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="O6" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~48 Boy</t>
-        </is>
-      </c>
-      <c r="P6" s="33" t="n">
-        <v>1.001</v>
-      </c>
-      <c r="Q6" s="29" t="n">
-        <v>35</v>
-      </c>
-      <c r="R6" s="34" t="inlineStr">
+      <c r="P6" s="34" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="Q6" s="35" t="inlineStr">
         <is>
           <t>Hat 103</t>
         </is>
       </c>
-      <c r="S6" s="13" t="inlineStr">
+      <c r="R6" s="36" t="inlineStr">
         <is>
           <t>Çift Göz (2 Kafa)</t>
         </is>
       </c>
-      <c r="T6" s="35" t="n">
-        <v>1421</v>
-      </c>
-      <c r="U6" s="35" t="n">
-        <v>52.6</v>
-      </c>
-      <c r="V6" s="32" t="inlineStr">
+      <c r="S6" s="37" t="n">
+        <v>1445</v>
+      </c>
+      <c r="T6" s="37" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="U6" s="33" t="inlineStr">
         <is>
           <t>Saatte ~34 Boy</t>
         </is>
       </c>
-      <c r="W6" s="35" t="n">
+      <c r="V6" s="37" t="n">
         <v>53.1</v>
       </c>
-      <c r="X6" s="36" t="inlineStr">
+      <c r="W6" s="38" t="inlineStr">
         <is>
           <t>Hat 101</t>
         </is>
       </c>
-      <c r="Y6" s="24" t="inlineStr">
+      <c r="X6" s="25" t="inlineStr">
         <is>
           <t>Aktif Çift Hatlı Üretim (Yüksek Hacimli)</t>
         </is>
@@ -1169,7 +1163,7 @@
         </is>
       </c>
       <c r="F7" s="11" t="n">
-        <v>172895</v>
+        <v>175893</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1182,21 +1176,21 @@
         </is>
       </c>
       <c r="I7" s="14" t="n">
-        <v>1585.3</v>
+        <v>1609.3</v>
       </c>
       <c r="J7" s="15" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K7" s="16" t="n">
-        <v>72.09999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="L7" s="17" t="inlineStr">
         <is>
-          <t>Saatte ~15 Boy</t>
+          <t>Saatte ~14 Boy</t>
         </is>
       </c>
       <c r="M7" s="11" t="n">
-        <v>1730.4</v>
+        <v>1723.2</v>
       </c>
       <c r="N7" s="14" t="n">
         <v>74.09999999999999</v>
@@ -1207,53 +1201,50 @@
         </is>
       </c>
       <c r="P7" s="19" t="n">
-        <v>0.973</v>
-      </c>
-      <c r="Q7" s="15" t="n">
-        <v>55</v>
-      </c>
-      <c r="R7" s="20" t="inlineStr">
+        <v>0.9690000000000001</v>
+      </c>
+      <c r="Q7" s="20" t="inlineStr">
         <is>
           <t>Hat 108</t>
         </is>
       </c>
-      <c r="S7" s="18" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="T7" s="21" t="n">
+      <c r="R7" s="18" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="S7" s="22" t="n">
         <v>590.2</v>
       </c>
-      <c r="U7" s="21" t="n">
+      <c r="T7" s="22" t="n">
         <v>64.90000000000001</v>
       </c>
-      <c r="V7" s="18" t="inlineStr">
+      <c r="U7" s="18" t="inlineStr">
         <is>
           <t>Saatte ~13 Boy</t>
         </is>
       </c>
-      <c r="W7" s="21" t="n">
+      <c r="V7" s="22" t="n">
         <v>64.90000000000001</v>
       </c>
-      <c r="X7" s="22" t="inlineStr">
+      <c r="W7" s="23" t="inlineStr">
         <is>
           <t>Hat 102</t>
         </is>
       </c>
-      <c r="Y7" s="8" t="inlineStr">
+      <c r="X7" s="8" t="inlineStr">
         <is>
           <t>Aktif Çift Hatlı Üretim (Yüksek Hacimli)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>100 mm KASA</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Kasa Profili</t>
         </is>
@@ -1263,90 +1254,87 @@
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="D8" s="24" t="inlineStr">
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>100 x 36 mm</t>
         </is>
       </c>
-      <c r="E8" s="25" t="inlineStr">
+      <c r="E8" s="26" t="inlineStr">
         <is>
           <t>4.00 kg/boy</t>
         </is>
       </c>
-      <c r="F8" s="26" t="n">
-        <v>132867.8</v>
-      </c>
-      <c r="G8" s="27" t="inlineStr">
+      <c r="F8" s="27" t="n">
+        <v>134340.8</v>
+      </c>
+      <c r="G8" s="28" t="inlineStr">
         <is>
           <t>Hat 102</t>
         </is>
       </c>
-      <c r="H8" s="32" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="I8" s="28" t="n">
+      <c r="H8" s="33" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="I8" s="29" t="n">
         <v>1074.1</v>
       </c>
-      <c r="J8" s="29" t="n">
+      <c r="J8" s="30" t="n">
         <v>95</v>
       </c>
-      <c r="K8" s="30" t="n">
+      <c r="K8" s="31" t="n">
         <v>63.3</v>
       </c>
-      <c r="L8" s="31" t="inlineStr">
+      <c r="L8" s="32" t="inlineStr">
         <is>
           <t>Saatte ~16 Boy</t>
         </is>
       </c>
-      <c r="M8" s="26" t="n">
+      <c r="M8" s="27" t="n">
         <v>1519.2</v>
       </c>
-      <c r="N8" s="28" t="n">
+      <c r="N8" s="29" t="n">
         <v>63.3</v>
       </c>
-      <c r="O8" s="32" t="inlineStr">
+      <c r="O8" s="33" t="inlineStr">
         <is>
           <t>Saatte ~16 Boy</t>
         </is>
       </c>
-      <c r="P8" s="33" t="n">
+      <c r="P8" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="Q8" s="29" t="n">
-        <v>65</v>
-      </c>
-      <c r="R8" s="34" t="inlineStr">
+      <c r="Q8" s="35" t="inlineStr">
         <is>
           <t>Hat 108</t>
         </is>
       </c>
-      <c r="S8" s="32" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="T8" s="35" t="n">
-        <v>935</v>
-      </c>
-      <c r="U8" s="35" t="n">
-        <v>67.3</v>
-      </c>
-      <c r="V8" s="32" t="inlineStr">
+      <c r="R8" s="33" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="S8" s="37" t="n">
+        <v>959</v>
+      </c>
+      <c r="T8" s="37" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="U8" s="33" t="inlineStr">
         <is>
           <t>Saatte ~17 Boy</t>
         </is>
       </c>
-      <c r="W8" s="35" t="n">
+      <c r="V8" s="37" t="n">
         <v>69.5</v>
       </c>
-      <c r="X8" s="36" t="inlineStr">
+      <c r="W8" s="38" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="Y8" s="24" t="inlineStr">
+      <c r="X8" s="25" t="inlineStr">
         <is>
           <t>Aktif Çift Hatlı Üretim (Yüksek Hacimli)</t>
         </is>
@@ -1379,7 +1367,7 @@
         </is>
       </c>
       <c r="F9" s="11" t="n">
-        <v>119746.08</v>
+        <v>122751.18</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1392,13 +1380,13 @@
         </is>
       </c>
       <c r="I9" s="14" t="n">
-        <v>1204.5</v>
+        <v>1218.5</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K9" s="16" t="n">
-        <v>99.40000000000001</v>
+        <v>100.7</v>
       </c>
       <c r="L9" s="17" t="inlineStr">
         <is>
@@ -1406,7 +1394,7 @@
         </is>
       </c>
       <c r="M9" s="11" t="n">
-        <v>2385.6</v>
+        <v>2416.8</v>
       </c>
       <c r="N9" s="14" t="n">
         <v>187.9</v>
@@ -1416,18 +1404,20 @@
           <t>Saatte ~39 Plaka</t>
         </is>
       </c>
-      <c r="P9" s="37" t="n">
-        <v>0.529</v>
-      </c>
-      <c r="Q9" s="15" t="n">
-        <v>90</v>
-      </c>
-      <c r="R9" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S9" s="18" t="inlineStr">
+      <c r="P9" s="39" t="n">
+        <v>0.536</v>
+      </c>
+      <c r="Q9" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R9" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1437,39 +1427,34 @@
           <t>—</t>
         </is>
       </c>
-      <c r="U9" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V9" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W9" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X9" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y9" s="8" t="inlineStr">
+      <c r="U9" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V9" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W9" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X9" s="8" t="inlineStr">
         <is>
           <t>Levha Özel Hattı (Hat 201)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>200 mm KASA</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>Kasa Profili</t>
         </is>
@@ -1479,90 +1464,87 @@
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="D10" s="25" t="inlineStr">
         <is>
           <t>200 x 36 mm</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="26" t="inlineStr">
         <is>
           <t>6.66 kg/boy</t>
         </is>
       </c>
-      <c r="F10" s="26" t="n">
+      <c r="F10" s="27" t="n">
         <v>81332</v>
       </c>
-      <c r="G10" s="27" t="inlineStr">
+      <c r="G10" s="28" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="H10" s="32" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="I10" s="28" t="n">
+      <c r="H10" s="33" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="I10" s="29" t="n">
         <v>910</v>
       </c>
-      <c r="J10" s="29" t="n">
+      <c r="J10" s="30" t="n">
         <v>86</v>
       </c>
-      <c r="K10" s="30" t="n">
+      <c r="K10" s="31" t="n">
         <v>84.59999999999999</v>
       </c>
-      <c r="L10" s="31" t="inlineStr">
+      <c r="L10" s="32" t="inlineStr">
         <is>
           <t>Saatte ~13 Boy</t>
         </is>
       </c>
-      <c r="M10" s="26" t="n">
+      <c r="M10" s="27" t="n">
         <v>2030.4</v>
       </c>
-      <c r="N10" s="28" t="n">
+      <c r="N10" s="29" t="n">
         <v>84.59999999999999</v>
       </c>
-      <c r="O10" s="32" t="inlineStr">
+      <c r="O10" s="33" t="inlineStr">
         <is>
           <t>Saatte ~13 Boy</t>
         </is>
       </c>
-      <c r="P10" s="33" t="n">
+      <c r="P10" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="Q10" s="29" t="n">
-        <v>60</v>
-      </c>
-      <c r="R10" s="34" t="inlineStr">
+      <c r="Q10" s="35" t="inlineStr">
         <is>
           <t>Hat 106</t>
         </is>
       </c>
-      <c r="S10" s="32" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="T10" s="35" t="n">
+      <c r="R10" s="33" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="S10" s="37" t="n">
         <v>24</v>
       </c>
-      <c r="U10" s="35" t="n">
+      <c r="T10" s="37" t="n">
         <v>100.9</v>
       </c>
-      <c r="V10" s="32" t="inlineStr">
+      <c r="U10" s="33" t="inlineStr">
         <is>
           <t>Saatte ~15 Boy</t>
         </is>
       </c>
-      <c r="W10" s="35" t="n">
+      <c r="V10" s="37" t="n">
         <v>100.9</v>
       </c>
-      <c r="X10" s="36" t="inlineStr">
+      <c r="W10" s="38" t="inlineStr">
         <is>
           <t>Hat 108</t>
         </is>
       </c>
-      <c r="Y10" s="24" t="inlineStr">
+      <c r="X10" s="25" t="inlineStr">
         <is>
           <t>Aktif Çift Hatlı Üretim (Yüksek Hacimli)</t>
         </is>
@@ -1632,18 +1614,20 @@
           <t>Saatte ~34 Plaka</t>
         </is>
       </c>
-      <c r="P11" s="37" t="n">
+      <c r="P11" s="39" t="n">
         <v>0.78</v>
       </c>
-      <c r="Q11" s="15" t="n">
-        <v>90</v>
-      </c>
-      <c r="R11" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S11" s="18" t="inlineStr">
+      <c r="Q11" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R11" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1653,39 +1637,34 @@
           <t>—</t>
         </is>
       </c>
-      <c r="U11" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V11" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W11" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X11" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y11" s="8" t="inlineStr">
+      <c r="U11" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V11" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W11" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X11" s="8" t="inlineStr">
         <is>
           <t>Levha Özel Hattı (Hat 201)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="23" t="inlineStr">
-        <is>
-          <t>BEYAZ TEAK Levha</t>
-        </is>
-      </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>MIX TEAK Levha</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>WPC Levha Plaka</t>
         </is>
@@ -1695,96 +1674,93 @@
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="D12" s="24" t="inlineStr">
+      <c r="D12" s="25" t="inlineStr">
         <is>
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E12" s="25" t="inlineStr">
-        <is>
-          <t>4.41 kg/plaka</t>
-        </is>
-      </c>
-      <c r="F12" s="26" t="n">
-        <v>32060.7</v>
-      </c>
-      <c r="G12" s="27" t="inlineStr">
+      <c r="E12" s="26" t="inlineStr">
+        <is>
+          <t>4.25 kg/plaka</t>
+        </is>
+      </c>
+      <c r="F12" s="27" t="n">
+        <v>32618.75</v>
+      </c>
+      <c r="G12" s="28" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="H12" s="32" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="I12" s="28" t="n">
-        <v>260</v>
-      </c>
-      <c r="J12" s="29" t="n">
-        <v>30</v>
-      </c>
-      <c r="K12" s="30" t="n">
-        <v>123.3</v>
-      </c>
-      <c r="L12" s="31" t="inlineStr">
-        <is>
-          <t>Saatte ~28 Plaka</t>
-        </is>
-      </c>
-      <c r="M12" s="26" t="n">
-        <v>2959.2</v>
-      </c>
-      <c r="N12" s="28" t="n">
-        <v>148.4</v>
-      </c>
-      <c r="O12" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~34 Plaka</t>
-        </is>
-      </c>
-      <c r="P12" s="33" t="n">
-        <v>0.831</v>
-      </c>
-      <c r="Q12" s="29" t="n">
-        <v>90</v>
-      </c>
-      <c r="R12" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S12" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T12" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U12" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V12" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W12" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X12" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y12" s="24" t="inlineStr">
+      <c r="H12" s="33" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="I12" s="29" t="n">
+        <v>343</v>
+      </c>
+      <c r="J12" s="30" t="n">
+        <v>31</v>
+      </c>
+      <c r="K12" s="31" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="L12" s="32" t="inlineStr">
+        <is>
+          <t>Saatte ~22 Plaka</t>
+        </is>
+      </c>
+      <c r="M12" s="27" t="n">
+        <v>2282.4</v>
+      </c>
+      <c r="N12" s="29" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="O12" s="33" t="inlineStr">
+        <is>
+          <t>Saatte ~31 Plaka</t>
+        </is>
+      </c>
+      <c r="P12" s="40" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="Q12" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R12" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S12" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V12" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W12" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X12" s="25" t="inlineStr">
         <is>
           <t>Levha Özel Hattı (Hat 201)</t>
         </is>
@@ -1793,222 +1769,216 @@
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>MIX TEAK Levha</t>
+          <t>SEREN(39mm)</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
+          <t>Seren Çıtası</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>2.10 Metre</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>39 x 45 mm</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>3.81 kg/boy</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>32593</v>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>Hat 107</t>
+        </is>
+      </c>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>303</v>
+      </c>
+      <c r="J13" s="15" t="n">
+        <v>27</v>
+      </c>
+      <c r="K13" s="16" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="L13" s="17" t="inlineStr">
+        <is>
+          <t>Saatte ~28 Boy</t>
+        </is>
+      </c>
+      <c r="M13" s="11" t="n">
+        <v>2582.4</v>
+      </c>
+      <c r="N13" s="14" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="O13" s="18" t="inlineStr">
+        <is>
+          <t>Saatte ~25 Boy</t>
+        </is>
+      </c>
+      <c r="P13" s="19" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Q13" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R13" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T13" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U13" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V13" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W13" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X13" s="8" t="inlineStr">
+        <is>
+          <t>Tek Hat Atamalı</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>BEYAZ TEAK Levha</t>
+        </is>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
           <t>WPC Levha Plaka</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D14" s="25" t="inlineStr">
         <is>
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>4.25 kg/plaka</t>
-        </is>
-      </c>
-      <c r="F13" s="11" t="n">
-        <v>32023.75</v>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t>4.41 kg/plaka</t>
+        </is>
+      </c>
+      <c r="F14" s="27" t="n">
+        <v>32060.7</v>
+      </c>
+      <c r="G14" s="28" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="H13" s="18" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="I13" s="14" t="n">
-        <v>341</v>
-      </c>
-      <c r="J13" s="15" t="n">
+      <c r="H14" s="33" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="I14" s="29" t="n">
+        <v>260</v>
+      </c>
+      <c r="J14" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="K13" s="16" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="L13" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~22 Plaka</t>
-        </is>
-      </c>
-      <c r="M13" s="11" t="n">
-        <v>2253.6</v>
-      </c>
-      <c r="N13" s="14" t="n">
-        <v>131.5</v>
-      </c>
-      <c r="O13" s="18" t="inlineStr">
-        <is>
-          <t>Saatte ~31 Plaka</t>
-        </is>
-      </c>
-      <c r="P13" s="37" t="n">
-        <v>0.7140000000000001</v>
-      </c>
-      <c r="Q13" s="15" t="n">
-        <v>90</v>
-      </c>
-      <c r="R13" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S13" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T13" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U13" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V13" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W13" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X13" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y13" s="8" t="inlineStr">
+      <c r="K14" s="31" t="n">
+        <v>123.3</v>
+      </c>
+      <c r="L14" s="32" t="inlineStr">
+        <is>
+          <t>Saatte ~28 Plaka</t>
+        </is>
+      </c>
+      <c r="M14" s="27" t="n">
+        <v>2959.2</v>
+      </c>
+      <c r="N14" s="29" t="n">
+        <v>148.4</v>
+      </c>
+      <c r="O14" s="33" t="inlineStr">
+        <is>
+          <t>Saatte ~34 Plaka</t>
+        </is>
+      </c>
+      <c r="P14" s="34" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="Q14" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R14" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S14" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U14" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V14" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W14" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X14" s="25" t="inlineStr">
         <is>
           <t>Levha Özel Hattı (Hat 201)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="23" t="inlineStr">
-        <is>
-          <t>SEREN(39mm)</t>
-        </is>
-      </c>
-      <c r="B14" s="24" t="inlineStr">
-        <is>
-          <t>Seren Çıtası</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>2.10 Metre</t>
-        </is>
-      </c>
-      <c r="D14" s="24" t="inlineStr">
-        <is>
-          <t>39 x 45 mm</t>
-        </is>
-      </c>
-      <c r="E14" s="25" t="inlineStr">
-        <is>
-          <t>3.81 kg/boy</t>
-        </is>
-      </c>
-      <c r="F14" s="26" t="n">
-        <v>30342</v>
-      </c>
-      <c r="G14" s="27" t="inlineStr">
-        <is>
-          <t>Hat 107</t>
-        </is>
-      </c>
-      <c r="H14" s="32" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="I14" s="28" t="n">
-        <v>279</v>
-      </c>
-      <c r="J14" s="29" t="n">
-        <v>25</v>
-      </c>
-      <c r="K14" s="30" t="n">
-        <v>108.8</v>
-      </c>
-      <c r="L14" s="31" t="inlineStr">
-        <is>
-          <t>Saatte ~29 Boy</t>
-        </is>
-      </c>
-      <c r="M14" s="26" t="n">
-        <v>2611.2</v>
-      </c>
-      <c r="N14" s="28" t="n">
-        <v>96.09999999999999</v>
-      </c>
-      <c r="O14" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~25 Boy</t>
-        </is>
-      </c>
-      <c r="P14" s="33" t="n">
-        <v>1.132</v>
-      </c>
-      <c r="Q14" s="29" t="n">
-        <v>60</v>
-      </c>
-      <c r="R14" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S14" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T14" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U14" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V14" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W14" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X14" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y14" s="24" t="inlineStr">
-        <is>
-          <t>Tek Hat Atamalı</t>
         </is>
       </c>
     </row>
@@ -2079,15 +2049,17 @@
       <c r="P15" s="19" t="n">
         <v>0.8190000000000001</v>
       </c>
-      <c r="Q15" s="15" t="n">
-        <v>90</v>
-      </c>
-      <c r="R15" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S15" s="18" t="inlineStr">
+      <c r="Q15" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R15" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2097,39 +2069,34 @@
           <t>—</t>
         </is>
       </c>
-      <c r="U15" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V15" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W15" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X15" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y15" s="8" t="inlineStr">
+      <c r="U15" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V15" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W15" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X15" s="8" t="inlineStr">
         <is>
           <t>Levha Özel Hattı (Hat 201)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="23" t="inlineStr">
+      <c r="A16" s="24" t="inlineStr">
         <is>
           <t>KT100-220x24-ANT</t>
         </is>
       </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>Deck / WPC Zemin</t>
         </is>
@@ -2139,96 +2106,93 @@
           <t>3.00 Metre</t>
         </is>
       </c>
-      <c r="D16" s="24" t="inlineStr">
+      <c r="D16" s="25" t="inlineStr">
         <is>
           <t>220 x 24 mm</t>
         </is>
       </c>
-      <c r="E16" s="25" t="inlineStr">
+      <c r="E16" s="26" t="inlineStr">
         <is>
           <t>10.33 kg/boy</t>
         </is>
       </c>
-      <c r="F16" s="26" t="n">
+      <c r="F16" s="27" t="n">
         <v>17678</v>
       </c>
-      <c r="G16" s="27" t="inlineStr">
+      <c r="G16" s="28" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="H16" s="32" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="I16" s="28" t="n">
+      <c r="H16" s="33" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="I16" s="29" t="n">
         <v>205.7</v>
       </c>
-      <c r="J16" s="29" t="n">
+      <c r="J16" s="30" t="n">
         <v>23</v>
       </c>
-      <c r="K16" s="30" t="n">
+      <c r="K16" s="31" t="n">
         <v>85.90000000000001</v>
       </c>
-      <c r="L16" s="31" t="inlineStr">
+      <c r="L16" s="32" t="inlineStr">
         <is>
           <t>Saatte ~8 Boy</t>
         </is>
       </c>
-      <c r="M16" s="26" t="n">
+      <c r="M16" s="27" t="n">
         <v>2061.6</v>
       </c>
-      <c r="N16" s="28" t="n">
+      <c r="N16" s="29" t="n">
         <v>84.7</v>
       </c>
-      <c r="O16" s="32" t="inlineStr">
+      <c r="O16" s="33" t="inlineStr">
         <is>
           <t>Saatte ~8 Boy</t>
         </is>
       </c>
-      <c r="P16" s="33" t="n">
+      <c r="P16" s="34" t="n">
         <v>1.014</v>
       </c>
-      <c r="Q16" s="29" t="n">
-        <v>45</v>
-      </c>
-      <c r="R16" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S16" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T16" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U16" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V16" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W16" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X16" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y16" s="24" t="inlineStr">
+      <c r="Q16" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R16" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S16" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U16" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V16" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W16" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X16" s="25" t="inlineStr">
         <is>
           <t>Tek Hat Atamalı</t>
         </is>
@@ -2301,51 +2265,48 @@
       <c r="P17" s="19" t="n">
         <v>1.099</v>
       </c>
-      <c r="Q17" s="15" t="n">
-        <v>40</v>
-      </c>
-      <c r="R17" s="20" t="inlineStr">
+      <c r="Q17" s="20" t="inlineStr">
         <is>
           <t>Hat 109</t>
         </is>
       </c>
-      <c r="S17" s="13" t="inlineStr">
+      <c r="R17" s="21" t="inlineStr">
         <is>
           <t>Çift Göz (2 Kafa)</t>
         </is>
       </c>
-      <c r="T17" s="21" t="n">
+      <c r="S17" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="U17" s="21" t="n">
+      <c r="T17" s="22" t="n">
         <v>85.09999999999999</v>
       </c>
-      <c r="V17" s="18" t="inlineStr">
+      <c r="U17" s="18" t="inlineStr">
         <is>
           <t>Saatte ~39 Boy</t>
         </is>
       </c>
-      <c r="W17" s="21" t="n">
+      <c r="V17" s="22" t="n">
         <v>85.09999999999999</v>
       </c>
-      <c r="X17" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y17" s="8" t="inlineStr">
+      <c r="W17" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X17" s="8" t="inlineStr">
         <is>
           <t>Aktif Çift Hatlı Üretim (Yüksek Hacimli)</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="23" t="inlineStr">
+      <c r="A18" s="24" t="inlineStr">
         <is>
           <t>35X100 PERVAZ</t>
         </is>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>Pervaz Profili</t>
         </is>
@@ -2355,96 +2316,93 @@
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="D18" s="24" t="inlineStr">
+      <c r="D18" s="25" t="inlineStr">
         <is>
           <t>35 x 100 mm</t>
         </is>
       </c>
-      <c r="E18" s="25" t="inlineStr">
+      <c r="E18" s="26" t="inlineStr">
         <is>
           <t>2.08 kg/boy</t>
         </is>
       </c>
-      <c r="F18" s="26" t="n">
+      <c r="F18" s="27" t="n">
         <v>10435</v>
       </c>
-      <c r="G18" s="27" t="inlineStr">
+      <c r="G18" s="28" t="inlineStr">
         <is>
           <t>Hat 101</t>
         </is>
       </c>
-      <c r="H18" s="32" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="I18" s="28" t="n">
+      <c r="H18" s="33" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="I18" s="29" t="n">
         <v>241</v>
       </c>
-      <c r="J18" s="29" t="n">
+      <c r="J18" s="30" t="n">
         <v>22</v>
       </c>
-      <c r="K18" s="30" t="n">
+      <c r="K18" s="31" t="n">
         <v>43.3</v>
       </c>
-      <c r="L18" s="31" t="inlineStr">
+      <c r="L18" s="32" t="inlineStr">
         <is>
           <t>Saatte ~21 Boy</t>
         </is>
       </c>
-      <c r="M18" s="26" t="n">
+      <c r="M18" s="27" t="n">
         <v>1039.2</v>
       </c>
-      <c r="N18" s="28" t="n">
+      <c r="N18" s="29" t="n">
         <v>46.8</v>
       </c>
-      <c r="O18" s="32" t="inlineStr">
+      <c r="O18" s="33" t="inlineStr">
         <is>
           <t>Saatte ~22 Boy</t>
         </is>
       </c>
-      <c r="P18" s="33" t="n">
+      <c r="P18" s="34" t="n">
         <v>0.925</v>
       </c>
-      <c r="Q18" s="29" t="n">
-        <v>40</v>
-      </c>
-      <c r="R18" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S18" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T18" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U18" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V18" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W18" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X18" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y18" s="24" t="inlineStr">
+      <c r="Q18" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R18" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S18" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T18" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U18" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V18" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W18" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X18" s="25" t="inlineStr">
         <is>
           <t>Tek Hat Atamalı</t>
         </is>
@@ -2517,15 +2475,17 @@
       <c r="P19" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="Q19" s="15" t="n">
-        <v>40</v>
-      </c>
-      <c r="R19" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S19" s="18" t="inlineStr">
+      <c r="Q19" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R19" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2535,39 +2495,34 @@
           <t>—</t>
         </is>
       </c>
-      <c r="U19" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V19" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W19" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X19" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y19" s="8" t="inlineStr">
+      <c r="U19" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V19" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W19" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X19" s="8" t="inlineStr">
         <is>
           <t>Tek Hat Atamalı</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="23" t="inlineStr">
+      <c r="A20" s="24" t="inlineStr">
         <is>
           <t>KT102-219x26-ANT</t>
         </is>
       </c>
-      <c r="B20" s="24" t="inlineStr">
+      <c r="B20" s="25" t="inlineStr">
         <is>
           <t>Deck / WPC Zemin</t>
         </is>
@@ -2577,96 +2532,93 @@
           <t>3.00 Metre</t>
         </is>
       </c>
-      <c r="D20" s="24" t="inlineStr">
+      <c r="D20" s="25" t="inlineStr">
         <is>
           <t>219 x 26 mm</t>
         </is>
       </c>
-      <c r="E20" s="25" t="inlineStr">
+      <c r="E20" s="26" t="inlineStr">
         <is>
           <t>10.52 kg/boy</t>
         </is>
       </c>
-      <c r="F20" s="26" t="n">
+      <c r="F20" s="27" t="n">
         <v>9415</v>
       </c>
-      <c r="G20" s="27" t="inlineStr">
+      <c r="G20" s="28" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="H20" s="32" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="I20" s="28" t="n">
+      <c r="H20" s="33" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="I20" s="29" t="n">
         <v>87</v>
       </c>
-      <c r="J20" s="29" t="n">
+      <c r="J20" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="K20" s="30" t="n">
+      <c r="K20" s="31" t="n">
         <v>108.2</v>
       </c>
-      <c r="L20" s="31" t="inlineStr">
+      <c r="L20" s="32" t="inlineStr">
         <is>
           <t>Saatte ~10 Boy</t>
         </is>
       </c>
-      <c r="M20" s="26" t="n">
+      <c r="M20" s="27" t="n">
         <v>2596.8</v>
       </c>
-      <c r="N20" s="28" t="n">
+      <c r="N20" s="29" t="n">
         <v>108.2</v>
       </c>
-      <c r="O20" s="32" t="inlineStr">
+      <c r="O20" s="33" t="inlineStr">
         <is>
           <t>Saatte ~10 Boy</t>
         </is>
       </c>
-      <c r="P20" s="33" t="n">
+      <c r="P20" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="Q20" s="29" t="n">
-        <v>45</v>
-      </c>
-      <c r="R20" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S20" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T20" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U20" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V20" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W20" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X20" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y20" s="24" t="inlineStr">
+      <c r="Q20" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R20" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S20" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U20" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V20" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W20" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X20" s="25" t="inlineStr">
         <is>
           <t>Tek Hat Atamalı</t>
         </is>
@@ -2739,15 +2691,17 @@
       <c r="P21" s="19" t="n">
         <v>1.115</v>
       </c>
-      <c r="Q21" s="15" t="n">
-        <v>90</v>
-      </c>
-      <c r="R21" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S21" s="18" t="inlineStr">
+      <c r="Q21" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R21" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2757,39 +2711,34 @@
           <t>—</t>
         </is>
       </c>
-      <c r="U21" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V21" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W21" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X21" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y21" s="8" t="inlineStr">
+      <c r="U21" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V21" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W21" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X21" s="8" t="inlineStr">
         <is>
           <t>Levha Özel Hattı (Hat 201)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="23" t="inlineStr">
+      <c r="A22" s="24" t="inlineStr">
         <is>
           <t>CAM ÇITASI</t>
         </is>
       </c>
-      <c r="B22" s="24" t="inlineStr">
+      <c r="B22" s="25" t="inlineStr">
         <is>
           <t>Cam Çıtası</t>
         </is>
@@ -2799,96 +2748,93 @@
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="D22" s="24" t="inlineStr">
+      <c r="D22" s="25" t="inlineStr">
         <is>
           <t>15 x 20 mm</t>
         </is>
       </c>
-      <c r="E22" s="25" t="inlineStr">
+      <c r="E22" s="26" t="inlineStr">
         <is>
           <t>1.50 kg/boy</t>
         </is>
       </c>
-      <c r="F22" s="26" t="n">
+      <c r="F22" s="27" t="n">
         <v>7805</v>
       </c>
-      <c r="G22" s="27" t="inlineStr">
+      <c r="G22" s="28" t="inlineStr">
         <is>
           <t>Hat 102</t>
         </is>
       </c>
-      <c r="H22" s="32" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="I22" s="28" t="n">
+      <c r="H22" s="33" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="I22" s="29" t="n">
         <v>150</v>
       </c>
-      <c r="J22" s="29" t="n">
+      <c r="J22" s="30" t="n">
         <v>14</v>
       </c>
-      <c r="K22" s="30" t="n">
+      <c r="K22" s="31" t="n">
         <v>52</v>
       </c>
-      <c r="L22" s="31" t="inlineStr">
+      <c r="L22" s="32" t="inlineStr">
         <is>
           <t>Saatte ~35 Boy</t>
         </is>
       </c>
-      <c r="M22" s="26" t="n">
+      <c r="M22" s="27" t="n">
         <v>1248</v>
       </c>
-      <c r="N22" s="28" t="n">
+      <c r="N22" s="29" t="n">
         <v>50</v>
       </c>
-      <c r="O22" s="32" t="inlineStr">
+      <c r="O22" s="33" t="inlineStr">
         <is>
           <t>Saatte ~33 Boy</t>
         </is>
       </c>
-      <c r="P22" s="33" t="n">
+      <c r="P22" s="34" t="n">
         <v>1.04</v>
       </c>
-      <c r="Q22" s="29" t="n">
-        <v>40</v>
-      </c>
-      <c r="R22" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S22" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T22" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U22" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V22" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W22" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X22" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y22" s="24" t="inlineStr">
+      <c r="Q22" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R22" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S22" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T22" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U22" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V22" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W22" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X22" s="25" t="inlineStr">
         <is>
           <t>Tek Hat Atamalı</t>
         </is>
@@ -2958,18 +2904,20 @@
           <t>Saatte ~26 Plaka</t>
         </is>
       </c>
-      <c r="P23" s="37" t="n">
+      <c r="P23" s="39" t="n">
         <v>0.6409999999999999</v>
       </c>
-      <c r="Q23" s="15" t="n">
-        <v>90</v>
-      </c>
-      <c r="R23" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S23" s="18" t="inlineStr">
+      <c r="Q23" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R23" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2979,39 +2927,34 @@
           <t>—</t>
         </is>
       </c>
-      <c r="U23" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V23" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W23" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X23" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y23" s="8" t="inlineStr">
+      <c r="U23" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V23" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W23" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X23" s="8" t="inlineStr">
         <is>
           <t>Levha Özel Hattı (Hat 201)</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="23" t="inlineStr">
+      <c r="A24" s="24" t="inlineStr">
         <is>
           <t>AY GRİ Levha</t>
         </is>
       </c>
-      <c r="B24" s="24" t="inlineStr">
+      <c r="B24" s="25" t="inlineStr">
         <is>
           <t>WPC Levha Plaka</t>
         </is>
@@ -3021,96 +2964,93 @@
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="D24" s="24" t="inlineStr">
+      <c r="D24" s="25" t="inlineStr">
         <is>
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E24" s="25" t="inlineStr">
+      <c r="E24" s="26" t="inlineStr">
         <is>
           <t>4.64 kg/plaka</t>
         </is>
       </c>
-      <c r="F24" s="26" t="n">
+      <c r="F24" s="27" t="n">
         <v>6018.08</v>
       </c>
-      <c r="G24" s="27" t="inlineStr">
+      <c r="G24" s="28" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="H24" s="32" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="I24" s="28" t="n">
+      <c r="H24" s="33" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="I24" s="29" t="n">
         <v>57.5</v>
       </c>
-      <c r="J24" s="29" t="n">
+      <c r="J24" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="K24" s="30" t="n">
+      <c r="K24" s="31" t="n">
         <v>104.7</v>
       </c>
-      <c r="L24" s="31" t="inlineStr">
+      <c r="L24" s="32" t="inlineStr">
         <is>
           <t>Saatte ~23 Plaka</t>
         </is>
       </c>
-      <c r="M24" s="26" t="n">
+      <c r="M24" s="27" t="n">
         <v>2512.8</v>
       </c>
-      <c r="N24" s="28" t="n">
+      <c r="N24" s="29" t="n">
         <v>144.9</v>
       </c>
-      <c r="O24" s="32" t="inlineStr">
+      <c r="O24" s="33" t="inlineStr">
         <is>
           <t>Saatte ~31 Plaka</t>
         </is>
       </c>
-      <c r="P24" s="38" t="n">
+      <c r="P24" s="40" t="n">
         <v>0.723</v>
       </c>
-      <c r="Q24" s="29" t="n">
-        <v>90</v>
-      </c>
-      <c r="R24" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S24" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T24" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U24" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V24" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W24" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X24" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y24" s="24" t="inlineStr">
+      <c r="Q24" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R24" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S24" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T24" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U24" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V24" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W24" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X24" s="25" t="inlineStr">
         <is>
           <t>Levha Özel Hattı (Hat 201)</t>
         </is>
@@ -3180,18 +3120,20 @@
           <t>Saatte ~23 Plaka</t>
         </is>
       </c>
-      <c r="P25" s="37" t="n">
+      <c r="P25" s="39" t="n">
         <v>0.643</v>
       </c>
-      <c r="Q25" s="15" t="n">
-        <v>90</v>
-      </c>
-      <c r="R25" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S25" s="18" t="inlineStr">
+      <c r="Q25" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R25" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3201,39 +3143,34 @@
           <t>—</t>
         </is>
       </c>
-      <c r="U25" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V25" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W25" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X25" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y25" s="8" t="inlineStr">
+      <c r="U25" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V25" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W25" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X25" s="8" t="inlineStr">
         <is>
           <t>Levha Özel Hattı (Hat 201)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="23" t="inlineStr">
+      <c r="A26" s="24" t="inlineStr">
         <is>
           <t>KOYU CEVİZ Levha</t>
         </is>
       </c>
-      <c r="B26" s="24" t="inlineStr">
+      <c r="B26" s="25" t="inlineStr">
         <is>
           <t>WPC Levha Plaka</t>
         </is>
@@ -3243,96 +3180,93 @@
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="D26" s="24" t="inlineStr">
+      <c r="D26" s="25" t="inlineStr">
         <is>
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E26" s="25" t="inlineStr">
+      <c r="E26" s="26" t="inlineStr">
         <is>
           <t>4.79 kg/plaka</t>
         </is>
       </c>
-      <c r="F26" s="26" t="n">
+      <c r="F26" s="27" t="n">
         <v>3846.37</v>
       </c>
-      <c r="G26" s="27" t="inlineStr">
+      <c r="G26" s="28" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="H26" s="32" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="I26" s="28" t="n">
+      <c r="H26" s="33" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="I26" s="29" t="n">
         <v>72.5</v>
       </c>
-      <c r="J26" s="29" t="n">
+      <c r="J26" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="K26" s="30" t="n">
+      <c r="K26" s="31" t="n">
         <v>53.1</v>
       </c>
-      <c r="L26" s="31" t="inlineStr">
+      <c r="L26" s="32" t="inlineStr">
         <is>
           <t>Saatte ~11 Plaka</t>
         </is>
       </c>
-      <c r="M26" s="26" t="n">
+      <c r="M26" s="27" t="n">
         <v>1274.4</v>
       </c>
-      <c r="N26" s="28" t="n">
+      <c r="N26" s="29" t="n">
         <v>79.2</v>
       </c>
-      <c r="O26" s="32" t="inlineStr">
+      <c r="O26" s="33" t="inlineStr">
         <is>
           <t>Saatte ~16 Plaka</t>
         </is>
       </c>
-      <c r="P26" s="38" t="n">
+      <c r="P26" s="40" t="n">
         <v>0.67</v>
       </c>
-      <c r="Q26" s="29" t="n">
-        <v>45</v>
-      </c>
-      <c r="R26" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S26" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T26" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U26" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V26" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W26" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X26" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y26" s="24" t="inlineStr">
+      <c r="Q26" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R26" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S26" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T26" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U26" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V26" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W26" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X26" s="25" t="inlineStr">
         <is>
           <t>Levha Özel Hattı (Hat 201)</t>
         </is>
@@ -3402,18 +3336,20 @@
           <t>Saatte ~57 Plaka</t>
         </is>
       </c>
-      <c r="P27" s="37" t="n">
+      <c r="P27" s="39" t="n">
         <v>0.7240000000000001</v>
       </c>
-      <c r="Q27" s="15" t="n">
-        <v>45</v>
-      </c>
-      <c r="R27" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S27" s="18" t="inlineStr">
+      <c r="Q27" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R27" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3423,39 +3359,34 @@
           <t>—</t>
         </is>
       </c>
-      <c r="U27" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V27" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W27" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X27" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y27" s="8" t="inlineStr">
+      <c r="U27" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V27" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W27" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X27" s="8" t="inlineStr">
         <is>
           <t>Levha Özel Hattı (Hat 201)</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="23" t="inlineStr">
+      <c r="A28" s="24" t="inlineStr">
         <is>
           <t>U KAPAMA</t>
         </is>
       </c>
-      <c r="B28" s="24" t="inlineStr">
+      <c r="B28" s="25" t="inlineStr">
         <is>
           <t>U Kapama / Lambiri</t>
         </is>
@@ -3465,96 +3396,93 @@
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="D28" s="24" t="inlineStr">
+      <c r="D28" s="25" t="inlineStr">
         <is>
           <t>30 x 15 mm</t>
         </is>
       </c>
-      <c r="E28" s="25" t="inlineStr">
+      <c r="E28" s="26" t="inlineStr">
         <is>
           <t>0.48 kg/boy</t>
         </is>
       </c>
-      <c r="F28" s="26" t="n">
+      <c r="F28" s="27" t="n">
         <v>1385</v>
       </c>
-      <c r="G28" s="27" t="inlineStr">
+      <c r="G28" s="28" t="inlineStr">
         <is>
           <t>Hat 102</t>
         </is>
       </c>
-      <c r="H28" s="32" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="I28" s="28" t="n">
+      <c r="H28" s="33" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="I28" s="29" t="n">
         <v>34</v>
       </c>
-      <c r="J28" s="29" t="n">
+      <c r="J28" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="K28" s="30" t="n">
+      <c r="K28" s="31" t="n">
         <v>40.7</v>
       </c>
-      <c r="L28" s="31" t="inlineStr">
+      <c r="L28" s="32" t="inlineStr">
         <is>
           <t>Saatte ~85 Boy</t>
         </is>
       </c>
-      <c r="M28" s="26" t="n">
+      <c r="M28" s="27" t="n">
         <v>976.8</v>
       </c>
-      <c r="N28" s="28" t="n">
+      <c r="N28" s="29" t="n">
         <v>40.7</v>
       </c>
-      <c r="O28" s="32" t="inlineStr">
+      <c r="O28" s="33" t="inlineStr">
         <is>
           <t>Saatte ~85 Boy</t>
         </is>
       </c>
-      <c r="P28" s="33" t="n">
+      <c r="P28" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="Q28" s="29" t="n">
-        <v>40</v>
-      </c>
-      <c r="R28" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S28" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T28" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U28" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V28" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W28" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X28" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y28" s="24" t="inlineStr">
+      <c r="Q28" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R28" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S28" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T28" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U28" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V28" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W28" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X28" s="25" t="inlineStr">
         <is>
           <t>Tek Hat Atamalı</t>
         </is>
@@ -3627,15 +3555,17 @@
       <c r="P29" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="Q29" s="15" t="n">
-        <v>40</v>
-      </c>
-      <c r="R29" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S29" s="18" t="inlineStr">
+      <c r="Q29" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R29" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3645,39 +3575,34 @@
           <t>—</t>
         </is>
       </c>
-      <c r="U29" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V29" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W29" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X29" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y29" s="8" t="inlineStr">
+      <c r="U29" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V29" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W29" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X29" s="8" t="inlineStr">
         <is>
           <t>Tek Hat Atamalı</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="23" t="inlineStr">
+      <c r="A30" s="24" t="inlineStr">
         <is>
           <t>KT102-219x26-KAH</t>
         </is>
       </c>
-      <c r="B30" s="24" t="inlineStr">
+      <c r="B30" s="25" t="inlineStr">
         <is>
           <t>Deck / WPC Zemin</t>
         </is>
@@ -3687,147 +3612,143 @@
           <t>3.00 Metre</t>
         </is>
       </c>
-      <c r="D30" s="24" t="inlineStr">
+      <c r="D30" s="25" t="inlineStr">
         <is>
           <t>219 x 26 mm</t>
         </is>
       </c>
-      <c r="E30" s="25" t="inlineStr">
+      <c r="E30" s="26" t="inlineStr">
         <is>
           <t>9.26 kg/boy</t>
         </is>
       </c>
-      <c r="F30" s="26" t="n">
+      <c r="F30" s="27" t="n">
         <v>463</v>
       </c>
-      <c r="G30" s="27" t="inlineStr">
+      <c r="G30" s="28" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="H30" s="32" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="I30" s="28" t="n">
+      <c r="H30" s="33" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="I30" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="J30" s="29" t="n">
+      <c r="J30" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="K30" s="30" t="n">
+      <c r="K30" s="31" t="n">
         <v>115.8</v>
       </c>
-      <c r="L30" s="31" t="inlineStr">
+      <c r="L30" s="32" t="inlineStr">
         <is>
           <t>Saatte ~12 Boy</t>
         </is>
       </c>
-      <c r="M30" s="26" t="n">
+      <c r="M30" s="27" t="n">
         <v>2779.2</v>
       </c>
-      <c r="N30" s="28" t="n">
+      <c r="N30" s="29" t="n">
         <v>115.8</v>
       </c>
-      <c r="O30" s="32" t="inlineStr">
+      <c r="O30" s="33" t="inlineStr">
         <is>
           <t>Saatte ~12 Boy</t>
         </is>
       </c>
-      <c r="P30" s="33" t="n">
+      <c r="P30" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="Q30" s="29" t="n">
-        <v>45</v>
-      </c>
-      <c r="R30" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S30" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T30" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U30" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V30" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W30" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X30" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y30" s="24" t="inlineStr">
+      <c r="Q30" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R30" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S30" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T30" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U30" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V30" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W30" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X30" s="25" t="inlineStr">
         <is>
           <t>Tek Hat Atamalı</t>
         </is>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="39" t="inlineStr">
+      <c r="A31" s="41" t="inlineStr">
         <is>
           <t>GENEL TOPLAM / FABRİKA</t>
         </is>
       </c>
-      <c r="B31" s="40" t="n"/>
-      <c r="C31" s="40" t="n"/>
-      <c r="D31" s="40" t="n"/>
-      <c r="E31" s="40" t="n"/>
-      <c r="F31" s="41" t="n">
-        <v>1252309.48</v>
-      </c>
-      <c r="G31" s="40" t="n"/>
-      <c r="H31" s="40" t="n"/>
-      <c r="I31" s="42" t="n">
-        <v>10980.7</v>
-      </c>
-      <c r="J31" s="40" t="n"/>
-      <c r="K31" s="40" t="n"/>
-      <c r="L31" s="40" t="n"/>
-      <c r="M31" s="40" t="n"/>
-      <c r="N31" s="40" t="n"/>
-      <c r="O31" s="40" t="n"/>
-      <c r="P31" s="40" t="n"/>
-      <c r="Q31" s="40" t="n"/>
-      <c r="R31" s="40" t="n"/>
-      <c r="S31" s="40" t="n"/>
-      <c r="T31" s="42" t="n">
-        <v>4484.7</v>
-      </c>
-      <c r="U31" s="40" t="n"/>
-      <c r="V31" s="40" t="n"/>
-      <c r="W31" s="40" t="n"/>
-      <c r="X31" s="40" t="n"/>
-      <c r="Y31" s="40" t="n"/>
+      <c r="B31" s="42" t="n"/>
+      <c r="C31" s="42" t="n"/>
+      <c r="D31" s="42" t="n"/>
+      <c r="E31" s="42" t="n"/>
+      <c r="F31" s="43" t="n">
+        <v>1266753.58</v>
+      </c>
+      <c r="G31" s="42" t="n"/>
+      <c r="H31" s="42" t="n"/>
+      <c r="I31" s="44" t="n">
+        <v>11092.7</v>
+      </c>
+      <c r="J31" s="42" t="n"/>
+      <c r="K31" s="42" t="n"/>
+      <c r="L31" s="42" t="n"/>
+      <c r="M31" s="42" t="n"/>
+      <c r="N31" s="42" t="n"/>
+      <c r="O31" s="42" t="n"/>
+      <c r="P31" s="42" t="n"/>
+      <c r="Q31" s="42" t="n"/>
+      <c r="R31" s="42" t="n"/>
+      <c r="S31" s="42" t="n"/>
+      <c r="T31" s="44" t="n">
+        <v>4532.7</v>
+      </c>
+      <c r="U31" s="42" t="n"/>
+      <c r="V31" s="42" t="n"/>
+      <c r="W31" s="42" t="n"/>
+      <c r="X31" s="42" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="G3:Q3"/>
+    <mergeCell ref="W3"/>
     <mergeCell ref="X3"/>
-    <mergeCell ref="A2:Y2"/>
-    <mergeCell ref="R3:W3"/>
-    <mergeCell ref="A1:Y1"/>
-    <mergeCell ref="Y3"/>
+    <mergeCell ref="A2:X2"/>
+    <mergeCell ref="G3:P3"/>
+    <mergeCell ref="A1:X1"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="Q3:V3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3927,54 +3848,54 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="45" t="inlineStr">
         <is>
           <t>Hat 101</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Pervaz Ekstrüder 1</t>
         </is>
       </c>
-      <c r="C4" s="24" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>Profil Ekstrüzyon</t>
         </is>
       </c>
-      <c r="D4" s="28" t="n">
+      <c r="D4" s="29" t="n">
         <v>744.5</v>
       </c>
-      <c r="E4" s="29" t="n">
+      <c r="E4" s="30" t="n">
         <v>70</v>
       </c>
-      <c r="F4" s="26" t="n">
+      <c r="F4" s="27" t="n">
         <v>33805</v>
       </c>
-      <c r="G4" s="30" t="n">
+      <c r="G4" s="31" t="n">
         <v>45.4</v>
       </c>
-      <c r="H4" s="44" t="n">
+      <c r="H4" s="46" t="n">
         <v>4</v>
       </c>
-      <c r="I4" s="27" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="J4" s="24" t="inlineStr">
+      <c r="I4" s="28" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="J4" s="25" t="inlineStr">
         <is>
           <t>Pervazlar (35x100, 35x150, 80x80)</t>
         </is>
       </c>
-      <c r="K4" s="27" t="inlineStr">
+      <c r="K4" s="28" t="inlineStr">
         <is>
           <t>Aktif Üretimde</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="45" t="inlineStr">
+      <c r="A5" s="47" t="inlineStr">
         <is>
           <t>Hat 102</t>
         </is>
@@ -3990,18 +3911,18 @@
         </is>
       </c>
       <c r="D5" s="14" t="n">
-        <v>1560.1</v>
+        <v>1584.1</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>95369</v>
+        <v>96990</v>
       </c>
       <c r="G5" s="16" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="H5" s="46" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="H5" s="48" t="n">
         <v>4</v>
       </c>
       <c r="I5" s="12" t="inlineStr">
@@ -4021,54 +3942,54 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="45" t="inlineStr">
         <is>
           <t>Hat 103</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Pervaz &amp; Seren Ekstrüder 3</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="25" t="inlineStr">
         <is>
           <t>Profil Ekstrüzyon</t>
         </is>
       </c>
-      <c r="D6" s="28" t="n">
-        <v>1433</v>
-      </c>
-      <c r="E6" s="29" t="n">
-        <v>130</v>
-      </c>
-      <c r="F6" s="26" t="n">
-        <v>75496</v>
-      </c>
-      <c r="G6" s="30" t="n">
-        <v>52.7</v>
-      </c>
-      <c r="H6" s="44" t="n">
+      <c r="D6" s="29" t="n">
+        <v>1457</v>
+      </c>
+      <c r="E6" s="30" t="n">
+        <v>132</v>
+      </c>
+      <c r="F6" s="27" t="n">
+        <v>76929</v>
+      </c>
+      <c r="G6" s="31" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="H6" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="I6" s="27" t="inlineStr">
+      <c r="I6" s="28" t="inlineStr">
         <is>
           <t>Tek Göz &amp; Çift Göz (2 Kafa)</t>
         </is>
       </c>
-      <c r="J6" s="24" t="inlineStr">
+      <c r="J6" s="25" t="inlineStr">
         <is>
           <t>50x80 Pervaz (Çift Göz), Seren</t>
         </is>
       </c>
-      <c r="K6" s="27" t="inlineStr">
+      <c r="K6" s="28" t="inlineStr">
         <is>
           <t>Aktif Üretimde</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="45" t="inlineStr">
+      <c r="A7" s="47" t="inlineStr">
         <is>
           <t>Hat 104</t>
         </is>
@@ -4084,18 +4005,18 @@
         </is>
       </c>
       <c r="D7" s="14" t="n">
-        <v>1622.4</v>
+        <v>1646.4</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>157051.32</v>
+        <v>158335.32</v>
       </c>
       <c r="G7" s="16" t="n">
-        <v>96.8</v>
-      </c>
-      <c r="H7" s="46" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="H7" s="48" t="n">
         <v>1</v>
       </c>
       <c r="I7" s="12" t="inlineStr">
@@ -4115,54 +4036,54 @@
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="43" t="inlineStr">
+      <c r="A8" s="45" t="inlineStr">
         <is>
           <t>Hat 105</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Yüksek Hızlı Seren Ekstrüder 5</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>Profil Ekstrüzyon</t>
         </is>
       </c>
-      <c r="D8" s="28" t="n">
+      <c r="D8" s="29" t="n">
         <v>1514.5</v>
       </c>
-      <c r="E8" s="29" t="n">
+      <c r="E8" s="30" t="n">
         <v>136</v>
       </c>
-      <c r="F8" s="26" t="n">
+      <c r="F8" s="27" t="n">
         <v>137521.47</v>
       </c>
-      <c r="G8" s="30" t="n">
+      <c r="G8" s="31" t="n">
         <v>90.8</v>
       </c>
-      <c r="H8" s="44" t="n">
+      <c r="H8" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="I8" s="27" t="inlineStr">
+      <c r="I8" s="28" t="inlineStr">
         <is>
           <t>Tek Göz &amp; Çift Göz (2 Kafa)</t>
         </is>
       </c>
-      <c r="J8" s="24" t="inlineStr">
+      <c r="J8" s="25" t="inlineStr">
         <is>
           <t>Masif Kapı Sereni (Çift Göz Ağırlıklı)</t>
         </is>
       </c>
-      <c r="K8" s="27" t="inlineStr">
+      <c r="K8" s="28" t="inlineStr">
         <is>
           <t>Aktif Üretimde</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="45" t="inlineStr">
+      <c r="A9" s="47" t="inlineStr">
         <is>
           <t>Hat 106</t>
         </is>
@@ -4178,248 +4099,248 @@
         </is>
       </c>
       <c r="D9" s="14" t="n">
-        <v>1621.3</v>
+        <v>1645.3</v>
       </c>
       <c r="E9" s="15" t="n">
+        <v>147</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>118886</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="H9" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>140 mm Kasa, 200 mm Kasa</t>
+        </is>
+      </c>
+      <c r="K9" s="12" t="inlineStr">
+        <is>
+          <t>Aktif Üretimde</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="45" t="inlineStr">
+        <is>
+          <t>Hat 107</t>
+        </is>
+      </c>
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t>Geniş Kasa &amp; Deck Ekstrüder 7</t>
+        </is>
+      </c>
+      <c r="C10" s="25" t="inlineStr">
+        <is>
+          <t>Profil Ekstrüzyon</t>
+        </is>
+      </c>
+      <c r="D10" s="29" t="n">
+        <v>1593.7</v>
+      </c>
+      <c r="E10" s="30" t="n">
+        <v>155</v>
+      </c>
+      <c r="F10" s="27" t="n">
+        <v>143176</v>
+      </c>
+      <c r="G10" s="31" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="H10" s="46" t="n">
+        <v>8</v>
+      </c>
+      <c r="I10" s="28" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="J10" s="25" t="inlineStr">
+        <is>
+          <t>200 mm Kasa, Zemin Deck (KT100/102)</t>
+        </is>
+      </c>
+      <c r="K10" s="28" t="inlineStr">
+        <is>
+          <t>Aktif Üretimde</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="47" t="inlineStr">
+        <is>
+          <t>Hat 108</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Kasa Ekstrüder 8</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Profil Ekstrüzyon</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>1573.2</v>
+      </c>
+      <c r="E11" s="15" t="n">
         <v>144</v>
       </c>
-      <c r="F9" s="11" t="n">
-        <v>117509</v>
-      </c>
-      <c r="G9" s="16" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="H9" s="46" t="n">
+      <c r="F11" s="11" t="n">
+        <v>104613.8</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="H11" s="48" t="n">
         <v>3</v>
       </c>
-      <c r="I9" s="12" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="J9" s="8" t="inlineStr">
-        <is>
-          <t>140 mm Kasa, 200 mm Kasa</t>
-        </is>
-      </c>
-      <c r="K9" s="12" t="inlineStr">
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>100 mm &amp; 140 mm Kasa</t>
+        </is>
+      </c>
+      <c r="K11" s="12" t="inlineStr">
         <is>
           <t>Aktif Üretimde</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="43" t="inlineStr">
-        <is>
-          <t>Hat 107</t>
-        </is>
-      </c>
-      <c r="B10" s="24" t="inlineStr">
-        <is>
-          <t>Geniş Kasa &amp; Deck Ekstrüder 7</t>
-        </is>
-      </c>
-      <c r="C10" s="24" t="inlineStr">
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="45" t="inlineStr">
+        <is>
+          <t>Hat 109</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>Yüksek Hızlı Pervaz Ekstrüder 9</t>
+        </is>
+      </c>
+      <c r="C12" s="25" t="inlineStr">
         <is>
           <t>Profil Ekstrüzyon</t>
         </is>
       </c>
-      <c r="D10" s="28" t="n">
-        <v>1569.7</v>
-      </c>
-      <c r="E10" s="29" t="n">
+      <c r="D12" s="29" t="n">
+        <v>1574.2</v>
+      </c>
+      <c r="E12" s="30" t="n">
         <v>153</v>
       </c>
-      <c r="F10" s="26" t="n">
-        <v>140925</v>
-      </c>
-      <c r="G10" s="30" t="n">
-        <v>89.8</v>
-      </c>
-      <c r="H10" s="44" t="n">
-        <v>8</v>
-      </c>
-      <c r="I10" s="27" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="J10" s="24" t="inlineStr">
-        <is>
-          <t>200 mm Kasa, Zemin Deck (KT100/102)</t>
-        </is>
-      </c>
-      <c r="K10" s="27" t="inlineStr">
+      <c r="F12" s="27" t="n">
+        <v>115763.31</v>
+      </c>
+      <c r="G12" s="31" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="H12" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="28" t="inlineStr">
+        <is>
+          <t>Tek Göz &amp; Çift Göz (2 Kafa)</t>
+        </is>
+      </c>
+      <c r="J12" s="25" t="inlineStr">
+        <is>
+          <t>50x80 Pervaz (Çift Göz), 80x80 Pervaz</t>
+        </is>
+      </c>
+      <c r="K12" s="28" t="inlineStr">
         <is>
           <t>Aktif Üretimde</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="45" t="inlineStr">
-        <is>
-          <t>Hat 108</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Kasa Ekstrüder 8</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Profil Ekstrüzyon</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="n">
-        <v>1549.2</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>141</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>103140.8</v>
-      </c>
-      <c r="G11" s="16" t="n">
-        <v>66.59999999999999</v>
-      </c>
-      <c r="H11" s="46" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" s="12" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="J11" s="8" t="inlineStr">
-        <is>
-          <t>100 mm &amp; 140 mm Kasa</t>
-        </is>
-      </c>
-      <c r="K11" s="12" t="inlineStr">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="47" t="inlineStr">
+        <is>
+          <t>Hat 201</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>WPC Levha Makinesi 1</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Levha Ekstrüzyon</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>2762.5</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>252</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>280733.6800000001</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="H13" s="48" t="n">
+        <v>11</v>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>Levha Kalıbı (Tek Kafa)</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>WPC Kapı Yüzey Levhaları (Tüm Renkler)</t>
+        </is>
+      </c>
+      <c r="K13" s="12" t="inlineStr">
         <is>
           <t>Aktif Üretimde</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="43" t="inlineStr">
-        <is>
-          <t>Hat 109</t>
-        </is>
-      </c>
-      <c r="B12" s="24" t="inlineStr">
-        <is>
-          <t>Yüksek Hızlı Pervaz Ekstrüder 9</t>
-        </is>
-      </c>
-      <c r="C12" s="24" t="inlineStr">
-        <is>
-          <t>Profil Ekstrüzyon</t>
-        </is>
-      </c>
-      <c r="D12" s="28" t="n">
-        <v>1550.2</v>
-      </c>
-      <c r="E12" s="29" t="n">
-        <v>151</v>
-      </c>
-      <c r="F12" s="26" t="n">
-        <v>114358.31</v>
-      </c>
-      <c r="G12" s="30" t="n">
-        <v>73.8</v>
-      </c>
-      <c r="H12" s="44" t="n">
-        <v>2</v>
-      </c>
-      <c r="I12" s="27" t="inlineStr">
-        <is>
-          <t>Tek Göz &amp; Çift Göz (2 Kafa)</t>
-        </is>
-      </c>
-      <c r="J12" s="24" t="inlineStr">
-        <is>
-          <t>50x80 Pervaz (Çift Göz), 80x80 Pervaz</t>
-        </is>
-      </c>
-      <c r="K12" s="27" t="inlineStr">
-        <is>
-          <t>Aktif Üretimde</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="45" t="inlineStr">
-        <is>
-          <t>Hat 201</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>WPC Levha Makinesi 1</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Levha Ekstrüzyon</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>2746.5</v>
-      </c>
-      <c r="E13" s="15" t="n">
-        <v>249</v>
-      </c>
-      <c r="F13" s="11" t="n">
-        <v>277133.5800000001</v>
-      </c>
-      <c r="G13" s="16" t="n">
-        <v>100.9</v>
-      </c>
-      <c r="H13" s="46" t="n">
-        <v>11</v>
-      </c>
-      <c r="I13" s="12" t="inlineStr">
-        <is>
-          <t>Levha Kalıbı (Tek Kafa)</t>
-        </is>
-      </c>
-      <c r="J13" s="8" t="inlineStr">
-        <is>
-          <t>WPC Kapı Yüzey Levhaları (Tüm Renkler)</t>
-        </is>
-      </c>
-      <c r="K13" s="12" t="inlineStr">
-        <is>
-          <t>Aktif Üretimde</t>
-        </is>
-      </c>
-    </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="47" t="inlineStr">
+      <c r="A14" s="49" t="inlineStr">
         <is>
           <t>GENEL TOPLAM (10 HAT)</t>
         </is>
       </c>
-      <c r="B14" s="40" t="n"/>
-      <c r="C14" s="40" t="n"/>
-      <c r="D14" s="42" t="n">
-        <v>15911.4</v>
-      </c>
-      <c r="E14" s="41" t="n">
-        <v>1461</v>
-      </c>
-      <c r="F14" s="41" t="n">
-        <v>1252309.48</v>
-      </c>
-      <c r="G14" s="42" t="n">
+      <c r="B14" s="42" t="n"/>
+      <c r="C14" s="42" t="n"/>
+      <c r="D14" s="44" t="n">
+        <v>16095.4</v>
+      </c>
+      <c r="E14" s="43" t="n">
+        <v>1480</v>
+      </c>
+      <c r="F14" s="43" t="n">
+        <v>1266753.58</v>
+      </c>
+      <c r="G14" s="44" t="n">
         <v>78.7</v>
       </c>
-      <c r="H14" s="40" t="n"/>
-      <c r="I14" s="40" t="n"/>
-      <c r="J14" s="40" t="n"/>
-      <c r="K14" s="40" t="n"/>
+      <c r="H14" s="42" t="n"/>
+      <c r="I14" s="42" t="n"/>
+      <c r="J14" s="42" t="n"/>
+      <c r="K14" s="42" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4548,12 +4469,12 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>SEREN</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Seren Çıtası</t>
         </is>
@@ -4563,12 +4484,12 @@
           <t>2.10 Metre</t>
         </is>
       </c>
-      <c r="D4" s="24" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>38 x 45 mm</t>
         </is>
       </c>
-      <c r="E4" s="43" t="inlineStr">
+      <c r="E4" s="45" t="inlineStr">
         <is>
           <t>Hat 104</t>
         </is>
@@ -4578,38 +4499,38 @@
           <t>Çift Göz (2 Kafa)</t>
         </is>
       </c>
-      <c r="G4" s="27" t="inlineStr">
+      <c r="G4" s="28" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="H4" s="28" t="n">
-        <v>1622.4</v>
-      </c>
-      <c r="I4" s="29" t="n">
-        <v>146</v>
-      </c>
-      <c r="J4" s="29" t="n">
-        <v>46047</v>
-      </c>
-      <c r="K4" s="25" t="inlineStr">
+      <c r="H4" s="29" t="n">
+        <v>1646.4</v>
+      </c>
+      <c r="I4" s="30" t="n">
+        <v>148</v>
+      </c>
+      <c r="J4" s="30" t="n">
+        <v>46427</v>
+      </c>
+      <c r="K4" s="26" t="inlineStr">
         <is>
           <t>3.39 kg/boy</t>
         </is>
       </c>
-      <c r="L4" s="26" t="n">
-        <v>157051.32</v>
-      </c>
-      <c r="M4" s="30" t="n">
-        <v>96.8</v>
-      </c>
-      <c r="N4" s="31" t="inlineStr">
+      <c r="L4" s="27" t="n">
+        <v>158335.32</v>
+      </c>
+      <c r="M4" s="31" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="N4" s="32" t="inlineStr">
         <is>
           <t>Saatte ~28 Boy</t>
         </is>
       </c>
-      <c r="O4" s="48" t="n">
-        <v>0.526852035394632</v>
+      <c r="O4" s="50" t="n">
+        <v>0.5288813174818345</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -4633,7 +4554,7 @@
           <t>38 x 45 mm</t>
         </is>
       </c>
-      <c r="E5" s="45" t="inlineStr">
+      <c r="E5" s="47" t="inlineStr">
         <is>
           <t>Hat 105</t>
         </is>
@@ -4673,17 +4594,17 @@
           <t>Saatte ~27 Boy</t>
         </is>
       </c>
-      <c r="O5" s="49" t="n">
-        <v>0.4589343172831611</v>
+      <c r="O5" s="51" t="n">
+        <v>0.4569659960413229</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>DİŞBUDAK Levha</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>WPC Levha Plaka</t>
         </is>
@@ -4693,52 +4614,52 @@
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E6" s="43" t="inlineStr">
+      <c r="E6" s="45" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="F6" s="32" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="G6" s="27" t="inlineStr">
+      <c r="F6" s="33" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="G6" s="28" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="H6" s="28" t="n">
-        <v>1204.5</v>
-      </c>
-      <c r="I6" s="29" t="n">
-        <v>82</v>
-      </c>
-      <c r="J6" s="29" t="n">
-        <v>25104</v>
-      </c>
-      <c r="K6" s="25" t="inlineStr">
+      <c r="H6" s="29" t="n">
+        <v>1218.5</v>
+      </c>
+      <c r="I6" s="30" t="n">
+        <v>84</v>
+      </c>
+      <c r="J6" s="30" t="n">
+        <v>25734</v>
+      </c>
+      <c r="K6" s="26" t="inlineStr">
         <is>
           <t>4.77 kg/plaka</t>
         </is>
       </c>
-      <c r="L6" s="26" t="n">
-        <v>119746.08</v>
-      </c>
-      <c r="M6" s="30" t="n">
-        <v>99.40000000000001</v>
-      </c>
-      <c r="N6" s="31" t="inlineStr">
+      <c r="L6" s="27" t="n">
+        <v>122751.18</v>
+      </c>
+      <c r="M6" s="31" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="N6" s="32" t="inlineStr">
         <is>
           <t>Saatte ~21 Plaka</t>
         </is>
       </c>
-      <c r="O6" s="48" t="n">
+      <c r="O6" s="50" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4763,7 +4684,7 @@
           <t>140 x 36 mm</t>
         </is>
       </c>
-      <c r="E7" s="45" t="inlineStr">
+      <c r="E7" s="47" t="inlineStr">
         <is>
           <t>Hat 106</t>
         </is>
@@ -4779,13 +4700,13 @@
         </is>
       </c>
       <c r="H7" s="14" t="n">
-        <v>1585.3</v>
+        <v>1609.3</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="J7" s="15" t="n">
-        <v>22355</v>
+        <v>22612</v>
       </c>
       <c r="K7" s="10" t="inlineStr">
         <is>
@@ -4793,27 +4714,27 @@
         </is>
       </c>
       <c r="L7" s="11" t="n">
-        <v>114247</v>
+        <v>115624</v>
       </c>
       <c r="M7" s="16" t="n">
-        <v>72.09999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="N7" s="17" t="inlineStr">
         <is>
           <t>Saatte ~14 Boy</t>
         </is>
       </c>
-      <c r="O7" s="49" t="n">
-        <v>0.6607883397437752</v>
+      <c r="O7" s="51" t="n">
+        <v>0.6573541869204573</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>50X80 PERVAZ</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Pervaz Profili</t>
         </is>
@@ -4823,12 +4744,12 @@
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="D8" s="24" t="inlineStr">
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>50 x 80 mm</t>
         </is>
       </c>
-      <c r="E8" s="43" t="inlineStr">
+      <c r="E8" s="45" t="inlineStr">
         <is>
           <t>Hat 109</t>
         </is>
@@ -4838,38 +4759,38 @@
           <t>Çift Göz (2 Kafa)</t>
         </is>
       </c>
-      <c r="G8" s="27" t="inlineStr">
+      <c r="G8" s="28" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="H8" s="28" t="n">
-        <v>1538.2</v>
-      </c>
-      <c r="I8" s="29" t="n">
-        <v>150</v>
-      </c>
-      <c r="J8" s="29" t="n">
-        <v>75716</v>
-      </c>
-      <c r="K8" s="25" t="inlineStr">
+      <c r="H8" s="29" t="n">
+        <v>1562.2</v>
+      </c>
+      <c r="I8" s="30" t="n">
+        <v>152</v>
+      </c>
+      <c r="J8" s="30" t="n">
+        <v>76681</v>
+      </c>
+      <c r="K8" s="26" t="inlineStr">
         <is>
           <t>1.55 kg/boy</t>
         </is>
       </c>
-      <c r="L8" s="26" t="n">
-        <v>113337.31</v>
-      </c>
-      <c r="M8" s="30" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="N8" s="31" t="inlineStr">
+      <c r="L8" s="27" t="n">
+        <v>114742.31</v>
+      </c>
+      <c r="M8" s="31" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="N8" s="32" t="inlineStr">
         <is>
           <t>Saatte ~49 Boy</t>
         </is>
       </c>
-      <c r="O8" s="48" t="n">
-        <v>0.6026230409833272</v>
+      <c r="O8" s="50" t="n">
+        <v>0.601024161428676</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -4893,7 +4814,7 @@
           <t>200 x 36 mm</t>
         </is>
       </c>
-      <c r="E9" s="45" t="inlineStr">
+      <c r="E9" s="47" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
@@ -4933,17 +4854,17 @@
           <t>Saatte ~12 Boy</t>
         </is>
       </c>
-      <c r="O9" s="49" t="n">
+      <c r="O9" s="51" t="n">
         <v>0.9470688044066297</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>50X80 PERVAZ</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>Pervaz Profili</t>
         </is>
@@ -4953,12 +4874,12 @@
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="D10" s="25" t="inlineStr">
         <is>
           <t>50 x 80 mm</t>
         </is>
       </c>
-      <c r="E10" s="43" t="inlineStr">
+      <c r="E10" s="45" t="inlineStr">
         <is>
           <t>Hat 103</t>
         </is>
@@ -4968,38 +4889,38 @@
           <t>Çift Göz (2 Kafa)</t>
         </is>
       </c>
-      <c r="G10" s="34" t="inlineStr">
+      <c r="G10" s="35" t="inlineStr">
         <is>
           <t>YEDEK ROTA 1</t>
         </is>
       </c>
-      <c r="H10" s="28" t="n">
-        <v>1421</v>
-      </c>
-      <c r="I10" s="29" t="n">
-        <v>129</v>
-      </c>
-      <c r="J10" s="29" t="n">
-        <v>45110</v>
-      </c>
-      <c r="K10" s="25" t="inlineStr">
+      <c r="H10" s="29" t="n">
+        <v>1445</v>
+      </c>
+      <c r="I10" s="30" t="n">
+        <v>131</v>
+      </c>
+      <c r="J10" s="30" t="n">
+        <v>45990</v>
+      </c>
+      <c r="K10" s="26" t="inlineStr">
         <is>
           <t>1.55 kg/boy</t>
         </is>
       </c>
-      <c r="L10" s="26" t="n">
-        <v>74736</v>
-      </c>
-      <c r="M10" s="30" t="n">
-        <v>52.6</v>
-      </c>
-      <c r="N10" s="31" t="inlineStr">
+      <c r="L10" s="27" t="n">
+        <v>76169</v>
+      </c>
+      <c r="M10" s="31" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="N10" s="32" t="inlineStr">
         <is>
           <t>Saatte ~32 Boy</t>
         </is>
       </c>
-      <c r="O10" s="48" t="n">
-        <v>0.3973769590166728</v>
+      <c r="O10" s="50" t="n">
+        <v>0.398975838571324</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -5023,7 +4944,7 @@
           <t>100 x 36 mm</t>
         </is>
       </c>
-      <c r="E11" s="45" t="inlineStr">
+      <c r="E11" s="47" t="inlineStr">
         <is>
           <t>Hat 102</t>
         </is>
@@ -5063,17 +4984,17 @@
           <t>Saatte ~16 Boy</t>
         </is>
       </c>
-      <c r="O11" s="49" t="n">
-        <v>0.511342853573251</v>
+      <c r="O11" s="51" t="n">
+        <v>0.5057361575932257</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t>100 mm KASA</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Kasa Profili</t>
         </is>
@@ -5083,53 +5004,53 @@
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="D12" s="24" t="inlineStr">
+      <c r="D12" s="25" t="inlineStr">
         <is>
           <t>100 x 36 mm</t>
         </is>
       </c>
-      <c r="E12" s="43" t="inlineStr">
+      <c r="E12" s="45" t="inlineStr">
         <is>
           <t>Hat 108</t>
         </is>
       </c>
-      <c r="F12" s="32" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="G12" s="34" t="inlineStr">
+      <c r="F12" s="33" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="G12" s="35" t="inlineStr">
         <is>
           <t>YEDEK ROTA 1</t>
         </is>
       </c>
-      <c r="H12" s="28" t="n">
-        <v>935</v>
-      </c>
-      <c r="I12" s="29" t="n">
-        <v>86</v>
-      </c>
-      <c r="J12" s="29" t="n">
-        <v>16287</v>
-      </c>
-      <c r="K12" s="25" t="inlineStr">
+      <c r="H12" s="29" t="n">
+        <v>959</v>
+      </c>
+      <c r="I12" s="30" t="n">
+        <v>89</v>
+      </c>
+      <c r="J12" s="30" t="n">
+        <v>16653</v>
+      </c>
+      <c r="K12" s="26" t="inlineStr">
         <is>
           <t>4.00 kg/boy</t>
         </is>
       </c>
-      <c r="L12" s="26" t="n">
-        <v>62932.8</v>
-      </c>
-      <c r="M12" s="30" t="n">
-        <v>67.3</v>
-      </c>
-      <c r="N12" s="31" t="inlineStr">
+      <c r="L12" s="27" t="n">
+        <v>64405.8</v>
+      </c>
+      <c r="M12" s="31" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="N12" s="32" t="inlineStr">
         <is>
           <t>Saatte ~17 Boy</t>
         </is>
       </c>
-      <c r="O12" s="48" t="n">
-        <v>0.4736497480954754</v>
+      <c r="O12" s="50" t="n">
+        <v>0.4794209949620667</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -5153,7 +5074,7 @@
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E13" s="45" t="inlineStr">
+      <c r="E13" s="47" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
@@ -5193,17 +5114,17 @@
           <t>Saatte ~27 Plaka</t>
         </is>
       </c>
-      <c r="O13" s="49" t="n">
+      <c r="O13" s="51" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>140 mm KASA</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>Kasa Profili</t>
         </is>
@@ -5213,59 +5134,59 @@
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="D14" s="24" t="inlineStr">
+      <c r="D14" s="25" t="inlineStr">
         <is>
           <t>140 x 36 mm</t>
         </is>
       </c>
-      <c r="E14" s="43" t="inlineStr">
+      <c r="E14" s="45" t="inlineStr">
         <is>
           <t>Hat 108</t>
         </is>
       </c>
-      <c r="F14" s="32" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="G14" s="34" t="inlineStr">
+      <c r="F14" s="33" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="G14" s="35" t="inlineStr">
         <is>
           <t>YEDEK ROTA 1</t>
         </is>
       </c>
-      <c r="H14" s="28" t="n">
+      <c r="H14" s="29" t="n">
         <v>590.2</v>
       </c>
-      <c r="I14" s="29" t="n">
+      <c r="I14" s="30" t="n">
         <v>53</v>
       </c>
-      <c r="J14" s="29" t="n">
+      <c r="J14" s="30" t="n">
         <v>8661</v>
       </c>
-      <c r="K14" s="25" t="inlineStr">
+      <c r="K14" s="26" t="inlineStr">
         <is>
           <t>4.95 kg/boy</t>
         </is>
       </c>
-      <c r="L14" s="26" t="n">
+      <c r="L14" s="27" t="n">
         <v>38324</v>
       </c>
-      <c r="M14" s="30" t="n">
+      <c r="M14" s="31" t="n">
         <v>64.90000000000001</v>
       </c>
-      <c r="N14" s="31" t="inlineStr">
+      <c r="N14" s="32" t="inlineStr">
         <is>
           <t>Saatte ~15 Boy</t>
         </is>
       </c>
-      <c r="O14" s="48" t="n">
-        <v>0.2216605454177391</v>
+      <c r="O14" s="50" t="n">
+        <v>0.2178824626335329</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>BEYAZ TEAK Levha</t>
+          <t>MIX TEAK Levha</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -5283,7 +5204,7 @@
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E15" s="45" t="inlineStr">
+      <c r="E15" s="47" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
@@ -5299,123 +5220,123 @@
         </is>
       </c>
       <c r="H15" s="14" t="n">
-        <v>260</v>
+        <v>343</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>7270</v>
+        <v>7675</v>
       </c>
       <c r="K15" s="10" t="inlineStr">
         <is>
-          <t>4.41 kg/plaka</t>
+          <t>4.25 kg/plaka</t>
         </is>
       </c>
       <c r="L15" s="11" t="n">
-        <v>32060.7</v>
+        <v>32618.75</v>
       </c>
       <c r="M15" s="16" t="n">
-        <v>123.3</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="N15" s="17" t="inlineStr">
         <is>
-          <t>Saatte ~28 Plaka</t>
-        </is>
-      </c>
-      <c r="O15" s="49" t="n">
+          <t>Saatte ~22 Plaka</t>
+        </is>
+      </c>
+      <c r="O15" s="51" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="23" t="inlineStr">
-        <is>
-          <t>MIX TEAK Levha</t>
-        </is>
-      </c>
-      <c r="B16" s="24" t="inlineStr">
-        <is>
-          <t>WPC Levha Plaka</t>
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>SEREN(39mm)</t>
+        </is>
+      </c>
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>Seren Çıtası</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>207 cm (2.07 m)</t>
-        </is>
-      </c>
-      <c r="D16" s="24" t="inlineStr">
-        <is>
-          <t>En: 94 cm (2 mm)</t>
-        </is>
-      </c>
-      <c r="E16" s="43" t="inlineStr">
-        <is>
-          <t>Hat 201</t>
-        </is>
-      </c>
-      <c r="F16" s="32" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="G16" s="27" t="inlineStr">
+          <t>2.10 Metre</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>39 x 45 mm</t>
+        </is>
+      </c>
+      <c r="E16" s="45" t="inlineStr">
+        <is>
+          <t>Hat 107</t>
+        </is>
+      </c>
+      <c r="F16" s="33" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="G16" s="28" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="H16" s="28" t="n">
-        <v>341</v>
-      </c>
-      <c r="I16" s="29" t="n">
-        <v>30</v>
-      </c>
-      <c r="J16" s="29" t="n">
-        <v>7535</v>
-      </c>
-      <c r="K16" s="25" t="inlineStr">
-        <is>
-          <t>4.25 kg/plaka</t>
-        </is>
-      </c>
-      <c r="L16" s="26" t="n">
-        <v>32023.75</v>
-      </c>
-      <c r="M16" s="30" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="N16" s="31" t="inlineStr">
-        <is>
-          <t>Saatte ~22 Plaka</t>
-        </is>
-      </c>
-      <c r="O16" s="48" t="n">
+      <c r="H16" s="29" t="n">
+        <v>303</v>
+      </c>
+      <c r="I16" s="30" t="n">
+        <v>27</v>
+      </c>
+      <c r="J16" s="30" t="n">
+        <v>8583</v>
+      </c>
+      <c r="K16" s="26" t="inlineStr">
+        <is>
+          <t>3.81 kg/boy</t>
+        </is>
+      </c>
+      <c r="L16" s="27" t="n">
+        <v>32593</v>
+      </c>
+      <c r="M16" s="31" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="N16" s="32" t="inlineStr">
+        <is>
+          <t>Saatte ~28 Boy</t>
+        </is>
+      </c>
+      <c r="O16" s="50" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>SEREN(39mm)</t>
+          <t>BEYAZ TEAK Levha</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Seren Çıtası</t>
+          <t>WPC Levha Plaka</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>2.10 Metre</t>
+          <t>207 cm (2.07 m)</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>39 x 45 mm</t>
-        </is>
-      </c>
-      <c r="E17" s="45" t="inlineStr">
-        <is>
-          <t>Hat 107</t>
+          <t>En: 94 cm (2 mm)</t>
+        </is>
+      </c>
+      <c r="E17" s="47" t="inlineStr">
+        <is>
+          <t>Hat 201</t>
         </is>
       </c>
       <c r="F17" s="18" t="inlineStr">
@@ -5429,123 +5350,123 @@
         </is>
       </c>
       <c r="H17" s="14" t="n">
-        <v>279</v>
+        <v>260</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>7938</v>
+        <v>7270</v>
       </c>
       <c r="K17" s="10" t="inlineStr">
         <is>
-          <t>3.81 kg/boy</t>
+          <t>4.41 kg/plaka</t>
         </is>
       </c>
       <c r="L17" s="11" t="n">
-        <v>30342</v>
+        <v>32060.7</v>
       </c>
       <c r="M17" s="16" t="n">
-        <v>108.8</v>
+        <v>123.3</v>
       </c>
       <c r="N17" s="17" t="inlineStr">
         <is>
-          <t>Saatte ~28 Boy</t>
-        </is>
-      </c>
-      <c r="O17" s="49" t="n">
+          <t>Saatte ~28 Plaka</t>
+        </is>
+      </c>
+      <c r="O17" s="51" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="23" t="inlineStr">
-        <is>
-          <t>VIZON Levha</t>
-        </is>
-      </c>
-      <c r="B18" s="24" t="inlineStr">
-        <is>
-          <t>WPC Levha Plaka</t>
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>140 mm KASA</t>
+        </is>
+      </c>
+      <c r="B18" s="25" t="inlineStr">
+        <is>
+          <t>Kasa Profili</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>207 cm (2.07 m)</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
-        <is>
-          <t>En: 94 cm (2 mm)</t>
-        </is>
-      </c>
-      <c r="E18" s="43" t="inlineStr">
-        <is>
-          <t>Hat 201</t>
-        </is>
-      </c>
-      <c r="F18" s="32" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="G18" s="27" t="inlineStr">
-        <is>
-          <t>ANA ROTA</t>
-        </is>
-      </c>
-      <c r="H18" s="28" t="n">
-        <v>193</v>
-      </c>
-      <c r="I18" s="29" t="n">
-        <v>22</v>
-      </c>
-      <c r="J18" s="29" t="n">
-        <v>3850</v>
-      </c>
-      <c r="K18" s="25" t="inlineStr">
-        <is>
-          <t>4.77 kg/plaka</t>
-        </is>
-      </c>
-      <c r="L18" s="26" t="n">
-        <v>18364.5</v>
-      </c>
-      <c r="M18" s="30" t="n">
-        <v>95.2</v>
-      </c>
-      <c r="N18" s="31" t="inlineStr">
-        <is>
-          <t>Saatte ~20 Plaka</t>
-        </is>
-      </c>
-      <c r="O18" s="48" t="n">
-        <v>1</v>
+          <t>2.15 Metre (215 cm)</t>
+        </is>
+      </c>
+      <c r="D18" s="25" t="inlineStr">
+        <is>
+          <t>140 x 36 mm</t>
+        </is>
+      </c>
+      <c r="E18" s="45" t="inlineStr">
+        <is>
+          <t>Hat 102</t>
+        </is>
+      </c>
+      <c r="F18" s="33" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="G18" s="35" t="inlineStr">
+        <is>
+          <t>YEDEK ROTA 2</t>
+        </is>
+      </c>
+      <c r="H18" s="29" t="n">
+        <v>326</v>
+      </c>
+      <c r="I18" s="30" t="n">
+        <v>30</v>
+      </c>
+      <c r="J18" s="30" t="n">
+        <v>3611</v>
+      </c>
+      <c r="K18" s="26" t="inlineStr">
+        <is>
+          <t>4.95 kg/boy</t>
+        </is>
+      </c>
+      <c r="L18" s="27" t="n">
+        <v>19859</v>
+      </c>
+      <c r="M18" s="31" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="N18" s="32" t="inlineStr">
+        <is>
+          <t>Saatte ~11 Boy</t>
+        </is>
+      </c>
+      <c r="O18" s="50" t="n">
+        <v>0.1129038676922902</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>140 mm KASA</t>
+          <t>VIZON Levha</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Kasa Profili</t>
+          <t>WPC Levha Plaka</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>2.15 Metre (215 cm)</t>
+          <t>207 cm (2.07 m)</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>140 x 36 mm</t>
-        </is>
-      </c>
-      <c r="E19" s="45" t="inlineStr">
-        <is>
-          <t>Hat 102</t>
+          <t>En: 94 cm (2 mm)</t>
+        </is>
+      </c>
+      <c r="E19" s="47" t="inlineStr">
+        <is>
+          <t>Hat 201</t>
         </is>
       </c>
       <c r="F19" s="18" t="inlineStr">
@@ -5553,47 +5474,47 @@
           <t>Tek Göz (1 Kafa)</t>
         </is>
       </c>
-      <c r="G19" s="20" t="inlineStr">
-        <is>
-          <t>YEDEK ROTA 2</t>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>ANA ROTA</t>
         </is>
       </c>
       <c r="H19" s="14" t="n">
-        <v>302</v>
+        <v>193</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>3301</v>
+        <v>3850</v>
       </c>
       <c r="K19" s="10" t="inlineStr">
         <is>
-          <t>4.95 kg/boy</t>
+          <t>4.77 kg/plaka</t>
         </is>
       </c>
       <c r="L19" s="11" t="n">
-        <v>18238</v>
+        <v>18364.5</v>
       </c>
       <c r="M19" s="16" t="n">
-        <v>60.4</v>
+        <v>95.2</v>
       </c>
       <c r="N19" s="17" t="inlineStr">
         <is>
-          <t>Saatte ~11 Boy</t>
-        </is>
-      </c>
-      <c r="O19" s="49" t="n">
-        <v>0.1054859886058012</v>
+          <t>Saatte ~20 Plaka</t>
+        </is>
+      </c>
+      <c r="O19" s="51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="23" t="inlineStr">
+      <c r="A20" s="24" t="inlineStr">
         <is>
           <t>KT100-220x24-ANT</t>
         </is>
       </c>
-      <c r="B20" s="24" t="inlineStr">
+      <c r="B20" s="25" t="inlineStr">
         <is>
           <t>Deck / WPC Zemin</t>
         </is>
@@ -5603,52 +5524,52 @@
           <t>3.00 Metre</t>
         </is>
       </c>
-      <c r="D20" s="24" t="inlineStr">
+      <c r="D20" s="25" t="inlineStr">
         <is>
           <t>220 x 24 mm</t>
         </is>
       </c>
-      <c r="E20" s="43" t="inlineStr">
+      <c r="E20" s="45" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="F20" s="32" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="G20" s="27" t="inlineStr">
+      <c r="F20" s="33" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="G20" s="28" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="H20" s="28" t="n">
+      <c r="H20" s="29" t="n">
         <v>205.7</v>
       </c>
-      <c r="I20" s="29" t="n">
+      <c r="I20" s="30" t="n">
         <v>23</v>
       </c>
-      <c r="J20" s="29" t="n">
+      <c r="J20" s="30" t="n">
         <v>1712</v>
       </c>
-      <c r="K20" s="25" t="inlineStr">
+      <c r="K20" s="26" t="inlineStr">
         <is>
           <t>10.33 kg/boy</t>
         </is>
       </c>
-      <c r="L20" s="26" t="n">
+      <c r="L20" s="27" t="n">
         <v>17678</v>
       </c>
-      <c r="M20" s="30" t="n">
+      <c r="M20" s="31" t="n">
         <v>85.90000000000001</v>
       </c>
-      <c r="N20" s="31" t="inlineStr">
+      <c r="N20" s="32" t="inlineStr">
         <is>
           <t>Saatte ~8 Boy</t>
         </is>
       </c>
-      <c r="O20" s="48" t="n">
+      <c r="O20" s="50" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5673,7 +5594,7 @@
           <t>80 x 80 mm</t>
         </is>
       </c>
-      <c r="E21" s="45" t="inlineStr">
+      <c r="E21" s="47" t="inlineStr">
         <is>
           <t>Hat 101</t>
         </is>
@@ -5713,17 +5634,17 @@
           <t>Saatte ~22 Boy</t>
         </is>
       </c>
-      <c r="O21" s="49" t="n">
+      <c r="O21" s="51" t="n">
         <v>0.928795592440198</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="23" t="inlineStr">
+      <c r="A22" s="24" t="inlineStr">
         <is>
           <t>35X100 PERVAZ</t>
         </is>
       </c>
-      <c r="B22" s="24" t="inlineStr">
+      <c r="B22" s="25" t="inlineStr">
         <is>
           <t>Pervaz Profili</t>
         </is>
@@ -5733,52 +5654,52 @@
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="D22" s="24" t="inlineStr">
+      <c r="D22" s="25" t="inlineStr">
         <is>
           <t>35 x 100 mm</t>
         </is>
       </c>
-      <c r="E22" s="43" t="inlineStr">
+      <c r="E22" s="45" t="inlineStr">
         <is>
           <t>Hat 101</t>
         </is>
       </c>
-      <c r="F22" s="32" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="G22" s="27" t="inlineStr">
+      <c r="F22" s="33" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="G22" s="28" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="H22" s="28" t="n">
+      <c r="H22" s="29" t="n">
         <v>241</v>
       </c>
-      <c r="I22" s="29" t="n">
+      <c r="I22" s="30" t="n">
         <v>22</v>
       </c>
-      <c r="J22" s="29" t="n">
+      <c r="J22" s="30" t="n">
         <v>4995</v>
       </c>
-      <c r="K22" s="25" t="inlineStr">
+      <c r="K22" s="26" t="inlineStr">
         <is>
           <t>2.08 kg/boy</t>
         </is>
       </c>
-      <c r="L22" s="26" t="n">
+      <c r="L22" s="27" t="n">
         <v>10435</v>
       </c>
-      <c r="M22" s="30" t="n">
+      <c r="M22" s="31" t="n">
         <v>43.3</v>
       </c>
-      <c r="N22" s="31" t="inlineStr">
+      <c r="N22" s="32" t="inlineStr">
         <is>
           <t>Saatte ~21 Boy</t>
         </is>
       </c>
-      <c r="O22" s="48" t="n">
+      <c r="O22" s="50" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5803,7 +5724,7 @@
           <t>35 x 150 mm</t>
         </is>
       </c>
-      <c r="E23" s="45" t="inlineStr">
+      <c r="E23" s="47" t="inlineStr">
         <is>
           <t>Hat 101</t>
         </is>
@@ -5843,17 +5764,17 @@
           <t>Saatte ~14 Boy</t>
         </is>
       </c>
-      <c r="O23" s="49" t="n">
+      <c r="O23" s="51" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="23" t="inlineStr">
+      <c r="A24" s="24" t="inlineStr">
         <is>
           <t>KT102-219x26-ANT</t>
         </is>
       </c>
-      <c r="B24" s="24" t="inlineStr">
+      <c r="B24" s="25" t="inlineStr">
         <is>
           <t>Deck / WPC Zemin</t>
         </is>
@@ -5863,52 +5784,52 @@
           <t>3.00 Metre</t>
         </is>
       </c>
-      <c r="D24" s="24" t="inlineStr">
+      <c r="D24" s="25" t="inlineStr">
         <is>
           <t>219 x 26 mm</t>
         </is>
       </c>
-      <c r="E24" s="43" t="inlineStr">
+      <c r="E24" s="45" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="F24" s="32" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="G24" s="27" t="inlineStr">
+      <c r="F24" s="33" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="G24" s="28" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="H24" s="28" t="n">
+      <c r="H24" s="29" t="n">
         <v>87</v>
       </c>
-      <c r="I24" s="29" t="n">
+      <c r="I24" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="J24" s="29" t="n">
+      <c r="J24" s="30" t="n">
         <v>895</v>
       </c>
-      <c r="K24" s="25" t="inlineStr">
+      <c r="K24" s="26" t="inlineStr">
         <is>
           <t>10.52 kg/boy</t>
         </is>
       </c>
-      <c r="L24" s="26" t="n">
+      <c r="L24" s="27" t="n">
         <v>9415</v>
       </c>
-      <c r="M24" s="30" t="n">
+      <c r="M24" s="31" t="n">
         <v>108.2</v>
       </c>
-      <c r="N24" s="31" t="inlineStr">
+      <c r="N24" s="32" t="inlineStr">
         <is>
           <t>Saatte ~10 Boy</t>
         </is>
       </c>
-      <c r="O24" s="48" t="n">
+      <c r="O24" s="50" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5933,7 +5854,7 @@
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E25" s="45" t="inlineStr">
+      <c r="E25" s="47" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
@@ -5973,17 +5894,17 @@
           <t>Saatte ~31 Plaka</t>
         </is>
       </c>
-      <c r="O25" s="49" t="n">
+      <c r="O25" s="51" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="23" t="inlineStr">
+      <c r="A26" s="24" t="inlineStr">
         <is>
           <t>CAM ÇITASI</t>
         </is>
       </c>
-      <c r="B26" s="24" t="inlineStr">
+      <c r="B26" s="25" t="inlineStr">
         <is>
           <t>Cam Çıtası</t>
         </is>
@@ -5993,52 +5914,52 @@
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="D26" s="24" t="inlineStr">
+      <c r="D26" s="25" t="inlineStr">
         <is>
           <t>15 x 20 mm</t>
         </is>
       </c>
-      <c r="E26" s="43" t="inlineStr">
+      <c r="E26" s="45" t="inlineStr">
         <is>
           <t>Hat 102</t>
         </is>
       </c>
-      <c r="F26" s="32" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="G26" s="27" t="inlineStr">
+      <c r="F26" s="33" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="G26" s="28" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="H26" s="28" t="n">
+      <c r="H26" s="29" t="n">
         <v>150</v>
       </c>
-      <c r="I26" s="29" t="n">
+      <c r="I26" s="30" t="n">
         <v>14</v>
       </c>
-      <c r="J26" s="29" t="n">
+      <c r="J26" s="30" t="n">
         <v>5187</v>
       </c>
-      <c r="K26" s="25" t="inlineStr">
+      <c r="K26" s="26" t="inlineStr">
         <is>
           <t>1.50 kg/boy</t>
         </is>
       </c>
-      <c r="L26" s="26" t="n">
+      <c r="L26" s="27" t="n">
         <v>7805</v>
       </c>
-      <c r="M26" s="30" t="n">
+      <c r="M26" s="31" t="n">
         <v>52</v>
       </c>
-      <c r="N26" s="31" t="inlineStr">
+      <c r="N26" s="32" t="inlineStr">
         <is>
           <t>Saatte ~35 Boy</t>
         </is>
       </c>
-      <c r="O26" s="48" t="n">
+      <c r="O26" s="50" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6063,7 +5984,7 @@
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E27" s="45" t="inlineStr">
+      <c r="E27" s="47" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
@@ -6103,17 +6024,17 @@
           <t>Saatte ~17 Plaka</t>
         </is>
       </c>
-      <c r="O27" s="49" t="n">
+      <c r="O27" s="51" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="23" t="inlineStr">
+      <c r="A28" s="24" t="inlineStr">
         <is>
           <t>AY GRİ Levha</t>
         </is>
       </c>
-      <c r="B28" s="24" t="inlineStr">
+      <c r="B28" s="25" t="inlineStr">
         <is>
           <t>WPC Levha Plaka</t>
         </is>
@@ -6123,52 +6044,52 @@
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="D28" s="24" t="inlineStr">
+      <c r="D28" s="25" t="inlineStr">
         <is>
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E28" s="43" t="inlineStr">
+      <c r="E28" s="45" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="F28" s="32" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="G28" s="27" t="inlineStr">
+      <c r="F28" s="33" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="G28" s="28" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="H28" s="28" t="n">
+      <c r="H28" s="29" t="n">
         <v>57.5</v>
       </c>
-      <c r="I28" s="29" t="n">
+      <c r="I28" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="J28" s="29" t="n">
+      <c r="J28" s="30" t="n">
         <v>1297</v>
       </c>
-      <c r="K28" s="25" t="inlineStr">
+      <c r="K28" s="26" t="inlineStr">
         <is>
           <t>4.64 kg/plaka</t>
         </is>
       </c>
-      <c r="L28" s="26" t="n">
+      <c r="L28" s="27" t="n">
         <v>6018.08</v>
       </c>
-      <c r="M28" s="30" t="n">
+      <c r="M28" s="31" t="n">
         <v>104.7</v>
       </c>
-      <c r="N28" s="31" t="inlineStr">
+      <c r="N28" s="32" t="inlineStr">
         <is>
           <t>Saatte ~23 Plaka</t>
         </is>
       </c>
-      <c r="O28" s="48" t="n">
+      <c r="O28" s="50" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6193,7 +6114,7 @@
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E29" s="45" t="inlineStr">
+      <c r="E29" s="47" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
@@ -6233,17 +6154,17 @@
           <t>Saatte ~15 Plaka</t>
         </is>
       </c>
-      <c r="O29" s="49" t="n">
+      <c r="O29" s="51" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="23" t="inlineStr">
+      <c r="A30" s="24" t="inlineStr">
         <is>
           <t>KOYU CEVİZ Levha</t>
         </is>
       </c>
-      <c r="B30" s="24" t="inlineStr">
+      <c r="B30" s="25" t="inlineStr">
         <is>
           <t>WPC Levha Plaka</t>
         </is>
@@ -6253,52 +6174,52 @@
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="D30" s="24" t="inlineStr">
+      <c r="D30" s="25" t="inlineStr">
         <is>
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E30" s="43" t="inlineStr">
+      <c r="E30" s="45" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="F30" s="32" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="G30" s="27" t="inlineStr">
+      <c r="F30" s="33" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="G30" s="28" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="H30" s="28" t="n">
+      <c r="H30" s="29" t="n">
         <v>72.5</v>
       </c>
-      <c r="I30" s="29" t="n">
+      <c r="I30" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="J30" s="29" t="n">
+      <c r="J30" s="30" t="n">
         <v>803</v>
       </c>
-      <c r="K30" s="25" t="inlineStr">
+      <c r="K30" s="26" t="inlineStr">
         <is>
           <t>4.79 kg/plaka</t>
         </is>
       </c>
-      <c r="L30" s="26" t="n">
+      <c r="L30" s="27" t="n">
         <v>3846.37</v>
       </c>
-      <c r="M30" s="30" t="n">
+      <c r="M30" s="31" t="n">
         <v>53.1</v>
       </c>
-      <c r="N30" s="31" t="inlineStr">
+      <c r="N30" s="32" t="inlineStr">
         <is>
           <t>Saatte ~11 Plaka</t>
         </is>
       </c>
-      <c r="O30" s="48" t="n">
+      <c r="O30" s="50" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6323,7 +6244,7 @@
           <t>38 x 45 mm</t>
         </is>
       </c>
-      <c r="E31" s="45" t="inlineStr">
+      <c r="E31" s="47" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
@@ -6363,17 +6284,17 @@
           <t>Saatte ~21 Boy</t>
         </is>
       </c>
-      <c r="O31" s="49" t="n">
-        <v>0.01166411417024152</v>
+      <c r="O31" s="51" t="n">
+        <v>0.01161408800566001</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="23" t="inlineStr">
+      <c r="A32" s="24" t="inlineStr">
         <is>
           <t>COCO Levha</t>
         </is>
       </c>
-      <c r="B32" s="24" t="inlineStr">
+      <c r="B32" s="25" t="inlineStr">
         <is>
           <t>WPC Levha Plaka</t>
         </is>
@@ -6383,52 +6304,52 @@
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="D32" s="24" t="inlineStr">
+      <c r="D32" s="25" t="inlineStr">
         <is>
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E32" s="43" t="inlineStr">
+      <c r="E32" s="45" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="F32" s="32" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="G32" s="27" t="inlineStr">
+      <c r="F32" s="33" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="G32" s="28" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="H32" s="28" t="n">
+      <c r="H32" s="29" t="n">
         <v>14.5</v>
       </c>
-      <c r="I32" s="29" t="n">
+      <c r="I32" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="J32" s="29" t="n">
+      <c r="J32" s="30" t="n">
         <v>600</v>
       </c>
-      <c r="K32" s="25" t="inlineStr">
+      <c r="K32" s="26" t="inlineStr">
         <is>
           <t>4.79 kg/plaka</t>
         </is>
       </c>
-      <c r="L32" s="26" t="n">
+      <c r="L32" s="27" t="n">
         <v>2874</v>
       </c>
-      <c r="M32" s="30" t="n">
+      <c r="M32" s="31" t="n">
         <v>198.2</v>
       </c>
-      <c r="N32" s="31" t="inlineStr">
+      <c r="N32" s="32" t="inlineStr">
         <is>
           <t>Saatte ~41 Plaka</t>
         </is>
       </c>
-      <c r="O32" s="48" t="n">
+      <c r="O32" s="50" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6453,7 +6374,7 @@
           <t>200 x 36 mm</t>
         </is>
       </c>
-      <c r="E33" s="45" t="inlineStr">
+      <c r="E33" s="47" t="inlineStr">
         <is>
           <t>Hat 106</t>
         </is>
@@ -6493,17 +6414,17 @@
           <t>Saatte ~20 Boy</t>
         </is>
       </c>
-      <c r="O33" s="49" t="n">
+      <c r="O33" s="51" t="n">
         <v>0.02976688142428564</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="23" t="inlineStr">
+      <c r="A34" s="24" t="inlineStr">
         <is>
           <t>200 mm KASA</t>
         </is>
       </c>
-      <c r="B34" s="24" t="inlineStr">
+      <c r="B34" s="25" t="inlineStr">
         <is>
           <t>Kasa Profili</t>
         </is>
@@ -6513,52 +6434,52 @@
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="D34" s="24" t="inlineStr">
+      <c r="D34" s="25" t="inlineStr">
         <is>
           <t>200 x 36 mm</t>
         </is>
       </c>
-      <c r="E34" s="43" t="inlineStr">
+      <c r="E34" s="45" t="inlineStr">
         <is>
           <t>Hat 108</t>
         </is>
       </c>
-      <c r="F34" s="32" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="G34" s="34" t="inlineStr">
+      <c r="F34" s="33" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="G34" s="35" t="inlineStr">
         <is>
           <t>YEDEK ROTA 2</t>
         </is>
       </c>
-      <c r="H34" s="28" t="n">
+      <c r="H34" s="29" t="n">
         <v>24</v>
       </c>
-      <c r="I34" s="29" t="n">
+      <c r="I34" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="J34" s="29" t="n">
+      <c r="J34" s="30" t="n">
         <v>348</v>
       </c>
-      <c r="K34" s="25" t="inlineStr">
+      <c r="K34" s="26" t="inlineStr">
         <is>
           <t>6.66 kg/boy</t>
         </is>
       </c>
-      <c r="L34" s="26" t="n">
+      <c r="L34" s="27" t="n">
         <v>1884</v>
       </c>
-      <c r="M34" s="30" t="n">
+      <c r="M34" s="31" t="n">
         <v>78.5</v>
       </c>
-      <c r="N34" s="31" t="inlineStr">
+      <c r="N34" s="32" t="inlineStr">
         <is>
           <t>Saatte ~14 Boy</t>
         </is>
       </c>
-      <c r="O34" s="48" t="n">
+      <c r="O34" s="50" t="n">
         <v>0.02316431416908474</v>
       </c>
     </row>
@@ -6583,7 +6504,7 @@
           <t>30 x 15 mm</t>
         </is>
       </c>
-      <c r="E35" s="45" t="inlineStr">
+      <c r="E35" s="47" t="inlineStr">
         <is>
           <t>Hat 102</t>
         </is>
@@ -6623,17 +6544,17 @@
           <t>Saatte ~85 Boy</t>
         </is>
       </c>
-      <c r="O35" s="49" t="n">
+      <c r="O35" s="51" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="23" t="inlineStr">
+      <c r="A36" s="24" t="inlineStr">
         <is>
           <t>140 mm KASA</t>
         </is>
       </c>
-      <c r="B36" s="24" t="inlineStr">
+      <c r="B36" s="25" t="inlineStr">
         <is>
           <t>Kasa Profili</t>
         </is>
@@ -6643,53 +6564,53 @@
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="D36" s="24" t="inlineStr">
+      <c r="D36" s="25" t="inlineStr">
         <is>
           <t>140 x 36 mm</t>
         </is>
       </c>
-      <c r="E36" s="43" t="inlineStr">
+      <c r="E36" s="45" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="F36" s="32" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="G36" s="34" t="inlineStr">
+      <c r="F36" s="33" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="G36" s="35" t="inlineStr">
         <is>
           <t>YEDEK ROTA 3</t>
         </is>
       </c>
-      <c r="H36" s="28" t="n">
+      <c r="H36" s="29" t="n">
         <v>30</v>
       </c>
-      <c r="I36" s="29" t="n">
+      <c r="I36" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="J36" s="29" t="n">
+      <c r="J36" s="30" t="n">
         <v>220</v>
       </c>
-      <c r="K36" s="25" t="inlineStr">
+      <c r="K36" s="26" t="inlineStr">
         <is>
           <t>4.95 kg/boy</t>
         </is>
       </c>
-      <c r="L36" s="26" t="n">
+      <c r="L36" s="27" t="n">
         <v>1370</v>
       </c>
-      <c r="M36" s="30" t="n">
+      <c r="M36" s="31" t="n">
         <v>45.7</v>
       </c>
-      <c r="N36" s="31" t="inlineStr">
+      <c r="N36" s="32" t="inlineStr">
         <is>
           <t>Saatte ~7 Boy</t>
         </is>
       </c>
-      <c r="O36" s="48" t="n">
-        <v>0.007923884438532057</v>
+      <c r="O36" s="50" t="n">
+        <v>0.007788826161359463</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
@@ -6713,7 +6634,7 @@
           <t>100 x 36 mm</t>
         </is>
       </c>
-      <c r="E37" s="45" t="inlineStr">
+      <c r="E37" s="47" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
@@ -6753,17 +6674,17 @@
           <t>Saatte ~14 Boy</t>
         </is>
       </c>
-      <c r="O37" s="49" t="n">
-        <v>0.008677798533579995</v>
+      <c r="O37" s="51" t="n">
+        <v>0.008582649500375166</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="23" t="inlineStr">
+      <c r="A38" s="24" t="inlineStr">
         <is>
           <t>80X80 PERVAZ</t>
         </is>
       </c>
-      <c r="B38" s="24" t="inlineStr">
+      <c r="B38" s="25" t="inlineStr">
         <is>
           <t>Pervaz Profili</t>
         </is>
@@ -6773,12 +6694,12 @@
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="D38" s="24" t="inlineStr">
+      <c r="D38" s="25" t="inlineStr">
         <is>
           <t>80 x 80 mm</t>
         </is>
       </c>
-      <c r="E38" s="43" t="inlineStr">
+      <c r="E38" s="45" t="inlineStr">
         <is>
           <t>Hat 109</t>
         </is>
@@ -6788,37 +6709,37 @@
           <t>Çift Göz (2 Kafa)</t>
         </is>
       </c>
-      <c r="G38" s="34" t="inlineStr">
+      <c r="G38" s="35" t="inlineStr">
         <is>
           <t>YEDEK ROTA 1</t>
         </is>
       </c>
-      <c r="H38" s="28" t="n">
+      <c r="H38" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="I38" s="29" t="n">
+      <c r="I38" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="J38" s="29" t="n">
+      <c r="J38" s="30" t="n">
         <v>690</v>
       </c>
-      <c r="K38" s="25" t="inlineStr">
+      <c r="K38" s="26" t="inlineStr">
         <is>
           <t>2.20 kg/boy</t>
         </is>
       </c>
-      <c r="L38" s="26" t="n">
+      <c r="L38" s="27" t="n">
         <v>1021</v>
       </c>
-      <c r="M38" s="30" t="n">
+      <c r="M38" s="31" t="n">
         <v>85.09999999999999</v>
       </c>
-      <c r="N38" s="31" t="inlineStr">
+      <c r="N38" s="32" t="inlineStr">
         <is>
           <t>Saatte ~58 Boy</t>
         </is>
       </c>
-      <c r="O38" s="48" t="n">
+      <c r="O38" s="50" t="n">
         <v>0.07120440755980194</v>
       </c>
     </row>
@@ -6843,7 +6764,7 @@
           <t>100 x 36 mm</t>
         </is>
       </c>
-      <c r="E39" s="45" t="inlineStr">
+      <c r="E39" s="47" t="inlineStr">
         <is>
           <t>Hat 106</t>
         </is>
@@ -6883,17 +6804,17 @@
           <t>Saatte ~14 Boy</t>
         </is>
       </c>
-      <c r="O39" s="49" t="n">
-        <v>0.006329599797693648</v>
+      <c r="O39" s="51" t="n">
+        <v>0.006260197944332623</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="23" t="inlineStr">
+      <c r="A40" s="24" t="inlineStr">
         <is>
           <t>SEREN</t>
         </is>
       </c>
-      <c r="B40" s="24" t="inlineStr">
+      <c r="B40" s="25" t="inlineStr">
         <is>
           <t>Seren Çıtası</t>
         </is>
@@ -6903,12 +6824,12 @@
           <t>2.10 Metre</t>
         </is>
       </c>
-      <c r="D40" s="24" t="inlineStr">
+      <c r="D40" s="25" t="inlineStr">
         <is>
           <t>38 x 45 mm</t>
         </is>
       </c>
-      <c r="E40" s="43" t="inlineStr">
+      <c r="E40" s="45" t="inlineStr">
         <is>
           <t>Hat 103</t>
         </is>
@@ -6918,38 +6839,38 @@
           <t>Çift Göz (2 Kafa)</t>
         </is>
       </c>
-      <c r="G40" s="34" t="inlineStr">
+      <c r="G40" s="35" t="inlineStr">
         <is>
           <t>YEDEK ROTA 3</t>
         </is>
       </c>
-      <c r="H40" s="28" t="n">
+      <c r="H40" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="I40" s="29" t="n">
+      <c r="I40" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="J40" s="29" t="n">
+      <c r="J40" s="30" t="n">
         <v>450</v>
       </c>
-      <c r="K40" s="25" t="inlineStr">
+      <c r="K40" s="26" t="inlineStr">
         <is>
           <t>3.39 kg/boy</t>
         </is>
       </c>
-      <c r="L40" s="26" t="n">
+      <c r="L40" s="27" t="n">
         <v>760</v>
       </c>
-      <c r="M40" s="30" t="n">
+      <c r="M40" s="31" t="n">
         <v>63.3</v>
       </c>
-      <c r="N40" s="31" t="inlineStr">
+      <c r="N40" s="32" t="inlineStr">
         <is>
           <t>Saatte ~38 Boy</t>
         </is>
       </c>
-      <c r="O40" s="48" t="n">
-        <v>0.00254953315196536</v>
+      <c r="O40" s="50" t="n">
+        <v>0.002538598471182515</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
@@ -6973,7 +6894,7 @@
           <t>140 x 36 mm</t>
         </is>
       </c>
-      <c r="E41" s="45" t="inlineStr">
+      <c r="E41" s="47" t="inlineStr">
         <is>
           <t>Hat 105</t>
         </is>
@@ -7013,17 +6934,17 @@
           <t>Saatte ~17 Boy</t>
         </is>
       </c>
-      <c r="O41" s="49" t="n">
-        <v>0.00414124179415252</v>
+      <c r="O41" s="51" t="n">
+        <v>0.004070656592360128</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="23" t="inlineStr">
+      <c r="A42" s="24" t="inlineStr">
         <is>
           <t>35X80 PERVAZ</t>
         </is>
       </c>
-      <c r="B42" s="24" t="inlineStr">
+      <c r="B42" s="25" t="inlineStr">
         <is>
           <t>Pervaz Profili</t>
         </is>
@@ -7033,52 +6954,52 @@
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="D42" s="24" t="inlineStr">
+      <c r="D42" s="25" t="inlineStr">
         <is>
           <t>35 x 80 mm</t>
         </is>
       </c>
-      <c r="E42" s="43" t="inlineStr">
+      <c r="E42" s="45" t="inlineStr">
         <is>
           <t>Hat 101</t>
         </is>
       </c>
-      <c r="F42" s="32" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="G42" s="27" t="inlineStr">
+      <c r="F42" s="33" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="G42" s="28" t="inlineStr">
         <is>
           <t>ANA ROTA</t>
         </is>
       </c>
-      <c r="H42" s="28" t="n">
+      <c r="H42" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="I42" s="29" t="n">
+      <c r="I42" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="J42" s="29" t="n">
+      <c r="J42" s="30" t="n">
         <v>180</v>
       </c>
-      <c r="K42" s="25" t="inlineStr">
+      <c r="K42" s="26" t="inlineStr">
         <is>
           <t>2.94 kg/boy</t>
         </is>
       </c>
-      <c r="L42" s="26" t="n">
+      <c r="L42" s="27" t="n">
         <v>530</v>
       </c>
-      <c r="M42" s="30" t="n">
+      <c r="M42" s="31" t="n">
         <v>44.2</v>
       </c>
-      <c r="N42" s="31" t="inlineStr">
+      <c r="N42" s="32" t="inlineStr">
         <is>
           <t>Saatte ~15 Boy</t>
         </is>
       </c>
-      <c r="O42" s="48" t="n">
+      <c r="O42" s="50" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7103,7 +7024,7 @@
           <t>219 x 26 mm</t>
         </is>
       </c>
-      <c r="E43" s="45" t="inlineStr">
+      <c r="E43" s="47" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
@@ -7143,36 +7064,36 @@
           <t>Saatte ~12 Boy</t>
         </is>
       </c>
-      <c r="O43" s="49" t="n">
+      <c r="O43" s="51" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1">
-      <c r="A44" s="47" t="inlineStr">
+      <c r="A44" s="49" t="inlineStr">
         <is>
           <t>GENEL TOPLAM</t>
         </is>
       </c>
-      <c r="B44" s="40" t="n"/>
-      <c r="C44" s="40" t="n"/>
-      <c r="D44" s="40" t="n"/>
-      <c r="E44" s="40" t="n"/>
-      <c r="F44" s="40" t="n"/>
-      <c r="G44" s="40" t="n"/>
-      <c r="H44" s="42" t="n">
-        <v>15911.4</v>
-      </c>
-      <c r="I44" s="40" t="n"/>
-      <c r="J44" s="41" t="n">
-        <v>383119</v>
-      </c>
-      <c r="K44" s="40" t="n"/>
-      <c r="L44" s="41" t="n">
-        <v>1252309.48</v>
-      </c>
-      <c r="M44" s="40" t="n"/>
-      <c r="N44" s="40" t="n"/>
-      <c r="O44" s="40" t="n"/>
+      <c r="B44" s="42" t="n"/>
+      <c r="C44" s="42" t="n"/>
+      <c r="D44" s="42" t="n"/>
+      <c r="E44" s="42" t="n"/>
+      <c r="F44" s="42" t="n"/>
+      <c r="G44" s="42" t="n"/>
+      <c r="H44" s="44" t="n">
+        <v>16095.4</v>
+      </c>
+      <c r="I44" s="42" t="n"/>
+      <c r="J44" s="43" t="n">
+        <v>387692</v>
+      </c>
+      <c r="K44" s="42" t="n"/>
+      <c r="L44" s="43" t="n">
+        <v>1266753.58</v>
+      </c>
+      <c r="M44" s="42" t="n"/>
+      <c r="N44" s="42" t="n"/>
+      <c r="O44" s="42" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7289,53 +7210,53 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>100 mm KASA</t>
         </is>
       </c>
-      <c r="B4" s="50" t="inlineStr">
+      <c r="B4" s="52" t="inlineStr">
         <is>
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="C4" s="43" t="inlineStr">
+      <c r="C4" s="45" t="inlineStr">
         <is>
           <t>Hat 102</t>
         </is>
       </c>
-      <c r="D4" s="43" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="E4" s="28" t="n">
+      <c r="D4" s="45" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="E4" s="29" t="n">
         <v>1074.1</v>
       </c>
-      <c r="F4" s="29" t="n">
+      <c r="F4" s="30" t="n">
         <v>95</v>
       </c>
-      <c r="G4" s="26" t="n">
+      <c r="G4" s="27" t="n">
         <v>67941</v>
       </c>
-      <c r="H4" s="29" t="n">
+      <c r="H4" s="30" t="n">
         <v>16716</v>
       </c>
-      <c r="I4" s="30" t="n">
+      <c r="I4" s="31" t="n">
         <v>63.3</v>
       </c>
-      <c r="J4" s="31" t="inlineStr">
+      <c r="J4" s="32" t="inlineStr">
         <is>
           <t>Saatte ~16 Boy</t>
         </is>
       </c>
-      <c r="K4" s="28" t="n">
+      <c r="K4" s="29" t="n">
         <v>63.3</v>
       </c>
-      <c r="L4" s="33" t="n">
+      <c r="L4" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="M4" s="24" t="inlineStr">
+      <c r="M4" s="25" t="inlineStr">
         <is>
           <t>Standart Tek Çıkışlı Kalıp</t>
         </is>
@@ -7347,17 +7268,17 @@
           <t>100 mm KASA</t>
         </is>
       </c>
-      <c r="B5" s="51" t="inlineStr">
+      <c r="B5" s="53" t="inlineStr">
         <is>
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="C5" s="45" t="inlineStr">
+      <c r="C5" s="47" t="inlineStr">
         <is>
           <t>Hat 106</t>
         </is>
       </c>
-      <c r="D5" s="45" t="inlineStr">
+      <c r="D5" s="47" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -7395,53 +7316,53 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>100 mm KASA</t>
         </is>
       </c>
-      <c r="B6" s="50" t="inlineStr">
+      <c r="B6" s="52" t="inlineStr">
         <is>
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="C6" s="43" t="inlineStr">
+      <c r="C6" s="45" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="D6" s="43" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="E6" s="28" t="n">
+      <c r="D6" s="45" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="E6" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="F6" s="29" t="n">
+      <c r="F6" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="26" t="n">
+      <c r="G6" s="27" t="n">
         <v>1153</v>
       </c>
-      <c r="H6" s="29" t="n">
+      <c r="H6" s="30" t="n">
         <v>174</v>
       </c>
-      <c r="I6" s="30" t="n">
+      <c r="I6" s="31" t="n">
         <v>96.09999999999999</v>
       </c>
-      <c r="J6" s="31" t="inlineStr">
+      <c r="J6" s="32" t="inlineStr">
         <is>
           <t>Saatte ~14 Boy</t>
         </is>
       </c>
-      <c r="K6" s="28" t="n">
+      <c r="K6" s="29" t="n">
         <v>96.09999999999999</v>
       </c>
-      <c r="L6" s="33" t="n">
+      <c r="L6" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="M6" s="24" t="inlineStr">
+      <c r="M6" s="25" t="inlineStr">
         <is>
           <t>Standart Tek Çıkışlı Kalıp</t>
         </is>
@@ -7453,35 +7374,35 @@
           <t>100 mm KASA</t>
         </is>
       </c>
-      <c r="B7" s="51" t="inlineStr">
+      <c r="B7" s="53" t="inlineStr">
         <is>
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="C7" s="45" t="inlineStr">
+      <c r="C7" s="47" t="inlineStr">
         <is>
           <t>Hat 108</t>
         </is>
       </c>
-      <c r="D7" s="45" t="inlineStr">
+      <c r="D7" s="47" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
       </c>
       <c r="E7" s="14" t="n">
-        <v>935</v>
+        <v>959</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>62932.8</v>
+        <v>64405.8</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>16287</v>
+        <v>16653</v>
       </c>
       <c r="I7" s="16" t="n">
-        <v>67.3</v>
+        <v>67.2</v>
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
@@ -7492,7 +7413,7 @@
         <v>69.5</v>
       </c>
       <c r="L7" s="19" t="n">
-        <v>0.9683453237410071</v>
+        <v>0.9669064748201438</v>
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
@@ -7501,53 +7422,53 @@
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>140 mm KASA</t>
         </is>
       </c>
-      <c r="B8" s="50" t="inlineStr">
+      <c r="B8" s="52" t="inlineStr">
         <is>
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="C8" s="43" t="inlineStr">
+      <c r="C8" s="45" t="inlineStr">
         <is>
           <t>Hat 102</t>
         </is>
       </c>
-      <c r="D8" s="43" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="E8" s="28" t="n">
-        <v>302</v>
-      </c>
-      <c r="F8" s="29" t="n">
-        <v>28</v>
-      </c>
-      <c r="G8" s="26" t="n">
-        <v>18238</v>
-      </c>
-      <c r="H8" s="29" t="n">
-        <v>3301</v>
-      </c>
-      <c r="I8" s="30" t="n">
-        <v>60.4</v>
-      </c>
-      <c r="J8" s="31" t="inlineStr">
+      <c r="D8" s="45" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="E8" s="29" t="n">
+        <v>326</v>
+      </c>
+      <c r="F8" s="30" t="n">
+        <v>30</v>
+      </c>
+      <c r="G8" s="27" t="n">
+        <v>19859</v>
+      </c>
+      <c r="H8" s="30" t="n">
+        <v>3611</v>
+      </c>
+      <c r="I8" s="31" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="J8" s="32" t="inlineStr">
         <is>
           <t>Saatte ~11 Boy</t>
         </is>
       </c>
-      <c r="K8" s="28" t="n">
+      <c r="K8" s="29" t="n">
         <v>51.8</v>
       </c>
-      <c r="L8" s="33" t="n">
-        <v>1.166023166023166</v>
-      </c>
-      <c r="M8" s="24" t="inlineStr">
+      <c r="L8" s="34" t="n">
+        <v>1.175675675675676</v>
+      </c>
+      <c r="M8" s="25" t="inlineStr">
         <is>
           <t>Standart Tek Çıkışlı Kalıp</t>
         </is>
@@ -7559,17 +7480,17 @@
           <t>140 mm KASA</t>
         </is>
       </c>
-      <c r="B9" s="51" t="inlineStr">
+      <c r="B9" s="53" t="inlineStr">
         <is>
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="C9" s="45" t="inlineStr">
+      <c r="C9" s="47" t="inlineStr">
         <is>
           <t>Hat 105</t>
         </is>
       </c>
-      <c r="D9" s="45" t="inlineStr">
+      <c r="D9" s="47" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -7607,53 +7528,53 @@
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>140 mm KASA</t>
         </is>
       </c>
-      <c r="B10" s="50" t="inlineStr">
+      <c r="B10" s="52" t="inlineStr">
         <is>
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="C10" s="43" t="inlineStr">
+      <c r="C10" s="45" t="inlineStr">
         <is>
           <t>Hat 106</t>
         </is>
       </c>
-      <c r="D10" s="43" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="E10" s="28" t="n">
-        <v>1585.3</v>
-      </c>
-      <c r="F10" s="29" t="n">
-        <v>141</v>
-      </c>
-      <c r="G10" s="26" t="n">
-        <v>114247</v>
-      </c>
-      <c r="H10" s="29" t="n">
-        <v>22355</v>
-      </c>
-      <c r="I10" s="30" t="n">
-        <v>72.09999999999999</v>
-      </c>
-      <c r="J10" s="31" t="inlineStr">
+      <c r="D10" s="45" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="E10" s="29" t="n">
+        <v>1609.3</v>
+      </c>
+      <c r="F10" s="30" t="n">
+        <v>144</v>
+      </c>
+      <c r="G10" s="27" t="n">
+        <v>115624</v>
+      </c>
+      <c r="H10" s="30" t="n">
+        <v>22612</v>
+      </c>
+      <c r="I10" s="31" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="J10" s="32" t="inlineStr">
         <is>
           <t>Saatte ~14 Boy</t>
         </is>
       </c>
-      <c r="K10" s="28" t="n">
+      <c r="K10" s="29" t="n">
         <v>74.09999999999999</v>
       </c>
-      <c r="L10" s="33" t="n">
-        <v>0.9730094466936572</v>
-      </c>
-      <c r="M10" s="24" t="inlineStr">
+      <c r="L10" s="34" t="n">
+        <v>0.9689608636977058</v>
+      </c>
+      <c r="M10" s="25" t="inlineStr">
         <is>
           <t>Standart Tek Çıkışlı Kalıp</t>
         </is>
@@ -7665,17 +7586,17 @@
           <t>140 mm KASA</t>
         </is>
       </c>
-      <c r="B11" s="51" t="inlineStr">
+      <c r="B11" s="53" t="inlineStr">
         <is>
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="C11" s="45" t="inlineStr">
+      <c r="C11" s="47" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="D11" s="45" t="inlineStr">
+      <c r="D11" s="47" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -7713,53 +7634,53 @@
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t>140 mm KASA</t>
         </is>
       </c>
-      <c r="B12" s="50" t="inlineStr">
+      <c r="B12" s="52" t="inlineStr">
         <is>
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="C12" s="43" t="inlineStr">
+      <c r="C12" s="45" t="inlineStr">
         <is>
           <t>Hat 108</t>
         </is>
       </c>
-      <c r="D12" s="43" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="E12" s="28" t="n">
+      <c r="D12" s="45" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="E12" s="29" t="n">
         <v>590.2</v>
       </c>
-      <c r="F12" s="29" t="n">
+      <c r="F12" s="30" t="n">
         <v>53</v>
       </c>
-      <c r="G12" s="26" t="n">
+      <c r="G12" s="27" t="n">
         <v>38324</v>
       </c>
-      <c r="H12" s="29" t="n">
+      <c r="H12" s="30" t="n">
         <v>8661</v>
       </c>
-      <c r="I12" s="30" t="n">
+      <c r="I12" s="31" t="n">
         <v>64.90000000000001</v>
       </c>
-      <c r="J12" s="31" t="inlineStr">
+      <c r="J12" s="32" t="inlineStr">
         <is>
           <t>Saatte ~15 Boy</t>
         </is>
       </c>
-      <c r="K12" s="28" t="n">
+      <c r="K12" s="29" t="n">
         <v>64.90000000000001</v>
       </c>
-      <c r="L12" s="33" t="n">
+      <c r="L12" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="M12" s="24" t="inlineStr">
+      <c r="M12" s="25" t="inlineStr">
         <is>
           <t>Standart Tek Çıkışlı Kalıp</t>
         </is>
@@ -7771,17 +7692,17 @@
           <t>200 mm KASA</t>
         </is>
       </c>
-      <c r="B13" s="51" t="inlineStr">
+      <c r="B13" s="53" t="inlineStr">
         <is>
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="C13" s="45" t="inlineStr">
+      <c r="C13" s="47" t="inlineStr">
         <is>
           <t>Hat 106</t>
         </is>
       </c>
-      <c r="D13" s="45" t="inlineStr">
+      <c r="D13" s="47" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -7819,53 +7740,53 @@
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>200 mm KASA</t>
         </is>
       </c>
-      <c r="B14" s="50" t="inlineStr">
+      <c r="B14" s="52" t="inlineStr">
         <is>
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="C14" s="43" t="inlineStr">
+      <c r="C14" s="45" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="D14" s="43" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="E14" s="28" t="n">
+      <c r="D14" s="45" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="E14" s="29" t="n">
         <v>910</v>
       </c>
-      <c r="F14" s="29" t="n">
+      <c r="F14" s="30" t="n">
         <v>86</v>
       </c>
-      <c r="G14" s="26" t="n">
+      <c r="G14" s="27" t="n">
         <v>77027</v>
       </c>
-      <c r="H14" s="29" t="n">
+      <c r="H14" s="30" t="n">
         <v>11377</v>
       </c>
-      <c r="I14" s="30" t="n">
+      <c r="I14" s="31" t="n">
         <v>84.59999999999999</v>
       </c>
-      <c r="J14" s="31" t="inlineStr">
+      <c r="J14" s="32" t="inlineStr">
         <is>
           <t>Saatte ~12 Boy</t>
         </is>
       </c>
-      <c r="K14" s="28" t="n">
+      <c r="K14" s="29" t="n">
         <v>84.59999999999999</v>
       </c>
-      <c r="L14" s="33" t="n">
+      <c r="L14" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="M14" s="24" t="inlineStr">
+      <c r="M14" s="25" t="inlineStr">
         <is>
           <t>Standart Tek Çıkışlı Kalıp</t>
         </is>
@@ -7877,17 +7798,17 @@
           <t>200 mm KASA</t>
         </is>
       </c>
-      <c r="B15" s="51" t="inlineStr">
+      <c r="B15" s="53" t="inlineStr">
         <is>
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="C15" s="45" t="inlineStr">
+      <c r="C15" s="47" t="inlineStr">
         <is>
           <t>Hat 108</t>
         </is>
       </c>
-      <c r="D15" s="45" t="inlineStr">
+      <c r="D15" s="47" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -7925,53 +7846,53 @@
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="23" t="inlineStr">
+      <c r="A16" s="24" t="inlineStr">
         <is>
           <t>35X100 PERVAZ</t>
         </is>
       </c>
-      <c r="B16" s="50" t="inlineStr">
+      <c r="B16" s="52" t="inlineStr">
         <is>
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="C16" s="43" t="inlineStr">
+      <c r="C16" s="45" t="inlineStr">
         <is>
           <t>Hat 101</t>
         </is>
       </c>
-      <c r="D16" s="43" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="E16" s="28" t="n">
+      <c r="D16" s="45" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="E16" s="29" t="n">
         <v>241</v>
       </c>
-      <c r="F16" s="29" t="n">
+      <c r="F16" s="30" t="n">
         <v>22</v>
       </c>
-      <c r="G16" s="26" t="n">
+      <c r="G16" s="27" t="n">
         <v>10435</v>
       </c>
-      <c r="H16" s="29" t="n">
+      <c r="H16" s="30" t="n">
         <v>4995</v>
       </c>
-      <c r="I16" s="30" t="n">
+      <c r="I16" s="31" t="n">
         <v>43.3</v>
       </c>
-      <c r="J16" s="31" t="inlineStr">
+      <c r="J16" s="32" t="inlineStr">
         <is>
           <t>Saatte ~21 Boy</t>
         </is>
       </c>
-      <c r="K16" s="28" t="n">
+      <c r="K16" s="29" t="n">
         <v>46.8</v>
       </c>
-      <c r="L16" s="33" t="n">
+      <c r="L16" s="34" t="n">
         <v>0.9252136752136753</v>
       </c>
-      <c r="M16" s="24" t="inlineStr">
+      <c r="M16" s="25" t="inlineStr">
         <is>
           <t>Standart Tek Çıkışlı Kalıp</t>
         </is>
@@ -7983,17 +7904,17 @@
           <t>35X150 PERVAZ</t>
         </is>
       </c>
-      <c r="B17" s="51" t="inlineStr">
+      <c r="B17" s="53" t="inlineStr">
         <is>
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="C17" s="45" t="inlineStr">
+      <c r="C17" s="47" t="inlineStr">
         <is>
           <t>Hat 101</t>
         </is>
       </c>
-      <c r="D17" s="45" t="inlineStr">
+      <c r="D17" s="47" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -8031,53 +7952,53 @@
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="23" t="inlineStr">
+      <c r="A18" s="24" t="inlineStr">
         <is>
           <t>35X80 PERVAZ</t>
         </is>
       </c>
-      <c r="B18" s="50" t="inlineStr">
+      <c r="B18" s="52" t="inlineStr">
         <is>
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="C18" s="43" t="inlineStr">
+      <c r="C18" s="45" t="inlineStr">
         <is>
           <t>Hat 101</t>
         </is>
       </c>
-      <c r="D18" s="43" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="E18" s="28" t="n">
+      <c r="D18" s="45" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="E18" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="F18" s="29" t="n">
+      <c r="F18" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="26" t="n">
+      <c r="G18" s="27" t="n">
         <v>530</v>
       </c>
-      <c r="H18" s="29" t="n">
+      <c r="H18" s="30" t="n">
         <v>180</v>
       </c>
-      <c r="I18" s="30" t="n">
+      <c r="I18" s="31" t="n">
         <v>44.2</v>
       </c>
-      <c r="J18" s="31" t="inlineStr">
+      <c r="J18" s="32" t="inlineStr">
         <is>
           <t>Saatte ~15 Boy</t>
         </is>
       </c>
-      <c r="K18" s="28" t="n">
+      <c r="K18" s="29" t="n">
         <v>44.2</v>
       </c>
-      <c r="L18" s="33" t="n">
+      <c r="L18" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="M18" s="24" t="inlineStr">
+      <c r="M18" s="25" t="inlineStr">
         <is>
           <t>Standart Tek Çıkışlı Kalıp</t>
         </is>
@@ -8089,17 +8010,17 @@
           <t>50X80 PERVAZ</t>
         </is>
       </c>
-      <c r="B19" s="51" t="inlineStr">
+      <c r="B19" s="53" t="inlineStr">
         <is>
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="C19" s="45" t="inlineStr">
+      <c r="C19" s="47" t="inlineStr">
         <is>
           <t>Hat 103</t>
         </is>
       </c>
-      <c r="D19" s="45" t="inlineStr">
+      <c r="D19" s="47" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -8137,17 +8058,17 @@
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="52" t="inlineStr">
+      <c r="A20" s="54" t="inlineStr">
         <is>
           <t>50X80 PERVAZ</t>
         </is>
       </c>
-      <c r="B20" s="53" t="inlineStr">
+      <c r="B20" s="55" t="inlineStr">
         <is>
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="C20" s="54" t="inlineStr">
+      <c r="C20" s="56" t="inlineStr">
         <is>
           <t>Hat 103</t>
         </is>
@@ -8157,33 +8078,33 @@
           <t>Çift Göz (2 Kafa)</t>
         </is>
       </c>
-      <c r="E20" s="55" t="n">
-        <v>1349</v>
-      </c>
-      <c r="F20" s="56" t="n">
-        <v>123</v>
-      </c>
-      <c r="G20" s="57" t="n">
-        <v>70445</v>
-      </c>
-      <c r="H20" s="56" t="n">
-        <v>42370</v>
-      </c>
-      <c r="I20" s="58" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="J20" s="59" t="inlineStr">
-        <is>
-          <t>Saatte ~31 Boy</t>
-        </is>
-      </c>
-      <c r="K20" s="55" t="n">
+      <c r="E20" s="57" t="n">
+        <v>1373</v>
+      </c>
+      <c r="F20" s="58" t="n">
+        <v>125</v>
+      </c>
+      <c r="G20" s="59" t="n">
+        <v>71878</v>
+      </c>
+      <c r="H20" s="58" t="n">
+        <v>43250</v>
+      </c>
+      <c r="I20" s="60" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="J20" s="61" t="inlineStr">
+        <is>
+          <t>Saatte ~32 Boy</t>
+        </is>
+      </c>
+      <c r="K20" s="57" t="n">
         <v>53.1</v>
       </c>
-      <c r="L20" s="60" t="n">
-        <v>0.9830508474576272</v>
-      </c>
-      <c r="M20" s="61" t="inlineStr">
+      <c r="L20" s="62" t="n">
+        <v>0.9868173258003766</v>
+      </c>
+      <c r="M20" s="63" t="inlineStr">
         <is>
           <t>Çift Çıkışlı Yüksek Hızlı Kalıp</t>
         </is>
@@ -8195,17 +8116,17 @@
           <t>50X80 PERVAZ</t>
         </is>
       </c>
-      <c r="B21" s="51" t="inlineStr">
+      <c r="B21" s="53" t="inlineStr">
         <is>
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="C21" s="45" t="inlineStr">
+      <c r="C21" s="47" t="inlineStr">
         <is>
           <t>Hat 109</t>
         </is>
       </c>
-      <c r="D21" s="45" t="inlineStr">
+      <c r="D21" s="47" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -8243,17 +8164,17 @@
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="52" t="inlineStr">
+      <c r="A22" s="54" t="inlineStr">
         <is>
           <t>50X80 PERVAZ</t>
         </is>
       </c>
-      <c r="B22" s="53" t="inlineStr">
+      <c r="B22" s="55" t="inlineStr">
         <is>
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="C22" s="54" t="inlineStr">
+      <c r="C22" s="56" t="inlineStr">
         <is>
           <t>Hat 109</t>
         </is>
@@ -8263,33 +8184,33 @@
           <t>Çift Göz (2 Kafa)</t>
         </is>
       </c>
-      <c r="E22" s="55" t="n">
-        <v>1420.2</v>
-      </c>
-      <c r="F22" s="56" t="n">
-        <v>139</v>
-      </c>
-      <c r="G22" s="57" t="n">
-        <v>105596.75</v>
-      </c>
-      <c r="H22" s="56" t="n">
-        <v>70470</v>
-      </c>
-      <c r="I22" s="58" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="J22" s="59" t="inlineStr">
+      <c r="E22" s="57" t="n">
+        <v>1444.2</v>
+      </c>
+      <c r="F22" s="58" t="n">
+        <v>141</v>
+      </c>
+      <c r="G22" s="59" t="n">
+        <v>107001.75</v>
+      </c>
+      <c r="H22" s="58" t="n">
+        <v>71435</v>
+      </c>
+      <c r="I22" s="60" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="J22" s="61" t="inlineStr">
         <is>
           <t>Saatte ~50 Boy</t>
         </is>
       </c>
-      <c r="K22" s="55" t="n">
+      <c r="K22" s="57" t="n">
         <v>73.59999999999999</v>
       </c>
-      <c r="L22" s="60" t="n">
-        <v>1.010869565217391</v>
-      </c>
-      <c r="M22" s="61" t="inlineStr">
+      <c r="L22" s="62" t="n">
+        <v>1.00679347826087</v>
+      </c>
+      <c r="M22" s="63" t="inlineStr">
         <is>
           <t>Çift Çıkışlı Yüksek Hızlı Kalıp</t>
         </is>
@@ -8301,17 +8222,17 @@
           <t>80X80 PERVAZ</t>
         </is>
       </c>
-      <c r="B23" s="51" t="inlineStr">
+      <c r="B23" s="53" t="inlineStr">
         <is>
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="C23" s="45" t="inlineStr">
+      <c r="C23" s="47" t="inlineStr">
         <is>
           <t>Hat 101</t>
         </is>
       </c>
-      <c r="D23" s="45" t="inlineStr">
+      <c r="D23" s="47" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -8349,17 +8270,17 @@
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="52" t="inlineStr">
+      <c r="A24" s="54" t="inlineStr">
         <is>
           <t>80X80 PERVAZ</t>
         </is>
       </c>
-      <c r="B24" s="53" t="inlineStr">
+      <c r="B24" s="55" t="inlineStr">
         <is>
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="C24" s="54" t="inlineStr">
+      <c r="C24" s="56" t="inlineStr">
         <is>
           <t>Hat 109</t>
         </is>
@@ -8369,33 +8290,33 @@
           <t>Çift Göz (2 Kafa)</t>
         </is>
       </c>
-      <c r="E24" s="55" t="n">
+      <c r="E24" s="57" t="n">
         <v>12</v>
       </c>
-      <c r="F24" s="56" t="n">
+      <c r="F24" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="57" t="n">
+      <c r="G24" s="59" t="n">
         <v>1021</v>
       </c>
-      <c r="H24" s="56" t="n">
+      <c r="H24" s="58" t="n">
         <v>690</v>
       </c>
-      <c r="I24" s="58" t="n">
+      <c r="I24" s="60" t="n">
         <v>85.09999999999999</v>
       </c>
-      <c r="J24" s="59" t="inlineStr">
+      <c r="J24" s="61" t="inlineStr">
         <is>
           <t>Saatte ~58 Boy</t>
         </is>
       </c>
-      <c r="K24" s="55" t="n">
+      <c r="K24" s="57" t="n">
         <v>85.09999999999999</v>
       </c>
-      <c r="L24" s="60" t="n">
+      <c r="L24" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="M24" s="61" t="inlineStr">
+      <c r="M24" s="63" t="inlineStr">
         <is>
           <t>Çift Çıkışlı Yüksek Hızlı Kalıp</t>
         </is>
@@ -8407,17 +8328,17 @@
           <t>ANTRASİT Levha</t>
         </is>
       </c>
-      <c r="B25" s="51" t="inlineStr">
+      <c r="B25" s="53" t="inlineStr">
         <is>
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="C25" s="45" t="inlineStr">
+      <c r="C25" s="47" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="D25" s="45" t="inlineStr">
+      <c r="D25" s="47" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -8445,7 +8366,7 @@
       <c r="K25" s="14" t="n">
         <v>111.8</v>
       </c>
-      <c r="L25" s="37" t="n">
+      <c r="L25" s="39" t="n">
         <v>0.6431127012522362</v>
       </c>
       <c r="M25" s="8" t="inlineStr">
@@ -8455,53 +8376,53 @@
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="23" t="inlineStr">
+      <c r="A26" s="24" t="inlineStr">
         <is>
           <t>AY GRİ Levha</t>
         </is>
       </c>
-      <c r="B26" s="50" t="inlineStr">
+      <c r="B26" s="52" t="inlineStr">
         <is>
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="C26" s="43" t="inlineStr">
+      <c r="C26" s="45" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="D26" s="43" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="E26" s="28" t="n">
+      <c r="D26" s="45" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="E26" s="29" t="n">
         <v>57.5</v>
       </c>
-      <c r="F26" s="29" t="n">
+      <c r="F26" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="G26" s="26" t="n">
+      <c r="G26" s="27" t="n">
         <v>6018.08</v>
       </c>
-      <c r="H26" s="29" t="n">
+      <c r="H26" s="30" t="n">
         <v>1297</v>
       </c>
-      <c r="I26" s="30" t="n">
+      <c r="I26" s="31" t="n">
         <v>104.7</v>
       </c>
-      <c r="J26" s="31" t="inlineStr">
+      <c r="J26" s="32" t="inlineStr">
         <is>
           <t>Saatte ~23 Plaka</t>
         </is>
       </c>
-      <c r="K26" s="28" t="n">
+      <c r="K26" s="29" t="n">
         <v>144.9</v>
       </c>
-      <c r="L26" s="38" t="n">
+      <c r="L26" s="40" t="n">
         <v>0.722567287784679</v>
       </c>
-      <c r="M26" s="24" t="inlineStr">
+      <c r="M26" s="25" t="inlineStr">
         <is>
           <t>Standart Tek Çıkışlı Kalıp</t>
         </is>
@@ -8513,17 +8434,17 @@
           <t>BEYAZ TEAK Levha</t>
         </is>
       </c>
-      <c r="B27" s="51" t="inlineStr">
+      <c r="B27" s="53" t="inlineStr">
         <is>
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="C27" s="45" t="inlineStr">
+      <c r="C27" s="47" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="D27" s="45" t="inlineStr">
+      <c r="D27" s="47" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -8561,53 +8482,53 @@
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="23" t="inlineStr">
+      <c r="A28" s="24" t="inlineStr">
         <is>
           <t>CAM ÇITASI</t>
         </is>
       </c>
-      <c r="B28" s="50" t="inlineStr">
+      <c r="B28" s="52" t="inlineStr">
         <is>
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="C28" s="43" t="inlineStr">
+      <c r="C28" s="45" t="inlineStr">
         <is>
           <t>Hat 102</t>
         </is>
       </c>
-      <c r="D28" s="43" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="E28" s="28" t="n">
+      <c r="D28" s="45" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="E28" s="29" t="n">
         <v>150</v>
       </c>
-      <c r="F28" s="29" t="n">
+      <c r="F28" s="30" t="n">
         <v>14</v>
       </c>
-      <c r="G28" s="26" t="n">
+      <c r="G28" s="27" t="n">
         <v>7805</v>
       </c>
-      <c r="H28" s="29" t="n">
+      <c r="H28" s="30" t="n">
         <v>5187</v>
       </c>
-      <c r="I28" s="30" t="n">
+      <c r="I28" s="31" t="n">
         <v>52</v>
       </c>
-      <c r="J28" s="31" t="inlineStr">
+      <c r="J28" s="32" t="inlineStr">
         <is>
           <t>Saatte ~35 Boy</t>
         </is>
       </c>
-      <c r="K28" s="28" t="n">
+      <c r="K28" s="29" t="n">
         <v>50</v>
       </c>
-      <c r="L28" s="33" t="n">
+      <c r="L28" s="34" t="n">
         <v>1.04</v>
       </c>
-      <c r="M28" s="24" t="inlineStr">
+      <c r="M28" s="25" t="inlineStr">
         <is>
           <t>Standart Tek Çıkışlı Kalıp</t>
         </is>
@@ -8619,17 +8540,17 @@
           <t>COCO Levha</t>
         </is>
       </c>
-      <c r="B29" s="51" t="inlineStr">
+      <c r="B29" s="53" t="inlineStr">
         <is>
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="C29" s="45" t="inlineStr">
+      <c r="C29" s="47" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="D29" s="45" t="inlineStr">
+      <c r="D29" s="47" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -8657,7 +8578,7 @@
       <c r="K29" s="14" t="n">
         <v>273.6</v>
       </c>
-      <c r="L29" s="37" t="n">
+      <c r="L29" s="39" t="n">
         <v>0.7244152046783625</v>
       </c>
       <c r="M29" s="8" t="inlineStr">
@@ -8667,53 +8588,53 @@
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="23" t="inlineStr">
+      <c r="A30" s="24" t="inlineStr">
         <is>
           <t>DİŞBUDAK Levha</t>
         </is>
       </c>
-      <c r="B30" s="50" t="inlineStr">
+      <c r="B30" s="52" t="inlineStr">
         <is>
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="C30" s="43" t="inlineStr">
+      <c r="C30" s="45" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="D30" s="43" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="E30" s="28" t="n">
-        <v>1204.5</v>
-      </c>
-      <c r="F30" s="29" t="n">
-        <v>82</v>
-      </c>
-      <c r="G30" s="26" t="n">
-        <v>119746.08</v>
-      </c>
-      <c r="H30" s="29" t="n">
-        <v>25104</v>
-      </c>
-      <c r="I30" s="30" t="n">
-        <v>99.40000000000001</v>
-      </c>
-      <c r="J30" s="31" t="inlineStr">
+      <c r="D30" s="45" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="E30" s="29" t="n">
+        <v>1218.5</v>
+      </c>
+      <c r="F30" s="30" t="n">
+        <v>84</v>
+      </c>
+      <c r="G30" s="27" t="n">
+        <v>122751.18</v>
+      </c>
+      <c r="H30" s="30" t="n">
+        <v>25734</v>
+      </c>
+      <c r="I30" s="31" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="J30" s="32" t="inlineStr">
         <is>
           <t>Saatte ~21 Plaka</t>
         </is>
       </c>
-      <c r="K30" s="28" t="n">
+      <c r="K30" s="29" t="n">
         <v>187.9</v>
       </c>
-      <c r="L30" s="38" t="n">
-        <v>0.5290047897817989</v>
-      </c>
-      <c r="M30" s="24" t="inlineStr">
+      <c r="L30" s="40" t="n">
+        <v>0.5359233634912187</v>
+      </c>
+      <c r="M30" s="25" t="inlineStr">
         <is>
           <t>Standart Tek Çıkışlı Kalıp</t>
         </is>
@@ -8725,17 +8646,17 @@
           <t>KOYU CEVİZ Levha</t>
         </is>
       </c>
-      <c r="B31" s="51" t="inlineStr">
+      <c r="B31" s="53" t="inlineStr">
         <is>
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="C31" s="45" t="inlineStr">
+      <c r="C31" s="47" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="D31" s="45" t="inlineStr">
+      <c r="D31" s="47" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -8763,7 +8684,7 @@
       <c r="K31" s="14" t="n">
         <v>79.2</v>
       </c>
-      <c r="L31" s="37" t="n">
+      <c r="L31" s="39" t="n">
         <v>0.6704545454545454</v>
       </c>
       <c r="M31" s="8" t="inlineStr">
@@ -8773,53 +8694,53 @@
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="23" t="inlineStr">
+      <c r="A32" s="24" t="inlineStr">
         <is>
           <t>KT100-220x24-ANT</t>
         </is>
       </c>
-      <c r="B32" s="50" t="inlineStr">
+      <c r="B32" s="52" t="inlineStr">
         <is>
           <t>3.00 Metre</t>
         </is>
       </c>
-      <c r="C32" s="43" t="inlineStr">
+      <c r="C32" s="45" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="D32" s="43" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="E32" s="28" t="n">
+      <c r="D32" s="45" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="E32" s="29" t="n">
         <v>205.7</v>
       </c>
-      <c r="F32" s="29" t="n">
+      <c r="F32" s="30" t="n">
         <v>23</v>
       </c>
-      <c r="G32" s="26" t="n">
+      <c r="G32" s="27" t="n">
         <v>17678</v>
       </c>
-      <c r="H32" s="29" t="n">
+      <c r="H32" s="30" t="n">
         <v>1712</v>
       </c>
-      <c r="I32" s="30" t="n">
+      <c r="I32" s="31" t="n">
         <v>85.90000000000001</v>
       </c>
-      <c r="J32" s="31" t="inlineStr">
+      <c r="J32" s="32" t="inlineStr">
         <is>
           <t>Saatte ~8 Boy</t>
         </is>
       </c>
-      <c r="K32" s="28" t="n">
+      <c r="K32" s="29" t="n">
         <v>84.7</v>
       </c>
-      <c r="L32" s="33" t="n">
+      <c r="L32" s="34" t="n">
         <v>1.014167650531287</v>
       </c>
-      <c r="M32" s="24" t="inlineStr">
+      <c r="M32" s="25" t="inlineStr">
         <is>
           <t>Standart Tek Çıkışlı Kalıp</t>
         </is>
@@ -8831,17 +8752,17 @@
           <t>KT102-219x26-ANT</t>
         </is>
       </c>
-      <c r="B33" s="51" t="inlineStr">
+      <c r="B33" s="53" t="inlineStr">
         <is>
           <t>3.00 Metre</t>
         </is>
       </c>
-      <c r="C33" s="45" t="inlineStr">
+      <c r="C33" s="47" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="D33" s="45" t="inlineStr">
+      <c r="D33" s="47" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -8879,53 +8800,53 @@
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="23" t="inlineStr">
+      <c r="A34" s="24" t="inlineStr">
         <is>
           <t>KT102-219x26-KAH</t>
         </is>
       </c>
-      <c r="B34" s="50" t="inlineStr">
+      <c r="B34" s="52" t="inlineStr">
         <is>
           <t>3.00 Metre</t>
         </is>
       </c>
-      <c r="C34" s="43" t="inlineStr">
+      <c r="C34" s="45" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="D34" s="43" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="E34" s="28" t="n">
+      <c r="D34" s="45" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="E34" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="F34" s="29" t="n">
+      <c r="F34" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="G34" s="26" t="n">
+      <c r="G34" s="27" t="n">
         <v>463</v>
       </c>
-      <c r="H34" s="29" t="n">
+      <c r="H34" s="30" t="n">
         <v>50</v>
       </c>
-      <c r="I34" s="30" t="n">
+      <c r="I34" s="31" t="n">
         <v>115.8</v>
       </c>
-      <c r="J34" s="31" t="inlineStr">
+      <c r="J34" s="32" t="inlineStr">
         <is>
           <t>Saatte ~12 Boy</t>
         </is>
       </c>
-      <c r="K34" s="28" t="n">
+      <c r="K34" s="29" t="n">
         <v>115.8</v>
       </c>
-      <c r="L34" s="33" t="n">
+      <c r="L34" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="M34" s="24" t="inlineStr">
+      <c r="M34" s="25" t="inlineStr">
         <is>
           <t>Standart Tek Çıkışlı Kalıp</t>
         </is>
@@ -8937,17 +8858,17 @@
           <t>MIX BEYAZ TEAK Levha</t>
         </is>
       </c>
-      <c r="B35" s="51" t="inlineStr">
+      <c r="B35" s="53" t="inlineStr">
         <is>
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="C35" s="45" t="inlineStr">
+      <c r="C35" s="47" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="D35" s="45" t="inlineStr">
+      <c r="D35" s="47" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -8985,70 +8906,70 @@
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="23" t="inlineStr">
+      <c r="A36" s="24" t="inlineStr">
         <is>
           <t>MIX TEAK Levha</t>
         </is>
       </c>
-      <c r="B36" s="50" t="inlineStr">
+      <c r="B36" s="52" t="inlineStr">
         <is>
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="C36" s="43" t="inlineStr">
+      <c r="C36" s="45" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="D36" s="43" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="E36" s="28" t="n">
-        <v>341</v>
-      </c>
-      <c r="F36" s="29" t="n">
-        <v>30</v>
-      </c>
-      <c r="G36" s="26" t="n">
-        <v>32023.75</v>
-      </c>
-      <c r="H36" s="29" t="n">
-        <v>7535</v>
-      </c>
-      <c r="I36" s="30" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="J36" s="31" t="inlineStr">
+      <c r="D36" s="45" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="E36" s="29" t="n">
+        <v>343</v>
+      </c>
+      <c r="F36" s="30" t="n">
+        <v>31</v>
+      </c>
+      <c r="G36" s="27" t="n">
+        <v>32618.75</v>
+      </c>
+      <c r="H36" s="30" t="n">
+        <v>7675</v>
+      </c>
+      <c r="I36" s="31" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="J36" s="32" t="inlineStr">
         <is>
           <t>Saatte ~22 Plaka</t>
         </is>
       </c>
-      <c r="K36" s="28" t="n">
+      <c r="K36" s="29" t="n">
         <v>131.5</v>
       </c>
-      <c r="L36" s="38" t="n">
-        <v>0.7140684410646387</v>
-      </c>
-      <c r="M36" s="24" t="inlineStr">
+      <c r="L36" s="40" t="n">
+        <v>0.7231939163498099</v>
+      </c>
+      <c r="M36" s="25" t="inlineStr">
         <is>
           <t>Standart Tek Çıkışlı Kalıp</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="52" t="inlineStr">
+      <c r="A37" s="54" t="inlineStr">
         <is>
           <t>SEREN</t>
         </is>
       </c>
-      <c r="B37" s="53" t="inlineStr">
+      <c r="B37" s="55" t="inlineStr">
         <is>
           <t>2.10 Metre</t>
         </is>
       </c>
-      <c r="C37" s="54" t="inlineStr">
+      <c r="C37" s="56" t="inlineStr">
         <is>
           <t>Hat 103</t>
         </is>
@@ -9058,103 +8979,103 @@
           <t>Çift Göz (2 Kafa)</t>
         </is>
       </c>
-      <c r="E37" s="55" t="n">
+      <c r="E37" s="57" t="n">
         <v>12</v>
       </c>
-      <c r="F37" s="56" t="n">
+      <c r="F37" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="G37" s="57" t="n">
+      <c r="G37" s="59" t="n">
         <v>760</v>
       </c>
-      <c r="H37" s="56" t="n">
+      <c r="H37" s="58" t="n">
         <v>450</v>
       </c>
-      <c r="I37" s="58" t="n">
+      <c r="I37" s="60" t="n">
         <v>63.3</v>
       </c>
-      <c r="J37" s="59" t="inlineStr">
+      <c r="J37" s="61" t="inlineStr">
         <is>
           <t>Saatte ~38 Boy</t>
         </is>
       </c>
-      <c r="K37" s="55" t="n">
+      <c r="K37" s="57" t="n">
         <v>63.3</v>
       </c>
-      <c r="L37" s="60" t="n">
+      <c r="L37" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="M37" s="61" t="inlineStr">
+      <c r="M37" s="63" t="inlineStr">
         <is>
           <t>Çift Çıkışlı Yüksek Hızlı Kalıp</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="23" t="inlineStr">
+      <c r="A38" s="24" t="inlineStr">
         <is>
           <t>SEREN</t>
         </is>
       </c>
-      <c r="B38" s="50" t="inlineStr">
+      <c r="B38" s="52" t="inlineStr">
         <is>
           <t>2.10 Metre</t>
         </is>
       </c>
-      <c r="C38" s="43" t="inlineStr">
+      <c r="C38" s="45" t="inlineStr">
         <is>
           <t>Hat 104</t>
         </is>
       </c>
-      <c r="D38" s="43" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="E38" s="28" t="n">
+      <c r="D38" s="45" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="E38" s="29" t="n">
         <v>96</v>
       </c>
-      <c r="F38" s="29" t="n">
+      <c r="F38" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="G38" s="26" t="n">
+      <c r="G38" s="27" t="n">
         <v>10910</v>
       </c>
-      <c r="H38" s="29" t="n">
+      <c r="H38" s="30" t="n">
         <v>3171</v>
       </c>
-      <c r="I38" s="30" t="n">
+      <c r="I38" s="31" t="n">
         <v>113.6</v>
       </c>
-      <c r="J38" s="31" t="inlineStr">
+      <c r="J38" s="32" t="inlineStr">
         <is>
           <t>Saatte ~33 Boy</t>
         </is>
       </c>
-      <c r="K38" s="28" t="n">
+      <c r="K38" s="29" t="n">
         <v>99.2</v>
       </c>
-      <c r="L38" s="33" t="n">
+      <c r="L38" s="34" t="n">
         <v>1.145161290322581</v>
       </c>
-      <c r="M38" s="24" t="inlineStr">
+      <c r="M38" s="25" t="inlineStr">
         <is>
           <t>Standart Tek Çıkışlı Kalıp</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="52" t="inlineStr">
+      <c r="A39" s="54" t="inlineStr">
         <is>
           <t>SEREN</t>
         </is>
       </c>
-      <c r="B39" s="53" t="inlineStr">
+      <c r="B39" s="55" t="inlineStr">
         <is>
           <t>2.10 Metre</t>
         </is>
       </c>
-      <c r="C39" s="54" t="inlineStr">
+      <c r="C39" s="56" t="inlineStr">
         <is>
           <t>Hat 104</t>
         </is>
@@ -9164,103 +9085,103 @@
           <t>Çift Göz (2 Kafa)</t>
         </is>
       </c>
-      <c r="E39" s="55" t="n">
-        <v>1526.4</v>
-      </c>
-      <c r="F39" s="56" t="n">
-        <v>138</v>
-      </c>
-      <c r="G39" s="57" t="n">
-        <v>146141.32</v>
-      </c>
-      <c r="H39" s="56" t="n">
-        <v>42876</v>
-      </c>
-      <c r="I39" s="58" t="n">
-        <v>95.7</v>
-      </c>
-      <c r="J39" s="59" t="inlineStr">
+      <c r="E39" s="57" t="n">
+        <v>1550.4</v>
+      </c>
+      <c r="F39" s="58" t="n">
+        <v>140</v>
+      </c>
+      <c r="G39" s="59" t="n">
+        <v>147425.32</v>
+      </c>
+      <c r="H39" s="58" t="n">
+        <v>43256</v>
+      </c>
+      <c r="I39" s="60" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="J39" s="61" t="inlineStr">
         <is>
           <t>Saatte ~28 Boy</t>
         </is>
       </c>
-      <c r="K39" s="55" t="n">
+      <c r="K39" s="57" t="n">
         <v>99.2</v>
       </c>
-      <c r="L39" s="60" t="n">
-        <v>0.9647177419354839</v>
-      </c>
-      <c r="M39" s="61" t="inlineStr">
+      <c r="L39" s="62" t="n">
+        <v>0.9586693548387096</v>
+      </c>
+      <c r="M39" s="63" t="inlineStr">
         <is>
           <t>Çift Çıkışlı Yüksek Hızlı Kalıp</t>
         </is>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="23" t="inlineStr">
+      <c r="A40" s="24" t="inlineStr">
         <is>
           <t>SEREN</t>
         </is>
       </c>
-      <c r="B40" s="50" t="inlineStr">
+      <c r="B40" s="52" t="inlineStr">
         <is>
           <t>2.10 Metre</t>
         </is>
       </c>
-      <c r="C40" s="43" t="inlineStr">
+      <c r="C40" s="45" t="inlineStr">
         <is>
           <t>Hat 105</t>
         </is>
       </c>
-      <c r="D40" s="43" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="E40" s="28" t="n">
+      <c r="D40" s="45" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="E40" s="29" t="n">
         <v>129</v>
       </c>
-      <c r="F40" s="29" t="n">
+      <c r="F40" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="G40" s="26" t="n">
+      <c r="G40" s="27" t="n">
         <v>13117</v>
       </c>
-      <c r="H40" s="29" t="n">
+      <c r="H40" s="30" t="n">
         <v>3772</v>
       </c>
-      <c r="I40" s="30" t="n">
+      <c r="I40" s="31" t="n">
         <v>101.7</v>
       </c>
-      <c r="J40" s="31" t="inlineStr">
+      <c r="J40" s="32" t="inlineStr">
         <is>
           <t>Saatte ~29 Boy</t>
         </is>
       </c>
-      <c r="K40" s="28" t="n">
+      <c r="K40" s="29" t="n">
         <v>92.2</v>
       </c>
-      <c r="L40" s="33" t="n">
+      <c r="L40" s="34" t="n">
         <v>1.103036876355748</v>
       </c>
-      <c r="M40" s="24" t="inlineStr">
+      <c r="M40" s="25" t="inlineStr">
         <is>
           <t>Standart Tek Çıkışlı Kalıp</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="52" t="inlineStr">
+      <c r="A41" s="54" t="inlineStr">
         <is>
           <t>SEREN</t>
         </is>
       </c>
-      <c r="B41" s="53" t="inlineStr">
+      <c r="B41" s="55" t="inlineStr">
         <is>
           <t>2.10 Metre</t>
         </is>
       </c>
-      <c r="C41" s="54" t="inlineStr">
+      <c r="C41" s="56" t="inlineStr">
         <is>
           <t>Hat 105</t>
         </is>
@@ -9270,86 +9191,86 @@
           <t>Çift Göz (2 Kafa)</t>
         </is>
       </c>
-      <c r="E41" s="55" t="n">
+      <c r="E41" s="57" t="n">
         <v>1373.5</v>
       </c>
-      <c r="F41" s="56" t="n">
+      <c r="F41" s="58" t="n">
         <v>123</v>
       </c>
-      <c r="G41" s="57" t="n">
+      <c r="G41" s="59" t="n">
         <v>123688.47</v>
       </c>
-      <c r="H41" s="56" t="n">
+      <c r="H41" s="58" t="n">
         <v>36357</v>
       </c>
-      <c r="I41" s="58" t="n">
+      <c r="I41" s="60" t="n">
         <v>90.09999999999999</v>
       </c>
-      <c r="J41" s="59" t="inlineStr">
+      <c r="J41" s="61" t="inlineStr">
         <is>
           <t>Saatte ~26 Boy</t>
         </is>
       </c>
-      <c r="K41" s="55" t="n">
+      <c r="K41" s="57" t="n">
         <v>92.2</v>
       </c>
-      <c r="L41" s="60" t="n">
+      <c r="L41" s="62" t="n">
         <v>0.9772234273318872</v>
       </c>
-      <c r="M41" s="61" t="inlineStr">
+      <c r="M41" s="63" t="inlineStr">
         <is>
           <t>Çift Çıkışlı Yüksek Hızlı Kalıp</t>
         </is>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="23" t="inlineStr">
+      <c r="A42" s="24" t="inlineStr">
         <is>
           <t>SEREN</t>
         </is>
       </c>
-      <c r="B42" s="50" t="inlineStr">
+      <c r="B42" s="52" t="inlineStr">
         <is>
           <t>2.10 Metre</t>
         </is>
       </c>
-      <c r="C42" s="43" t="inlineStr">
+      <c r="C42" s="45" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="D42" s="43" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="E42" s="28" t="n">
+      <c r="D42" s="45" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="E42" s="29" t="n">
         <v>42</v>
       </c>
-      <c r="F42" s="29" t="n">
+      <c r="F42" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="G42" s="26" t="n">
+      <c r="G42" s="27" t="n">
         <v>3477</v>
       </c>
-      <c r="H42" s="29" t="n">
+      <c r="H42" s="30" t="n">
         <v>865</v>
       </c>
-      <c r="I42" s="30" t="n">
+      <c r="I42" s="31" t="n">
         <v>82.8</v>
       </c>
-      <c r="J42" s="31" t="inlineStr">
+      <c r="J42" s="32" t="inlineStr">
         <is>
           <t>Saatte ~21 Boy</t>
         </is>
       </c>
-      <c r="K42" s="28" t="n">
+      <c r="K42" s="29" t="n">
         <v>82.59999999999999</v>
       </c>
-      <c r="L42" s="33" t="n">
+      <c r="L42" s="34" t="n">
         <v>1.002421307506053</v>
       </c>
-      <c r="M42" s="24" t="inlineStr">
+      <c r="M42" s="25" t="inlineStr">
         <is>
           <t>Standart Tek Çıkışlı Kalıp</t>
         </is>
@@ -9361,35 +9282,35 @@
           <t>SEREN(39mm)</t>
         </is>
       </c>
-      <c r="B43" s="51" t="inlineStr">
+      <c r="B43" s="53" t="inlineStr">
         <is>
           <t>2.10 Metre</t>
         </is>
       </c>
-      <c r="C43" s="45" t="inlineStr">
+      <c r="C43" s="47" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="D43" s="45" t="inlineStr">
+      <c r="D43" s="47" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
       </c>
       <c r="E43" s="14" t="n">
-        <v>279</v>
+        <v>303</v>
       </c>
       <c r="F43" s="15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G43" s="11" t="n">
-        <v>30342</v>
+        <v>32593</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>7938</v>
+        <v>8583</v>
       </c>
       <c r="I43" s="16" t="n">
-        <v>108.8</v>
+        <v>107.6</v>
       </c>
       <c r="J43" s="17" t="inlineStr">
         <is>
@@ -9400,7 +9321,7 @@
         <v>96.09999999999999</v>
       </c>
       <c r="L43" s="19" t="n">
-        <v>1.132154006243496</v>
+        <v>1.119667013527575</v>
       </c>
       <c r="M43" s="8" t="inlineStr">
         <is>
@@ -9409,53 +9330,53 @@
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="23" t="inlineStr">
+      <c r="A44" s="24" t="inlineStr">
         <is>
           <t>SONOMO Levha</t>
         </is>
       </c>
-      <c r="B44" s="50" t="inlineStr">
+      <c r="B44" s="52" t="inlineStr">
         <is>
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="C44" s="43" t="inlineStr">
+      <c r="C44" s="45" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="D44" s="43" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="E44" s="28" t="n">
+      <c r="D44" s="45" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="E44" s="29" t="n">
         <v>106</v>
       </c>
-      <c r="F44" s="29" t="n">
+      <c r="F44" s="30" t="n">
         <v>13</v>
       </c>
-      <c r="G44" s="26" t="n">
+      <c r="G44" s="27" t="n">
         <v>7690.08</v>
       </c>
-      <c r="H44" s="29" t="n">
+      <c r="H44" s="30" t="n">
         <v>1776</v>
       </c>
-      <c r="I44" s="30" t="n">
+      <c r="I44" s="31" t="n">
         <v>72.5</v>
       </c>
-      <c r="J44" s="31" t="inlineStr">
+      <c r="J44" s="32" t="inlineStr">
         <is>
           <t>Saatte ~17 Plaka</t>
         </is>
       </c>
-      <c r="K44" s="28" t="n">
+      <c r="K44" s="29" t="n">
         <v>113.1</v>
       </c>
-      <c r="L44" s="38" t="n">
+      <c r="L44" s="40" t="n">
         <v>0.641025641025641</v>
       </c>
-      <c r="M44" s="24" t="inlineStr">
+      <c r="M44" s="25" t="inlineStr">
         <is>
           <t>Standart Tek Çıkışlı Kalıp</t>
         </is>
@@ -9467,17 +9388,17 @@
           <t>TEAK Levha</t>
         </is>
       </c>
-      <c r="B45" s="51" t="inlineStr">
+      <c r="B45" s="53" t="inlineStr">
         <is>
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="C45" s="45" t="inlineStr">
+      <c r="C45" s="47" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="D45" s="45" t="inlineStr">
+      <c r="D45" s="47" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -9505,7 +9426,7 @@
       <c r="K45" s="14" t="n">
         <v>145.5</v>
       </c>
-      <c r="L45" s="37" t="n">
+      <c r="L45" s="39" t="n">
         <v>0.7800687285223369</v>
       </c>
       <c r="M45" s="8" t="inlineStr">
@@ -9515,53 +9436,53 @@
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="23" t="inlineStr">
+      <c r="A46" s="24" t="inlineStr">
         <is>
           <t>U KAPAMA</t>
         </is>
       </c>
-      <c r="B46" s="50" t="inlineStr">
+      <c r="B46" s="52" t="inlineStr">
         <is>
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="C46" s="43" t="inlineStr">
+      <c r="C46" s="45" t="inlineStr">
         <is>
           <t>Hat 102</t>
         </is>
       </c>
-      <c r="D46" s="43" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="E46" s="28" t="n">
+      <c r="D46" s="45" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="E46" s="29" t="n">
         <v>34</v>
       </c>
-      <c r="F46" s="29" t="n">
+      <c r="F46" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="G46" s="26" t="n">
+      <c r="G46" s="27" t="n">
         <v>1385</v>
       </c>
-      <c r="H46" s="29" t="n">
+      <c r="H46" s="30" t="n">
         <v>2901</v>
       </c>
-      <c r="I46" s="30" t="n">
+      <c r="I46" s="31" t="n">
         <v>40.7</v>
       </c>
-      <c r="J46" s="31" t="inlineStr">
+      <c r="J46" s="32" t="inlineStr">
         <is>
           <t>Saatte ~85 Boy</t>
         </is>
       </c>
-      <c r="K46" s="28" t="n">
+      <c r="K46" s="29" t="n">
         <v>40.7</v>
       </c>
-      <c r="L46" s="33" t="n">
+      <c r="L46" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="M46" s="24" t="inlineStr">
+      <c r="M46" s="25" t="inlineStr">
         <is>
           <t>Standart Tek Çıkışlı Kalıp</t>
         </is>
@@ -9573,17 +9494,17 @@
           <t>VIZON Levha</t>
         </is>
       </c>
-      <c r="B47" s="51" t="inlineStr">
+      <c r="B47" s="53" t="inlineStr">
         <is>
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="C47" s="45" t="inlineStr">
+      <c r="C47" s="47" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="D47" s="45" t="inlineStr">
+      <c r="D47" s="47" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>

--- a/static/Ergunbas_Urun_Hat_Rotalari_ve_Kapasite_Analizi.xlsx
+++ b/static/Ergunbas_Urun_Hat_Rotalari_ve_Kapasite_Analizi.xlsx
@@ -868,7 +868,7 @@
       </c>
       <c r="L4" s="6" t="inlineStr">
         <is>
-          <t>Fiili Hız (Saatte ~X Boy)</t>
+          <t>Fiili Hız (Saatte ~X Boy/Plaka)</t>
         </is>
       </c>
       <c r="M4" s="6" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>Standart Hız (Saatte ~X Boy)</t>
+          <t>Standart Hız (Saatte ~X Boy/Plaka)</t>
         </is>
       </c>
       <c r="P4" s="6" t="inlineStr">
@@ -1380,32 +1380,32 @@
         </is>
       </c>
       <c r="I9" s="14" t="n">
-        <v>1218.5</v>
+        <v>622.6096835790281</v>
       </c>
       <c r="J9" s="15" t="n">
         <v>84</v>
       </c>
       <c r="K9" s="16" t="n">
-        <v>100.7</v>
+        <v>203.9</v>
       </c>
       <c r="L9" s="17" t="inlineStr">
         <is>
-          <t>Saatte ~21 Plaka</t>
+          <t>Saatte ~43 Plaka</t>
         </is>
       </c>
       <c r="M9" s="11" t="n">
-        <v>2416.8</v>
+        <v>4893.6</v>
       </c>
       <c r="N9" s="14" t="n">
-        <v>187.9</v>
+        <v>190</v>
       </c>
       <c r="O9" s="18" t="inlineStr">
         <is>
-          <t>Saatte ~39 Plaka</t>
-        </is>
-      </c>
-      <c r="P9" s="39" t="n">
-        <v>0.536</v>
+          <t>Saatte ~40 Plaka</t>
+        </is>
+      </c>
+      <c r="P9" s="19" t="n">
+        <v>1.073</v>
       </c>
       <c r="Q9" s="23" t="inlineStr">
         <is>
@@ -1590,32 +1590,32 @@
         </is>
       </c>
       <c r="I11" s="14" t="n">
-        <v>350.5</v>
+        <v>235.1702808249805</v>
       </c>
       <c r="J11" s="15" t="n">
         <v>37</v>
       </c>
       <c r="K11" s="16" t="n">
-        <v>113.5</v>
+        <v>165.8</v>
       </c>
       <c r="L11" s="17" t="inlineStr">
         <is>
-          <t>Saatte ~27 Plaka</t>
+          <t>Saatte ~39 Plaka</t>
         </is>
       </c>
       <c r="M11" s="11" t="n">
-        <v>2724</v>
+        <v>3979.2</v>
       </c>
       <c r="N11" s="14" t="n">
-        <v>145.5</v>
+        <v>190</v>
       </c>
       <c r="O11" s="18" t="inlineStr">
         <is>
-          <t>Saatte ~34 Plaka</t>
-        </is>
-      </c>
-      <c r="P11" s="39" t="n">
-        <v>0.78</v>
+          <t>Saatte ~45 Plaka</t>
+        </is>
+      </c>
+      <c r="P11" s="19" t="n">
+        <v>0.873</v>
       </c>
       <c r="Q11" s="23" t="inlineStr">
         <is>
@@ -1698,32 +1698,32 @@
         </is>
       </c>
       <c r="I12" s="29" t="n">
-        <v>343</v>
+        <v>187.6562562708018</v>
       </c>
       <c r="J12" s="30" t="n">
         <v>31</v>
       </c>
       <c r="K12" s="31" t="n">
-        <v>95.09999999999999</v>
+        <v>174</v>
       </c>
       <c r="L12" s="32" t="inlineStr">
         <is>
-          <t>Saatte ~22 Plaka</t>
+          <t>Saatte ~41 Plaka</t>
         </is>
       </c>
       <c r="M12" s="27" t="n">
-        <v>2282.4</v>
+        <v>4176</v>
       </c>
       <c r="N12" s="29" t="n">
-        <v>131.5</v>
+        <v>190</v>
       </c>
       <c r="O12" s="33" t="inlineStr">
         <is>
-          <t>Saatte ~31 Plaka</t>
-        </is>
-      </c>
-      <c r="P12" s="40" t="n">
-        <v>0.723</v>
+          <t>Saatte ~45 Plaka</t>
+        </is>
+      </c>
+      <c r="P12" s="34" t="n">
+        <v>0.9159999999999999</v>
       </c>
       <c r="Q12" s="38" t="inlineStr">
         <is>
@@ -1914,32 +1914,32 @@
         </is>
       </c>
       <c r="I14" s="29" t="n">
-        <v>260</v>
+        <v>173.7487454529077</v>
       </c>
       <c r="J14" s="30" t="n">
         <v>30</v>
       </c>
       <c r="K14" s="31" t="n">
-        <v>123.3</v>
+        <v>178.7</v>
       </c>
       <c r="L14" s="32" t="inlineStr">
         <is>
-          <t>Saatte ~28 Plaka</t>
+          <t>Saatte ~40 Plaka</t>
         </is>
       </c>
       <c r="M14" s="27" t="n">
-        <v>2959.2</v>
+        <v>4288.8</v>
       </c>
       <c r="N14" s="29" t="n">
-        <v>148.4</v>
+        <v>190</v>
       </c>
       <c r="O14" s="33" t="inlineStr">
         <is>
-          <t>Saatte ~34 Plaka</t>
+          <t>Saatte ~43 Plaka</t>
         </is>
       </c>
       <c r="P14" s="34" t="n">
-        <v>0.831</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="Q14" s="38" t="inlineStr">
         <is>
@@ -2022,32 +2022,32 @@
         </is>
       </c>
       <c r="I15" s="14" t="n">
-        <v>193</v>
+        <v>114.2245721724266</v>
       </c>
       <c r="J15" s="15" t="n">
         <v>22</v>
       </c>
       <c r="K15" s="16" t="n">
-        <v>95.2</v>
+        <v>159.9</v>
       </c>
       <c r="L15" s="17" t="inlineStr">
         <is>
-          <t>Saatte ~20 Plaka</t>
+          <t>Saatte ~34 Plaka</t>
         </is>
       </c>
       <c r="M15" s="11" t="n">
-        <v>2284.8</v>
+        <v>3837.6</v>
       </c>
       <c r="N15" s="14" t="n">
-        <v>116.2</v>
+        <v>190</v>
       </c>
       <c r="O15" s="18" t="inlineStr">
         <is>
-          <t>Saatte ~24 Plaka</t>
+          <t>Saatte ~40 Plaka</t>
         </is>
       </c>
       <c r="P15" s="19" t="n">
-        <v>0.8190000000000001</v>
+        <v>0.8420000000000001</v>
       </c>
       <c r="Q15" s="23" t="inlineStr">
         <is>
@@ -2664,32 +2664,32 @@
         </is>
       </c>
       <c r="I21" s="14" t="n">
-        <v>69</v>
+        <v>48.79255891118007</v>
       </c>
       <c r="J21" s="15" t="n">
         <v>9</v>
       </c>
       <c r="K21" s="16" t="n">
-        <v>132.2</v>
+        <v>187.5</v>
       </c>
       <c r="L21" s="17" t="inlineStr">
         <is>
-          <t>Saatte ~31 Plaka</t>
+          <t>Saatte ~44 Plaka</t>
         </is>
       </c>
       <c r="M21" s="11" t="n">
-        <v>3172.8</v>
+        <v>4500</v>
       </c>
       <c r="N21" s="14" t="n">
-        <v>118.6</v>
+        <v>190</v>
       </c>
       <c r="O21" s="18" t="inlineStr">
         <is>
-          <t>Saatte ~28 Plaka</t>
+          <t>Saatte ~45 Plaka</t>
         </is>
       </c>
       <c r="P21" s="19" t="n">
-        <v>1.115</v>
+        <v>0.987</v>
       </c>
       <c r="Q21" s="23" t="inlineStr">
         <is>
@@ -2880,32 +2880,32 @@
         </is>
       </c>
       <c r="I23" s="14" t="n">
-        <v>106</v>
+        <v>57.25702552864577</v>
       </c>
       <c r="J23" s="15" t="n">
         <v>13</v>
       </c>
       <c r="K23" s="16" t="n">
-        <v>72.5</v>
+        <v>131.6</v>
       </c>
       <c r="L23" s="17" t="inlineStr">
         <is>
-          <t>Saatte ~17 Plaka</t>
+          <t>Saatte ~30 Plaka</t>
         </is>
       </c>
       <c r="M23" s="11" t="n">
-        <v>1740</v>
+        <v>3158.4</v>
       </c>
       <c r="N23" s="14" t="n">
-        <v>113.1</v>
+        <v>190</v>
       </c>
       <c r="O23" s="18" t="inlineStr">
         <is>
-          <t>Saatte ~26 Plaka</t>
+          <t>Saatte ~44 Plaka</t>
         </is>
       </c>
       <c r="P23" s="39" t="n">
-        <v>0.6409999999999999</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="Q23" s="23" t="inlineStr">
         <is>
@@ -2988,32 +2988,32 @@
         </is>
       </c>
       <c r="I24" s="29" t="n">
-        <v>57.5</v>
+        <v>38.03440860215053</v>
       </c>
       <c r="J24" s="30" t="n">
         <v>8</v>
       </c>
       <c r="K24" s="31" t="n">
-        <v>104.7</v>
+        <v>185.6</v>
       </c>
       <c r="L24" s="32" t="inlineStr">
         <is>
-          <t>Saatte ~23 Plaka</t>
+          <t>Saatte ~40 Plaka</t>
         </is>
       </c>
       <c r="M24" s="27" t="n">
-        <v>2512.8</v>
+        <v>4454.4</v>
       </c>
       <c r="N24" s="29" t="n">
-        <v>144.9</v>
+        <v>190</v>
       </c>
       <c r="O24" s="33" t="inlineStr">
         <is>
-          <t>Saatte ~31 Plaka</t>
-        </is>
-      </c>
-      <c r="P24" s="40" t="n">
-        <v>0.723</v>
+          <t>Saatte ~41 Plaka</t>
+        </is>
+      </c>
+      <c r="P24" s="34" t="n">
+        <v>0.977</v>
       </c>
       <c r="Q24" s="38" t="inlineStr">
         <is>
@@ -3096,32 +3096,32 @@
         </is>
       </c>
       <c r="I25" s="14" t="n">
-        <v>78</v>
+        <v>41.52884989747753</v>
       </c>
       <c r="J25" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K25" s="16" t="n">
-        <v>71.90000000000001</v>
+        <v>35</v>
       </c>
       <c r="L25" s="17" t="inlineStr">
         <is>
-          <t>Saatte ~15 Plaka</t>
+          <t>Saatte ~7 Plaka</t>
         </is>
       </c>
       <c r="M25" s="11" t="n">
-        <v>1725.6</v>
+        <v>840</v>
       </c>
       <c r="N25" s="14" t="n">
-        <v>111.8</v>
+        <v>190</v>
       </c>
       <c r="O25" s="18" t="inlineStr">
         <is>
-          <t>Saatte ~23 Plaka</t>
+          <t>Saatte ~40 Plaka</t>
         </is>
       </c>
       <c r="P25" s="39" t="n">
-        <v>0.643</v>
+        <v>0.184</v>
       </c>
       <c r="Q25" s="23" t="inlineStr">
         <is>
@@ -3204,32 +3204,32 @@
         </is>
       </c>
       <c r="I26" s="29" t="n">
-        <v>72.5</v>
+        <v>31.97761876040141</v>
       </c>
       <c r="J26" s="30" t="n">
         <v>7</v>
       </c>
       <c r="K26" s="31" t="n">
-        <v>53.1</v>
+        <v>95.8</v>
       </c>
       <c r="L26" s="32" t="inlineStr">
         <is>
-          <t>Saatte ~11 Plaka</t>
+          <t>Saatte ~20 Plaka</t>
         </is>
       </c>
       <c r="M26" s="27" t="n">
-        <v>1274.4</v>
+        <v>2299.2</v>
       </c>
       <c r="N26" s="29" t="n">
-        <v>79.2</v>
+        <v>190</v>
       </c>
       <c r="O26" s="33" t="inlineStr">
         <is>
-          <t>Saatte ~16 Plaka</t>
+          <t>Saatte ~40 Plaka</t>
         </is>
       </c>
       <c r="P26" s="40" t="n">
-        <v>0.67</v>
+        <v>0.504</v>
       </c>
       <c r="Q26" s="38" t="inlineStr">
         <is>
@@ -3318,26 +3318,26 @@
         <v>3</v>
       </c>
       <c r="K27" s="16" t="n">
-        <v>198.2</v>
+        <v>134.1</v>
       </c>
       <c r="L27" s="17" t="inlineStr">
         <is>
-          <t>Saatte ~41 Plaka</t>
+          <t>Saatte ~28 Plaka</t>
         </is>
       </c>
       <c r="M27" s="11" t="n">
-        <v>4756.8</v>
+        <v>3218.4</v>
       </c>
       <c r="N27" s="14" t="n">
-        <v>273.6</v>
+        <v>190</v>
       </c>
       <c r="O27" s="18" t="inlineStr">
         <is>
-          <t>Saatte ~57 Plaka</t>
+          <t>Saatte ~40 Plaka</t>
         </is>
       </c>
       <c r="P27" s="39" t="n">
-        <v>0.7240000000000001</v>
+        <v>0.706</v>
       </c>
       <c r="Q27" s="23" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
       <c r="G31" s="42" t="n"/>
       <c r="H31" s="42" t="n"/>
       <c r="I31" s="44" t="n">
-        <v>11092.7</v>
+        <v>9895.700000000003</v>
       </c>
       <c r="J31" s="42" t="n"/>
       <c r="K31" s="42" t="n"/>
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="D13" s="14" t="n">
-        <v>2762.5</v>
+        <v>1565.5</v>
       </c>
       <c r="E13" s="15" t="n">
         <v>252</v>
@@ -4296,7 +4296,7 @@
         <v>280733.6800000001</v>
       </c>
       <c r="G13" s="16" t="n">
-        <v>101.6</v>
+        <v>179.3</v>
       </c>
       <c r="H13" s="48" t="n">
         <v>11</v>
@@ -4326,7 +4326,7 @@
       <c r="B14" s="42" t="n"/>
       <c r="C14" s="42" t="n"/>
       <c r="D14" s="44" t="n">
-        <v>16095.4</v>
+        <v>14898.4</v>
       </c>
       <c r="E14" s="43" t="n">
         <v>1480</v>
@@ -4335,7 +4335,7 @@
         <v>1266753.58</v>
       </c>
       <c r="G14" s="44" t="n">
-        <v>78.7</v>
+        <v>85</v>
       </c>
       <c r="H14" s="42" t="n"/>
       <c r="I14" s="42" t="n"/>
@@ -4459,7 +4459,7 @@
       </c>
       <c r="N3" s="6" t="inlineStr">
         <is>
-          <t>Fiili Hız (Saatte ~X Boy)</t>
+          <t>Fiili Hız (Saatte ~X Boy/Plaka)</t>
         </is>
       </c>
       <c r="O3" s="6" t="inlineStr">
@@ -4635,7 +4635,7 @@
         </is>
       </c>
       <c r="H6" s="29" t="n">
-        <v>1218.5</v>
+        <v>622.6096835790281</v>
       </c>
       <c r="I6" s="30" t="n">
         <v>84</v>
@@ -4652,11 +4652,11 @@
         <v>122751.18</v>
       </c>
       <c r="M6" s="31" t="n">
-        <v>100.7</v>
+        <v>197.2</v>
       </c>
       <c r="N6" s="32" t="inlineStr">
         <is>
-          <t>Saatte ~21 Plaka</t>
+          <t>Saatte ~41 Plaka</t>
         </is>
       </c>
       <c r="O6" s="50" t="n">
@@ -5090,7 +5090,7 @@
         </is>
       </c>
       <c r="H13" s="14" t="n">
-        <v>350.5</v>
+        <v>235.1702808249805</v>
       </c>
       <c r="I13" s="15" t="n">
         <v>37</v>
@@ -5107,11 +5107,11 @@
         <v>39775.75</v>
       </c>
       <c r="M13" s="16" t="n">
-        <v>113.5</v>
+        <v>169.1</v>
       </c>
       <c r="N13" s="17" t="inlineStr">
         <is>
-          <t>Saatte ~27 Plaka</t>
+          <t>Saatte ~40 Plaka</t>
         </is>
       </c>
       <c r="O13" s="51" t="n">
@@ -5220,7 +5220,7 @@
         </is>
       </c>
       <c r="H15" s="14" t="n">
-        <v>343</v>
+        <v>187.6562562708018</v>
       </c>
       <c r="I15" s="15" t="n">
         <v>31</v>
@@ -5237,11 +5237,11 @@
         <v>32618.75</v>
       </c>
       <c r="M15" s="16" t="n">
-        <v>95.09999999999999</v>
+        <v>173.8</v>
       </c>
       <c r="N15" s="17" t="inlineStr">
         <is>
-          <t>Saatte ~22 Plaka</t>
+          <t>Saatte ~41 Plaka</t>
         </is>
       </c>
       <c r="O15" s="51" t="n">
@@ -5350,7 +5350,7 @@
         </is>
       </c>
       <c r="H17" s="14" t="n">
-        <v>260</v>
+        <v>173.7487454529077</v>
       </c>
       <c r="I17" s="15" t="n">
         <v>30</v>
@@ -5367,11 +5367,11 @@
         <v>32060.7</v>
       </c>
       <c r="M17" s="16" t="n">
-        <v>123.3</v>
+        <v>184.5</v>
       </c>
       <c r="N17" s="17" t="inlineStr">
         <is>
-          <t>Saatte ~28 Plaka</t>
+          <t>Saatte ~42 Plaka</t>
         </is>
       </c>
       <c r="O17" s="51" t="n">
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="H19" s="14" t="n">
-        <v>193</v>
+        <v>114.2245721724266</v>
       </c>
       <c r="I19" s="15" t="n">
         <v>22</v>
@@ -5497,11 +5497,11 @@
         <v>18364.5</v>
       </c>
       <c r="M19" s="16" t="n">
-        <v>95.2</v>
+        <v>160.8</v>
       </c>
       <c r="N19" s="17" t="inlineStr">
         <is>
-          <t>Saatte ~20 Plaka</t>
+          <t>Saatte ~34 Plaka</t>
         </is>
       </c>
       <c r="O19" s="51" t="n">
@@ -5870,7 +5870,7 @@
         </is>
       </c>
       <c r="H25" s="14" t="n">
-        <v>69</v>
+        <v>48.79255891118007</v>
       </c>
       <c r="I25" s="15" t="n">
         <v>9</v>
@@ -5887,11 +5887,11 @@
         <v>9124.75</v>
       </c>
       <c r="M25" s="16" t="n">
-        <v>132.2</v>
+        <v>187</v>
       </c>
       <c r="N25" s="17" t="inlineStr">
         <is>
-          <t>Saatte ~31 Plaka</t>
+          <t>Saatte ~44 Plaka</t>
         </is>
       </c>
       <c r="O25" s="51" t="n">
@@ -6000,7 +6000,7 @@
         </is>
       </c>
       <c r="H27" s="14" t="n">
-        <v>106</v>
+        <v>57.25702552864577</v>
       </c>
       <c r="I27" s="15" t="n">
         <v>13</v>
@@ -6017,11 +6017,11 @@
         <v>7690.08</v>
       </c>
       <c r="M27" s="16" t="n">
-        <v>72.5</v>
+        <v>134.3</v>
       </c>
       <c r="N27" s="17" t="inlineStr">
         <is>
-          <t>Saatte ~17 Plaka</t>
+          <t>Saatte ~31 Plaka</t>
         </is>
       </c>
       <c r="O27" s="51" t="n">
@@ -6065,7 +6065,7 @@
         </is>
       </c>
       <c r="H28" s="29" t="n">
-        <v>57.5</v>
+        <v>38.03440860215053</v>
       </c>
       <c r="I28" s="30" t="n">
         <v>8</v>
@@ -6082,11 +6082,11 @@
         <v>6018.08</v>
       </c>
       <c r="M28" s="31" t="n">
-        <v>104.7</v>
+        <v>158.2</v>
       </c>
       <c r="N28" s="32" t="inlineStr">
         <is>
-          <t>Saatte ~23 Plaka</t>
+          <t>Saatte ~34 Plaka</t>
         </is>
       </c>
       <c r="O28" s="50" t="n">
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c r="H29" s="14" t="n">
-        <v>78</v>
+        <v>41.52884989747753</v>
       </c>
       <c r="I29" s="15" t="n">
         <v>8</v>
@@ -6147,11 +6147,11 @@
         <v>5609.52</v>
       </c>
       <c r="M29" s="16" t="n">
-        <v>71.90000000000001</v>
+        <v>135.1</v>
       </c>
       <c r="N29" s="17" t="inlineStr">
         <is>
-          <t>Saatte ~15 Plaka</t>
+          <t>Saatte ~28 Plaka</t>
         </is>
       </c>
       <c r="O29" s="51" t="n">
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="H30" s="29" t="n">
-        <v>72.5</v>
+        <v>31.97761876040141</v>
       </c>
       <c r="I30" s="30" t="n">
         <v>7</v>
@@ -6212,11 +6212,11 @@
         <v>3846.37</v>
       </c>
       <c r="M30" s="31" t="n">
-        <v>53.1</v>
+        <v>120.3</v>
       </c>
       <c r="N30" s="32" t="inlineStr">
         <is>
-          <t>Saatte ~11 Plaka</t>
+          <t>Saatte ~25 Plaka</t>
         </is>
       </c>
       <c r="O30" s="50" t="n">
@@ -7081,7 +7081,7 @@
       <c r="F44" s="42" t="n"/>
       <c r="G44" s="42" t="n"/>
       <c r="H44" s="44" t="n">
-        <v>16095.4</v>
+        <v>14898.4</v>
       </c>
       <c r="I44" s="42" t="n"/>
       <c r="J44" s="43" t="n">
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="E25" s="14" t="n">
-        <v>78</v>
+        <v>41.52884989747753</v>
       </c>
       <c r="F25" s="15" t="n">
         <v>8</v>
@@ -8356,18 +8356,18 @@
         <v>1176</v>
       </c>
       <c r="I25" s="16" t="n">
-        <v>71.90000000000001</v>
+        <v>135.1</v>
       </c>
       <c r="J25" s="17" t="inlineStr">
         <is>
-          <t>Saatte ~15 Plaka</t>
+          <t>Saatte ~28 Plaka</t>
         </is>
       </c>
       <c r="K25" s="14" t="n">
-        <v>111.8</v>
+        <v>190</v>
       </c>
       <c r="L25" s="39" t="n">
-        <v>0.6431127012522362</v>
+        <v>0.7110526315789474</v>
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         </is>
       </c>
       <c r="E26" s="29" t="n">
-        <v>57.5</v>
+        <v>38.03440860215053</v>
       </c>
       <c r="F26" s="30" t="n">
         <v>8</v>
@@ -8409,18 +8409,18 @@
         <v>1297</v>
       </c>
       <c r="I26" s="31" t="n">
-        <v>104.7</v>
+        <v>158.2</v>
       </c>
       <c r="J26" s="32" t="inlineStr">
         <is>
-          <t>Saatte ~23 Plaka</t>
+          <t>Saatte ~34 Plaka</t>
         </is>
       </c>
       <c r="K26" s="29" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="L26" s="40" t="n">
-        <v>0.722567287784679</v>
+        <v>190</v>
+      </c>
+      <c r="L26" s="34" t="n">
+        <v>0.8326315789473684</v>
       </c>
       <c r="M26" s="25" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         </is>
       </c>
       <c r="E27" s="14" t="n">
-        <v>260</v>
+        <v>173.7487454529077</v>
       </c>
       <c r="F27" s="15" t="n">
         <v>30</v>
@@ -8462,18 +8462,18 @@
         <v>7270</v>
       </c>
       <c r="I27" s="16" t="n">
-        <v>123.3</v>
+        <v>184.5</v>
       </c>
       <c r="J27" s="17" t="inlineStr">
         <is>
-          <t>Saatte ~28 Plaka</t>
+          <t>Saatte ~42 Plaka</t>
         </is>
       </c>
       <c r="K27" s="14" t="n">
-        <v>148.4</v>
+        <v>190</v>
       </c>
       <c r="L27" s="19" t="n">
-        <v>0.8308625336927222</v>
+        <v>0.9710526315789474</v>
       </c>
       <c r="M27" s="8" t="inlineStr">
         <is>
@@ -8576,10 +8576,10 @@
         </is>
       </c>
       <c r="K29" s="14" t="n">
-        <v>273.6</v>
-      </c>
-      <c r="L29" s="39" t="n">
-        <v>0.7244152046783625</v>
+        <v>190</v>
+      </c>
+      <c r="L29" s="19" t="n">
+        <v>1.043157894736842</v>
       </c>
       <c r="M29" s="8" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         </is>
       </c>
       <c r="E30" s="29" t="n">
-        <v>1218.5</v>
+        <v>622.6096835790281</v>
       </c>
       <c r="F30" s="30" t="n">
         <v>84</v>
@@ -8621,18 +8621,18 @@
         <v>25734</v>
       </c>
       <c r="I30" s="31" t="n">
-        <v>100.7</v>
+        <v>197.2</v>
       </c>
       <c r="J30" s="32" t="inlineStr">
         <is>
-          <t>Saatte ~21 Plaka</t>
+          <t>Saatte ~41 Plaka</t>
         </is>
       </c>
       <c r="K30" s="29" t="n">
-        <v>187.9</v>
-      </c>
-      <c r="L30" s="40" t="n">
-        <v>0.5359233634912187</v>
+        <v>190</v>
+      </c>
+      <c r="L30" s="34" t="n">
+        <v>1.037894736842105</v>
       </c>
       <c r="M30" s="25" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         </is>
       </c>
       <c r="E31" s="14" t="n">
-        <v>72.5</v>
+        <v>31.97761876040141</v>
       </c>
       <c r="F31" s="15" t="n">
         <v>7</v>
@@ -8674,18 +8674,18 @@
         <v>803</v>
       </c>
       <c r="I31" s="16" t="n">
-        <v>53.1</v>
+        <v>120.3</v>
       </c>
       <c r="J31" s="17" t="inlineStr">
         <is>
-          <t>Saatte ~11 Plaka</t>
+          <t>Saatte ~25 Plaka</t>
         </is>
       </c>
       <c r="K31" s="14" t="n">
-        <v>79.2</v>
+        <v>190</v>
       </c>
       <c r="L31" s="39" t="n">
-        <v>0.6704545454545454</v>
+        <v>0.6331578947368421</v>
       </c>
       <c r="M31" s="8" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         </is>
       </c>
       <c r="E35" s="14" t="n">
-        <v>69</v>
+        <v>48.79255891118007</v>
       </c>
       <c r="F35" s="15" t="n">
         <v>9</v>
@@ -8886,18 +8886,18 @@
         <v>2147</v>
       </c>
       <c r="I35" s="16" t="n">
-        <v>132.2</v>
+        <v>187</v>
       </c>
       <c r="J35" s="17" t="inlineStr">
         <is>
-          <t>Saatte ~31 Plaka</t>
+          <t>Saatte ~44 Plaka</t>
         </is>
       </c>
       <c r="K35" s="14" t="n">
-        <v>118.6</v>
+        <v>190</v>
       </c>
       <c r="L35" s="19" t="n">
-        <v>1.114671163575042</v>
+        <v>0.9842105263157894</v>
       </c>
       <c r="M35" s="8" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         </is>
       </c>
       <c r="E36" s="29" t="n">
-        <v>343</v>
+        <v>187.6562562708018</v>
       </c>
       <c r="F36" s="30" t="n">
         <v>31</v>
@@ -8939,18 +8939,18 @@
         <v>7675</v>
       </c>
       <c r="I36" s="31" t="n">
-        <v>95.09999999999999</v>
+        <v>173.8</v>
       </c>
       <c r="J36" s="32" t="inlineStr">
         <is>
-          <t>Saatte ~22 Plaka</t>
+          <t>Saatte ~41 Plaka</t>
         </is>
       </c>
       <c r="K36" s="29" t="n">
-        <v>131.5</v>
-      </c>
-      <c r="L36" s="40" t="n">
-        <v>0.7231939163498099</v>
+        <v>190</v>
+      </c>
+      <c r="L36" s="34" t="n">
+        <v>0.9147368421052632</v>
       </c>
       <c r="M36" s="25" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         </is>
       </c>
       <c r="E44" s="29" t="n">
-        <v>106</v>
+        <v>57.25702552864577</v>
       </c>
       <c r="F44" s="30" t="n">
         <v>13</v>
@@ -9363,18 +9363,18 @@
         <v>1776</v>
       </c>
       <c r="I44" s="31" t="n">
-        <v>72.5</v>
+        <v>134.3</v>
       </c>
       <c r="J44" s="32" t="inlineStr">
         <is>
-          <t>Saatte ~17 Plaka</t>
+          <t>Saatte ~31 Plaka</t>
         </is>
       </c>
       <c r="K44" s="29" t="n">
-        <v>113.1</v>
+        <v>190</v>
       </c>
       <c r="L44" s="40" t="n">
-        <v>0.641025641025641</v>
+        <v>0.7068421052631579</v>
       </c>
       <c r="M44" s="25" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="E45" s="14" t="n">
-        <v>350.5</v>
+        <v>235.1702808249805</v>
       </c>
       <c r="F45" s="15" t="n">
         <v>37</v>
@@ -9416,18 +9416,18 @@
         <v>9359</v>
       </c>
       <c r="I45" s="16" t="n">
-        <v>113.5</v>
+        <v>169.1</v>
       </c>
       <c r="J45" s="17" t="inlineStr">
         <is>
-          <t>Saatte ~27 Plaka</t>
+          <t>Saatte ~40 Plaka</t>
         </is>
       </c>
       <c r="K45" s="14" t="n">
-        <v>145.5</v>
-      </c>
-      <c r="L45" s="39" t="n">
-        <v>0.7800687285223369</v>
+        <v>190</v>
+      </c>
+      <c r="L45" s="19" t="n">
+        <v>0.89</v>
       </c>
       <c r="M45" s="8" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="E47" s="14" t="n">
-        <v>193</v>
+        <v>114.2245721724266</v>
       </c>
       <c r="F47" s="15" t="n">
         <v>22</v>
@@ -9522,18 +9522,18 @@
         <v>3850</v>
       </c>
       <c r="I47" s="16" t="n">
-        <v>95.2</v>
+        <v>160.8</v>
       </c>
       <c r="J47" s="17" t="inlineStr">
         <is>
-          <t>Saatte ~20 Plaka</t>
+          <t>Saatte ~34 Plaka</t>
         </is>
       </c>
       <c r="K47" s="14" t="n">
-        <v>116.2</v>
+        <v>190</v>
       </c>
       <c r="L47" s="19" t="n">
-        <v>0.8192771084337349</v>
+        <v>0.8463157894736842</v>
       </c>
       <c r="M47" s="8" t="inlineStr">
         <is>

--- a/static/Ergunbas_Urun_Hat_Rotalari_ve_Kapasite_Analizi.xlsx
+++ b/static/Ergunbas_Urun_Hat_Rotalari_ve_Kapasite_Analizi.xlsx
@@ -12,16 +12,24 @@
     <sheet name="Ürün x Hat Fiili Üretim" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Tek Göz vs Çift Göz Analizi" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ürün Rotaları &amp; Kapasite'!$A$4:$X$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Hat &amp; Makine Çalışma Özeti'!$A$3:$K$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Ürün x Hat Fiili Üretim'!$A$3:$O$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Tek Göz vs Çift Göz Analizi'!$A$3:$M$47</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.0"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
+  <numFmts count="5">
+    <numFmt numFmtId="164" formatCode="0.00 &quot;kg&quot;"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0"/>
+    <numFmt numFmtId="166" formatCode="#,##0 &quot; Boy/sa&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="#,##0 &quot; Plaka/sa&quot;"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -192,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -221,7 +229,7 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -233,22 +241,22 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -257,7 +265,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -269,7 +277,7 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -278,22 +286,22 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="166" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="166" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -302,16 +310,40 @@
     <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -319,7 +351,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -333,10 +365,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -354,7 +386,7 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -363,13 +395,13 @@
     <xf numFmtId="3" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="166" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -953,13 +985,11 @@
           <t>38 x 45 mm</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>3.39 kg/boy</t>
-        </is>
+      <c r="E5" s="10" t="n">
+        <v>3.39</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>299377.79</v>
+        <v>303801.79</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -972,32 +1002,28 @@
         </is>
       </c>
       <c r="I5" s="14" t="n">
-        <v>1646.4</v>
+        <v>1670.4</v>
       </c>
       <c r="J5" s="15" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K5" s="16" t="n">
-        <v>96.2</v>
-      </c>
-      <c r="L5" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~28 Boy</t>
-        </is>
+        <v>96.3</v>
+      </c>
+      <c r="L5" s="17" t="n">
+        <v>28</v>
       </c>
       <c r="M5" s="11" t="n">
-        <v>2308.8</v>
+        <v>2311.2</v>
       </c>
       <c r="N5" s="14" t="n">
         <v>99.2</v>
       </c>
-      <c r="O5" s="18" t="inlineStr">
-        <is>
-          <t>Saatte ~29 Boy</t>
-        </is>
+      <c r="O5" s="18" t="n">
+        <v>29</v>
       </c>
       <c r="P5" s="19" t="n">
-        <v>0.97</v>
+        <v>0.971</v>
       </c>
       <c r="Q5" s="20" t="inlineStr">
         <is>
@@ -1010,15 +1036,13 @@
         </is>
       </c>
       <c r="S5" s="22" t="n">
-        <v>1502.5</v>
+        <v>1524.5</v>
       </c>
       <c r="T5" s="22" t="n">
-        <v>91.09999999999999</v>
-      </c>
-      <c r="U5" s="18" t="inlineStr">
-        <is>
-          <t>Saatte ~27 Boy</t>
-        </is>
+        <v>91</v>
+      </c>
+      <c r="U5" s="18" t="n">
+        <v>27</v>
       </c>
       <c r="V5" s="22" t="n">
         <v>92.2</v>
@@ -1055,13 +1079,11 @@
           <t>50 x 80 mm</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
-        <is>
-          <t>1.55 kg/boy</t>
-        </is>
+      <c r="E6" s="26" t="n">
+        <v>1.55</v>
       </c>
       <c r="F6" s="27" t="n">
-        <v>190911.31</v>
+        <v>192461.31</v>
       </c>
       <c r="G6" s="28" t="inlineStr">
         <is>
@@ -1074,32 +1096,28 @@
         </is>
       </c>
       <c r="I6" s="29" t="n">
-        <v>1562.2</v>
+        <v>1586.2</v>
       </c>
       <c r="J6" s="30" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K6" s="31" t="n">
-        <v>73.40000000000001</v>
-      </c>
-      <c r="L6" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~47 Boy</t>
-        </is>
+        <v>73</v>
+      </c>
+      <c r="L6" s="32" t="n">
+        <v>47</v>
       </c>
       <c r="M6" s="27" t="n">
-        <v>1761.6</v>
+        <v>1752</v>
       </c>
       <c r="N6" s="29" t="n">
         <v>73.59999999999999</v>
       </c>
-      <c r="O6" s="33" t="inlineStr">
-        <is>
-          <t>Saatte ~48 Boy</t>
-        </is>
+      <c r="O6" s="33" t="n">
+        <v>48</v>
       </c>
       <c r="P6" s="34" t="n">
-        <v>0.997</v>
+        <v>0.992</v>
       </c>
       <c r="Q6" s="35" t="inlineStr">
         <is>
@@ -1112,15 +1130,13 @@
         </is>
       </c>
       <c r="S6" s="37" t="n">
-        <v>1445</v>
+        <v>1469</v>
       </c>
       <c r="T6" s="37" t="n">
-        <v>52.7</v>
-      </c>
-      <c r="U6" s="33" t="inlineStr">
-        <is>
-          <t>Saatte ~34 Boy</t>
-        </is>
+        <v>52.1</v>
+      </c>
+      <c r="U6" s="33" t="n">
+        <v>34</v>
       </c>
       <c r="V6" s="37" t="n">
         <v>53.1</v>
@@ -1157,58 +1173,52 @@
           <t>140 x 36 mm</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>4.95 kg/boy</t>
-        </is>
+      <c r="E7" s="10" t="n">
+        <v>4.95</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>175893</v>
+        <v>177376</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
           <t>Hat 106</t>
         </is>
       </c>
-      <c r="H7" s="18" t="inlineStr">
+      <c r="H7" s="39" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
       </c>
       <c r="I7" s="14" t="n">
-        <v>1609.3</v>
+        <v>1633.3</v>
       </c>
       <c r="J7" s="15" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K7" s="16" t="n">
-        <v>71.8</v>
-      </c>
-      <c r="L7" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~14 Boy</t>
-        </is>
+        <v>71.5</v>
+      </c>
+      <c r="L7" s="17" t="n">
+        <v>14</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>1723.2</v>
+        <v>1716</v>
       </c>
       <c r="N7" s="14" t="n">
         <v>74.09999999999999</v>
       </c>
-      <c r="O7" s="18" t="inlineStr">
-        <is>
-          <t>Saatte ~15 Boy</t>
-        </is>
+      <c r="O7" s="18" t="n">
+        <v>15</v>
       </c>
       <c r="P7" s="19" t="n">
-        <v>0.9690000000000001</v>
+        <v>0.965</v>
       </c>
       <c r="Q7" s="20" t="inlineStr">
         <is>
           <t>Hat 108</t>
         </is>
       </c>
-      <c r="R7" s="18" t="inlineStr">
+      <c r="R7" s="39" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -1219,10 +1229,8 @@
       <c r="T7" s="22" t="n">
         <v>64.90000000000001</v>
       </c>
-      <c r="U7" s="18" t="inlineStr">
-        <is>
-          <t>Saatte ~13 Boy</t>
-        </is>
+      <c r="U7" s="18" t="n">
+        <v>13</v>
       </c>
       <c r="V7" s="22" t="n">
         <v>64.90000000000001</v>
@@ -1259,20 +1267,18 @@
           <t>100 x 36 mm</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
-        <is>
-          <t>4.00 kg/boy</t>
-        </is>
+      <c r="E8" s="26" t="n">
+        <v>4</v>
       </c>
       <c r="F8" s="27" t="n">
-        <v>134340.8</v>
+        <v>135602.8</v>
       </c>
       <c r="G8" s="28" t="inlineStr">
         <is>
           <t>Hat 102</t>
         </is>
       </c>
-      <c r="H8" s="33" t="inlineStr">
+      <c r="H8" s="40" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -1286,10 +1292,8 @@
       <c r="K8" s="31" t="n">
         <v>63.3</v>
       </c>
-      <c r="L8" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~16 Boy</t>
-        </is>
+      <c r="L8" s="32" t="n">
+        <v>16</v>
       </c>
       <c r="M8" s="27" t="n">
         <v>1519.2</v>
@@ -1297,10 +1301,8 @@
       <c r="N8" s="29" t="n">
         <v>63.3</v>
       </c>
-      <c r="O8" s="33" t="inlineStr">
-        <is>
-          <t>Saatte ~16 Boy</t>
-        </is>
+      <c r="O8" s="33" t="n">
+        <v>16</v>
       </c>
       <c r="P8" s="34" t="n">
         <v>1</v>
@@ -1310,21 +1312,19 @@
           <t>Hat 108</t>
         </is>
       </c>
-      <c r="R8" s="33" t="inlineStr">
+      <c r="R8" s="40" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
       </c>
       <c r="S8" s="37" t="n">
-        <v>959</v>
+        <v>983</v>
       </c>
       <c r="T8" s="37" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="U8" s="33" t="inlineStr">
-        <is>
-          <t>Saatte ~17 Boy</t>
-        </is>
+        <v>66.8</v>
+      </c>
+      <c r="U8" s="33" t="n">
+        <v>17</v>
       </c>
       <c r="V8" s="37" t="n">
         <v>69.5</v>
@@ -1361,78 +1361,72 @@
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>4.77 kg/plaka</t>
-        </is>
+      <c r="E9" s="10" t="n">
+        <v>4.77</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>122751.18</v>
+        <v>125422.38</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="H9" s="18" t="inlineStr">
+      <c r="H9" s="39" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
       </c>
       <c r="I9" s="14" t="n">
-        <v>622.6096835790281</v>
+        <v>632.6096835790281</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K9" s="16" t="n">
-        <v>203.9</v>
-      </c>
-      <c r="L9" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~43 Plaka</t>
-        </is>
+        <v>206.1</v>
+      </c>
+      <c r="L9" s="41" t="n">
+        <v>43</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>4893.6</v>
+        <v>4946.4</v>
       </c>
       <c r="N9" s="14" t="n">
         <v>190</v>
       </c>
-      <c r="O9" s="18" t="inlineStr">
-        <is>
-          <t>Saatte ~40 Plaka</t>
-        </is>
+      <c r="O9" s="42" t="n">
+        <v>40</v>
       </c>
       <c r="P9" s="19" t="n">
-        <v>1.073</v>
+        <v>1.085</v>
       </c>
       <c r="Q9" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="R9" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T9" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U9" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V9" s="10" t="inlineStr">
+      <c r="R9" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S9" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T9" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U9" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V9" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1469,10 +1463,8 @@
           <t>200 x 36 mm</t>
         </is>
       </c>
-      <c r="E10" s="26" t="inlineStr">
-        <is>
-          <t>6.66 kg/boy</t>
-        </is>
+      <c r="E10" s="26" t="n">
+        <v>6.66</v>
       </c>
       <c r="F10" s="27" t="n">
         <v>81332</v>
@@ -1482,7 +1474,7 @@
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="H10" s="33" t="inlineStr">
+      <c r="H10" s="40" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -1496,10 +1488,8 @@
       <c r="K10" s="31" t="n">
         <v>84.59999999999999</v>
       </c>
-      <c r="L10" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~13 Boy</t>
-        </is>
+      <c r="L10" s="32" t="n">
+        <v>13</v>
       </c>
       <c r="M10" s="27" t="n">
         <v>2030.4</v>
@@ -1507,10 +1497,8 @@
       <c r="N10" s="29" t="n">
         <v>84.59999999999999</v>
       </c>
-      <c r="O10" s="33" t="inlineStr">
-        <is>
-          <t>Saatte ~13 Boy</t>
-        </is>
+      <c r="O10" s="33" t="n">
+        <v>13</v>
       </c>
       <c r="P10" s="34" t="n">
         <v>1</v>
@@ -1520,7 +1508,7 @@
           <t>Hat 106</t>
         </is>
       </c>
-      <c r="R10" s="33" t="inlineStr">
+      <c r="R10" s="40" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -1531,10 +1519,8 @@
       <c r="T10" s="37" t="n">
         <v>100.9</v>
       </c>
-      <c r="U10" s="33" t="inlineStr">
-        <is>
-          <t>Saatte ~15 Boy</t>
-        </is>
+      <c r="U10" s="33" t="n">
+        <v>15</v>
       </c>
       <c r="V10" s="37" t="n">
         <v>100.9</v>
@@ -1571,10 +1557,8 @@
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>4.25 kg/plaka</t>
-        </is>
+      <c r="E11" s="10" t="n">
+        <v>4.25</v>
       </c>
       <c r="F11" s="11" t="n">
         <v>39775.75</v>
@@ -1584,7 +1568,7 @@
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="H11" s="18" t="inlineStr">
+      <c r="H11" s="39" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -1598,10 +1582,8 @@
       <c r="K11" s="16" t="n">
         <v>165.8</v>
       </c>
-      <c r="L11" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~39 Plaka</t>
-        </is>
+      <c r="L11" s="41" t="n">
+        <v>39</v>
       </c>
       <c r="M11" s="11" t="n">
         <v>3979.2</v>
@@ -1609,10 +1591,8 @@
       <c r="N11" s="14" t="n">
         <v>190</v>
       </c>
-      <c r="O11" s="18" t="inlineStr">
-        <is>
-          <t>Saatte ~45 Plaka</t>
-        </is>
+      <c r="O11" s="42" t="n">
+        <v>45</v>
       </c>
       <c r="P11" s="19" t="n">
         <v>0.873</v>
@@ -1622,27 +1602,27 @@
           <t>—</t>
         </is>
       </c>
-      <c r="R11" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T11" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U11" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V11" s="10" t="inlineStr">
+      <c r="R11" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S11" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T11" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U11" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V11" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1661,96 +1641,90 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>MIX TEAK Levha</t>
+          <t>SEREN(39mm)</t>
         </is>
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>WPC Levha Plaka</t>
+          <t>Seren Çıtası</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>207 cm (2.07 m)</t>
+          <t>2.10 Metre</t>
         </is>
       </c>
       <c r="D12" s="25" t="inlineStr">
         <is>
-          <t>En: 94 cm (2 mm)</t>
-        </is>
-      </c>
-      <c r="E12" s="26" t="inlineStr">
-        <is>
-          <t>4.25 kg/plaka</t>
-        </is>
+          <t>39 x 45 mm</t>
+        </is>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>3.81</v>
       </c>
       <c r="F12" s="27" t="n">
-        <v>32618.75</v>
+        <v>34458</v>
       </c>
       <c r="G12" s="28" t="inlineStr">
         <is>
-          <t>Hat 201</t>
-        </is>
-      </c>
-      <c r="H12" s="33" t="inlineStr">
+          <t>Hat 107</t>
+        </is>
+      </c>
+      <c r="H12" s="40" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
       </c>
       <c r="I12" s="29" t="n">
-        <v>187.6562562708018</v>
+        <v>327</v>
       </c>
       <c r="J12" s="30" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="K12" s="31" t="n">
-        <v>174</v>
-      </c>
-      <c r="L12" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~41 Plaka</t>
-        </is>
+        <v>105.4</v>
+      </c>
+      <c r="L12" s="32" t="n">
+        <v>28</v>
       </c>
       <c r="M12" s="27" t="n">
-        <v>4176</v>
+        <v>2529.6</v>
       </c>
       <c r="N12" s="29" t="n">
-        <v>190</v>
-      </c>
-      <c r="O12" s="33" t="inlineStr">
-        <is>
-          <t>Saatte ~45 Plaka</t>
-        </is>
+        <v>96.09999999999999</v>
+      </c>
+      <c r="O12" s="33" t="n">
+        <v>25</v>
       </c>
       <c r="P12" s="34" t="n">
-        <v>0.9159999999999999</v>
+        <v>1.097</v>
       </c>
       <c r="Q12" s="38" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="R12" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S12" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T12" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U12" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V12" s="26" t="inlineStr">
+      <c r="R12" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S12" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V12" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1762,103 +1736,97 @@
       </c>
       <c r="X12" s="25" t="inlineStr">
         <is>
-          <t>Levha Özel Hattı (Hat 201)</t>
+          <t>Tek Hat Atamalı</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>SEREN(39mm)</t>
+          <t>MIX TEAK Levha</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Seren Çıtası</t>
+          <t>WPC Levha Plaka</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>2.10 Metre</t>
+          <t>207 cm (2.07 m)</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>39 x 45 mm</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>3.81 kg/boy</t>
-        </is>
+          <t>En: 94 cm (2 mm)</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>4.25</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>32593</v>
+        <v>32618.75</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>Hat 107</t>
-        </is>
-      </c>
-      <c r="H13" s="18" t="inlineStr">
+          <t>Hat 201</t>
+        </is>
+      </c>
+      <c r="H13" s="39" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
       </c>
       <c r="I13" s="14" t="n">
-        <v>303</v>
+        <v>187.6562562708018</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K13" s="16" t="n">
-        <v>107.6</v>
-      </c>
-      <c r="L13" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~28 Boy</t>
-        </is>
+        <v>174</v>
+      </c>
+      <c r="L13" s="41" t="n">
+        <v>41</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>2582.4</v>
+        <v>4176</v>
       </c>
       <c r="N13" s="14" t="n">
-        <v>96.09999999999999</v>
-      </c>
-      <c r="O13" s="18" t="inlineStr">
-        <is>
-          <t>Saatte ~25 Boy</t>
-        </is>
+        <v>190</v>
+      </c>
+      <c r="O13" s="42" t="n">
+        <v>45</v>
       </c>
       <c r="P13" s="19" t="n">
-        <v>1.12</v>
+        <v>0.9159999999999999</v>
       </c>
       <c r="Q13" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="R13" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T13" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U13" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V13" s="10" t="inlineStr">
+      <c r="R13" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S13" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T13" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U13" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V13" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1870,7 +1838,7 @@
       </c>
       <c r="X13" s="8" t="inlineStr">
         <is>
-          <t>Tek Hat Atamalı</t>
+          <t>Levha Özel Hattı (Hat 201)</t>
         </is>
       </c>
     </row>
@@ -1895,10 +1863,8 @@
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E14" s="26" t="inlineStr">
-        <is>
-          <t>4.41 kg/plaka</t>
-        </is>
+      <c r="E14" s="26" t="n">
+        <v>4.41</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>32060.7</v>
@@ -1908,7 +1874,7 @@
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="H14" s="33" t="inlineStr">
+      <c r="H14" s="40" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -1922,10 +1888,8 @@
       <c r="K14" s="31" t="n">
         <v>178.7</v>
       </c>
-      <c r="L14" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~40 Plaka</t>
-        </is>
+      <c r="L14" s="45" t="n">
+        <v>40</v>
       </c>
       <c r="M14" s="27" t="n">
         <v>4288.8</v>
@@ -1933,10 +1897,8 @@
       <c r="N14" s="29" t="n">
         <v>190</v>
       </c>
-      <c r="O14" s="33" t="inlineStr">
-        <is>
-          <t>Saatte ~43 Plaka</t>
-        </is>
+      <c r="O14" s="46" t="n">
+        <v>43</v>
       </c>
       <c r="P14" s="34" t="n">
         <v>0.9409999999999999</v>
@@ -1946,27 +1908,27 @@
           <t>—</t>
         </is>
       </c>
-      <c r="R14" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S14" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T14" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U14" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V14" s="26" t="inlineStr">
+      <c r="R14" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S14" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U14" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V14" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2003,10 +1965,8 @@
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>4.77 kg/plaka</t>
-        </is>
+      <c r="E15" s="10" t="n">
+        <v>4.77</v>
       </c>
       <c r="F15" s="11" t="n">
         <v>18364.5</v>
@@ -2016,7 +1976,7 @@
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="H15" s="18" t="inlineStr">
+      <c r="H15" s="39" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -2030,10 +1990,8 @@
       <c r="K15" s="16" t="n">
         <v>159.9</v>
       </c>
-      <c r="L15" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~34 Plaka</t>
-        </is>
+      <c r="L15" s="41" t="n">
+        <v>34</v>
       </c>
       <c r="M15" s="11" t="n">
         <v>3837.6</v>
@@ -2041,10 +1999,8 @@
       <c r="N15" s="14" t="n">
         <v>190</v>
       </c>
-      <c r="O15" s="18" t="inlineStr">
-        <is>
-          <t>Saatte ~40 Plaka</t>
-        </is>
+      <c r="O15" s="42" t="n">
+        <v>40</v>
       </c>
       <c r="P15" s="19" t="n">
         <v>0.8420000000000001</v>
@@ -2054,27 +2010,27 @@
           <t>—</t>
         </is>
       </c>
-      <c r="R15" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T15" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U15" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V15" s="10" t="inlineStr">
+      <c r="R15" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S15" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T15" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U15" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V15" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2111,10 +2067,8 @@
           <t>220 x 24 mm</t>
         </is>
       </c>
-      <c r="E16" s="26" t="inlineStr">
-        <is>
-          <t>10.33 kg/boy</t>
-        </is>
+      <c r="E16" s="26" t="n">
+        <v>10.33</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>17678</v>
@@ -2124,7 +2078,7 @@
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="H16" s="33" t="inlineStr">
+      <c r="H16" s="40" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -2138,10 +2092,8 @@
       <c r="K16" s="31" t="n">
         <v>85.90000000000001</v>
       </c>
-      <c r="L16" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~8 Boy</t>
-        </is>
+      <c r="L16" s="32" t="n">
+        <v>8</v>
       </c>
       <c r="M16" s="27" t="n">
         <v>2061.6</v>
@@ -2149,10 +2101,8 @@
       <c r="N16" s="29" t="n">
         <v>84.7</v>
       </c>
-      <c r="O16" s="33" t="inlineStr">
-        <is>
-          <t>Saatte ~8 Boy</t>
-        </is>
+      <c r="O16" s="33" t="n">
+        <v>8</v>
       </c>
       <c r="P16" s="34" t="n">
         <v>1.014</v>
@@ -2162,27 +2112,27 @@
           <t>—</t>
         </is>
       </c>
-      <c r="R16" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S16" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T16" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U16" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V16" s="26" t="inlineStr">
+      <c r="R16" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S16" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U16" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V16" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2219,10 +2169,8 @@
           <t>80 x 80 mm</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>2.20 kg/boy</t>
-        </is>
+      <c r="E17" s="10" t="n">
+        <v>2.2</v>
       </c>
       <c r="F17" s="11" t="n">
         <v>14339</v>
@@ -2232,7 +2180,7 @@
           <t>Hat 101</t>
         </is>
       </c>
-      <c r="H17" s="18" t="inlineStr">
+      <c r="H17" s="39" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -2246,10 +2194,8 @@
       <c r="K17" s="16" t="n">
         <v>51.1</v>
       </c>
-      <c r="L17" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~23 Boy</t>
-        </is>
+      <c r="L17" s="17" t="n">
+        <v>23</v>
       </c>
       <c r="M17" s="11" t="n">
         <v>1226.4</v>
@@ -2257,10 +2203,8 @@
       <c r="N17" s="14" t="n">
         <v>46.5</v>
       </c>
-      <c r="O17" s="18" t="inlineStr">
-        <is>
-          <t>Saatte ~21 Boy</t>
-        </is>
+      <c r="O17" s="18" t="n">
+        <v>21</v>
       </c>
       <c r="P17" s="19" t="n">
         <v>1.099</v>
@@ -2281,10 +2225,8 @@
       <c r="T17" s="22" t="n">
         <v>85.09999999999999</v>
       </c>
-      <c r="U17" s="18" t="inlineStr">
-        <is>
-          <t>Saatte ~39 Boy</t>
-        </is>
+      <c r="U17" s="18" t="n">
+        <v>39</v>
       </c>
       <c r="V17" s="22" t="n">
         <v>85.09999999999999</v>
@@ -2321,10 +2263,8 @@
           <t>35 x 100 mm</t>
         </is>
       </c>
-      <c r="E18" s="26" t="inlineStr">
-        <is>
-          <t>2.08 kg/boy</t>
-        </is>
+      <c r="E18" s="26" t="n">
+        <v>2.08</v>
       </c>
       <c r="F18" s="27" t="n">
         <v>10435</v>
@@ -2334,7 +2274,7 @@
           <t>Hat 101</t>
         </is>
       </c>
-      <c r="H18" s="33" t="inlineStr">
+      <c r="H18" s="40" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -2348,10 +2288,8 @@
       <c r="K18" s="31" t="n">
         <v>43.3</v>
       </c>
-      <c r="L18" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~21 Boy</t>
-        </is>
+      <c r="L18" s="32" t="n">
+        <v>21</v>
       </c>
       <c r="M18" s="27" t="n">
         <v>1039.2</v>
@@ -2359,10 +2297,8 @@
       <c r="N18" s="29" t="n">
         <v>46.8</v>
       </c>
-      <c r="O18" s="33" t="inlineStr">
-        <is>
-          <t>Saatte ~22 Boy</t>
-        </is>
+      <c r="O18" s="33" t="n">
+        <v>22</v>
       </c>
       <c r="P18" s="34" t="n">
         <v>0.925</v>
@@ -2372,27 +2308,27 @@
           <t>—</t>
         </is>
       </c>
-      <c r="R18" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S18" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T18" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U18" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V18" s="26" t="inlineStr">
+      <c r="R18" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S18" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T18" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U18" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V18" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2429,10 +2365,8 @@
           <t>35 x 150 mm</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
-        <is>
-          <t>2.97 kg/boy</t>
-        </is>
+      <c r="E19" s="10" t="n">
+        <v>2.97</v>
       </c>
       <c r="F19" s="11" t="n">
         <v>9522</v>
@@ -2442,7 +2376,7 @@
           <t>Hat 101</t>
         </is>
       </c>
-      <c r="H19" s="18" t="inlineStr">
+      <c r="H19" s="39" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -2456,10 +2390,8 @@
       <c r="K19" s="16" t="n">
         <v>41.2</v>
       </c>
-      <c r="L19" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~14 Boy</t>
-        </is>
+      <c r="L19" s="17" t="n">
+        <v>14</v>
       </c>
       <c r="M19" s="11" t="n">
         <v>988.8</v>
@@ -2467,10 +2399,8 @@
       <c r="N19" s="14" t="n">
         <v>41.2</v>
       </c>
-      <c r="O19" s="18" t="inlineStr">
-        <is>
-          <t>Saatte ~14 Boy</t>
-        </is>
+      <c r="O19" s="18" t="n">
+        <v>14</v>
       </c>
       <c r="P19" s="19" t="n">
         <v>1</v>
@@ -2480,27 +2410,27 @@
           <t>—</t>
         </is>
       </c>
-      <c r="R19" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T19" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U19" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V19" s="10" t="inlineStr">
+      <c r="R19" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S19" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V19" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2537,10 +2467,8 @@
           <t>219 x 26 mm</t>
         </is>
       </c>
-      <c r="E20" s="26" t="inlineStr">
-        <is>
-          <t>10.52 kg/boy</t>
-        </is>
+      <c r="E20" s="26" t="n">
+        <v>10.52</v>
       </c>
       <c r="F20" s="27" t="n">
         <v>9415</v>
@@ -2550,7 +2478,7 @@
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="H20" s="33" t="inlineStr">
+      <c r="H20" s="40" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -2564,10 +2492,8 @@
       <c r="K20" s="31" t="n">
         <v>108.2</v>
       </c>
-      <c r="L20" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~10 Boy</t>
-        </is>
+      <c r="L20" s="32" t="n">
+        <v>10</v>
       </c>
       <c r="M20" s="27" t="n">
         <v>2596.8</v>
@@ -2575,10 +2501,8 @@
       <c r="N20" s="29" t="n">
         <v>108.2</v>
       </c>
-      <c r="O20" s="33" t="inlineStr">
-        <is>
-          <t>Saatte ~10 Boy</t>
-        </is>
+      <c r="O20" s="33" t="n">
+        <v>10</v>
       </c>
       <c r="P20" s="34" t="n">
         <v>1</v>
@@ -2588,27 +2512,27 @@
           <t>—</t>
         </is>
       </c>
-      <c r="R20" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S20" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T20" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U20" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V20" s="26" t="inlineStr">
+      <c r="R20" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S20" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U20" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V20" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2645,10 +2569,8 @@
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
-        <is>
-          <t>4.25 kg/plaka</t>
-        </is>
+      <c r="E21" s="10" t="n">
+        <v>4.25</v>
       </c>
       <c r="F21" s="11" t="n">
         <v>9124.75</v>
@@ -2658,7 +2580,7 @@
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="H21" s="18" t="inlineStr">
+      <c r="H21" s="39" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -2672,10 +2594,8 @@
       <c r="K21" s="16" t="n">
         <v>187.5</v>
       </c>
-      <c r="L21" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~44 Plaka</t>
-        </is>
+      <c r="L21" s="41" t="n">
+        <v>44</v>
       </c>
       <c r="M21" s="11" t="n">
         <v>4500</v>
@@ -2683,10 +2603,8 @@
       <c r="N21" s="14" t="n">
         <v>190</v>
       </c>
-      <c r="O21" s="18" t="inlineStr">
-        <is>
-          <t>Saatte ~45 Plaka</t>
-        </is>
+      <c r="O21" s="42" t="n">
+        <v>45</v>
       </c>
       <c r="P21" s="19" t="n">
         <v>0.987</v>
@@ -2696,27 +2614,27 @@
           <t>—</t>
         </is>
       </c>
-      <c r="R21" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T21" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U21" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V21" s="10" t="inlineStr">
+      <c r="R21" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S21" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T21" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U21" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V21" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2753,10 +2671,8 @@
           <t>15 x 20 mm</t>
         </is>
       </c>
-      <c r="E22" s="26" t="inlineStr">
-        <is>
-          <t>1.50 kg/boy</t>
-        </is>
+      <c r="E22" s="26" t="n">
+        <v>1.5</v>
       </c>
       <c r="F22" s="27" t="n">
         <v>7805</v>
@@ -2766,7 +2682,7 @@
           <t>Hat 102</t>
         </is>
       </c>
-      <c r="H22" s="33" t="inlineStr">
+      <c r="H22" s="40" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -2780,10 +2696,8 @@
       <c r="K22" s="31" t="n">
         <v>52</v>
       </c>
-      <c r="L22" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~35 Boy</t>
-        </is>
+      <c r="L22" s="32" t="n">
+        <v>35</v>
       </c>
       <c r="M22" s="27" t="n">
         <v>1248</v>
@@ -2791,10 +2705,8 @@
       <c r="N22" s="29" t="n">
         <v>50</v>
       </c>
-      <c r="O22" s="33" t="inlineStr">
-        <is>
-          <t>Saatte ~33 Boy</t>
-        </is>
+      <c r="O22" s="33" t="n">
+        <v>33</v>
       </c>
       <c r="P22" s="34" t="n">
         <v>1.04</v>
@@ -2804,27 +2716,27 @@
           <t>—</t>
         </is>
       </c>
-      <c r="R22" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S22" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T22" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U22" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V22" s="26" t="inlineStr">
+      <c r="R22" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S22" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T22" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U22" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V22" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2861,10 +2773,8 @@
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E23" s="10" t="inlineStr">
-        <is>
-          <t>4.33 kg/plaka</t>
-        </is>
+      <c r="E23" s="10" t="n">
+        <v>4.33</v>
       </c>
       <c r="F23" s="11" t="n">
         <v>7690.08</v>
@@ -2874,65 +2784,61 @@
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="H23" s="18" t="inlineStr">
+      <c r="H23" s="39" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
       </c>
       <c r="I23" s="14" t="n">
-        <v>57.25702552864577</v>
+        <v>47.95702552864577</v>
       </c>
       <c r="J23" s="15" t="n">
         <v>13</v>
       </c>
       <c r="K23" s="16" t="n">
-        <v>131.6</v>
-      </c>
-      <c r="L23" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~30 Plaka</t>
-        </is>
+        <v>167.9</v>
+      </c>
+      <c r="L23" s="41" t="n">
+        <v>39</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>3158.4</v>
+        <v>4029.6</v>
       </c>
       <c r="N23" s="14" t="n">
         <v>190</v>
       </c>
-      <c r="O23" s="18" t="inlineStr">
-        <is>
-          <t>Saatte ~44 Plaka</t>
-        </is>
-      </c>
-      <c r="P23" s="39" t="n">
-        <v>0.6929999999999999</v>
+      <c r="O23" s="42" t="n">
+        <v>44</v>
+      </c>
+      <c r="P23" s="19" t="n">
+        <v>0.884</v>
       </c>
       <c r="Q23" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="R23" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T23" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U23" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V23" s="10" t="inlineStr">
+      <c r="R23" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S23" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T23" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U23" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V23" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2969,10 +2875,8 @@
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E24" s="26" t="inlineStr">
-        <is>
-          <t>4.64 kg/plaka</t>
-        </is>
+      <c r="E24" s="26" t="n">
+        <v>4.64</v>
       </c>
       <c r="F24" s="27" t="n">
         <v>6018.08</v>
@@ -2982,7 +2886,7 @@
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="H24" s="33" t="inlineStr">
+      <c r="H24" s="40" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -2996,10 +2900,8 @@
       <c r="K24" s="31" t="n">
         <v>185.6</v>
       </c>
-      <c r="L24" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~40 Plaka</t>
-        </is>
+      <c r="L24" s="45" t="n">
+        <v>40</v>
       </c>
       <c r="M24" s="27" t="n">
         <v>4454.4</v>
@@ -3007,10 +2909,8 @@
       <c r="N24" s="29" t="n">
         <v>190</v>
       </c>
-      <c r="O24" s="33" t="inlineStr">
-        <is>
-          <t>Saatte ~41 Plaka</t>
-        </is>
+      <c r="O24" s="46" t="n">
+        <v>41</v>
       </c>
       <c r="P24" s="34" t="n">
         <v>0.977</v>
@@ -3020,27 +2920,27 @@
           <t>—</t>
         </is>
       </c>
-      <c r="R24" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S24" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T24" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U24" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V24" s="26" t="inlineStr">
+      <c r="R24" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S24" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T24" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U24" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V24" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3077,10 +2977,8 @@
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E25" s="10" t="inlineStr">
-        <is>
-          <t>4.77 kg/plaka</t>
-        </is>
+      <c r="E25" s="10" t="n">
+        <v>4.77</v>
       </c>
       <c r="F25" s="11" t="n">
         <v>5609.52</v>
@@ -3090,65 +2988,61 @@
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="H25" s="18" t="inlineStr">
+      <c r="H25" s="39" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
       </c>
       <c r="I25" s="14" t="n">
-        <v>41.52884989747753</v>
+        <v>37.72884989747753</v>
       </c>
       <c r="J25" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K25" s="16" t="n">
-        <v>35</v>
-      </c>
-      <c r="L25" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~7 Plaka</t>
-        </is>
+        <v>190.8</v>
+      </c>
+      <c r="L25" s="41" t="n">
+        <v>40</v>
       </c>
       <c r="M25" s="11" t="n">
-        <v>840</v>
+        <v>4579.2</v>
       </c>
       <c r="N25" s="14" t="n">
         <v>190</v>
       </c>
-      <c r="O25" s="18" t="inlineStr">
-        <is>
-          <t>Saatte ~40 Plaka</t>
-        </is>
-      </c>
-      <c r="P25" s="39" t="n">
-        <v>0.184</v>
+      <c r="O25" s="42" t="n">
+        <v>40</v>
+      </c>
+      <c r="P25" s="19" t="n">
+        <v>1.004</v>
       </c>
       <c r="Q25" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="R25" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T25" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U25" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V25" s="10" t="inlineStr">
+      <c r="R25" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S25" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T25" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U25" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V25" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3185,10 +3079,8 @@
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E26" s="26" t="inlineStr">
-        <is>
-          <t>4.79 kg/plaka</t>
-        </is>
+      <c r="E26" s="26" t="n">
+        <v>4.79</v>
       </c>
       <c r="F26" s="27" t="n">
         <v>3846.37</v>
@@ -3198,7 +3090,7 @@
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="H26" s="33" t="inlineStr">
+      <c r="H26" s="40" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -3212,10 +3104,8 @@
       <c r="K26" s="31" t="n">
         <v>95.8</v>
       </c>
-      <c r="L26" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~20 Plaka</t>
-        </is>
+      <c r="L26" s="45" t="n">
+        <v>20</v>
       </c>
       <c r="M26" s="27" t="n">
         <v>2299.2</v>
@@ -3223,12 +3113,10 @@
       <c r="N26" s="29" t="n">
         <v>190</v>
       </c>
-      <c r="O26" s="33" t="inlineStr">
-        <is>
-          <t>Saatte ~40 Plaka</t>
-        </is>
-      </c>
-      <c r="P26" s="40" t="n">
+      <c r="O26" s="46" t="n">
+        <v>40</v>
+      </c>
+      <c r="P26" s="47" t="n">
         <v>0.504</v>
       </c>
       <c r="Q26" s="38" t="inlineStr">
@@ -3236,27 +3124,27 @@
           <t>—</t>
         </is>
       </c>
-      <c r="R26" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S26" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T26" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U26" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V26" s="26" t="inlineStr">
+      <c r="R26" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S26" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T26" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U26" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V26" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3293,10 +3181,8 @@
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E27" s="10" t="inlineStr">
-        <is>
-          <t>4.79 kg/plaka</t>
-        </is>
+      <c r="E27" s="10" t="n">
+        <v>4.79</v>
       </c>
       <c r="F27" s="11" t="n">
         <v>2874</v>
@@ -3306,7 +3192,7 @@
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="H27" s="18" t="inlineStr">
+      <c r="H27" s="39" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -3320,10 +3206,8 @@
       <c r="K27" s="16" t="n">
         <v>134.1</v>
       </c>
-      <c r="L27" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~28 Plaka</t>
-        </is>
+      <c r="L27" s="41" t="n">
+        <v>28</v>
       </c>
       <c r="M27" s="11" t="n">
         <v>3218.4</v>
@@ -3331,12 +3215,10 @@
       <c r="N27" s="14" t="n">
         <v>190</v>
       </c>
-      <c r="O27" s="18" t="inlineStr">
-        <is>
-          <t>Saatte ~40 Plaka</t>
-        </is>
-      </c>
-      <c r="P27" s="39" t="n">
+      <c r="O27" s="42" t="n">
+        <v>40</v>
+      </c>
+      <c r="P27" s="48" t="n">
         <v>0.706</v>
       </c>
       <c r="Q27" s="23" t="inlineStr">
@@ -3344,27 +3226,27 @@
           <t>—</t>
         </is>
       </c>
-      <c r="R27" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T27" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U27" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V27" s="10" t="inlineStr">
+      <c r="R27" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S27" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T27" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U27" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V27" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3401,10 +3283,8 @@
           <t>30 x 15 mm</t>
         </is>
       </c>
-      <c r="E28" s="26" t="inlineStr">
-        <is>
-          <t>0.48 kg/boy</t>
-        </is>
+      <c r="E28" s="26" t="n">
+        <v>0.48</v>
       </c>
       <c r="F28" s="27" t="n">
         <v>1385</v>
@@ -3414,7 +3294,7 @@
           <t>Hat 102</t>
         </is>
       </c>
-      <c r="H28" s="33" t="inlineStr">
+      <c r="H28" s="40" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -3428,10 +3308,8 @@
       <c r="K28" s="31" t="n">
         <v>40.7</v>
       </c>
-      <c r="L28" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~85 Boy</t>
-        </is>
+      <c r="L28" s="32" t="n">
+        <v>85</v>
       </c>
       <c r="M28" s="27" t="n">
         <v>976.8</v>
@@ -3439,10 +3317,8 @@
       <c r="N28" s="29" t="n">
         <v>40.7</v>
       </c>
-      <c r="O28" s="33" t="inlineStr">
-        <is>
-          <t>Saatte ~85 Boy</t>
-        </is>
+      <c r="O28" s="33" t="n">
+        <v>85</v>
       </c>
       <c r="P28" s="34" t="n">
         <v>1</v>
@@ -3452,27 +3328,27 @@
           <t>—</t>
         </is>
       </c>
-      <c r="R28" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S28" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T28" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U28" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V28" s="26" t="inlineStr">
+      <c r="R28" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S28" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T28" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U28" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V28" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3509,10 +3385,8 @@
           <t>35 x 80 mm</t>
         </is>
       </c>
-      <c r="E29" s="10" t="inlineStr">
-        <is>
-          <t>2.94 kg/boy</t>
-        </is>
+      <c r="E29" s="10" t="n">
+        <v>2.94</v>
       </c>
       <c r="F29" s="11" t="n">
         <v>530</v>
@@ -3522,7 +3396,7 @@
           <t>Hat 101</t>
         </is>
       </c>
-      <c r="H29" s="18" t="inlineStr">
+      <c r="H29" s="39" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -3536,10 +3410,8 @@
       <c r="K29" s="16" t="n">
         <v>44.2</v>
       </c>
-      <c r="L29" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~15 Boy</t>
-        </is>
+      <c r="L29" s="17" t="n">
+        <v>15</v>
       </c>
       <c r="M29" s="11" t="n">
         <v>1060.8</v>
@@ -3547,10 +3419,8 @@
       <c r="N29" s="14" t="n">
         <v>44.2</v>
       </c>
-      <c r="O29" s="18" t="inlineStr">
-        <is>
-          <t>Saatte ~15 Boy</t>
-        </is>
+      <c r="O29" s="18" t="n">
+        <v>15</v>
       </c>
       <c r="P29" s="19" t="n">
         <v>1</v>
@@ -3560,27 +3430,27 @@
           <t>—</t>
         </is>
       </c>
-      <c r="R29" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T29" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U29" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V29" s="10" t="inlineStr">
+      <c r="R29" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S29" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T29" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U29" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V29" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3617,10 +3487,8 @@
           <t>219 x 26 mm</t>
         </is>
       </c>
-      <c r="E30" s="26" t="inlineStr">
-        <is>
-          <t>9.26 kg/boy</t>
-        </is>
+      <c r="E30" s="26" t="n">
+        <v>9.26</v>
       </c>
       <c r="F30" s="27" t="n">
         <v>463</v>
@@ -3630,7 +3498,7 @@
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="H30" s="33" t="inlineStr">
+      <c r="H30" s="40" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -3644,10 +3512,8 @@
       <c r="K30" s="31" t="n">
         <v>115.8</v>
       </c>
-      <c r="L30" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~12 Boy</t>
-        </is>
+      <c r="L30" s="32" t="n">
+        <v>12</v>
       </c>
       <c r="M30" s="27" t="n">
         <v>2779.2</v>
@@ -3655,10 +3521,8 @@
       <c r="N30" s="29" t="n">
         <v>115.8</v>
       </c>
-      <c r="O30" s="33" t="inlineStr">
-        <is>
-          <t>Saatte ~12 Boy</t>
-        </is>
+      <c r="O30" s="33" t="n">
+        <v>12</v>
       </c>
       <c r="P30" s="34" t="n">
         <v>1</v>
@@ -3668,27 +3532,27 @@
           <t>—</t>
         </is>
       </c>
-      <c r="R30" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S30" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T30" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U30" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V30" s="26" t="inlineStr">
+      <c r="R30" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S30" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T30" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U30" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V30" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3705,42 +3569,52 @@
       </c>
     </row>
     <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="41" t="inlineStr">
-        <is>
-          <t>GENEL TOPLAM / FABRİKA</t>
-        </is>
-      </c>
-      <c r="B31" s="42" t="n"/>
-      <c r="C31" s="42" t="n"/>
-      <c r="D31" s="42" t="n"/>
-      <c r="E31" s="42" t="n"/>
-      <c r="F31" s="43" t="n">
-        <v>1266753.58</v>
-      </c>
-      <c r="G31" s="42" t="n"/>
-      <c r="H31" s="42" t="n"/>
-      <c r="I31" s="44" t="n">
-        <v>9895.700000000003</v>
-      </c>
-      <c r="J31" s="42" t="n"/>
-      <c r="K31" s="42" t="n"/>
-      <c r="L31" s="42" t="n"/>
-      <c r="M31" s="42" t="n"/>
-      <c r="N31" s="42" t="n"/>
-      <c r="O31" s="42" t="n"/>
-      <c r="P31" s="42" t="n"/>
-      <c r="Q31" s="42" t="n"/>
-      <c r="R31" s="42" t="n"/>
-      <c r="S31" s="42" t="n"/>
-      <c r="T31" s="44" t="n">
-        <v>4532.7</v>
-      </c>
-      <c r="U31" s="42" t="n"/>
-      <c r="V31" s="42" t="n"/>
-      <c r="W31" s="42" t="n"/>
-      <c r="X31" s="42" t="n"/>
+      <c r="A31" s="49" t="inlineStr">
+        <is>
+          <t>GENEL TOPLAM (FİLTREYE DUYARLI)</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+      <c r="E31" s="50" t="n"/>
+      <c r="F31" s="51">
+        <f>SUBTOTAL(109, F5:F30)</f>
+        <v/>
+      </c>
+      <c r="G31" s="50" t="n"/>
+      <c r="H31" s="50" t="n"/>
+      <c r="I31" s="52">
+        <f>SUBTOTAL(109, I5:I30)</f>
+        <v/>
+      </c>
+      <c r="J31" s="51">
+        <f>SUBTOTAL(109, J5:J30)</f>
+        <v/>
+      </c>
+      <c r="K31" s="50" t="n"/>
+      <c r="L31" s="50" t="n"/>
+      <c r="M31" s="51">
+        <f>SUBTOTAL(109, M5:M30)</f>
+        <v/>
+      </c>
+      <c r="N31" s="50" t="n"/>
+      <c r="O31" s="50" t="n"/>
+      <c r="P31" s="50" t="n"/>
+      <c r="Q31" s="50" t="n"/>
+      <c r="R31" s="50" t="n"/>
+      <c r="S31" s="52">
+        <f>SUBTOTAL(109, S5:S30)</f>
+        <v/>
+      </c>
+      <c r="T31" s="50" t="n"/>
+      <c r="U31" s="50" t="n"/>
+      <c r="V31" s="50" t="n"/>
+      <c r="W31" s="50" t="n"/>
+      <c r="X31" s="50" t="n"/>
     </row>
   </sheetData>
+  <autoFilter ref="A4:X30"/>
   <mergeCells count="7">
     <mergeCell ref="W3"/>
     <mergeCell ref="X3"/>
@@ -3848,7 +3722,7 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="45" t="inlineStr">
+      <c r="A4" s="53" t="inlineStr">
         <is>
           <t>Hat 101</t>
         </is>
@@ -3875,7 +3749,7 @@
       <c r="G4" s="31" t="n">
         <v>45.4</v>
       </c>
-      <c r="H4" s="46" t="n">
+      <c r="H4" s="54" t="n">
         <v>4</v>
       </c>
       <c r="I4" s="28" t="inlineStr">
@@ -3895,7 +3769,7 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="47" t="inlineStr">
+      <c r="A5" s="55" t="inlineStr">
         <is>
           <t>Hat 102</t>
         </is>
@@ -3911,18 +3785,18 @@
         </is>
       </c>
       <c r="D5" s="14" t="n">
-        <v>1584.1</v>
+        <v>1603.1</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>96990</v>
+        <v>97353</v>
       </c>
       <c r="G5" s="16" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="H5" s="48" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="H5" s="56" t="n">
         <v>4</v>
       </c>
       <c r="I5" s="12" t="inlineStr">
@@ -3942,7 +3816,7 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="45" t="inlineStr">
+      <c r="A6" s="53" t="inlineStr">
         <is>
           <t>Hat 103</t>
         </is>
@@ -3958,18 +3832,18 @@
         </is>
       </c>
       <c r="D6" s="29" t="n">
-        <v>1457</v>
+        <v>1481</v>
       </c>
       <c r="E6" s="30" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F6" s="27" t="n">
-        <v>76929</v>
+        <v>77366</v>
       </c>
       <c r="G6" s="31" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="H6" s="46" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="H6" s="54" t="n">
         <v>2</v>
       </c>
       <c r="I6" s="28" t="inlineStr">
@@ -3989,7 +3863,7 @@
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="47" t="inlineStr">
+      <c r="A7" s="55" t="inlineStr">
         <is>
           <t>Hat 104</t>
         </is>
@@ -4005,18 +3879,18 @@
         </is>
       </c>
       <c r="D7" s="14" t="n">
-        <v>1646.4</v>
+        <v>1670.4</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>158335.32</v>
+        <v>160791.32</v>
       </c>
       <c r="G7" s="16" t="n">
-        <v>96.2</v>
-      </c>
-      <c r="H7" s="48" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="H7" s="56" t="n">
         <v>1</v>
       </c>
       <c r="I7" s="12" t="inlineStr">
@@ -4036,7 +3910,7 @@
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="45" t="inlineStr">
+      <c r="A8" s="53" t="inlineStr">
         <is>
           <t>Hat 105</t>
         </is>
@@ -4052,18 +3926,18 @@
         </is>
       </c>
       <c r="D8" s="29" t="n">
-        <v>1514.5</v>
+        <v>1536.5</v>
       </c>
       <c r="E8" s="30" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F8" s="27" t="n">
-        <v>137521.47</v>
+        <v>139489.47</v>
       </c>
       <c r="G8" s="31" t="n">
         <v>90.8</v>
       </c>
-      <c r="H8" s="46" t="n">
+      <c r="H8" s="54" t="n">
         <v>2</v>
       </c>
       <c r="I8" s="28" t="inlineStr">
@@ -4083,7 +3957,7 @@
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="47" t="inlineStr">
+      <c r="A9" s="55" t="inlineStr">
         <is>
           <t>Hat 106</t>
         </is>
@@ -4099,18 +3973,18 @@
         </is>
       </c>
       <c r="D9" s="14" t="n">
-        <v>1645.3</v>
+        <v>1669.3</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>118886</v>
+        <v>120006</v>
       </c>
       <c r="G9" s="16" t="n">
-        <v>72.3</v>
-      </c>
-      <c r="H9" s="48" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="H9" s="56" t="n">
         <v>3</v>
       </c>
       <c r="I9" s="12" t="inlineStr">
@@ -4130,7 +4004,7 @@
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="45" t="inlineStr">
+      <c r="A10" s="53" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
@@ -4146,203 +4020,208 @@
         </is>
       </c>
       <c r="D10" s="29" t="n">
-        <v>1593.7</v>
+        <v>1617.7</v>
       </c>
       <c r="E10" s="30" t="n">
+        <v>157</v>
+      </c>
+      <c r="F10" s="27" t="n">
+        <v>145041</v>
+      </c>
+      <c r="G10" s="31" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="H10" s="54" t="n">
+        <v>8</v>
+      </c>
+      <c r="I10" s="28" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="J10" s="25" t="inlineStr">
+        <is>
+          <t>200 mm Kasa, Zemin Deck (KT100/102)</t>
+        </is>
+      </c>
+      <c r="K10" s="28" t="inlineStr">
+        <is>
+          <t>Aktif Üretimde</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="55" t="inlineStr">
+        <is>
+          <t>Hat 108</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Kasa Ekstrüder 8</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Profil Ekstrüzyon</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>1597.2</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>146</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>105875.8</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="H11" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>Tek Göz (1 Kafa)</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>100 mm &amp; 140 mm Kasa</t>
+        </is>
+      </c>
+      <c r="K11" s="12" t="inlineStr">
+        <is>
+          <t>Aktif Üretimde</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="53" t="inlineStr">
+        <is>
+          <t>Hat 109</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>Yüksek Hızlı Pervaz Ekstrüder 9</t>
+        </is>
+      </c>
+      <c r="C12" s="25" t="inlineStr">
+        <is>
+          <t>Profil Ekstrüzyon</t>
+        </is>
+      </c>
+      <c r="D12" s="29" t="n">
+        <v>1598.2</v>
+      </c>
+      <c r="E12" s="30" t="n">
         <v>155</v>
       </c>
-      <c r="F10" s="27" t="n">
-        <v>143176</v>
-      </c>
-      <c r="G10" s="31" t="n">
-        <v>89.8</v>
-      </c>
-      <c r="H10" s="46" t="n">
-        <v>8</v>
-      </c>
-      <c r="I10" s="28" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="J10" s="25" t="inlineStr">
-        <is>
-          <t>200 mm Kasa, Zemin Deck (KT100/102)</t>
-        </is>
-      </c>
-      <c r="K10" s="28" t="inlineStr">
+      <c r="F12" s="27" t="n">
+        <v>116876.31</v>
+      </c>
+      <c r="G12" s="31" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="H12" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="28" t="inlineStr">
+        <is>
+          <t>Tek Göz &amp; Çift Göz (2 Kafa)</t>
+        </is>
+      </c>
+      <c r="J12" s="25" t="inlineStr">
+        <is>
+          <t>50x80 Pervaz (Çift Göz), 80x80 Pervaz</t>
+        </is>
+      </c>
+      <c r="K12" s="28" t="inlineStr">
         <is>
           <t>Aktif Üretimde</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="47" t="inlineStr">
-        <is>
-          <t>Hat 108</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Kasa Ekstrüder 8</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Profil Ekstrüzyon</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="n">
-        <v>1573.2</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>144</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>104613.8</v>
-      </c>
-      <c r="G11" s="16" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="H11" s="48" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" s="12" t="inlineStr">
-        <is>
-          <t>Tek Göz (1 Kafa)</t>
-        </is>
-      </c>
-      <c r="J11" s="8" t="inlineStr">
-        <is>
-          <t>100 mm &amp; 140 mm Kasa</t>
-        </is>
-      </c>
-      <c r="K11" s="12" t="inlineStr">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="55" t="inlineStr">
+        <is>
+          <t>Hat 201</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>WPC Levha Makinesi 1</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Levha Ekstrüzyon</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>1562.4</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>253</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>283404.8800000001</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="H13" s="56" t="n">
+        <v>11</v>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>Levha Kalıbı (Tek Kafa)</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>WPC Kapı Yüzey Levhaları (Tüm Renkler)</t>
+        </is>
+      </c>
+      <c r="K13" s="12" t="inlineStr">
         <is>
           <t>Aktif Üretimde</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="45" t="inlineStr">
-        <is>
-          <t>Hat 109</t>
-        </is>
-      </c>
-      <c r="B12" s="25" t="inlineStr">
-        <is>
-          <t>Yüksek Hızlı Pervaz Ekstrüder 9</t>
-        </is>
-      </c>
-      <c r="C12" s="25" t="inlineStr">
-        <is>
-          <t>Profil Ekstrüzyon</t>
-        </is>
-      </c>
-      <c r="D12" s="29" t="n">
-        <v>1574.2</v>
-      </c>
-      <c r="E12" s="30" t="n">
-        <v>153</v>
-      </c>
-      <c r="F12" s="27" t="n">
-        <v>115763.31</v>
-      </c>
-      <c r="G12" s="31" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="H12" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="I12" s="28" t="inlineStr">
-        <is>
-          <t>Tek Göz &amp; Çift Göz (2 Kafa)</t>
-        </is>
-      </c>
-      <c r="J12" s="25" t="inlineStr">
-        <is>
-          <t>50x80 Pervaz (Çift Göz), 80x80 Pervaz</t>
-        </is>
-      </c>
-      <c r="K12" s="28" t="inlineStr">
-        <is>
-          <t>Aktif Üretimde</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="47" t="inlineStr">
-        <is>
-          <t>Hat 201</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>WPC Levha Makinesi 1</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Levha Ekstrüzyon</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>1565.5</v>
-      </c>
-      <c r="E13" s="15" t="n">
-        <v>252</v>
-      </c>
-      <c r="F13" s="11" t="n">
-        <v>280733.6800000001</v>
-      </c>
-      <c r="G13" s="16" t="n">
-        <v>179.3</v>
-      </c>
-      <c r="H13" s="48" t="n">
-        <v>11</v>
-      </c>
-      <c r="I13" s="12" t="inlineStr">
-        <is>
-          <t>Levha Kalıbı (Tek Kafa)</t>
-        </is>
-      </c>
-      <c r="J13" s="8" t="inlineStr">
-        <is>
-          <t>WPC Kapı Yüzey Levhaları (Tüm Renkler)</t>
-        </is>
-      </c>
-      <c r="K13" s="12" t="inlineStr">
-        <is>
-          <t>Aktif Üretimde</t>
-        </is>
-      </c>
-    </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="49" t="inlineStr">
-        <is>
-          <t>GENEL TOPLAM (10 HAT)</t>
-        </is>
-      </c>
-      <c r="B14" s="42" t="n"/>
-      <c r="C14" s="42" t="n"/>
-      <c r="D14" s="44" t="n">
-        <v>14898.4</v>
-      </c>
-      <c r="E14" s="43" t="n">
-        <v>1480</v>
-      </c>
-      <c r="F14" s="43" t="n">
-        <v>1266753.58</v>
-      </c>
-      <c r="G14" s="44" t="n">
-        <v>85</v>
-      </c>
-      <c r="H14" s="42" t="n"/>
-      <c r="I14" s="42" t="n"/>
-      <c r="J14" s="42" t="n"/>
-      <c r="K14" s="42" t="n"/>
+      <c r="A14" s="57" t="inlineStr">
+        <is>
+          <t>GENEL TOPLAM (FİLTREYE DUYARLI)</t>
+        </is>
+      </c>
+      <c r="B14" s="50" t="n"/>
+      <c r="C14" s="50" t="n"/>
+      <c r="D14" s="52">
+        <f>SUBTOTAL(109, D4:D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="51">
+        <f>SUBTOTAL(109, E4:E13)</f>
+        <v/>
+      </c>
+      <c r="F14" s="51">
+        <f>SUBTOTAL(109, F4:F13)</f>
+        <v/>
+      </c>
+      <c r="G14" s="52">
+        <f>IF(SUBTOTAL(109, D4:D13)&gt;0, SUBTOTAL(109, F4:F13)/SUBTOTAL(109, D4:D13), 0)</f>
+        <v/>
+      </c>
+      <c r="H14" s="50" t="n"/>
+      <c r="I14" s="50" t="n"/>
+      <c r="J14" s="50" t="n"/>
+      <c r="K14" s="50" t="n"/>
     </row>
   </sheetData>
+  <autoFilter ref="A3:K13"/>
   <mergeCells count="2">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
@@ -4489,7 +4368,7 @@
           <t>38 x 45 mm</t>
         </is>
       </c>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="E4" s="53" t="inlineStr">
         <is>
           <t>Hat 104</t>
         </is>
@@ -4505,32 +4384,28 @@
         </is>
       </c>
       <c r="H4" s="29" t="n">
-        <v>1646.4</v>
+        <v>1670.4</v>
       </c>
       <c r="I4" s="30" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J4" s="30" t="n">
-        <v>46427</v>
-      </c>
-      <c r="K4" s="26" t="inlineStr">
-        <is>
-          <t>3.39 kg/boy</t>
-        </is>
+        <v>47142</v>
+      </c>
+      <c r="K4" s="26" t="n">
+        <v>3.39</v>
       </c>
       <c r="L4" s="27" t="n">
-        <v>158335.32</v>
+        <v>160791.32</v>
       </c>
       <c r="M4" s="31" t="n">
-        <v>96.2</v>
-      </c>
-      <c r="N4" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~28 Boy</t>
-        </is>
-      </c>
-      <c r="O4" s="50" t="n">
-        <v>0.5288813174818345</v>
+        <v>96.3</v>
+      </c>
+      <c r="N4" s="32" t="n">
+        <v>28</v>
+      </c>
+      <c r="O4" s="58" t="n">
+        <v>0.5292638993338387</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -4554,7 +4429,7 @@
           <t>38 x 45 mm</t>
         </is>
       </c>
-      <c r="E5" s="47" t="inlineStr">
+      <c r="E5" s="55" t="inlineStr">
         <is>
           <t>Hat 105</t>
         </is>
@@ -4570,32 +4445,28 @@
         </is>
       </c>
       <c r="H5" s="14" t="n">
-        <v>1502.5</v>
+        <v>1524.5</v>
       </c>
       <c r="I5" s="15" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J5" s="15" t="n">
-        <v>40129</v>
-      </c>
-      <c r="K5" s="10" t="inlineStr">
-        <is>
-          <t>3.39 kg/boy</t>
-        </is>
+        <v>40679</v>
+      </c>
+      <c r="K5" s="10" t="n">
+        <v>3.39</v>
       </c>
       <c r="L5" s="11" t="n">
-        <v>136805.47</v>
+        <v>138773.47</v>
       </c>
       <c r="M5" s="16" t="n">
-        <v>91.09999999999999</v>
-      </c>
-      <c r="N5" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~27 Boy</t>
-        </is>
-      </c>
-      <c r="O5" s="51" t="n">
-        <v>0.4569659960413229</v>
+        <v>91</v>
+      </c>
+      <c r="N5" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="O5" s="59" t="n">
+        <v>0.456789507395595</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -4619,12 +4490,12 @@
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E6" s="45" t="inlineStr">
+      <c r="E6" s="53" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="F6" s="33" t="inlineStr">
+      <c r="F6" s="40" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -4635,31 +4506,27 @@
         </is>
       </c>
       <c r="H6" s="29" t="n">
-        <v>622.6096835790281</v>
+        <v>632.6096835790281</v>
       </c>
       <c r="I6" s="30" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J6" s="30" t="n">
-        <v>25734</v>
-      </c>
-      <c r="K6" s="26" t="inlineStr">
-        <is>
-          <t>4.77 kg/plaka</t>
-        </is>
+        <v>26294</v>
+      </c>
+      <c r="K6" s="26" t="n">
+        <v>4.77</v>
       </c>
       <c r="L6" s="27" t="n">
-        <v>122751.18</v>
+        <v>125422.38</v>
       </c>
       <c r="M6" s="31" t="n">
-        <v>197.2</v>
-      </c>
-      <c r="N6" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~41 Plaka</t>
-        </is>
-      </c>
-      <c r="O6" s="50" t="n">
+        <v>198.3</v>
+      </c>
+      <c r="N6" s="45" t="n">
+        <v>42</v>
+      </c>
+      <c r="O6" s="58" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4684,12 +4551,12 @@
           <t>140 x 36 mm</t>
         </is>
       </c>
-      <c r="E7" s="47" t="inlineStr">
+      <c r="E7" s="55" t="inlineStr">
         <is>
           <t>Hat 106</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="F7" s="39" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -4700,32 +4567,28 @@
         </is>
       </c>
       <c r="H7" s="14" t="n">
-        <v>1609.3</v>
+        <v>1633.3</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J7" s="15" t="n">
-        <v>22612</v>
-      </c>
-      <c r="K7" s="10" t="inlineStr">
-        <is>
-          <t>4.95 kg/boy</t>
-        </is>
+        <v>22822</v>
+      </c>
+      <c r="K7" s="10" t="n">
+        <v>4.95</v>
       </c>
       <c r="L7" s="11" t="n">
-        <v>115624</v>
+        <v>116744</v>
       </c>
       <c r="M7" s="16" t="n">
-        <v>71.8</v>
-      </c>
-      <c r="N7" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~14 Boy</t>
-        </is>
-      </c>
-      <c r="O7" s="51" t="n">
-        <v>0.6573541869204573</v>
+        <v>71.5</v>
+      </c>
+      <c r="N7" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="O7" s="59" t="n">
+        <v>0.6581724697817066</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -4749,7 +4612,7 @@
           <t>50 x 80 mm</t>
         </is>
       </c>
-      <c r="E8" s="45" t="inlineStr">
+      <c r="E8" s="53" t="inlineStr">
         <is>
           <t>Hat 109</t>
         </is>
@@ -4765,32 +4628,28 @@
         </is>
       </c>
       <c r="H8" s="29" t="n">
-        <v>1562.2</v>
+        <v>1586.2</v>
       </c>
       <c r="I8" s="30" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="J8" s="30" t="n">
-        <v>76681</v>
-      </c>
-      <c r="K8" s="26" t="inlineStr">
-        <is>
-          <t>1.55 kg/boy</t>
-        </is>
+        <v>77316</v>
+      </c>
+      <c r="K8" s="26" t="n">
+        <v>1.55</v>
       </c>
       <c r="L8" s="27" t="n">
-        <v>114742.31</v>
+        <v>115855.31</v>
       </c>
       <c r="M8" s="31" t="n">
-        <v>73.40000000000001</v>
-      </c>
-      <c r="N8" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~49 Boy</t>
-        </is>
-      </c>
-      <c r="O8" s="50" t="n">
-        <v>0.601024161428676</v>
+        <v>73</v>
+      </c>
+      <c r="N8" s="32" t="n">
+        <v>49</v>
+      </c>
+      <c r="O8" s="58" t="n">
+        <v>0.6019667537335166</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -4814,12 +4673,12 @@
           <t>200 x 36 mm</t>
         </is>
       </c>
-      <c r="E9" s="47" t="inlineStr">
+      <c r="E9" s="55" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F9" s="39" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -4838,10 +4697,8 @@
       <c r="J9" s="15" t="n">
         <v>11377</v>
       </c>
-      <c r="K9" s="10" t="inlineStr">
-        <is>
-          <t>6.66 kg/boy</t>
-        </is>
+      <c r="K9" s="10" t="n">
+        <v>6.66</v>
       </c>
       <c r="L9" s="11" t="n">
         <v>77027</v>
@@ -4849,12 +4706,10 @@
       <c r="M9" s="16" t="n">
         <v>84.59999999999999</v>
       </c>
-      <c r="N9" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~12 Boy</t>
-        </is>
-      </c>
-      <c r="O9" s="51" t="n">
+      <c r="N9" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="O9" s="59" t="n">
         <v>0.9470688044066297</v>
       </c>
     </row>
@@ -4879,7 +4734,7 @@
           <t>50 x 80 mm</t>
         </is>
       </c>
-      <c r="E10" s="45" t="inlineStr">
+      <c r="E10" s="53" t="inlineStr">
         <is>
           <t>Hat 103</t>
         </is>
@@ -4895,32 +4750,28 @@
         </is>
       </c>
       <c r="H10" s="29" t="n">
-        <v>1445</v>
+        <v>1469</v>
       </c>
       <c r="I10" s="30" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="J10" s="30" t="n">
-        <v>45990</v>
-      </c>
-      <c r="K10" s="26" t="inlineStr">
-        <is>
-          <t>1.55 kg/boy</t>
-        </is>
+        <v>46260</v>
+      </c>
+      <c r="K10" s="26" t="n">
+        <v>1.55</v>
       </c>
       <c r="L10" s="27" t="n">
-        <v>76169</v>
+        <v>76606</v>
       </c>
       <c r="M10" s="31" t="n">
-        <v>52.7</v>
-      </c>
-      <c r="N10" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~32 Boy</t>
-        </is>
-      </c>
-      <c r="O10" s="50" t="n">
-        <v>0.398975838571324</v>
+        <v>52.1</v>
+      </c>
+      <c r="N10" s="32" t="n">
+        <v>31</v>
+      </c>
+      <c r="O10" s="58" t="n">
+        <v>0.3980332462664834</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -4944,12 +4795,12 @@
           <t>100 x 36 mm</t>
         </is>
       </c>
-      <c r="E11" s="47" t="inlineStr">
+      <c r="E11" s="55" t="inlineStr">
         <is>
           <t>Hat 102</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="39" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -4968,10 +4819,8 @@
       <c r="J11" s="15" t="n">
         <v>16716</v>
       </c>
-      <c r="K11" s="10" t="inlineStr">
-        <is>
-          <t>4.00 kg/boy</t>
-        </is>
+      <c r="K11" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="L11" s="11" t="n">
         <v>67941</v>
@@ -4979,13 +4828,11 @@
       <c r="M11" s="16" t="n">
         <v>63.3</v>
       </c>
-      <c r="N11" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~16 Boy</t>
-        </is>
-      </c>
-      <c r="O11" s="51" t="n">
-        <v>0.5057361575932257</v>
+      <c r="N11" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="O11" s="59" t="n">
+        <v>0.5010294772674311</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -5009,12 +4856,12 @@
           <t>100 x 36 mm</t>
         </is>
       </c>
-      <c r="E12" s="45" t="inlineStr">
+      <c r="E12" s="53" t="inlineStr">
         <is>
           <t>Hat 108</t>
         </is>
       </c>
-      <c r="F12" s="33" t="inlineStr">
+      <c r="F12" s="40" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -5025,32 +4872,28 @@
         </is>
       </c>
       <c r="H12" s="29" t="n">
-        <v>959</v>
+        <v>983</v>
       </c>
       <c r="I12" s="30" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J12" s="30" t="n">
-        <v>16653</v>
-      </c>
-      <c r="K12" s="26" t="inlineStr">
-        <is>
-          <t>4.00 kg/boy</t>
-        </is>
+        <v>16968</v>
+      </c>
+      <c r="K12" s="26" t="n">
+        <v>4</v>
       </c>
       <c r="L12" s="27" t="n">
-        <v>64405.8</v>
+        <v>65667.8</v>
       </c>
       <c r="M12" s="31" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="N12" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~17 Boy</t>
-        </is>
-      </c>
-      <c r="O12" s="50" t="n">
-        <v>0.4794209949620667</v>
+        <v>66.8</v>
+      </c>
+      <c r="N12" s="32" t="n">
+        <v>17</v>
+      </c>
+      <c r="O12" s="58" t="n">
+        <v>0.4842658116204091</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -5074,12 +4917,12 @@
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E13" s="47" t="inlineStr">
+      <c r="E13" s="55" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="F13" s="39" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -5098,10 +4941,8 @@
       <c r="J13" s="15" t="n">
         <v>9359</v>
       </c>
-      <c r="K13" s="10" t="inlineStr">
-        <is>
-          <t>4.25 kg/plaka</t>
-        </is>
+      <c r="K13" s="10" t="n">
+        <v>4.25</v>
       </c>
       <c r="L13" s="11" t="n">
         <v>39775.75</v>
@@ -5109,12 +4950,10 @@
       <c r="M13" s="16" t="n">
         <v>169.1</v>
       </c>
-      <c r="N13" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~40 Plaka</t>
-        </is>
-      </c>
-      <c r="O13" s="51" t="n">
+      <c r="N13" s="41" t="n">
+        <v>40</v>
+      </c>
+      <c r="O13" s="59" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5139,12 +4978,12 @@
           <t>140 x 36 mm</t>
         </is>
       </c>
-      <c r="E14" s="45" t="inlineStr">
+      <c r="E14" s="53" t="inlineStr">
         <is>
           <t>Hat 108</t>
         </is>
       </c>
-      <c r="F14" s="33" t="inlineStr">
+      <c r="F14" s="40" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -5163,10 +5002,8 @@
       <c r="J14" s="30" t="n">
         <v>8661</v>
       </c>
-      <c r="K14" s="26" t="inlineStr">
-        <is>
-          <t>4.95 kg/boy</t>
-        </is>
+      <c r="K14" s="26" t="n">
+        <v>4.95</v>
       </c>
       <c r="L14" s="27" t="n">
         <v>38324</v>
@@ -5174,42 +5011,40 @@
       <c r="M14" s="31" t="n">
         <v>64.90000000000001</v>
       </c>
-      <c r="N14" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~15 Boy</t>
-        </is>
-      </c>
-      <c r="O14" s="50" t="n">
-        <v>0.2178824626335329</v>
+      <c r="N14" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="O14" s="58" t="n">
+        <v>0.2160607974021288</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>MIX TEAK Levha</t>
+          <t>SEREN(39mm)</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>WPC Levha Plaka</t>
+          <t>Seren Çıtası</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>207 cm (2.07 m)</t>
+          <t>2.10 Metre</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>En: 94 cm (2 mm)</t>
-        </is>
-      </c>
-      <c r="E15" s="47" t="inlineStr">
-        <is>
-          <t>Hat 201</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
+          <t>39 x 45 mm</t>
+        </is>
+      </c>
+      <c r="E15" s="55" t="inlineStr">
+        <is>
+          <t>Hat 107</t>
+        </is>
+      </c>
+      <c r="F15" s="39" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -5220,61 +5055,57 @@
         </is>
       </c>
       <c r="H15" s="14" t="n">
-        <v>187.6562562708018</v>
+        <v>327</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>7675</v>
-      </c>
-      <c r="K15" s="10" t="inlineStr">
-        <is>
-          <t>4.25 kg/plaka</t>
-        </is>
+        <v>9123</v>
+      </c>
+      <c r="K15" s="10" t="n">
+        <v>3.81</v>
       </c>
       <c r="L15" s="11" t="n">
-        <v>32618.75</v>
+        <v>34458</v>
       </c>
       <c r="M15" s="16" t="n">
-        <v>173.8</v>
-      </c>
-      <c r="N15" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~41 Plaka</t>
-        </is>
-      </c>
-      <c r="O15" s="51" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="N15" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="O15" s="59" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>SEREN(39mm)</t>
+          <t>MIX TEAK Levha</t>
         </is>
       </c>
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>Seren Çıtası</t>
+          <t>WPC Levha Plaka</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>2.10 Metre</t>
+          <t>207 cm (2.07 m)</t>
         </is>
       </c>
       <c r="D16" s="25" t="inlineStr">
         <is>
-          <t>39 x 45 mm</t>
-        </is>
-      </c>
-      <c r="E16" s="45" t="inlineStr">
-        <is>
-          <t>Hat 107</t>
-        </is>
-      </c>
-      <c r="F16" s="33" t="inlineStr">
+          <t>En: 94 cm (2 mm)</t>
+        </is>
+      </c>
+      <c r="E16" s="53" t="inlineStr">
+        <is>
+          <t>Hat 201</t>
+        </is>
+      </c>
+      <c r="F16" s="40" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -5285,31 +5116,27 @@
         </is>
       </c>
       <c r="H16" s="29" t="n">
-        <v>303</v>
+        <v>187.6562562708018</v>
       </c>
       <c r="I16" s="30" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J16" s="30" t="n">
-        <v>8583</v>
-      </c>
-      <c r="K16" s="26" t="inlineStr">
-        <is>
-          <t>3.81 kg/boy</t>
-        </is>
+        <v>7675</v>
+      </c>
+      <c r="K16" s="26" t="n">
+        <v>4.25</v>
       </c>
       <c r="L16" s="27" t="n">
-        <v>32593</v>
+        <v>32618.75</v>
       </c>
       <c r="M16" s="31" t="n">
-        <v>107.6</v>
-      </c>
-      <c r="N16" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~28 Boy</t>
-        </is>
-      </c>
-      <c r="O16" s="50" t="n">
+        <v>173.8</v>
+      </c>
+      <c r="N16" s="45" t="n">
+        <v>41</v>
+      </c>
+      <c r="O16" s="58" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5334,12 +5161,12 @@
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E17" s="47" t="inlineStr">
+      <c r="E17" s="55" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="F17" s="18" t="inlineStr">
+      <c r="F17" s="39" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -5358,10 +5185,8 @@
       <c r="J17" s="15" t="n">
         <v>7270</v>
       </c>
-      <c r="K17" s="10" t="inlineStr">
-        <is>
-          <t>4.41 kg/plaka</t>
-        </is>
+      <c r="K17" s="10" t="n">
+        <v>4.41</v>
       </c>
       <c r="L17" s="11" t="n">
         <v>32060.7</v>
@@ -5369,12 +5194,10 @@
       <c r="M17" s="16" t="n">
         <v>184.5</v>
       </c>
-      <c r="N17" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~42 Plaka</t>
-        </is>
-      </c>
-      <c r="O17" s="51" t="n">
+      <c r="N17" s="41" t="n">
+        <v>42</v>
+      </c>
+      <c r="O17" s="59" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5399,12 +5222,12 @@
           <t>140 x 36 mm</t>
         </is>
       </c>
-      <c r="E18" s="45" t="inlineStr">
+      <c r="E18" s="53" t="inlineStr">
         <is>
           <t>Hat 102</t>
         </is>
       </c>
-      <c r="F18" s="33" t="inlineStr">
+      <c r="F18" s="40" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -5415,32 +5238,28 @@
         </is>
       </c>
       <c r="H18" s="29" t="n">
-        <v>326</v>
+        <v>345</v>
       </c>
       <c r="I18" s="30" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J18" s="30" t="n">
-        <v>3611</v>
-      </c>
-      <c r="K18" s="26" t="inlineStr">
-        <is>
-          <t>4.95 kg/boy</t>
-        </is>
+        <v>3677</v>
+      </c>
+      <c r="K18" s="26" t="n">
+        <v>4.95</v>
       </c>
       <c r="L18" s="27" t="n">
-        <v>19859</v>
+        <v>20222</v>
       </c>
       <c r="M18" s="31" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="N18" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~11 Boy</t>
-        </is>
-      </c>
-      <c r="O18" s="50" t="n">
-        <v>0.1129038676922902</v>
+        <v>58.6</v>
+      </c>
+      <c r="N18" s="32" t="n">
+        <v>11</v>
+      </c>
+      <c r="O18" s="58" t="n">
+        <v>0.1140064044741115</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -5464,12 +5283,12 @@
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E19" s="47" t="inlineStr">
+      <c r="E19" s="55" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="F19" s="18" t="inlineStr">
+      <c r="F19" s="39" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -5488,10 +5307,8 @@
       <c r="J19" s="15" t="n">
         <v>3850</v>
       </c>
-      <c r="K19" s="10" t="inlineStr">
-        <is>
-          <t>4.77 kg/plaka</t>
-        </is>
+      <c r="K19" s="10" t="n">
+        <v>4.77</v>
       </c>
       <c r="L19" s="11" t="n">
         <v>18364.5</v>
@@ -5499,12 +5316,10 @@
       <c r="M19" s="16" t="n">
         <v>160.8</v>
       </c>
-      <c r="N19" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~34 Plaka</t>
-        </is>
-      </c>
-      <c r="O19" s="51" t="n">
+      <c r="N19" s="41" t="n">
+        <v>34</v>
+      </c>
+      <c r="O19" s="59" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5529,12 +5344,12 @@
           <t>220 x 24 mm</t>
         </is>
       </c>
-      <c r="E20" s="45" t="inlineStr">
+      <c r="E20" s="53" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="F20" s="33" t="inlineStr">
+      <c r="F20" s="40" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -5553,10 +5368,8 @@
       <c r="J20" s="30" t="n">
         <v>1712</v>
       </c>
-      <c r="K20" s="26" t="inlineStr">
-        <is>
-          <t>10.33 kg/boy</t>
-        </is>
+      <c r="K20" s="26" t="n">
+        <v>10.33</v>
       </c>
       <c r="L20" s="27" t="n">
         <v>17678</v>
@@ -5564,12 +5377,10 @@
       <c r="M20" s="31" t="n">
         <v>85.90000000000001</v>
       </c>
-      <c r="N20" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~8 Boy</t>
-        </is>
-      </c>
-      <c r="O20" s="50" t="n">
+      <c r="N20" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="O20" s="58" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5594,12 +5405,12 @@
           <t>80 x 80 mm</t>
         </is>
       </c>
-      <c r="E21" s="47" t="inlineStr">
+      <c r="E21" s="55" t="inlineStr">
         <is>
           <t>Hat 101</t>
         </is>
       </c>
-      <c r="F21" s="18" t="inlineStr">
+      <c r="F21" s="39" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -5618,10 +5429,8 @@
       <c r="J21" s="15" t="n">
         <v>5830</v>
       </c>
-      <c r="K21" s="10" t="inlineStr">
-        <is>
-          <t>2.20 kg/boy</t>
-        </is>
+      <c r="K21" s="10" t="n">
+        <v>2.2</v>
       </c>
       <c r="L21" s="11" t="n">
         <v>13318</v>
@@ -5629,12 +5438,10 @@
       <c r="M21" s="16" t="n">
         <v>51.1</v>
       </c>
-      <c r="N21" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~22 Boy</t>
-        </is>
-      </c>
-      <c r="O21" s="51" t="n">
+      <c r="N21" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="O21" s="59" t="n">
         <v>0.928795592440198</v>
       </c>
     </row>
@@ -5659,12 +5466,12 @@
           <t>35 x 100 mm</t>
         </is>
       </c>
-      <c r="E22" s="45" t="inlineStr">
+      <c r="E22" s="53" t="inlineStr">
         <is>
           <t>Hat 101</t>
         </is>
       </c>
-      <c r="F22" s="33" t="inlineStr">
+      <c r="F22" s="40" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -5683,10 +5490,8 @@
       <c r="J22" s="30" t="n">
         <v>4995</v>
       </c>
-      <c r="K22" s="26" t="inlineStr">
-        <is>
-          <t>2.08 kg/boy</t>
-        </is>
+      <c r="K22" s="26" t="n">
+        <v>2.08</v>
       </c>
       <c r="L22" s="27" t="n">
         <v>10435</v>
@@ -5694,12 +5499,10 @@
       <c r="M22" s="31" t="n">
         <v>43.3</v>
       </c>
-      <c r="N22" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~21 Boy</t>
-        </is>
-      </c>
-      <c r="O22" s="50" t="n">
+      <c r="N22" s="32" t="n">
+        <v>21</v>
+      </c>
+      <c r="O22" s="58" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5724,12 +5527,12 @@
           <t>35 x 150 mm</t>
         </is>
       </c>
-      <c r="E23" s="47" t="inlineStr">
+      <c r="E23" s="55" t="inlineStr">
         <is>
           <t>Hat 101</t>
         </is>
       </c>
-      <c r="F23" s="18" t="inlineStr">
+      <c r="F23" s="39" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -5748,10 +5551,8 @@
       <c r="J23" s="15" t="n">
         <v>3205</v>
       </c>
-      <c r="K23" s="10" t="inlineStr">
-        <is>
-          <t>2.97 kg/boy</t>
-        </is>
+      <c r="K23" s="10" t="n">
+        <v>2.97</v>
       </c>
       <c r="L23" s="11" t="n">
         <v>9522</v>
@@ -5759,12 +5560,10 @@
       <c r="M23" s="16" t="n">
         <v>41.2</v>
       </c>
-      <c r="N23" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~14 Boy</t>
-        </is>
-      </c>
-      <c r="O23" s="51" t="n">
+      <c r="N23" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="O23" s="59" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5789,12 +5588,12 @@
           <t>219 x 26 mm</t>
         </is>
       </c>
-      <c r="E24" s="45" t="inlineStr">
+      <c r="E24" s="53" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="F24" s="33" t="inlineStr">
+      <c r="F24" s="40" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -5813,10 +5612,8 @@
       <c r="J24" s="30" t="n">
         <v>895</v>
       </c>
-      <c r="K24" s="26" t="inlineStr">
-        <is>
-          <t>10.52 kg/boy</t>
-        </is>
+      <c r="K24" s="26" t="n">
+        <v>10.52</v>
       </c>
       <c r="L24" s="27" t="n">
         <v>9415</v>
@@ -5824,12 +5621,10 @@
       <c r="M24" s="31" t="n">
         <v>108.2</v>
       </c>
-      <c r="N24" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~10 Boy</t>
-        </is>
-      </c>
-      <c r="O24" s="50" t="n">
+      <c r="N24" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="O24" s="58" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5854,12 +5649,12 @@
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E25" s="47" t="inlineStr">
+      <c r="E25" s="55" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="F25" s="18" t="inlineStr">
+      <c r="F25" s="39" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -5878,10 +5673,8 @@
       <c r="J25" s="15" t="n">
         <v>2147</v>
       </c>
-      <c r="K25" s="10" t="inlineStr">
-        <is>
-          <t>4.25 kg/plaka</t>
-        </is>
+      <c r="K25" s="10" t="n">
+        <v>4.25</v>
       </c>
       <c r="L25" s="11" t="n">
         <v>9124.75</v>
@@ -5889,12 +5682,10 @@
       <c r="M25" s="16" t="n">
         <v>187</v>
       </c>
-      <c r="N25" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~44 Plaka</t>
-        </is>
-      </c>
-      <c r="O25" s="51" t="n">
+      <c r="N25" s="41" t="n">
+        <v>44</v>
+      </c>
+      <c r="O25" s="59" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5919,12 +5710,12 @@
           <t>15 x 20 mm</t>
         </is>
       </c>
-      <c r="E26" s="45" t="inlineStr">
+      <c r="E26" s="53" t="inlineStr">
         <is>
           <t>Hat 102</t>
         </is>
       </c>
-      <c r="F26" s="33" t="inlineStr">
+      <c r="F26" s="40" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -5943,10 +5734,8 @@
       <c r="J26" s="30" t="n">
         <v>5187</v>
       </c>
-      <c r="K26" s="26" t="inlineStr">
-        <is>
-          <t>1.50 kg/boy</t>
-        </is>
+      <c r="K26" s="26" t="n">
+        <v>1.5</v>
       </c>
       <c r="L26" s="27" t="n">
         <v>7805</v>
@@ -5954,12 +5743,10 @@
       <c r="M26" s="31" t="n">
         <v>52</v>
       </c>
-      <c r="N26" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~35 Boy</t>
-        </is>
-      </c>
-      <c r="O26" s="50" t="n">
+      <c r="N26" s="32" t="n">
+        <v>35</v>
+      </c>
+      <c r="O26" s="58" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5984,12 +5771,12 @@
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E27" s="47" t="inlineStr">
+      <c r="E27" s="55" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="F27" s="18" t="inlineStr">
+      <c r="F27" s="39" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -6000,7 +5787,7 @@
         </is>
       </c>
       <c r="H27" s="14" t="n">
-        <v>57.25702552864577</v>
+        <v>47.95702552864577</v>
       </c>
       <c r="I27" s="15" t="n">
         <v>13</v>
@@ -6008,23 +5795,19 @@
       <c r="J27" s="15" t="n">
         <v>1776</v>
       </c>
-      <c r="K27" s="10" t="inlineStr">
-        <is>
-          <t>4.33 kg/plaka</t>
-        </is>
+      <c r="K27" s="10" t="n">
+        <v>4.33</v>
       </c>
       <c r="L27" s="11" t="n">
         <v>7690.08</v>
       </c>
       <c r="M27" s="16" t="n">
-        <v>134.3</v>
-      </c>
-      <c r="N27" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~31 Plaka</t>
-        </is>
-      </c>
-      <c r="O27" s="51" t="n">
+        <v>160.4</v>
+      </c>
+      <c r="N27" s="41" t="n">
+        <v>37</v>
+      </c>
+      <c r="O27" s="59" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6049,12 +5832,12 @@
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E28" s="45" t="inlineStr">
+      <c r="E28" s="53" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="F28" s="33" t="inlineStr">
+      <c r="F28" s="40" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -6073,10 +5856,8 @@
       <c r="J28" s="30" t="n">
         <v>1297</v>
       </c>
-      <c r="K28" s="26" t="inlineStr">
-        <is>
-          <t>4.64 kg/plaka</t>
-        </is>
+      <c r="K28" s="26" t="n">
+        <v>4.64</v>
       </c>
       <c r="L28" s="27" t="n">
         <v>6018.08</v>
@@ -6084,12 +5865,10 @@
       <c r="M28" s="31" t="n">
         <v>158.2</v>
       </c>
-      <c r="N28" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~34 Plaka</t>
-        </is>
-      </c>
-      <c r="O28" s="50" t="n">
+      <c r="N28" s="45" t="n">
+        <v>34</v>
+      </c>
+      <c r="O28" s="58" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6114,12 +5893,12 @@
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E29" s="47" t="inlineStr">
+      <c r="E29" s="55" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="F29" s="18" t="inlineStr">
+      <c r="F29" s="39" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -6130,7 +5909,7 @@
         </is>
       </c>
       <c r="H29" s="14" t="n">
-        <v>41.52884989747753</v>
+        <v>37.72884989747753</v>
       </c>
       <c r="I29" s="15" t="n">
         <v>8</v>
@@ -6138,23 +5917,19 @@
       <c r="J29" s="15" t="n">
         <v>1176</v>
       </c>
-      <c r="K29" s="10" t="inlineStr">
-        <is>
-          <t>4.77 kg/plaka</t>
-        </is>
+      <c r="K29" s="10" t="n">
+        <v>4.77</v>
       </c>
       <c r="L29" s="11" t="n">
         <v>5609.52</v>
       </c>
       <c r="M29" s="16" t="n">
-        <v>135.1</v>
-      </c>
-      <c r="N29" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~28 Plaka</t>
-        </is>
-      </c>
-      <c r="O29" s="51" t="n">
+        <v>148.7</v>
+      </c>
+      <c r="N29" s="41" t="n">
+        <v>31</v>
+      </c>
+      <c r="O29" s="59" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6179,12 +5954,12 @@
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E30" s="45" t="inlineStr">
+      <c r="E30" s="53" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="F30" s="33" t="inlineStr">
+      <c r="F30" s="40" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -6203,10 +5978,8 @@
       <c r="J30" s="30" t="n">
         <v>803</v>
       </c>
-      <c r="K30" s="26" t="inlineStr">
-        <is>
-          <t>4.79 kg/plaka</t>
-        </is>
+      <c r="K30" s="26" t="n">
+        <v>4.79</v>
       </c>
       <c r="L30" s="27" t="n">
         <v>3846.37</v>
@@ -6214,12 +5987,10 @@
       <c r="M30" s="31" t="n">
         <v>120.3</v>
       </c>
-      <c r="N30" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~25 Plaka</t>
-        </is>
-      </c>
-      <c r="O30" s="50" t="n">
+      <c r="N30" s="45" t="n">
+        <v>25</v>
+      </c>
+      <c r="O30" s="58" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6244,12 +6015,12 @@
           <t>38 x 45 mm</t>
         </is>
       </c>
-      <c r="E31" s="47" t="inlineStr">
+      <c r="E31" s="55" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="F31" s="18" t="inlineStr">
+      <c r="F31" s="39" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -6268,10 +6039,8 @@
       <c r="J31" s="15" t="n">
         <v>865</v>
       </c>
-      <c r="K31" s="10" t="inlineStr">
-        <is>
-          <t>3.39 kg/boy</t>
-        </is>
+      <c r="K31" s="10" t="n">
+        <v>3.39</v>
       </c>
       <c r="L31" s="11" t="n">
         <v>3477</v>
@@ -6279,13 +6048,11 @@
       <c r="M31" s="16" t="n">
         <v>82.8</v>
       </c>
-      <c r="N31" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~21 Boy</t>
-        </is>
-      </c>
-      <c r="O31" s="51" t="n">
-        <v>0.01161408800566001</v>
+      <c r="N31" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="O31" s="59" t="n">
+        <v>0.0114449621906441</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
@@ -6309,12 +6076,12 @@
           <t>En: 94 cm (2 mm)</t>
         </is>
       </c>
-      <c r="E32" s="45" t="inlineStr">
+      <c r="E32" s="53" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="F32" s="33" t="inlineStr">
+      <c r="F32" s="40" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -6333,10 +6100,8 @@
       <c r="J32" s="30" t="n">
         <v>600</v>
       </c>
-      <c r="K32" s="26" t="inlineStr">
-        <is>
-          <t>4.79 kg/plaka</t>
-        </is>
+      <c r="K32" s="26" t="n">
+        <v>4.79</v>
       </c>
       <c r="L32" s="27" t="n">
         <v>2874</v>
@@ -6344,12 +6109,10 @@
       <c r="M32" s="31" t="n">
         <v>198.2</v>
       </c>
-      <c r="N32" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~41 Plaka</t>
-        </is>
-      </c>
-      <c r="O32" s="50" t="n">
+      <c r="N32" s="45" t="n">
+        <v>41</v>
+      </c>
+      <c r="O32" s="58" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6374,12 +6137,12 @@
           <t>200 x 36 mm</t>
         </is>
       </c>
-      <c r="E33" s="47" t="inlineStr">
+      <c r="E33" s="55" t="inlineStr">
         <is>
           <t>Hat 106</t>
         </is>
       </c>
-      <c r="F33" s="18" t="inlineStr">
+      <c r="F33" s="39" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -6398,10 +6161,8 @@
       <c r="J33" s="15" t="n">
         <v>492</v>
       </c>
-      <c r="K33" s="10" t="inlineStr">
-        <is>
-          <t>6.66 kg/boy</t>
-        </is>
+      <c r="K33" s="10" t="n">
+        <v>6.66</v>
       </c>
       <c r="L33" s="11" t="n">
         <v>2421</v>
@@ -6409,12 +6170,10 @@
       <c r="M33" s="16" t="n">
         <v>100.9</v>
       </c>
-      <c r="N33" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~20 Boy</t>
-        </is>
-      </c>
-      <c r="O33" s="51" t="n">
+      <c r="N33" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="O33" s="59" t="n">
         <v>0.02976688142428564</v>
       </c>
     </row>
@@ -6439,12 +6198,12 @@
           <t>200 x 36 mm</t>
         </is>
       </c>
-      <c r="E34" s="45" t="inlineStr">
+      <c r="E34" s="53" t="inlineStr">
         <is>
           <t>Hat 108</t>
         </is>
       </c>
-      <c r="F34" s="33" t="inlineStr">
+      <c r="F34" s="40" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -6463,10 +6222,8 @@
       <c r="J34" s="30" t="n">
         <v>348</v>
       </c>
-      <c r="K34" s="26" t="inlineStr">
-        <is>
-          <t>6.66 kg/boy</t>
-        </is>
+      <c r="K34" s="26" t="n">
+        <v>6.66</v>
       </c>
       <c r="L34" s="27" t="n">
         <v>1884</v>
@@ -6474,12 +6231,10 @@
       <c r="M34" s="31" t="n">
         <v>78.5</v>
       </c>
-      <c r="N34" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~14 Boy</t>
-        </is>
-      </c>
-      <c r="O34" s="50" t="n">
+      <c r="N34" s="32" t="n">
+        <v>14</v>
+      </c>
+      <c r="O34" s="58" t="n">
         <v>0.02316431416908474</v>
       </c>
     </row>
@@ -6504,12 +6259,12 @@
           <t>30 x 15 mm</t>
         </is>
       </c>
-      <c r="E35" s="47" t="inlineStr">
+      <c r="E35" s="55" t="inlineStr">
         <is>
           <t>Hat 102</t>
         </is>
       </c>
-      <c r="F35" s="18" t="inlineStr">
+      <c r="F35" s="39" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -6528,10 +6283,8 @@
       <c r="J35" s="15" t="n">
         <v>2901</v>
       </c>
-      <c r="K35" s="10" t="inlineStr">
-        <is>
-          <t>0.48 kg/boy</t>
-        </is>
+      <c r="K35" s="10" t="n">
+        <v>0.48</v>
       </c>
       <c r="L35" s="11" t="n">
         <v>1385</v>
@@ -6539,12 +6292,10 @@
       <c r="M35" s="16" t="n">
         <v>40.7</v>
       </c>
-      <c r="N35" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~85 Boy</t>
-        </is>
-      </c>
-      <c r="O35" s="51" t="n">
+      <c r="N35" s="17" t="n">
+        <v>85</v>
+      </c>
+      <c r="O35" s="59" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6569,12 +6320,12 @@
           <t>140 x 36 mm</t>
         </is>
       </c>
-      <c r="E36" s="45" t="inlineStr">
+      <c r="E36" s="53" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="F36" s="33" t="inlineStr">
+      <c r="F36" s="40" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -6593,10 +6344,8 @@
       <c r="J36" s="30" t="n">
         <v>220</v>
       </c>
-      <c r="K36" s="26" t="inlineStr">
-        <is>
-          <t>4.95 kg/boy</t>
-        </is>
+      <c r="K36" s="26" t="n">
+        <v>4.95</v>
       </c>
       <c r="L36" s="27" t="n">
         <v>1370</v>
@@ -6604,13 +6353,11 @@
       <c r="M36" s="31" t="n">
         <v>45.7</v>
       </c>
-      <c r="N36" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~7 Boy</t>
-        </is>
-      </c>
-      <c r="O36" s="50" t="n">
-        <v>0.007788826161359463</v>
+      <c r="N36" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="O36" s="58" t="n">
+        <v>0.007723705574598593</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
@@ -6634,12 +6381,12 @@
           <t>100 x 36 mm</t>
         </is>
       </c>
-      <c r="E37" s="47" t="inlineStr">
+      <c r="E37" s="55" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="F37" s="18" t="inlineStr">
+      <c r="F37" s="39" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -6658,10 +6405,8 @@
       <c r="J37" s="15" t="n">
         <v>174</v>
       </c>
-      <c r="K37" s="10" t="inlineStr">
-        <is>
-          <t>4.00 kg/boy</t>
-        </is>
+      <c r="K37" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="L37" s="11" t="n">
         <v>1153</v>
@@ -6669,13 +6414,11 @@
       <c r="M37" s="16" t="n">
         <v>96.09999999999999</v>
       </c>
-      <c r="N37" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~14 Boy</t>
-        </is>
-      </c>
-      <c r="O37" s="51" t="n">
-        <v>0.008582649500375166</v>
+      <c r="N37" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="O37" s="59" t="n">
+        <v>0.008502774278997189</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
@@ -6699,7 +6442,7 @@
           <t>80 x 80 mm</t>
         </is>
       </c>
-      <c r="E38" s="45" t="inlineStr">
+      <c r="E38" s="53" t="inlineStr">
         <is>
           <t>Hat 109</t>
         </is>
@@ -6723,10 +6466,8 @@
       <c r="J38" s="30" t="n">
         <v>690</v>
       </c>
-      <c r="K38" s="26" t="inlineStr">
-        <is>
-          <t>2.20 kg/boy</t>
-        </is>
+      <c r="K38" s="26" t="n">
+        <v>2.2</v>
       </c>
       <c r="L38" s="27" t="n">
         <v>1021</v>
@@ -6734,12 +6475,10 @@
       <c r="M38" s="31" t="n">
         <v>85.09999999999999</v>
       </c>
-      <c r="N38" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~58 Boy</t>
-        </is>
-      </c>
-      <c r="O38" s="50" t="n">
+      <c r="N38" s="32" t="n">
+        <v>58</v>
+      </c>
+      <c r="O38" s="58" t="n">
         <v>0.07120440755980194</v>
       </c>
     </row>
@@ -6764,12 +6503,12 @@
           <t>100 x 36 mm</t>
         </is>
       </c>
-      <c r="E39" s="47" t="inlineStr">
+      <c r="E39" s="55" t="inlineStr">
         <is>
           <t>Hat 106</t>
         </is>
       </c>
-      <c r="F39" s="18" t="inlineStr">
+      <c r="F39" s="39" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -6788,10 +6527,8 @@
       <c r="J39" s="15" t="n">
         <v>162</v>
       </c>
-      <c r="K39" s="10" t="inlineStr">
-        <is>
-          <t>4.00 kg/boy</t>
-        </is>
+      <c r="K39" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="L39" s="11" t="n">
         <v>841</v>
@@ -6799,13 +6536,11 @@
       <c r="M39" s="16" t="n">
         <v>70.09999999999999</v>
       </c>
-      <c r="N39" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~14 Boy</t>
-        </is>
-      </c>
-      <c r="O39" s="51" t="n">
-        <v>0.006260197944332623</v>
+      <c r="N39" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="O39" s="59" t="n">
+        <v>0.006201936833162737</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
@@ -6829,7 +6564,7 @@
           <t>38 x 45 mm</t>
         </is>
       </c>
-      <c r="E40" s="45" t="inlineStr">
+      <c r="E40" s="53" t="inlineStr">
         <is>
           <t>Hat 103</t>
         </is>
@@ -6853,10 +6588,8 @@
       <c r="J40" s="30" t="n">
         <v>450</v>
       </c>
-      <c r="K40" s="26" t="inlineStr">
-        <is>
-          <t>3.39 kg/boy</t>
-        </is>
+      <c r="K40" s="26" t="n">
+        <v>3.39</v>
       </c>
       <c r="L40" s="27" t="n">
         <v>760</v>
@@ -6864,13 +6597,11 @@
       <c r="M40" s="31" t="n">
         <v>63.3</v>
       </c>
-      <c r="N40" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~38 Boy</t>
-        </is>
-      </c>
-      <c r="O40" s="50" t="n">
-        <v>0.002538598471182515</v>
+      <c r="N40" s="32" t="n">
+        <v>38</v>
+      </c>
+      <c r="O40" s="58" t="n">
+        <v>0.002501631079922209</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
@@ -6894,12 +6625,12 @@
           <t>140 x 36 mm</t>
         </is>
       </c>
-      <c r="E41" s="47" t="inlineStr">
+      <c r="E41" s="55" t="inlineStr">
         <is>
           <t>Hat 105</t>
         </is>
       </c>
-      <c r="F41" s="18" t="inlineStr">
+      <c r="F41" s="39" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -6918,10 +6649,8 @@
       <c r="J41" s="15" t="n">
         <v>209</v>
       </c>
-      <c r="K41" s="10" t="inlineStr">
-        <is>
-          <t>4.95 kg/boy</t>
-        </is>
+      <c r="K41" s="10" t="n">
+        <v>4.95</v>
       </c>
       <c r="L41" s="11" t="n">
         <v>716</v>
@@ -6929,13 +6658,11 @@
       <c r="M41" s="16" t="n">
         <v>59.7</v>
       </c>
-      <c r="N41" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~17 Boy</t>
-        </is>
-      </c>
-      <c r="O41" s="51" t="n">
-        <v>0.004070656592360128</v>
+      <c r="N41" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="O41" s="59" t="n">
+        <v>0.004036622767454447</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
@@ -6959,12 +6686,12 @@
           <t>35 x 80 mm</t>
         </is>
       </c>
-      <c r="E42" s="45" t="inlineStr">
+      <c r="E42" s="53" t="inlineStr">
         <is>
           <t>Hat 101</t>
         </is>
       </c>
-      <c r="F42" s="33" t="inlineStr">
+      <c r="F42" s="40" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -6983,10 +6710,8 @@
       <c r="J42" s="30" t="n">
         <v>180</v>
       </c>
-      <c r="K42" s="26" t="inlineStr">
-        <is>
-          <t>2.94 kg/boy</t>
-        </is>
+      <c r="K42" s="26" t="n">
+        <v>2.94</v>
       </c>
       <c r="L42" s="27" t="n">
         <v>530</v>
@@ -6994,12 +6719,10 @@
       <c r="M42" s="31" t="n">
         <v>44.2</v>
       </c>
-      <c r="N42" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~15 Boy</t>
-        </is>
-      </c>
-      <c r="O42" s="50" t="n">
+      <c r="N42" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="O42" s="58" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7024,12 +6747,12 @@
           <t>219 x 26 mm</t>
         </is>
       </c>
-      <c r="E43" s="47" t="inlineStr">
+      <c r="E43" s="55" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="F43" s="18" t="inlineStr">
+      <c r="F43" s="39" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -7048,10 +6771,8 @@
       <c r="J43" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="K43" s="10" t="inlineStr">
-        <is>
-          <t>9.26 kg/boy</t>
-        </is>
+      <c r="K43" s="10" t="n">
+        <v>9.26</v>
       </c>
       <c r="L43" s="11" t="n">
         <v>463</v>
@@ -7059,43 +6780,48 @@
       <c r="M43" s="16" t="n">
         <v>115.8</v>
       </c>
-      <c r="N43" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~12 Boy</t>
-        </is>
-      </c>
-      <c r="O43" s="51" t="n">
+      <c r="N43" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="O43" s="59" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1">
-      <c r="A44" s="49" t="inlineStr">
-        <is>
-          <t>GENEL TOPLAM</t>
-        </is>
-      </c>
-      <c r="B44" s="42" t="n"/>
-      <c r="C44" s="42" t="n"/>
-      <c r="D44" s="42" t="n"/>
-      <c r="E44" s="42" t="n"/>
-      <c r="F44" s="42" t="n"/>
-      <c r="G44" s="42" t="n"/>
-      <c r="H44" s="44" t="n">
-        <v>14898.4</v>
-      </c>
-      <c r="I44" s="42" t="n"/>
-      <c r="J44" s="43" t="n">
-        <v>387692</v>
-      </c>
-      <c r="K44" s="42" t="n"/>
-      <c r="L44" s="43" t="n">
-        <v>1266753.58</v>
-      </c>
-      <c r="M44" s="42" t="n"/>
-      <c r="N44" s="42" t="n"/>
-      <c r="O44" s="42" t="n"/>
+      <c r="A44" s="57" t="inlineStr">
+        <is>
+          <t>GENEL TOPLAM (FİLTREYE DUYARLI)</t>
+        </is>
+      </c>
+      <c r="B44" s="50" t="n"/>
+      <c r="C44" s="50" t="n"/>
+      <c r="D44" s="50" t="n"/>
+      <c r="E44" s="50" t="n"/>
+      <c r="F44" s="50" t="n"/>
+      <c r="G44" s="50" t="n"/>
+      <c r="H44" s="52">
+        <f>SUBTOTAL(109, H4:H43)</f>
+        <v/>
+      </c>
+      <c r="I44" s="51">
+        <f>SUBTOTAL(109, I4:I43)</f>
+        <v/>
+      </c>
+      <c r="J44" s="51">
+        <f>SUBTOTAL(109, J4:J43)</f>
+        <v/>
+      </c>
+      <c r="K44" s="50" t="n"/>
+      <c r="L44" s="51">
+        <f>SUBTOTAL(109, L4:L43)</f>
+        <v/>
+      </c>
+      <c r="M44" s="50" t="n"/>
+      <c r="N44" s="50" t="n"/>
+      <c r="O44" s="50" t="n"/>
     </row>
   </sheetData>
+  <autoFilter ref="A3:O43"/>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:O2"/>
@@ -7110,7 +6836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7215,17 +6941,17 @@
           <t>100 mm KASA</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="60" t="inlineStr">
         <is>
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="53" t="inlineStr">
         <is>
           <t>Hat 102</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="53" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -7245,10 +6971,8 @@
       <c r="I4" s="31" t="n">
         <v>63.3</v>
       </c>
-      <c r="J4" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~16 Boy</t>
-        </is>
+      <c r="J4" s="32" t="n">
+        <v>16</v>
       </c>
       <c r="K4" s="29" t="n">
         <v>63.3</v>
@@ -7268,17 +6992,17 @@
           <t>100 mm KASA</t>
         </is>
       </c>
-      <c r="B5" s="53" t="inlineStr">
+      <c r="B5" s="61" t="inlineStr">
         <is>
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="C5" s="47" t="inlineStr">
+      <c r="C5" s="55" t="inlineStr">
         <is>
           <t>Hat 106</t>
         </is>
       </c>
-      <c r="D5" s="47" t="inlineStr">
+      <c r="D5" s="55" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -7298,10 +7022,8 @@
       <c r="I5" s="16" t="n">
         <v>70.09999999999999</v>
       </c>
-      <c r="J5" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~14 Boy</t>
-        </is>
+      <c r="J5" s="17" t="n">
+        <v>14</v>
       </c>
       <c r="K5" s="14" t="n">
         <v>70.09999999999999</v>
@@ -7321,17 +7043,17 @@
           <t>100 mm KASA</t>
         </is>
       </c>
-      <c r="B6" s="52" t="inlineStr">
+      <c r="B6" s="60" t="inlineStr">
         <is>
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="C6" s="45" t="inlineStr">
+      <c r="C6" s="53" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="D6" s="45" t="inlineStr">
+      <c r="D6" s="53" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -7351,10 +7073,8 @@
       <c r="I6" s="31" t="n">
         <v>96.09999999999999</v>
       </c>
-      <c r="J6" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~14 Boy</t>
-        </is>
+      <c r="J6" s="32" t="n">
+        <v>14</v>
       </c>
       <c r="K6" s="29" t="n">
         <v>96.09999999999999</v>
@@ -7374,46 +7094,44 @@
           <t>100 mm KASA</t>
         </is>
       </c>
-      <c r="B7" s="53" t="inlineStr">
+      <c r="B7" s="61" t="inlineStr">
         <is>
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="C7" s="47" t="inlineStr">
+      <c r="C7" s="55" t="inlineStr">
         <is>
           <t>Hat 108</t>
         </is>
       </c>
-      <c r="D7" s="47" t="inlineStr">
+      <c r="D7" s="55" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
       </c>
       <c r="E7" s="14" t="n">
-        <v>959</v>
+        <v>983</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>64405.8</v>
+        <v>65667.8</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>16653</v>
+        <v>16968</v>
       </c>
       <c r="I7" s="16" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="J7" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~17 Boy</t>
-        </is>
+        <v>66.8</v>
+      </c>
+      <c r="J7" s="17" t="n">
+        <v>17</v>
       </c>
       <c r="K7" s="14" t="n">
         <v>69.5</v>
       </c>
       <c r="L7" s="19" t="n">
-        <v>0.9669064748201438</v>
+        <v>0.9611510791366906</v>
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
@@ -7427,46 +7145,44 @@
           <t>140 mm KASA</t>
         </is>
       </c>
-      <c r="B8" s="52" t="inlineStr">
+      <c r="B8" s="60" t="inlineStr">
         <is>
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="C8" s="45" t="inlineStr">
+      <c r="C8" s="53" t="inlineStr">
         <is>
           <t>Hat 102</t>
         </is>
       </c>
-      <c r="D8" s="45" t="inlineStr">
+      <c r="D8" s="53" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
       </c>
       <c r="E8" s="29" t="n">
-        <v>326</v>
+        <v>345</v>
       </c>
       <c r="F8" s="30" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G8" s="27" t="n">
-        <v>19859</v>
+        <v>20222</v>
       </c>
       <c r="H8" s="30" t="n">
-        <v>3611</v>
+        <v>3677</v>
       </c>
       <c r="I8" s="31" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="J8" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~11 Boy</t>
-        </is>
+        <v>58.6</v>
+      </c>
+      <c r="J8" s="32" t="n">
+        <v>11</v>
       </c>
       <c r="K8" s="29" t="n">
         <v>51.8</v>
       </c>
       <c r="L8" s="34" t="n">
-        <v>1.175675675675676</v>
+        <v>1.131274131274131</v>
       </c>
       <c r="M8" s="25" t="inlineStr">
         <is>
@@ -7480,17 +7196,17 @@
           <t>140 mm KASA</t>
         </is>
       </c>
-      <c r="B9" s="53" t="inlineStr">
+      <c r="B9" s="61" t="inlineStr">
         <is>
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="C9" s="47" t="inlineStr">
+      <c r="C9" s="55" t="inlineStr">
         <is>
           <t>Hat 105</t>
         </is>
       </c>
-      <c r="D9" s="47" t="inlineStr">
+      <c r="D9" s="55" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -7510,10 +7226,8 @@
       <c r="I9" s="16" t="n">
         <v>59.7</v>
       </c>
-      <c r="J9" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~17 Boy</t>
-        </is>
+      <c r="J9" s="17" t="n">
+        <v>17</v>
       </c>
       <c r="K9" s="14" t="n">
         <v>59.7</v>
@@ -7533,46 +7247,44 @@
           <t>140 mm KASA</t>
         </is>
       </c>
-      <c r="B10" s="52" t="inlineStr">
+      <c r="B10" s="60" t="inlineStr">
         <is>
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="C10" s="45" t="inlineStr">
+      <c r="C10" s="53" t="inlineStr">
         <is>
           <t>Hat 106</t>
         </is>
       </c>
-      <c r="D10" s="45" t="inlineStr">
+      <c r="D10" s="53" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
       </c>
       <c r="E10" s="29" t="n">
-        <v>1609.3</v>
+        <v>1633.3</v>
       </c>
       <c r="F10" s="30" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G10" s="27" t="n">
-        <v>115624</v>
+        <v>116744</v>
       </c>
       <c r="H10" s="30" t="n">
-        <v>22612</v>
+        <v>22822</v>
       </c>
       <c r="I10" s="31" t="n">
-        <v>71.8</v>
-      </c>
-      <c r="J10" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~14 Boy</t>
-        </is>
+        <v>71.5</v>
+      </c>
+      <c r="J10" s="32" t="n">
+        <v>14</v>
       </c>
       <c r="K10" s="29" t="n">
         <v>74.09999999999999</v>
       </c>
       <c r="L10" s="34" t="n">
-        <v>0.9689608636977058</v>
+        <v>0.9649122807017545</v>
       </c>
       <c r="M10" s="25" t="inlineStr">
         <is>
@@ -7586,17 +7298,17 @@
           <t>140 mm KASA</t>
         </is>
       </c>
-      <c r="B11" s="53" t="inlineStr">
+      <c r="B11" s="61" t="inlineStr">
         <is>
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="C11" s="47" t="inlineStr">
+      <c r="C11" s="55" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="D11" s="47" t="inlineStr">
+      <c r="D11" s="55" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -7616,10 +7328,8 @@
       <c r="I11" s="16" t="n">
         <v>45.7</v>
       </c>
-      <c r="J11" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~7 Boy</t>
-        </is>
+      <c r="J11" s="17" t="n">
+        <v>7</v>
       </c>
       <c r="K11" s="14" t="n">
         <v>45.7</v>
@@ -7639,17 +7349,17 @@
           <t>140 mm KASA</t>
         </is>
       </c>
-      <c r="B12" s="52" t="inlineStr">
+      <c r="B12" s="60" t="inlineStr">
         <is>
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="C12" s="45" t="inlineStr">
+      <c r="C12" s="53" t="inlineStr">
         <is>
           <t>Hat 108</t>
         </is>
       </c>
-      <c r="D12" s="45" t="inlineStr">
+      <c r="D12" s="53" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -7669,10 +7379,8 @@
       <c r="I12" s="31" t="n">
         <v>64.90000000000001</v>
       </c>
-      <c r="J12" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~15 Boy</t>
-        </is>
+      <c r="J12" s="32" t="n">
+        <v>15</v>
       </c>
       <c r="K12" s="29" t="n">
         <v>64.90000000000001</v>
@@ -7692,17 +7400,17 @@
           <t>200 mm KASA</t>
         </is>
       </c>
-      <c r="B13" s="53" t="inlineStr">
+      <c r="B13" s="61" t="inlineStr">
         <is>
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="C13" s="47" t="inlineStr">
+      <c r="C13" s="55" t="inlineStr">
         <is>
           <t>Hat 106</t>
         </is>
       </c>
-      <c r="D13" s="47" t="inlineStr">
+      <c r="D13" s="55" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -7722,10 +7430,8 @@
       <c r="I13" s="16" t="n">
         <v>100.9</v>
       </c>
-      <c r="J13" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~20 Boy</t>
-        </is>
+      <c r="J13" s="17" t="n">
+        <v>20</v>
       </c>
       <c r="K13" s="14" t="n">
         <v>100.9</v>
@@ -7745,17 +7451,17 @@
           <t>200 mm KASA</t>
         </is>
       </c>
-      <c r="B14" s="52" t="inlineStr">
+      <c r="B14" s="60" t="inlineStr">
         <is>
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="C14" s="45" t="inlineStr">
+      <c r="C14" s="53" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="D14" s="45" t="inlineStr">
+      <c r="D14" s="53" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -7775,10 +7481,8 @@
       <c r="I14" s="31" t="n">
         <v>84.59999999999999</v>
       </c>
-      <c r="J14" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~12 Boy</t>
-        </is>
+      <c r="J14" s="32" t="n">
+        <v>12</v>
       </c>
       <c r="K14" s="29" t="n">
         <v>84.59999999999999</v>
@@ -7798,17 +7502,17 @@
           <t>200 mm KASA</t>
         </is>
       </c>
-      <c r="B15" s="53" t="inlineStr">
+      <c r="B15" s="61" t="inlineStr">
         <is>
           <t>2.15 Metre (215 cm)</t>
         </is>
       </c>
-      <c r="C15" s="47" t="inlineStr">
+      <c r="C15" s="55" t="inlineStr">
         <is>
           <t>Hat 108</t>
         </is>
       </c>
-      <c r="D15" s="47" t="inlineStr">
+      <c r="D15" s="55" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -7828,10 +7532,8 @@
       <c r="I15" s="16" t="n">
         <v>78.5</v>
       </c>
-      <c r="J15" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~14 Boy</t>
-        </is>
+      <c r="J15" s="17" t="n">
+        <v>14</v>
       </c>
       <c r="K15" s="14" t="n">
         <v>78.5</v>
@@ -7851,17 +7553,17 @@
           <t>35X100 PERVAZ</t>
         </is>
       </c>
-      <c r="B16" s="52" t="inlineStr">
+      <c r="B16" s="60" t="inlineStr">
         <is>
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="C16" s="45" t="inlineStr">
+      <c r="C16" s="53" t="inlineStr">
         <is>
           <t>Hat 101</t>
         </is>
       </c>
-      <c r="D16" s="45" t="inlineStr">
+      <c r="D16" s="53" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -7881,10 +7583,8 @@
       <c r="I16" s="31" t="n">
         <v>43.3</v>
       </c>
-      <c r="J16" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~21 Boy</t>
-        </is>
+      <c r="J16" s="32" t="n">
+        <v>21</v>
       </c>
       <c r="K16" s="29" t="n">
         <v>46.8</v>
@@ -7904,17 +7604,17 @@
           <t>35X150 PERVAZ</t>
         </is>
       </c>
-      <c r="B17" s="53" t="inlineStr">
+      <c r="B17" s="61" t="inlineStr">
         <is>
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="C17" s="47" t="inlineStr">
+      <c r="C17" s="55" t="inlineStr">
         <is>
           <t>Hat 101</t>
         </is>
       </c>
-      <c r="D17" s="47" t="inlineStr">
+      <c r="D17" s="55" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -7934,10 +7634,8 @@
       <c r="I17" s="16" t="n">
         <v>41.2</v>
       </c>
-      <c r="J17" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~14 Boy</t>
-        </is>
+      <c r="J17" s="17" t="n">
+        <v>14</v>
       </c>
       <c r="K17" s="14" t="n">
         <v>41.2</v>
@@ -7957,17 +7655,17 @@
           <t>35X80 PERVAZ</t>
         </is>
       </c>
-      <c r="B18" s="52" t="inlineStr">
+      <c r="B18" s="60" t="inlineStr">
         <is>
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="C18" s="45" t="inlineStr">
+      <c r="C18" s="53" t="inlineStr">
         <is>
           <t>Hat 101</t>
         </is>
       </c>
-      <c r="D18" s="45" t="inlineStr">
+      <c r="D18" s="53" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -7987,10 +7685,8 @@
       <c r="I18" s="31" t="n">
         <v>44.2</v>
       </c>
-      <c r="J18" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~15 Boy</t>
-        </is>
+      <c r="J18" s="32" t="n">
+        <v>15</v>
       </c>
       <c r="K18" s="29" t="n">
         <v>44.2</v>
@@ -8010,17 +7706,17 @@
           <t>50X80 PERVAZ</t>
         </is>
       </c>
-      <c r="B19" s="53" t="inlineStr">
+      <c r="B19" s="61" t="inlineStr">
         <is>
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="C19" s="47" t="inlineStr">
+      <c r="C19" s="55" t="inlineStr">
         <is>
           <t>Hat 103</t>
         </is>
       </c>
-      <c r="D19" s="47" t="inlineStr">
+      <c r="D19" s="55" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -8040,10 +7736,8 @@
       <c r="I19" s="16" t="n">
         <v>59.6</v>
       </c>
-      <c r="J19" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~38 Boy</t>
-        </is>
+      <c r="J19" s="17" t="n">
+        <v>38</v>
       </c>
       <c r="K19" s="14" t="n">
         <v>53.1</v>
@@ -8058,17 +7752,17 @@
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="54" t="inlineStr">
+      <c r="A20" s="62" t="inlineStr">
         <is>
           <t>50X80 PERVAZ</t>
         </is>
       </c>
-      <c r="B20" s="55" t="inlineStr">
+      <c r="B20" s="63" t="inlineStr">
         <is>
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="C20" s="56" t="inlineStr">
+      <c r="C20" s="64" t="inlineStr">
         <is>
           <t>Hat 103</t>
         </is>
@@ -8078,33 +7772,31 @@
           <t>Çift Göz (2 Kafa)</t>
         </is>
       </c>
-      <c r="E20" s="57" t="n">
-        <v>1373</v>
-      </c>
-      <c r="F20" s="58" t="n">
-        <v>125</v>
-      </c>
-      <c r="G20" s="59" t="n">
-        <v>71878</v>
-      </c>
-      <c r="H20" s="58" t="n">
-        <v>43250</v>
-      </c>
-      <c r="I20" s="60" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="J20" s="61" t="inlineStr">
-        <is>
-          <t>Saatte ~32 Boy</t>
-        </is>
-      </c>
-      <c r="K20" s="57" t="n">
+      <c r="E20" s="65" t="n">
+        <v>1397</v>
+      </c>
+      <c r="F20" s="66" t="n">
+        <v>127</v>
+      </c>
+      <c r="G20" s="67" t="n">
+        <v>72315</v>
+      </c>
+      <c r="H20" s="66" t="n">
+        <v>43520</v>
+      </c>
+      <c r="I20" s="68" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="J20" s="69" t="n">
+        <v>31</v>
+      </c>
+      <c r="K20" s="65" t="n">
         <v>53.1</v>
       </c>
-      <c r="L20" s="62" t="n">
-        <v>0.9868173258003766</v>
-      </c>
-      <c r="M20" s="63" t="inlineStr">
+      <c r="L20" s="70" t="n">
+        <v>0.975517890772128</v>
+      </c>
+      <c r="M20" s="71" t="inlineStr">
         <is>
           <t>Çift Çıkışlı Yüksek Hızlı Kalıp</t>
         </is>
@@ -8116,17 +7808,17 @@
           <t>50X80 PERVAZ</t>
         </is>
       </c>
-      <c r="B21" s="53" t="inlineStr">
+      <c r="B21" s="61" t="inlineStr">
         <is>
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="C21" s="47" t="inlineStr">
+      <c r="C21" s="55" t="inlineStr">
         <is>
           <t>Hat 109</t>
         </is>
       </c>
-      <c r="D21" s="47" t="inlineStr">
+      <c r="D21" s="55" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -8146,10 +7838,8 @@
       <c r="I21" s="16" t="n">
         <v>65.59999999999999</v>
       </c>
-      <c r="J21" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~44 Boy</t>
-        </is>
+      <c r="J21" s="17" t="n">
+        <v>44</v>
       </c>
       <c r="K21" s="14" t="n">
         <v>73.59999999999999</v>
@@ -8164,17 +7854,17 @@
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="54" t="inlineStr">
+      <c r="A22" s="62" t="inlineStr">
         <is>
           <t>50X80 PERVAZ</t>
         </is>
       </c>
-      <c r="B22" s="55" t="inlineStr">
+      <c r="B22" s="63" t="inlineStr">
         <is>
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="C22" s="56" t="inlineStr">
+      <c r="C22" s="64" t="inlineStr">
         <is>
           <t>Hat 109</t>
         </is>
@@ -8184,33 +7874,31 @@
           <t>Çift Göz (2 Kafa)</t>
         </is>
       </c>
-      <c r="E22" s="57" t="n">
-        <v>1444.2</v>
-      </c>
-      <c r="F22" s="58" t="n">
-        <v>141</v>
-      </c>
-      <c r="G22" s="59" t="n">
-        <v>107001.75</v>
-      </c>
-      <c r="H22" s="58" t="n">
-        <v>71435</v>
-      </c>
-      <c r="I22" s="60" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="J22" s="61" t="inlineStr">
-        <is>
-          <t>Saatte ~50 Boy</t>
-        </is>
-      </c>
-      <c r="K22" s="57" t="n">
+      <c r="E22" s="65" t="n">
+        <v>1468.2</v>
+      </c>
+      <c r="F22" s="66" t="n">
+        <v>143</v>
+      </c>
+      <c r="G22" s="67" t="n">
+        <v>108114.75</v>
+      </c>
+      <c r="H22" s="66" t="n">
+        <v>72070</v>
+      </c>
+      <c r="I22" s="68" t="n">
         <v>73.59999999999999</v>
       </c>
-      <c r="L22" s="62" t="n">
-        <v>1.00679347826087</v>
-      </c>
-      <c r="M22" s="63" t="inlineStr">
+      <c r="J22" s="69" t="n">
+        <v>49</v>
+      </c>
+      <c r="K22" s="65" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="L22" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="71" t="inlineStr">
         <is>
           <t>Çift Çıkışlı Yüksek Hızlı Kalıp</t>
         </is>
@@ -8222,17 +7910,17 @@
           <t>80X80 PERVAZ</t>
         </is>
       </c>
-      <c r="B23" s="53" t="inlineStr">
+      <c r="B23" s="61" t="inlineStr">
         <is>
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="C23" s="47" t="inlineStr">
+      <c r="C23" s="55" t="inlineStr">
         <is>
           <t>Hat 101</t>
         </is>
       </c>
-      <c r="D23" s="47" t="inlineStr">
+      <c r="D23" s="55" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -8252,10 +7940,8 @@
       <c r="I23" s="16" t="n">
         <v>51.1</v>
       </c>
-      <c r="J23" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~22 Boy</t>
-        </is>
+      <c r="J23" s="17" t="n">
+        <v>22</v>
       </c>
       <c r="K23" s="14" t="n">
         <v>46.5</v>
@@ -8270,17 +7956,17 @@
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="54" t="inlineStr">
+      <c r="A24" s="62" t="inlineStr">
         <is>
           <t>80X80 PERVAZ</t>
         </is>
       </c>
-      <c r="B24" s="55" t="inlineStr">
+      <c r="B24" s="63" t="inlineStr">
         <is>
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="C24" s="56" t="inlineStr">
+      <c r="C24" s="64" t="inlineStr">
         <is>
           <t>Hat 109</t>
         </is>
@@ -8290,33 +7976,31 @@
           <t>Çift Göz (2 Kafa)</t>
         </is>
       </c>
-      <c r="E24" s="57" t="n">
+      <c r="E24" s="65" t="n">
         <v>12</v>
       </c>
-      <c r="F24" s="58" t="n">
+      <c r="F24" s="66" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="59" t="n">
+      <c r="G24" s="67" t="n">
         <v>1021</v>
       </c>
-      <c r="H24" s="58" t="n">
+      <c r="H24" s="66" t="n">
         <v>690</v>
       </c>
-      <c r="I24" s="60" t="n">
+      <c r="I24" s="68" t="n">
         <v>85.09999999999999</v>
       </c>
-      <c r="J24" s="61" t="inlineStr">
-        <is>
-          <t>Saatte ~58 Boy</t>
-        </is>
-      </c>
-      <c r="K24" s="57" t="n">
+      <c r="J24" s="69" t="n">
+        <v>58</v>
+      </c>
+      <c r="K24" s="65" t="n">
         <v>85.09999999999999</v>
       </c>
-      <c r="L24" s="62" t="n">
+      <c r="L24" s="70" t="n">
         <v>1</v>
       </c>
-      <c r="M24" s="63" t="inlineStr">
+      <c r="M24" s="71" t="inlineStr">
         <is>
           <t>Çift Çıkışlı Yüksek Hızlı Kalıp</t>
         </is>
@@ -8328,23 +8012,23 @@
           <t>ANTRASİT Levha</t>
         </is>
       </c>
-      <c r="B25" s="53" t="inlineStr">
+      <c r="B25" s="61" t="inlineStr">
         <is>
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="C25" s="47" t="inlineStr">
+      <c r="C25" s="55" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="D25" s="47" t="inlineStr">
+      <c r="D25" s="55" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
       </c>
       <c r="E25" s="14" t="n">
-        <v>41.52884989747753</v>
+        <v>37.72884989747753</v>
       </c>
       <c r="F25" s="15" t="n">
         <v>8</v>
@@ -8356,18 +8040,16 @@
         <v>1176</v>
       </c>
       <c r="I25" s="16" t="n">
-        <v>135.1</v>
-      </c>
-      <c r="J25" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~28 Plaka</t>
-        </is>
+        <v>148.7</v>
+      </c>
+      <c r="J25" s="41" t="n">
+        <v>31</v>
       </c>
       <c r="K25" s="14" t="n">
         <v>190</v>
       </c>
-      <c r="L25" s="39" t="n">
-        <v>0.7110526315789474</v>
+      <c r="L25" s="48" t="n">
+        <v>0.7826315789473683</v>
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
@@ -8381,17 +8063,17 @@
           <t>AY GRİ Levha</t>
         </is>
       </c>
-      <c r="B26" s="52" t="inlineStr">
+      <c r="B26" s="60" t="inlineStr">
         <is>
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="C26" s="45" t="inlineStr">
+      <c r="C26" s="53" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="D26" s="45" t="inlineStr">
+      <c r="D26" s="53" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -8411,10 +8093,8 @@
       <c r="I26" s="31" t="n">
         <v>158.2</v>
       </c>
-      <c r="J26" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~34 Plaka</t>
-        </is>
+      <c r="J26" s="45" t="n">
+        <v>34</v>
       </c>
       <c r="K26" s="29" t="n">
         <v>190</v>
@@ -8434,17 +8114,17 @@
           <t>BEYAZ TEAK Levha</t>
         </is>
       </c>
-      <c r="B27" s="53" t="inlineStr">
+      <c r="B27" s="61" t="inlineStr">
         <is>
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="C27" s="47" t="inlineStr">
+      <c r="C27" s="55" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="D27" s="47" t="inlineStr">
+      <c r="D27" s="55" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -8464,10 +8144,8 @@
       <c r="I27" s="16" t="n">
         <v>184.5</v>
       </c>
-      <c r="J27" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~42 Plaka</t>
-        </is>
+      <c r="J27" s="41" t="n">
+        <v>42</v>
       </c>
       <c r="K27" s="14" t="n">
         <v>190</v>
@@ -8487,17 +8165,17 @@
           <t>CAM ÇITASI</t>
         </is>
       </c>
-      <c r="B28" s="52" t="inlineStr">
+      <c r="B28" s="60" t="inlineStr">
         <is>
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="C28" s="45" t="inlineStr">
+      <c r="C28" s="53" t="inlineStr">
         <is>
           <t>Hat 102</t>
         </is>
       </c>
-      <c r="D28" s="45" t="inlineStr">
+      <c r="D28" s="53" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -8517,10 +8195,8 @@
       <c r="I28" s="31" t="n">
         <v>52</v>
       </c>
-      <c r="J28" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~35 Boy</t>
-        </is>
+      <c r="J28" s="32" t="n">
+        <v>35</v>
       </c>
       <c r="K28" s="29" t="n">
         <v>50</v>
@@ -8540,17 +8216,17 @@
           <t>COCO Levha</t>
         </is>
       </c>
-      <c r="B29" s="53" t="inlineStr">
+      <c r="B29" s="61" t="inlineStr">
         <is>
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="C29" s="47" t="inlineStr">
+      <c r="C29" s="55" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="D29" s="47" t="inlineStr">
+      <c r="D29" s="55" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -8570,10 +8246,8 @@
       <c r="I29" s="16" t="n">
         <v>198.2</v>
       </c>
-      <c r="J29" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~41 Plaka</t>
-        </is>
+      <c r="J29" s="41" t="n">
+        <v>41</v>
       </c>
       <c r="K29" s="14" t="n">
         <v>190</v>
@@ -8593,46 +8267,44 @@
           <t>DİŞBUDAK Levha</t>
         </is>
       </c>
-      <c r="B30" s="52" t="inlineStr">
+      <c r="B30" s="60" t="inlineStr">
         <is>
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="C30" s="45" t="inlineStr">
+      <c r="C30" s="53" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="D30" s="45" t="inlineStr">
+      <c r="D30" s="53" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
       </c>
       <c r="E30" s="29" t="n">
-        <v>622.6096835790281</v>
+        <v>632.6096835790281</v>
       </c>
       <c r="F30" s="30" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G30" s="27" t="n">
-        <v>122751.18</v>
+        <v>125422.38</v>
       </c>
       <c r="H30" s="30" t="n">
-        <v>25734</v>
+        <v>26294</v>
       </c>
       <c r="I30" s="31" t="n">
-        <v>197.2</v>
-      </c>
-      <c r="J30" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~41 Plaka</t>
-        </is>
+        <v>198.3</v>
+      </c>
+      <c r="J30" s="45" t="n">
+        <v>42</v>
       </c>
       <c r="K30" s="29" t="n">
         <v>190</v>
       </c>
       <c r="L30" s="34" t="n">
-        <v>1.037894736842105</v>
+        <v>1.043684210526316</v>
       </c>
       <c r="M30" s="25" t="inlineStr">
         <is>
@@ -8646,17 +8318,17 @@
           <t>KOYU CEVİZ Levha</t>
         </is>
       </c>
-      <c r="B31" s="53" t="inlineStr">
+      <c r="B31" s="61" t="inlineStr">
         <is>
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="C31" s="47" t="inlineStr">
+      <c r="C31" s="55" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="D31" s="47" t="inlineStr">
+      <c r="D31" s="55" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -8676,15 +8348,13 @@
       <c r="I31" s="16" t="n">
         <v>120.3</v>
       </c>
-      <c r="J31" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~25 Plaka</t>
-        </is>
+      <c r="J31" s="41" t="n">
+        <v>25</v>
       </c>
       <c r="K31" s="14" t="n">
         <v>190</v>
       </c>
-      <c r="L31" s="39" t="n">
+      <c r="L31" s="48" t="n">
         <v>0.6331578947368421</v>
       </c>
       <c r="M31" s="8" t="inlineStr">
@@ -8699,17 +8369,17 @@
           <t>KT100-220x24-ANT</t>
         </is>
       </c>
-      <c r="B32" s="52" t="inlineStr">
+      <c r="B32" s="60" t="inlineStr">
         <is>
           <t>3.00 Metre</t>
         </is>
       </c>
-      <c r="C32" s="45" t="inlineStr">
+      <c r="C32" s="53" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="D32" s="45" t="inlineStr">
+      <c r="D32" s="53" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -8729,10 +8399,8 @@
       <c r="I32" s="31" t="n">
         <v>85.90000000000001</v>
       </c>
-      <c r="J32" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~8 Boy</t>
-        </is>
+      <c r="J32" s="32" t="n">
+        <v>8</v>
       </c>
       <c r="K32" s="29" t="n">
         <v>84.7</v>
@@ -8752,17 +8420,17 @@
           <t>KT102-219x26-ANT</t>
         </is>
       </c>
-      <c r="B33" s="53" t="inlineStr">
+      <c r="B33" s="61" t="inlineStr">
         <is>
           <t>3.00 Metre</t>
         </is>
       </c>
-      <c r="C33" s="47" t="inlineStr">
+      <c r="C33" s="55" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="D33" s="47" t="inlineStr">
+      <c r="D33" s="55" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -8782,10 +8450,8 @@
       <c r="I33" s="16" t="n">
         <v>108.2</v>
       </c>
-      <c r="J33" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~10 Boy</t>
-        </is>
+      <c r="J33" s="17" t="n">
+        <v>10</v>
       </c>
       <c r="K33" s="14" t="n">
         <v>108.2</v>
@@ -8805,17 +8471,17 @@
           <t>KT102-219x26-KAH</t>
         </is>
       </c>
-      <c r="B34" s="52" t="inlineStr">
+      <c r="B34" s="60" t="inlineStr">
         <is>
           <t>3.00 Metre</t>
         </is>
       </c>
-      <c r="C34" s="45" t="inlineStr">
+      <c r="C34" s="53" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="D34" s="45" t="inlineStr">
+      <c r="D34" s="53" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -8835,10 +8501,8 @@
       <c r="I34" s="31" t="n">
         <v>115.8</v>
       </c>
-      <c r="J34" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~12 Boy</t>
-        </is>
+      <c r="J34" s="32" t="n">
+        <v>12</v>
       </c>
       <c r="K34" s="29" t="n">
         <v>115.8</v>
@@ -8858,17 +8522,17 @@
           <t>MIX BEYAZ TEAK Levha</t>
         </is>
       </c>
-      <c r="B35" s="53" t="inlineStr">
+      <c r="B35" s="61" t="inlineStr">
         <is>
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="C35" s="47" t="inlineStr">
+      <c r="C35" s="55" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="D35" s="47" t="inlineStr">
+      <c r="D35" s="55" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -8888,10 +8552,8 @@
       <c r="I35" s="16" t="n">
         <v>187</v>
       </c>
-      <c r="J35" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~44 Plaka</t>
-        </is>
+      <c r="J35" s="41" t="n">
+        <v>44</v>
       </c>
       <c r="K35" s="14" t="n">
         <v>190</v>
@@ -8911,17 +8573,17 @@
           <t>MIX TEAK Levha</t>
         </is>
       </c>
-      <c r="B36" s="52" t="inlineStr">
+      <c r="B36" s="60" t="inlineStr">
         <is>
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="C36" s="45" t="inlineStr">
+      <c r="C36" s="53" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="D36" s="45" t="inlineStr">
+      <c r="D36" s="53" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -8941,10 +8603,8 @@
       <c r="I36" s="31" t="n">
         <v>173.8</v>
       </c>
-      <c r="J36" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~41 Plaka</t>
-        </is>
+      <c r="J36" s="45" t="n">
+        <v>41</v>
       </c>
       <c r="K36" s="29" t="n">
         <v>190</v>
@@ -8959,17 +8619,17 @@
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="54" t="inlineStr">
+      <c r="A37" s="62" t="inlineStr">
         <is>
           <t>SEREN</t>
         </is>
       </c>
-      <c r="B37" s="55" t="inlineStr">
+      <c r="B37" s="63" t="inlineStr">
         <is>
           <t>2.10 Metre</t>
         </is>
       </c>
-      <c r="C37" s="56" t="inlineStr">
+      <c r="C37" s="64" t="inlineStr">
         <is>
           <t>Hat 103</t>
         </is>
@@ -8979,33 +8639,31 @@
           <t>Çift Göz (2 Kafa)</t>
         </is>
       </c>
-      <c r="E37" s="57" t="n">
+      <c r="E37" s="65" t="n">
         <v>12</v>
       </c>
-      <c r="F37" s="58" t="n">
+      <c r="F37" s="66" t="n">
         <v>1</v>
       </c>
-      <c r="G37" s="59" t="n">
+      <c r="G37" s="67" t="n">
         <v>760</v>
       </c>
-      <c r="H37" s="58" t="n">
+      <c r="H37" s="66" t="n">
         <v>450</v>
       </c>
-      <c r="I37" s="60" t="n">
+      <c r="I37" s="68" t="n">
         <v>63.3</v>
       </c>
-      <c r="J37" s="61" t="inlineStr">
-        <is>
-          <t>Saatte ~38 Boy</t>
-        </is>
-      </c>
-      <c r="K37" s="57" t="n">
+      <c r="J37" s="69" t="n">
+        <v>38</v>
+      </c>
+      <c r="K37" s="65" t="n">
         <v>63.3</v>
       </c>
-      <c r="L37" s="62" t="n">
+      <c r="L37" s="70" t="n">
         <v>1</v>
       </c>
-      <c r="M37" s="63" t="inlineStr">
+      <c r="M37" s="71" t="inlineStr">
         <is>
           <t>Çift Çıkışlı Yüksek Hızlı Kalıp</t>
         </is>
@@ -9017,17 +8675,17 @@
           <t>SEREN</t>
         </is>
       </c>
-      <c r="B38" s="52" t="inlineStr">
+      <c r="B38" s="60" t="inlineStr">
         <is>
           <t>2.10 Metre</t>
         </is>
       </c>
-      <c r="C38" s="45" t="inlineStr">
+      <c r="C38" s="53" t="inlineStr">
         <is>
           <t>Hat 104</t>
         </is>
       </c>
-      <c r="D38" s="45" t="inlineStr">
+      <c r="D38" s="53" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -9047,10 +8705,8 @@
       <c r="I38" s="31" t="n">
         <v>113.6</v>
       </c>
-      <c r="J38" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~33 Boy</t>
-        </is>
+      <c r="J38" s="32" t="n">
+        <v>33</v>
       </c>
       <c r="K38" s="29" t="n">
         <v>99.2</v>
@@ -9065,17 +8721,17 @@
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="54" t="inlineStr">
+      <c r="A39" s="62" t="inlineStr">
         <is>
           <t>SEREN</t>
         </is>
       </c>
-      <c r="B39" s="55" t="inlineStr">
+      <c r="B39" s="63" t="inlineStr">
         <is>
           <t>2.10 Metre</t>
         </is>
       </c>
-      <c r="C39" s="56" t="inlineStr">
+      <c r="C39" s="64" t="inlineStr">
         <is>
           <t>Hat 104</t>
         </is>
@@ -9085,33 +8741,31 @@
           <t>Çift Göz (2 Kafa)</t>
         </is>
       </c>
-      <c r="E39" s="57" t="n">
-        <v>1550.4</v>
-      </c>
-      <c r="F39" s="58" t="n">
-        <v>140</v>
-      </c>
-      <c r="G39" s="59" t="n">
-        <v>147425.32</v>
-      </c>
-      <c r="H39" s="58" t="n">
-        <v>43256</v>
-      </c>
-      <c r="I39" s="60" t="n">
-        <v>95.09999999999999</v>
-      </c>
-      <c r="J39" s="61" t="inlineStr">
-        <is>
-          <t>Saatte ~28 Boy</t>
-        </is>
-      </c>
-      <c r="K39" s="57" t="n">
+      <c r="E39" s="65" t="n">
+        <v>1574.4</v>
+      </c>
+      <c r="F39" s="66" t="n">
+        <v>142</v>
+      </c>
+      <c r="G39" s="67" t="n">
+        <v>149881.32</v>
+      </c>
+      <c r="H39" s="66" t="n">
+        <v>43971</v>
+      </c>
+      <c r="I39" s="68" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="J39" s="69" t="n">
+        <v>28</v>
+      </c>
+      <c r="K39" s="65" t="n">
         <v>99.2</v>
       </c>
-      <c r="L39" s="62" t="n">
-        <v>0.9586693548387096</v>
-      </c>
-      <c r="M39" s="63" t="inlineStr">
+      <c r="L39" s="70" t="n">
+        <v>0.9596774193548387</v>
+      </c>
+      <c r="M39" s="71" t="inlineStr">
         <is>
           <t>Çift Çıkışlı Yüksek Hızlı Kalıp</t>
         </is>
@@ -9123,17 +8777,17 @@
           <t>SEREN</t>
         </is>
       </c>
-      <c r="B40" s="52" t="inlineStr">
+      <c r="B40" s="60" t="inlineStr">
         <is>
           <t>2.10 Metre</t>
         </is>
       </c>
-      <c r="C40" s="45" t="inlineStr">
+      <c r="C40" s="53" t="inlineStr">
         <is>
           <t>Hat 105</t>
         </is>
       </c>
-      <c r="D40" s="45" t="inlineStr">
+      <c r="D40" s="53" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -9153,10 +8807,8 @@
       <c r="I40" s="31" t="n">
         <v>101.7</v>
       </c>
-      <c r="J40" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~29 Boy</t>
-        </is>
+      <c r="J40" s="32" t="n">
+        <v>29</v>
       </c>
       <c r="K40" s="29" t="n">
         <v>92.2</v>
@@ -9171,17 +8823,17 @@
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="54" t="inlineStr">
+      <c r="A41" s="62" t="inlineStr">
         <is>
           <t>SEREN</t>
         </is>
       </c>
-      <c r="B41" s="55" t="inlineStr">
+      <c r="B41" s="63" t="inlineStr">
         <is>
           <t>2.10 Metre</t>
         </is>
       </c>
-      <c r="C41" s="56" t="inlineStr">
+      <c r="C41" s="64" t="inlineStr">
         <is>
           <t>Hat 105</t>
         </is>
@@ -9191,33 +8843,31 @@
           <t>Çift Göz (2 Kafa)</t>
         </is>
       </c>
-      <c r="E41" s="57" t="n">
-        <v>1373.5</v>
-      </c>
-      <c r="F41" s="58" t="n">
-        <v>123</v>
-      </c>
-      <c r="G41" s="59" t="n">
-        <v>123688.47</v>
-      </c>
-      <c r="H41" s="58" t="n">
-        <v>36357</v>
-      </c>
-      <c r="I41" s="60" t="n">
-        <v>90.09999999999999</v>
-      </c>
-      <c r="J41" s="61" t="inlineStr">
-        <is>
-          <t>Saatte ~26 Boy</t>
-        </is>
-      </c>
-      <c r="K41" s="57" t="n">
+      <c r="E41" s="65" t="n">
+        <v>1395.5</v>
+      </c>
+      <c r="F41" s="66" t="n">
+        <v>125</v>
+      </c>
+      <c r="G41" s="67" t="n">
+        <v>125656.47</v>
+      </c>
+      <c r="H41" s="66" t="n">
+        <v>36907</v>
+      </c>
+      <c r="I41" s="68" t="n">
+        <v>90</v>
+      </c>
+      <c r="J41" s="69" t="n">
+        <v>26</v>
+      </c>
+      <c r="K41" s="65" t="n">
         <v>92.2</v>
       </c>
-      <c r="L41" s="62" t="n">
-        <v>0.9772234273318872</v>
-      </c>
-      <c r="M41" s="63" t="inlineStr">
+      <c r="L41" s="70" t="n">
+        <v>0.9761388286334056</v>
+      </c>
+      <c r="M41" s="71" t="inlineStr">
         <is>
           <t>Çift Çıkışlı Yüksek Hızlı Kalıp</t>
         </is>
@@ -9229,17 +8879,17 @@
           <t>SEREN</t>
         </is>
       </c>
-      <c r="B42" s="52" t="inlineStr">
+      <c r="B42" s="60" t="inlineStr">
         <is>
           <t>2.10 Metre</t>
         </is>
       </c>
-      <c r="C42" s="45" t="inlineStr">
+      <c r="C42" s="53" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="D42" s="45" t="inlineStr">
+      <c r="D42" s="53" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -9259,10 +8909,8 @@
       <c r="I42" s="31" t="n">
         <v>82.8</v>
       </c>
-      <c r="J42" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~21 Boy</t>
-        </is>
+      <c r="J42" s="32" t="n">
+        <v>21</v>
       </c>
       <c r="K42" s="29" t="n">
         <v>82.59999999999999</v>
@@ -9282,46 +8930,44 @@
           <t>SEREN(39mm)</t>
         </is>
       </c>
-      <c r="B43" s="53" t="inlineStr">
+      <c r="B43" s="61" t="inlineStr">
         <is>
           <t>2.10 Metre</t>
         </is>
       </c>
-      <c r="C43" s="47" t="inlineStr">
+      <c r="C43" s="55" t="inlineStr">
         <is>
           <t>Hat 107</t>
         </is>
       </c>
-      <c r="D43" s="47" t="inlineStr">
+      <c r="D43" s="55" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
       </c>
       <c r="E43" s="14" t="n">
-        <v>303</v>
+        <v>327</v>
       </c>
       <c r="F43" s="15" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G43" s="11" t="n">
-        <v>32593</v>
+        <v>34458</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>8583</v>
+        <v>9123</v>
       </c>
       <c r="I43" s="16" t="n">
-        <v>107.6</v>
-      </c>
-      <c r="J43" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~28 Boy</t>
-        </is>
+        <v>105.4</v>
+      </c>
+      <c r="J43" s="17" t="n">
+        <v>28</v>
       </c>
       <c r="K43" s="14" t="n">
         <v>96.09999999999999</v>
       </c>
       <c r="L43" s="19" t="n">
-        <v>1.119667013527575</v>
+        <v>1.096774193548387</v>
       </c>
       <c r="M43" s="8" t="inlineStr">
         <is>
@@ -9335,23 +8981,23 @@
           <t>SONOMO Levha</t>
         </is>
       </c>
-      <c r="B44" s="52" t="inlineStr">
+      <c r="B44" s="60" t="inlineStr">
         <is>
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="C44" s="45" t="inlineStr">
+      <c r="C44" s="53" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="D44" s="45" t="inlineStr">
+      <c r="D44" s="53" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
       </c>
       <c r="E44" s="29" t="n">
-        <v>57.25702552864577</v>
+        <v>47.95702552864577</v>
       </c>
       <c r="F44" s="30" t="n">
         <v>13</v>
@@ -9363,18 +9009,16 @@
         <v>1776</v>
       </c>
       <c r="I44" s="31" t="n">
-        <v>134.3</v>
-      </c>
-      <c r="J44" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~31 Plaka</t>
-        </is>
+        <v>160.4</v>
+      </c>
+      <c r="J44" s="45" t="n">
+        <v>37</v>
       </c>
       <c r="K44" s="29" t="n">
         <v>190</v>
       </c>
-      <c r="L44" s="40" t="n">
-        <v>0.7068421052631579</v>
+      <c r="L44" s="34" t="n">
+        <v>0.8442105263157896</v>
       </c>
       <c r="M44" s="25" t="inlineStr">
         <is>
@@ -9388,17 +9032,17 @@
           <t>TEAK Levha</t>
         </is>
       </c>
-      <c r="B45" s="53" t="inlineStr">
+      <c r="B45" s="61" t="inlineStr">
         <is>
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="C45" s="47" t="inlineStr">
+      <c r="C45" s="55" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="D45" s="47" t="inlineStr">
+      <c r="D45" s="55" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -9418,10 +9062,8 @@
       <c r="I45" s="16" t="n">
         <v>169.1</v>
       </c>
-      <c r="J45" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~40 Plaka</t>
-        </is>
+      <c r="J45" s="41" t="n">
+        <v>40</v>
       </c>
       <c r="K45" s="14" t="n">
         <v>190</v>
@@ -9441,17 +9083,17 @@
           <t>U KAPAMA</t>
         </is>
       </c>
-      <c r="B46" s="52" t="inlineStr">
+      <c r="B46" s="60" t="inlineStr">
         <is>
           <t>2.20 Metre</t>
         </is>
       </c>
-      <c r="C46" s="45" t="inlineStr">
+      <c r="C46" s="53" t="inlineStr">
         <is>
           <t>Hat 102</t>
         </is>
       </c>
-      <c r="D46" s="45" t="inlineStr">
+      <c r="D46" s="53" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -9471,10 +9113,8 @@
       <c r="I46" s="31" t="n">
         <v>40.7</v>
       </c>
-      <c r="J46" s="32" t="inlineStr">
-        <is>
-          <t>Saatte ~85 Boy</t>
-        </is>
+      <c r="J46" s="32" t="n">
+        <v>85</v>
       </c>
       <c r="K46" s="29" t="n">
         <v>40.7</v>
@@ -9494,17 +9134,17 @@
           <t>VIZON Levha</t>
         </is>
       </c>
-      <c r="B47" s="53" t="inlineStr">
+      <c r="B47" s="61" t="inlineStr">
         <is>
           <t>207 cm (2.07 m)</t>
         </is>
       </c>
-      <c r="C47" s="47" t="inlineStr">
+      <c r="C47" s="55" t="inlineStr">
         <is>
           <t>Hat 201</t>
         </is>
       </c>
-      <c r="D47" s="47" t="inlineStr">
+      <c r="D47" s="55" t="inlineStr">
         <is>
           <t>Tek Göz (1 Kafa)</t>
         </is>
@@ -9524,10 +9164,8 @@
       <c r="I47" s="16" t="n">
         <v>160.8</v>
       </c>
-      <c r="J47" s="17" t="inlineStr">
-        <is>
-          <t>Saatte ~34 Plaka</t>
-        </is>
+      <c r="J47" s="41" t="n">
+        <v>34</v>
       </c>
       <c r="K47" s="14" t="n">
         <v>190</v>
@@ -9541,7 +9179,39 @@
         </is>
       </c>
     </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="57" t="inlineStr">
+        <is>
+          <t>GENEL TOPLAM (FİLTREYE DUYARLI)</t>
+        </is>
+      </c>
+      <c r="B48" s="50" t="n"/>
+      <c r="C48" s="50" t="n"/>
+      <c r="D48" s="50" t="n"/>
+      <c r="E48" s="52">
+        <f>SUBTOTAL(109, E4:E47)</f>
+        <v/>
+      </c>
+      <c r="F48" s="51">
+        <f>SUBTOTAL(109, F4:F47)</f>
+        <v/>
+      </c>
+      <c r="G48" s="51">
+        <f>SUBTOTAL(109, G4:G47)</f>
+        <v/>
+      </c>
+      <c r="H48" s="51">
+        <f>SUBTOTAL(109, H4:H47)</f>
+        <v/>
+      </c>
+      <c r="I48" s="50" t="n"/>
+      <c r="J48" s="50" t="n"/>
+      <c r="K48" s="50" t="n"/>
+      <c r="L48" s="50" t="n"/>
+      <c r="M48" s="50" t="n"/>
+    </row>
   </sheetData>
+  <autoFilter ref="A3:M47"/>
   <mergeCells count="2">
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A1:M1"/>

--- a/static/Ergunbas_Urun_Hat_Rotalari_ve_Kapasite_Analizi.xlsx
+++ b/static/Ergunbas_Urun_Hat_Rotalari_ve_Kapasite_Analizi.xlsx
@@ -2790,19 +2790,19 @@
         </is>
       </c>
       <c r="I23" s="14" t="n">
-        <v>47.95702552864577</v>
+        <v>48.25702552864577</v>
       </c>
       <c r="J23" s="15" t="n">
         <v>13</v>
       </c>
       <c r="K23" s="16" t="n">
-        <v>167.9</v>
+        <v>166.5</v>
       </c>
       <c r="L23" s="41" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>4029.6</v>
+        <v>3996</v>
       </c>
       <c r="N23" s="14" t="n">
         <v>190</v>
@@ -2811,7 +2811,7 @@
         <v>44</v>
       </c>
       <c r="P23" s="19" t="n">
-        <v>0.884</v>
+        <v>0.8759999999999999</v>
       </c>
       <c r="Q23" s="23" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         </is>
       </c>
       <c r="I25" s="14" t="n">
-        <v>37.72884989747753</v>
+        <v>38.52884989747753</v>
       </c>
       <c r="J25" s="15" t="n">
         <v>8</v>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="D13" s="14" t="n">
-        <v>1562.4</v>
+        <v>1563.5</v>
       </c>
       <c r="E13" s="15" t="n">
         <v>253</v>
@@ -4170,7 +4170,7 @@
         <v>283404.8800000001</v>
       </c>
       <c r="G13" s="16" t="n">
-        <v>181.4</v>
+        <v>181.3</v>
       </c>
       <c r="H13" s="56" t="n">
         <v>11</v>
@@ -5787,7 +5787,7 @@
         </is>
       </c>
       <c r="H27" s="14" t="n">
-        <v>47.95702552864577</v>
+        <v>48.25702552864577</v>
       </c>
       <c r="I27" s="15" t="n">
         <v>13</v>
@@ -5802,7 +5802,7 @@
         <v>7690.08</v>
       </c>
       <c r="M27" s="16" t="n">
-        <v>160.4</v>
+        <v>159.4</v>
       </c>
       <c r="N27" s="41" t="n">
         <v>37</v>
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="H29" s="14" t="n">
-        <v>37.72884989747753</v>
+        <v>38.52884989747753</v>
       </c>
       <c r="I29" s="15" t="n">
         <v>8</v>
@@ -5924,7 +5924,7 @@
         <v>5609.52</v>
       </c>
       <c r="M29" s="16" t="n">
-        <v>148.7</v>
+        <v>145.6</v>
       </c>
       <c r="N29" s="41" t="n">
         <v>31</v>
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="E25" s="14" t="n">
-        <v>37.72884989747753</v>
+        <v>38.52884989747753</v>
       </c>
       <c r="F25" s="15" t="n">
         <v>8</v>
@@ -8040,16 +8040,16 @@
         <v>1176</v>
       </c>
       <c r="I25" s="16" t="n">
-        <v>148.7</v>
+        <v>145.6</v>
       </c>
       <c r="J25" s="41" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K25" s="14" t="n">
         <v>190</v>
       </c>
       <c r="L25" s="48" t="n">
-        <v>0.7826315789473683</v>
+        <v>0.7663157894736841</v>
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="E44" s="29" t="n">
-        <v>47.95702552864577</v>
+        <v>48.25702552864577</v>
       </c>
       <c r="F44" s="30" t="n">
         <v>13</v>
@@ -9009,7 +9009,7 @@
         <v>1776</v>
       </c>
       <c r="I44" s="31" t="n">
-        <v>160.4</v>
+        <v>159.4</v>
       </c>
       <c r="J44" s="45" t="n">
         <v>37</v>
@@ -9018,7 +9018,7 @@
         <v>190</v>
       </c>
       <c r="L44" s="34" t="n">
-        <v>0.8442105263157896</v>
+        <v>0.8389473684210526</v>
       </c>
       <c r="M44" s="25" t="inlineStr">
         <is>

--- a/static/Ergunbas_Urun_Hat_Rotalari_ve_Kapasite_Analizi.xlsx
+++ b/static/Ergunbas_Urun_Hat_Rotalari_ve_Kapasite_Analizi.xlsx
@@ -773,7 +773,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:X31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -3204,13 +3204,13 @@
         <v>3</v>
       </c>
       <c r="K27" s="16" t="n">
-        <v>134.1</v>
+        <v>198.2</v>
       </c>
       <c r="L27" s="41" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="M27" s="11" t="n">
-        <v>3218.4</v>
+        <v>4756.8</v>
       </c>
       <c r="N27" s="14" t="n">
         <v>190</v>
@@ -3219,7 +3219,7 @@
         <v>40</v>
       </c>
       <c r="P27" s="48" t="n">
-        <v>0.706</v>
+        <v>1.043158</v>
       </c>
       <c r="Q27" s="23" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
@@ -4237,7 +4237,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O44"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -6837,7 +6837,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M48"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
